--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G2">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G5">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G19">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G28">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G68">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G89">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G99">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G111">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G129">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G154">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G156">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G157">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G167">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G170">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>CD Badajoz</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G195">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>CD Badajoz</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="G196">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G213">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G214">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G220">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G221">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G224">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G225">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G242">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G243">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G244">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G245">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G246">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G262">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G263">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G264">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G265">

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G3">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G24">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G28">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G58">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G68">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G84">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G87">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G125">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G245">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G246">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G269">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G270">

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G28">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G58">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G77">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G87">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G125">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G136">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G200">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="G201">

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G112">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Arnedo</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Arnedo</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G150">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G248">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G249">

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G58">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G112">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G139">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G153">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G167">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G170">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G218">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G219">

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G125">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G247">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G248">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G249">

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G111">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G208">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G209">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G245">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G246">

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU276"/>
+  <dimension ref="A1:AU280"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PSS Sleman</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>PSS Sleman</t>
         </is>
       </c>
       <c r="G12">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G28">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G112">
@@ -43620,27 +43620,27 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G266">
@@ -43771,7 +43771,7 @@
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>2026-09-20 18:00:00</t>
+          <t>2026-09-20 17:30:00</t>
         </is>
       </c>
     </row>
@@ -43783,27 +43783,27 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G267">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>2026-09-20 18:00:00</t>
+          <t>2026-09-20 17:30:00</t>
         </is>
       </c>
     </row>
@@ -43946,27 +43946,27 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G268">
@@ -44097,7 +44097,7 @@
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>2026-09-20 18:30:00</t>
+          <t>2026-09-20 17:30:00</t>
         </is>
       </c>
     </row>
@@ -44109,27 +44109,27 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G269">
@@ -44260,7 +44260,7 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>2026-09-20 18:30:00</t>
+          <t>2026-09-20 17:30:00</t>
         </is>
       </c>
     </row>
@@ -44272,12 +44272,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G270">
@@ -44423,7 +44423,7 @@
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>2026-09-20 18:30:00</t>
+          <t>2026-09-20 18:00:00</t>
         </is>
       </c>
     </row>
@@ -44435,12 +44435,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G271">
@@ -44586,7 +44586,7 @@
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>2026-09-20 18:30:00</t>
+          <t>2026-09-20 18:00:00</t>
         </is>
       </c>
     </row>
@@ -44598,7 +44598,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G272">
@@ -44749,7 +44749,7 @@
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>2026-09-20 19:30:00</t>
+          <t>2026-09-20 18:30:00</t>
         </is>
       </c>
     </row>
@@ -44761,12 +44761,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G273">
@@ -44912,7 +44912,7 @@
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>2026-09-20 20:00:00</t>
+          <t>2026-09-20 18:30:00</t>
         </is>
       </c>
     </row>
@@ -44924,12 +44924,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G274">
@@ -45075,7 +45075,7 @@
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>2026-09-20 20:00:00</t>
+          <t>2026-09-20 18:30:00</t>
         </is>
       </c>
     </row>
@@ -45087,12 +45087,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G275">
@@ -45238,7 +45238,7 @@
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>2026-09-20 20:00:00</t>
+          <t>2026-09-20 18:30:00</t>
         </is>
       </c>
     </row>
@@ -45250,156 +45250,808 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="G276">
+        <v>0</v>
+      </c>
+      <c r="H276">
+        <v>0</v>
+      </c>
+      <c r="I276">
+        <v>0</v>
+      </c>
+      <c r="J276">
+        <v>0</v>
+      </c>
+      <c r="K276">
+        <v>0</v>
+      </c>
+      <c r="L276">
+        <v>0</v>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N276">
+        <v>0</v>
+      </c>
+      <c r="O276">
+        <v>0</v>
+      </c>
+      <c r="P276">
+        <v>0</v>
+      </c>
+      <c r="Q276">
+        <v>0</v>
+      </c>
+      <c r="R276">
+        <v>0</v>
+      </c>
+      <c r="S276">
+        <v>0</v>
+      </c>
+      <c r="T276">
+        <v>0</v>
+      </c>
+      <c r="U276">
+        <v>0</v>
+      </c>
+      <c r="V276">
+        <v>0</v>
+      </c>
+      <c r="W276">
+        <v>0</v>
+      </c>
+      <c r="X276">
+        <v>0</v>
+      </c>
+      <c r="Y276">
+        <v>0</v>
+      </c>
+      <c r="Z276">
+        <v>0</v>
+      </c>
+      <c r="AA276">
+        <v>0</v>
+      </c>
+      <c r="AB276">
+        <v>0</v>
+      </c>
+      <c r="AC276">
+        <v>0</v>
+      </c>
+      <c r="AD276">
+        <v>0</v>
+      </c>
+      <c r="AE276">
+        <v>0</v>
+      </c>
+      <c r="AF276">
+        <v>0</v>
+      </c>
+      <c r="AG276">
+        <v>0</v>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI276" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ276">
+        <v>0</v>
+      </c>
+      <c r="AK276">
+        <v>0</v>
+      </c>
+      <c r="AL276">
+        <v>0</v>
+      </c>
+      <c r="AM276">
+        <v>-1</v>
+      </c>
+      <c r="AN276">
+        <v>-1</v>
+      </c>
+      <c r="AO276">
+        <v>-1</v>
+      </c>
+      <c r="AP276">
+        <v>-1</v>
+      </c>
+      <c r="AQ276">
+        <v>0</v>
+      </c>
+      <c r="AR276">
+        <v>0</v>
+      </c>
+      <c r="AS276">
+        <v>0</v>
+      </c>
+      <c r="AT276">
+        <v>0</v>
+      </c>
+      <c r="AU276" t="inlineStr">
+        <is>
+          <t>2026-09-20 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr">
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="G277">
+        <v>0</v>
+      </c>
+      <c r="H277">
+        <v>0</v>
+      </c>
+      <c r="I277">
+        <v>0</v>
+      </c>
+      <c r="J277">
+        <v>0</v>
+      </c>
+      <c r="K277">
+        <v>0</v>
+      </c>
+      <c r="L277">
+        <v>0</v>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N277">
+        <v>0</v>
+      </c>
+      <c r="O277">
+        <v>0</v>
+      </c>
+      <c r="P277">
+        <v>0</v>
+      </c>
+      <c r="Q277">
+        <v>0</v>
+      </c>
+      <c r="R277">
+        <v>0</v>
+      </c>
+      <c r="S277">
+        <v>0</v>
+      </c>
+      <c r="T277">
+        <v>0</v>
+      </c>
+      <c r="U277">
+        <v>0</v>
+      </c>
+      <c r="V277">
+        <v>0</v>
+      </c>
+      <c r="W277">
+        <v>0</v>
+      </c>
+      <c r="X277">
+        <v>0</v>
+      </c>
+      <c r="Y277">
+        <v>0</v>
+      </c>
+      <c r="Z277">
+        <v>0</v>
+      </c>
+      <c r="AA277">
+        <v>0</v>
+      </c>
+      <c r="AB277">
+        <v>0</v>
+      </c>
+      <c r="AC277">
+        <v>0</v>
+      </c>
+      <c r="AD277">
+        <v>0</v>
+      </c>
+      <c r="AE277">
+        <v>0</v>
+      </c>
+      <c r="AF277">
+        <v>0</v>
+      </c>
+      <c r="AG277">
+        <v>0</v>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI277" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ277">
+        <v>0</v>
+      </c>
+      <c r="AK277">
+        <v>0</v>
+      </c>
+      <c r="AL277">
+        <v>0</v>
+      </c>
+      <c r="AM277">
+        <v>-1</v>
+      </c>
+      <c r="AN277">
+        <v>-1</v>
+      </c>
+      <c r="AO277">
+        <v>-1</v>
+      </c>
+      <c r="AP277">
+        <v>-1</v>
+      </c>
+      <c r="AQ277">
+        <v>0</v>
+      </c>
+      <c r="AR277">
+        <v>0</v>
+      </c>
+      <c r="AS277">
+        <v>0</v>
+      </c>
+      <c r="AT277">
+        <v>0</v>
+      </c>
+      <c r="AU277" t="inlineStr">
+        <is>
+          <t>2026-09-20 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Bay</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Racing Louisville</t>
+        </is>
+      </c>
+      <c r="G278">
+        <v>0</v>
+      </c>
+      <c r="H278">
+        <v>0</v>
+      </c>
+      <c r="I278">
+        <v>0</v>
+      </c>
+      <c r="J278">
+        <v>0</v>
+      </c>
+      <c r="K278">
+        <v>0</v>
+      </c>
+      <c r="L278">
+        <v>0</v>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N278">
+        <v>0</v>
+      </c>
+      <c r="O278">
+        <v>0</v>
+      </c>
+      <c r="P278">
+        <v>0</v>
+      </c>
+      <c r="Q278">
+        <v>0</v>
+      </c>
+      <c r="R278">
+        <v>0</v>
+      </c>
+      <c r="S278">
+        <v>0</v>
+      </c>
+      <c r="T278">
+        <v>0</v>
+      </c>
+      <c r="U278">
+        <v>0</v>
+      </c>
+      <c r="V278">
+        <v>0</v>
+      </c>
+      <c r="W278">
+        <v>0</v>
+      </c>
+      <c r="X278">
+        <v>0</v>
+      </c>
+      <c r="Y278">
+        <v>0</v>
+      </c>
+      <c r="Z278">
+        <v>0</v>
+      </c>
+      <c r="AA278">
+        <v>0</v>
+      </c>
+      <c r="AB278">
+        <v>0</v>
+      </c>
+      <c r="AC278">
+        <v>0</v>
+      </c>
+      <c r="AD278">
+        <v>0</v>
+      </c>
+      <c r="AE278">
+        <v>0</v>
+      </c>
+      <c r="AF278">
+        <v>0</v>
+      </c>
+      <c r="AG278">
+        <v>0</v>
+      </c>
+      <c r="AH278" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI278" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ278">
+        <v>0</v>
+      </c>
+      <c r="AK278">
+        <v>0</v>
+      </c>
+      <c r="AL278">
+        <v>0</v>
+      </c>
+      <c r="AM278">
+        <v>-1</v>
+      </c>
+      <c r="AN278">
+        <v>-1</v>
+      </c>
+      <c r="AO278">
+        <v>-1</v>
+      </c>
+      <c r="AP278">
+        <v>-1</v>
+      </c>
+      <c r="AQ278">
+        <v>0</v>
+      </c>
+      <c r="AR278">
+        <v>0</v>
+      </c>
+      <c r="AS278">
+        <v>0</v>
+      </c>
+      <c r="AT278">
+        <v>0</v>
+      </c>
+      <c r="AU278" t="inlineStr">
+        <is>
+          <t>2026-09-20 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Utah Royals</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Angel City</t>
+        </is>
+      </c>
+      <c r="G279">
+        <v>0</v>
+      </c>
+      <c r="H279">
+        <v>0</v>
+      </c>
+      <c r="I279">
+        <v>0</v>
+      </c>
+      <c r="J279">
+        <v>0</v>
+      </c>
+      <c r="K279">
+        <v>0</v>
+      </c>
+      <c r="L279">
+        <v>0</v>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N279">
+        <v>0</v>
+      </c>
+      <c r="O279">
+        <v>0</v>
+      </c>
+      <c r="P279">
+        <v>0</v>
+      </c>
+      <c r="Q279">
+        <v>0</v>
+      </c>
+      <c r="R279">
+        <v>0</v>
+      </c>
+      <c r="S279">
+        <v>0</v>
+      </c>
+      <c r="T279">
+        <v>0</v>
+      </c>
+      <c r="U279">
+        <v>0</v>
+      </c>
+      <c r="V279">
+        <v>0</v>
+      </c>
+      <c r="W279">
+        <v>0</v>
+      </c>
+      <c r="X279">
+        <v>0</v>
+      </c>
+      <c r="Y279">
+        <v>0</v>
+      </c>
+      <c r="Z279">
+        <v>0</v>
+      </c>
+      <c r="AA279">
+        <v>0</v>
+      </c>
+      <c r="AB279">
+        <v>0</v>
+      </c>
+      <c r="AC279">
+        <v>0</v>
+      </c>
+      <c r="AD279">
+        <v>0</v>
+      </c>
+      <c r="AE279">
+        <v>0</v>
+      </c>
+      <c r="AF279">
+        <v>0</v>
+      </c>
+      <c r="AG279">
+        <v>0</v>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ279">
+        <v>0</v>
+      </c>
+      <c r="AK279">
+        <v>0</v>
+      </c>
+      <c r="AL279">
+        <v>0</v>
+      </c>
+      <c r="AM279">
+        <v>-1</v>
+      </c>
+      <c r="AN279">
+        <v>-1</v>
+      </c>
+      <c r="AO279">
+        <v>-1</v>
+      </c>
+      <c r="AP279">
+        <v>-1</v>
+      </c>
+      <c r="AQ279">
+        <v>0</v>
+      </c>
+      <c r="AR279">
+        <v>0</v>
+      </c>
+      <c r="AS279">
+        <v>0</v>
+      </c>
+      <c r="AT279">
+        <v>0</v>
+      </c>
+      <c r="AU279" t="inlineStr">
+        <is>
+          <t>2026-09-20 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr">
+      <c r="D280" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr">
+      <c r="E280" t="inlineStr">
         <is>
           <t>Inter Miami</t>
         </is>
       </c>
-      <c r="F276" t="inlineStr">
+      <c r="F280" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="G276">
-        <v>0</v>
-      </c>
-      <c r="H276">
-        <v>0</v>
-      </c>
-      <c r="I276">
-        <v>0</v>
-      </c>
-      <c r="J276">
-        <v>0</v>
-      </c>
-      <c r="K276">
-        <v>0</v>
-      </c>
-      <c r="L276">
-        <v>0</v>
-      </c>
-      <c r="M276" t="inlineStr">
+      <c r="G280">
+        <v>0</v>
+      </c>
+      <c r="H280">
+        <v>0</v>
+      </c>
+      <c r="I280">
+        <v>0</v>
+      </c>
+      <c r="J280">
+        <v>0</v>
+      </c>
+      <c r="K280">
+        <v>0</v>
+      </c>
+      <c r="L280">
+        <v>0</v>
+      </c>
+      <c r="M280" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N276">
-        <v>0</v>
-      </c>
-      <c r="O276">
-        <v>0</v>
-      </c>
-      <c r="P276">
-        <v>0</v>
-      </c>
-      <c r="Q276">
-        <v>0</v>
-      </c>
-      <c r="R276">
-        <v>0</v>
-      </c>
-      <c r="S276">
-        <v>0</v>
-      </c>
-      <c r="T276">
-        <v>0</v>
-      </c>
-      <c r="U276">
-        <v>0</v>
-      </c>
-      <c r="V276">
-        <v>0</v>
-      </c>
-      <c r="W276">
-        <v>0</v>
-      </c>
-      <c r="X276">
-        <v>0</v>
-      </c>
-      <c r="Y276">
-        <v>0</v>
-      </c>
-      <c r="Z276">
-        <v>0</v>
-      </c>
-      <c r="AA276">
-        <v>0</v>
-      </c>
-      <c r="AB276">
-        <v>0</v>
-      </c>
-      <c r="AC276">
-        <v>0</v>
-      </c>
-      <c r="AD276">
-        <v>0</v>
-      </c>
-      <c r="AE276">
-        <v>0</v>
-      </c>
-      <c r="AF276">
-        <v>0</v>
-      </c>
-      <c r="AG276">
-        <v>0</v>
-      </c>
-      <c r="AH276" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI276" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ276">
-        <v>0</v>
-      </c>
-      <c r="AK276">
-        <v>0</v>
-      </c>
-      <c r="AL276">
-        <v>0</v>
-      </c>
-      <c r="AM276">
-        <v>-1</v>
-      </c>
-      <c r="AN276">
-        <v>-1</v>
-      </c>
-      <c r="AO276">
-        <v>-1</v>
-      </c>
-      <c r="AP276">
-        <v>-1</v>
-      </c>
-      <c r="AQ276">
-        <v>0</v>
-      </c>
-      <c r="AR276">
-        <v>0</v>
-      </c>
-      <c r="AS276">
-        <v>0</v>
-      </c>
-      <c r="AT276">
-        <v>0</v>
-      </c>
-      <c r="AU276" t="inlineStr">
+      <c r="N280">
+        <v>0</v>
+      </c>
+      <c r="O280">
+        <v>0</v>
+      </c>
+      <c r="P280">
+        <v>0</v>
+      </c>
+      <c r="Q280">
+        <v>0</v>
+      </c>
+      <c r="R280">
+        <v>0</v>
+      </c>
+      <c r="S280">
+        <v>0</v>
+      </c>
+      <c r="T280">
+        <v>0</v>
+      </c>
+      <c r="U280">
+        <v>0</v>
+      </c>
+      <c r="V280">
+        <v>0</v>
+      </c>
+      <c r="W280">
+        <v>0</v>
+      </c>
+      <c r="X280">
+        <v>0</v>
+      </c>
+      <c r="Y280">
+        <v>0</v>
+      </c>
+      <c r="Z280">
+        <v>0</v>
+      </c>
+      <c r="AA280">
+        <v>0</v>
+      </c>
+      <c r="AB280">
+        <v>0</v>
+      </c>
+      <c r="AC280">
+        <v>0</v>
+      </c>
+      <c r="AD280">
+        <v>0</v>
+      </c>
+      <c r="AE280">
+        <v>0</v>
+      </c>
+      <c r="AF280">
+        <v>0</v>
+      </c>
+      <c r="AG280">
+        <v>0</v>
+      </c>
+      <c r="AH280" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI280" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ280">
+        <v>0</v>
+      </c>
+      <c r="AK280">
+        <v>0</v>
+      </c>
+      <c r="AL280">
+        <v>0</v>
+      </c>
+      <c r="AM280">
+        <v>-1</v>
+      </c>
+      <c r="AN280">
+        <v>-1</v>
+      </c>
+      <c r="AO280">
+        <v>-1</v>
+      </c>
+      <c r="AP280">
+        <v>-1</v>
+      </c>
+      <c r="AQ280">
+        <v>0</v>
+      </c>
+      <c r="AR280">
+        <v>0</v>
+      </c>
+      <c r="AS280">
+        <v>0</v>
+      </c>
+      <c r="AT280">
+        <v>0</v>
+      </c>
+      <c r="AU280" t="inlineStr">
         <is>
           <t>2026-09-20 20:00:00</t>
         </is>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G28">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G112">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G266">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G267">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G268">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G269">

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU280"/>
+  <dimension ref="A1:AU282"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Arnedo</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G150">
@@ -24880,7 +24880,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Arnedo</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G151">
@@ -25043,22 +25043,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G153">
@@ -25532,22 +25532,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G155">
@@ -25695,7 +25695,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G156">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G157">
@@ -26021,22 +26021,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G158">
@@ -26184,22 +26184,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Atlético Tordesillas</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G159">
@@ -26347,7 +26347,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Atlético Tordesillas</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G160">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G161">
@@ -26673,7 +26673,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G162">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G163">
@@ -26999,22 +26999,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G167">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G170">
@@ -28135,27 +28135,27 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G171">
@@ -28286,7 +28286,7 @@
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>2026-09-20 12:15:00</t>
+          <t>2026-09-20 12:00:00</t>
         </is>
       </c>
     </row>
@@ -28303,7 +28303,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G172">
@@ -28461,12 +28461,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G173">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>2026-09-20 12:30:00</t>
+          <t>2026-09-20 12:15:00</t>
         </is>
       </c>
     </row>
@@ -28629,7 +28629,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G174">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G175">
@@ -28955,7 +28955,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G176">
@@ -29118,7 +29118,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G177">
@@ -29281,7 +29281,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G178">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G179">
@@ -29607,7 +29607,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G180">
@@ -29770,7 +29770,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G181">
@@ -29933,7 +29933,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G182">
@@ -30096,7 +30096,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G183">
@@ -30254,27 +30254,27 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G184">
@@ -30405,7 +30405,7 @@
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>2026-09-20 13:00:00</t>
+          <t>2026-09-20 12:30:00</t>
         </is>
       </c>
     </row>
@@ -30422,22 +30422,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G185">
@@ -30585,7 +30585,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G186">
@@ -30748,22 +30748,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="G187">
@@ -30911,22 +30911,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G188">
@@ -31074,22 +31074,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G189">
@@ -31237,7 +31237,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G190">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G193">
@@ -31889,22 +31889,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G194">
@@ -32052,7 +32052,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>CD Badajoz</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G195">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>CD Badajoz</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G196">
@@ -32378,7 +32378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="G197">
@@ -32541,7 +32541,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G198">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G199">
@@ -32867,7 +32867,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="G200">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G201">
@@ -33193,7 +33193,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="G202">
@@ -33351,12 +33351,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G203">
@@ -33502,7 +33502,7 @@
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>2026-09-20 13:15:00</t>
+          <t>2026-09-20 13:00:00</t>
         </is>
       </c>
     </row>
@@ -33514,12 +33514,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G204">
@@ -33665,7 +33665,7 @@
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>2026-09-20 13:30:00</t>
+          <t>2026-09-20 13:15:00</t>
         </is>
       </c>
     </row>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G205">
@@ -33845,7 +33845,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G206">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G207">
@@ -34171,7 +34171,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G208">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G209">
@@ -34497,7 +34497,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G210">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G211">
@@ -34818,12 +34818,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G212">
@@ -34969,7 +34969,7 @@
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>2026-09-20 13:45:00</t>
+          <t>2026-09-20 13:30:00</t>
         </is>
       </c>
     </row>
@@ -34981,12 +34981,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G213">
@@ -35132,7 +35132,7 @@
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>2026-09-20 14:00:00</t>
+          <t>2026-09-20 13:45:00</t>
         </is>
       </c>
     </row>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G214">
@@ -35312,7 +35312,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G215">
@@ -35475,7 +35475,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G216">
@@ -35638,7 +35638,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>CD Don Benito</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G217">
@@ -35801,7 +35801,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="G218">
@@ -35964,7 +35964,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>CD Don Benito</t>
         </is>
       </c>
       <c r="G219">
@@ -36127,7 +36127,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G220">
@@ -36290,7 +36290,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G221">
@@ -36453,7 +36453,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G222">
@@ -36616,7 +36616,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G223">
@@ -36779,7 +36779,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G224">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G225">
@@ -37105,7 +37105,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G226">
@@ -37263,27 +37263,27 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G227">
@@ -37414,7 +37414,7 @@
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>2026-09-20 14:15:00</t>
+          <t>2026-09-20 14:00:00</t>
         </is>
       </c>
     </row>
@@ -37426,12 +37426,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G228">
@@ -37577,7 +37577,7 @@
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>2026-09-20 14:15:00</t>
+          <t>2026-09-20 14:00:00</t>
         </is>
       </c>
     </row>
@@ -37594,22 +37594,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G229">
@@ -37752,12 +37752,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G230">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>2026-09-20 14:30:00</t>
+          <t>2026-09-20 14:15:00</t>
         </is>
       </c>
     </row>
@@ -37915,12 +37915,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G231">
@@ -38066,7 +38066,7 @@
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>2026-09-20 14:30:00</t>
+          <t>2026-09-20 14:15:00</t>
         </is>
       </c>
     </row>
@@ -38083,7 +38083,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G232">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O233">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P233">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="Q233">
         <v>0</v>
@@ -38409,7 +38409,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G234">
@@ -38572,7 +38572,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G235">
@@ -38614,13 +38614,13 @@
         </is>
       </c>
       <c r="N235">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O235">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P235">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="Q235">
         <v>0</v>
@@ -38730,27 +38730,27 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G236">
@@ -38773,7 +38773,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N236">
@@ -38881,7 +38881,7 @@
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>2026-09-20 15:00:00</t>
+          <t>2026-09-20 14:30:00</t>
         </is>
       </c>
     </row>
@@ -38893,12 +38893,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G237">
@@ -39044,7 +39044,7 @@
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>2026-09-20 15:00:00</t>
+          <t>2026-09-20 14:30:00</t>
         </is>
       </c>
     </row>
@@ -39061,7 +39061,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G238">
@@ -39224,7 +39224,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G239">
@@ -39382,27 +39382,27 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G240">
@@ -39533,7 +39533,7 @@
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>2026-09-20 15:15:00</t>
+          <t>2026-09-20 15:00:00</t>
         </is>
       </c>
     </row>
@@ -39545,12 +39545,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G241">
@@ -39696,7 +39696,7 @@
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>2026-09-20 15:15:00</t>
+          <t>2026-09-20 15:00:00</t>
         </is>
       </c>
     </row>
@@ -39708,12 +39708,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G242">
@@ -39859,7 +39859,7 @@
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>2026-09-20 15:30:00</t>
+          <t>2026-09-20 15:15:00</t>
         </is>
       </c>
     </row>
@@ -39871,12 +39871,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G243">
@@ -40022,7 +40022,7 @@
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>2026-09-20 15:30:00</t>
+          <t>2026-09-20 15:15:00</t>
         </is>
       </c>
     </row>
@@ -40039,22 +40039,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G244">
@@ -40202,22 +40202,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G245">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G246">
@@ -40528,22 +40528,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G247">
@@ -40691,22 +40691,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G248">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G249">
@@ -41012,12 +41012,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G250">
@@ -41163,7 +41163,7 @@
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>2026-09-20 15:45:00</t>
+          <t>2026-09-20 15:30:00</t>
         </is>
       </c>
     </row>
@@ -41175,12 +41175,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G251">
@@ -41326,7 +41326,7 @@
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>2026-09-20 15:45:00</t>
+          <t>2026-09-20 15:30:00</t>
         </is>
       </c>
     </row>
@@ -41338,27 +41338,27 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G252">
@@ -41489,7 +41489,7 @@
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>2026-09-20 16:00:00</t>
+          <t>2026-09-20 15:45:00</t>
         </is>
       </c>
     </row>
@@ -41501,27 +41501,27 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G253">
@@ -41652,7 +41652,7 @@
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>2026-09-20 16:00:00</t>
+          <t>2026-09-20 15:45:00</t>
         </is>
       </c>
     </row>
@@ -41669,7 +41669,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G254">
@@ -41832,7 +41832,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G255">
@@ -41995,22 +41995,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G256">
@@ -42158,7 +42158,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G257">
@@ -42321,7 +42321,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G258">
@@ -42484,7 +42484,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G259">
@@ -42642,27 +42642,27 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G260">
@@ -42793,7 +42793,7 @@
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>2026-09-20 16:30:00</t>
+          <t>2026-09-20 16:00:00</t>
         </is>
       </c>
     </row>
@@ -42805,27 +42805,27 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G261">
@@ -42956,7 +42956,7 @@
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>2026-09-20 16:30:00</t>
+          <t>2026-09-20 16:00:00</t>
         </is>
       </c>
     </row>
@@ -42968,7 +42968,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G262">
@@ -43119,7 +43119,7 @@
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>2026-09-20 17:00:00</t>
+          <t>2026-09-20 16:30:00</t>
         </is>
       </c>
     </row>
@@ -43131,27 +43131,27 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G263">
@@ -43282,7 +43282,7 @@
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>2026-09-20 17:00:00</t>
+          <t>2026-09-20 16:30:00</t>
         </is>
       </c>
     </row>
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G264">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G265">
@@ -43620,27 +43620,27 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G266">
@@ -43771,7 +43771,7 @@
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>2026-09-20 17:30:00</t>
+          <t>2026-09-20 17:00:00</t>
         </is>
       </c>
     </row>
@@ -43783,27 +43783,27 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G267">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>2026-09-20 17:30:00</t>
+          <t>2026-09-20 17:00:00</t>
         </is>
       </c>
     </row>
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G268">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G269">
@@ -44272,27 +44272,27 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G270">
@@ -44423,7 +44423,7 @@
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>2026-09-20 18:00:00</t>
+          <t>2026-09-20 17:30:00</t>
         </is>
       </c>
     </row>
@@ -44435,27 +44435,27 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G271">
@@ -44586,7 +44586,7 @@
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>2026-09-20 18:00:00</t>
+          <t>2026-09-20 17:30:00</t>
         </is>
       </c>
     </row>
@@ -44598,12 +44598,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G272">
@@ -44749,7 +44749,7 @@
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>2026-09-20 18:30:00</t>
+          <t>2026-09-20 18:00:00</t>
         </is>
       </c>
     </row>
@@ -44761,12 +44761,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G273">
@@ -44912,7 +44912,7 @@
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>2026-09-20 18:30:00</t>
+          <t>2026-09-20 18:00:00</t>
         </is>
       </c>
     </row>
@@ -44929,7 +44929,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G274">
@@ -45092,7 +45092,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G275">
@@ -45250,12 +45250,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G276">
@@ -45401,7 +45401,7 @@
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>2026-09-20 19:30:00</t>
+          <t>2026-09-20 18:30:00</t>
         </is>
       </c>
     </row>
@@ -45413,12 +45413,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G277">
@@ -45564,7 +45564,7 @@
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>2026-09-20 20:00:00</t>
+          <t>2026-09-20 18:30:00</t>
         </is>
       </c>
     </row>
@@ -45576,12 +45576,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G278">
@@ -45727,7 +45727,7 @@
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>2026-09-20 20:00:00</t>
+          <t>2026-09-20 19:30:00</t>
         </is>
       </c>
     </row>
@@ -45744,7 +45744,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G279">
@@ -45907,151 +45907,477 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Bay</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Racing Louisville</t>
+        </is>
+      </c>
+      <c r="G280">
+        <v>0</v>
+      </c>
+      <c r="H280">
+        <v>0</v>
+      </c>
+      <c r="I280">
+        <v>0</v>
+      </c>
+      <c r="J280">
+        <v>0</v>
+      </c>
+      <c r="K280">
+        <v>0</v>
+      </c>
+      <c r="L280">
+        <v>0</v>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N280">
+        <v>0</v>
+      </c>
+      <c r="O280">
+        <v>0</v>
+      </c>
+      <c r="P280">
+        <v>0</v>
+      </c>
+      <c r="Q280">
+        <v>0</v>
+      </c>
+      <c r="R280">
+        <v>0</v>
+      </c>
+      <c r="S280">
+        <v>0</v>
+      </c>
+      <c r="T280">
+        <v>0</v>
+      </c>
+      <c r="U280">
+        <v>0</v>
+      </c>
+      <c r="V280">
+        <v>0</v>
+      </c>
+      <c r="W280">
+        <v>0</v>
+      </c>
+      <c r="X280">
+        <v>0</v>
+      </c>
+      <c r="Y280">
+        <v>0</v>
+      </c>
+      <c r="Z280">
+        <v>0</v>
+      </c>
+      <c r="AA280">
+        <v>0</v>
+      </c>
+      <c r="AB280">
+        <v>0</v>
+      </c>
+      <c r="AC280">
+        <v>0</v>
+      </c>
+      <c r="AD280">
+        <v>0</v>
+      </c>
+      <c r="AE280">
+        <v>0</v>
+      </c>
+      <c r="AF280">
+        <v>0</v>
+      </c>
+      <c r="AG280">
+        <v>0</v>
+      </c>
+      <c r="AH280" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI280" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ280">
+        <v>0</v>
+      </c>
+      <c r="AK280">
+        <v>0</v>
+      </c>
+      <c r="AL280">
+        <v>0</v>
+      </c>
+      <c r="AM280">
+        <v>-1</v>
+      </c>
+      <c r="AN280">
+        <v>-1</v>
+      </c>
+      <c r="AO280">
+        <v>-1</v>
+      </c>
+      <c r="AP280">
+        <v>-1</v>
+      </c>
+      <c r="AQ280">
+        <v>0</v>
+      </c>
+      <c r="AR280">
+        <v>0</v>
+      </c>
+      <c r="AS280">
+        <v>0</v>
+      </c>
+      <c r="AT280">
+        <v>0</v>
+      </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>2026-09-20 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Utah Royals</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Angel City</t>
+        </is>
+      </c>
+      <c r="G281">
+        <v>0</v>
+      </c>
+      <c r="H281">
+        <v>0</v>
+      </c>
+      <c r="I281">
+        <v>0</v>
+      </c>
+      <c r="J281">
+        <v>0</v>
+      </c>
+      <c r="K281">
+        <v>0</v>
+      </c>
+      <c r="L281">
+        <v>0</v>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N281">
+        <v>0</v>
+      </c>
+      <c r="O281">
+        <v>0</v>
+      </c>
+      <c r="P281">
+        <v>0</v>
+      </c>
+      <c r="Q281">
+        <v>0</v>
+      </c>
+      <c r="R281">
+        <v>0</v>
+      </c>
+      <c r="S281">
+        <v>0</v>
+      </c>
+      <c r="T281">
+        <v>0</v>
+      </c>
+      <c r="U281">
+        <v>0</v>
+      </c>
+      <c r="V281">
+        <v>0</v>
+      </c>
+      <c r="W281">
+        <v>0</v>
+      </c>
+      <c r="X281">
+        <v>0</v>
+      </c>
+      <c r="Y281">
+        <v>0</v>
+      </c>
+      <c r="Z281">
+        <v>0</v>
+      </c>
+      <c r="AA281">
+        <v>0</v>
+      </c>
+      <c r="AB281">
+        <v>0</v>
+      </c>
+      <c r="AC281">
+        <v>0</v>
+      </c>
+      <c r="AD281">
+        <v>0</v>
+      </c>
+      <c r="AE281">
+        <v>0</v>
+      </c>
+      <c r="AF281">
+        <v>0</v>
+      </c>
+      <c r="AG281">
+        <v>0</v>
+      </c>
+      <c r="AH281" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI281" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ281">
+        <v>0</v>
+      </c>
+      <c r="AK281">
+        <v>0</v>
+      </c>
+      <c r="AL281">
+        <v>0</v>
+      </c>
+      <c r="AM281">
+        <v>-1</v>
+      </c>
+      <c r="AN281">
+        <v>-1</v>
+      </c>
+      <c r="AO281">
+        <v>-1</v>
+      </c>
+      <c r="AP281">
+        <v>-1</v>
+      </c>
+      <c r="AQ281">
+        <v>0</v>
+      </c>
+      <c r="AR281">
+        <v>0</v>
+      </c>
+      <c r="AS281">
+        <v>0</v>
+      </c>
+      <c r="AT281">
+        <v>0</v>
+      </c>
+      <c r="AU281" t="inlineStr">
+        <is>
+          <t>2026-09-20 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr">
+      <c r="D282" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr">
+      <c r="E282" t="inlineStr">
         <is>
           <t>Inter Miami</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr">
+      <c r="F282" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="G280">
-        <v>0</v>
-      </c>
-      <c r="H280">
-        <v>0</v>
-      </c>
-      <c r="I280">
-        <v>0</v>
-      </c>
-      <c r="J280">
-        <v>0</v>
-      </c>
-      <c r="K280">
-        <v>0</v>
-      </c>
-      <c r="L280">
-        <v>0</v>
-      </c>
-      <c r="M280" t="inlineStr">
+      <c r="G282">
+        <v>0</v>
+      </c>
+      <c r="H282">
+        <v>0</v>
+      </c>
+      <c r="I282">
+        <v>0</v>
+      </c>
+      <c r="J282">
+        <v>0</v>
+      </c>
+      <c r="K282">
+        <v>0</v>
+      </c>
+      <c r="L282">
+        <v>0</v>
+      </c>
+      <c r="M282" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N280">
-        <v>0</v>
-      </c>
-      <c r="O280">
-        <v>0</v>
-      </c>
-      <c r="P280">
-        <v>0</v>
-      </c>
-      <c r="Q280">
-        <v>0</v>
-      </c>
-      <c r="R280">
-        <v>0</v>
-      </c>
-      <c r="S280">
-        <v>0</v>
-      </c>
-      <c r="T280">
-        <v>0</v>
-      </c>
-      <c r="U280">
-        <v>0</v>
-      </c>
-      <c r="V280">
-        <v>0</v>
-      </c>
-      <c r="W280">
-        <v>0</v>
-      </c>
-      <c r="X280">
-        <v>0</v>
-      </c>
-      <c r="Y280">
-        <v>0</v>
-      </c>
-      <c r="Z280">
-        <v>0</v>
-      </c>
-      <c r="AA280">
-        <v>0</v>
-      </c>
-      <c r="AB280">
-        <v>0</v>
-      </c>
-      <c r="AC280">
-        <v>0</v>
-      </c>
-      <c r="AD280">
-        <v>0</v>
-      </c>
-      <c r="AE280">
-        <v>0</v>
-      </c>
-      <c r="AF280">
-        <v>0</v>
-      </c>
-      <c r="AG280">
-        <v>0</v>
-      </c>
-      <c r="AH280" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI280" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ280">
-        <v>0</v>
-      </c>
-      <c r="AK280">
-        <v>0</v>
-      </c>
-      <c r="AL280">
-        <v>0</v>
-      </c>
-      <c r="AM280">
-        <v>-1</v>
-      </c>
-      <c r="AN280">
-        <v>-1</v>
-      </c>
-      <c r="AO280">
-        <v>-1</v>
-      </c>
-      <c r="AP280">
-        <v>-1</v>
-      </c>
-      <c r="AQ280">
-        <v>0</v>
-      </c>
-      <c r="AR280">
-        <v>0</v>
-      </c>
-      <c r="AS280">
-        <v>0</v>
-      </c>
-      <c r="AT280">
-        <v>0</v>
-      </c>
-      <c r="AU280" t="inlineStr">
+      <c r="N282">
+        <v>0</v>
+      </c>
+      <c r="O282">
+        <v>0</v>
+      </c>
+      <c r="P282">
+        <v>0</v>
+      </c>
+      <c r="Q282">
+        <v>0</v>
+      </c>
+      <c r="R282">
+        <v>0</v>
+      </c>
+      <c r="S282">
+        <v>0</v>
+      </c>
+      <c r="T282">
+        <v>0</v>
+      </c>
+      <c r="U282">
+        <v>0</v>
+      </c>
+      <c r="V282">
+        <v>0</v>
+      </c>
+      <c r="W282">
+        <v>0</v>
+      </c>
+      <c r="X282">
+        <v>0</v>
+      </c>
+      <c r="Y282">
+        <v>0</v>
+      </c>
+      <c r="Z282">
+        <v>0</v>
+      </c>
+      <c r="AA282">
+        <v>0</v>
+      </c>
+      <c r="AB282">
+        <v>0</v>
+      </c>
+      <c r="AC282">
+        <v>0</v>
+      </c>
+      <c r="AD282">
+        <v>0</v>
+      </c>
+      <c r="AE282">
+        <v>0</v>
+      </c>
+      <c r="AF282">
+        <v>0</v>
+      </c>
+      <c r="AG282">
+        <v>0</v>
+      </c>
+      <c r="AH282" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI282" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ282">
+        <v>0</v>
+      </c>
+      <c r="AK282">
+        <v>0</v>
+      </c>
+      <c r="AL282">
+        <v>0</v>
+      </c>
+      <c r="AM282">
+        <v>-1</v>
+      </c>
+      <c r="AN282">
+        <v>-1</v>
+      </c>
+      <c r="AO282">
+        <v>-1</v>
+      </c>
+      <c r="AP282">
+        <v>-1</v>
+      </c>
+      <c r="AQ282">
+        <v>0</v>
+      </c>
+      <c r="AR282">
+        <v>0</v>
+      </c>
+      <c r="AS282">
+        <v>0</v>
+      </c>
+      <c r="AT282">
+        <v>0</v>
+      </c>
+      <c r="AU282" t="inlineStr">
         <is>
           <t>2026-09-20 20:00:00</t>
         </is>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G136">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G141">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G170">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G171">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G270">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G271">

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G112">

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU282"/>
+  <dimension ref="A1:AU283"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G73">
@@ -12324,27 +12324,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G74">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>2026-09-20 09:15:00</t>
+          <t>2026-09-20 09:00:00</t>
         </is>
       </c>
     </row>
@@ -12492,22 +12492,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G75">
@@ -12650,12 +12650,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G76">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>2026-09-20 09:30:00</t>
+          <t>2026-09-20 09:15:00</t>
         </is>
       </c>
     </row>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G77">
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G78">
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G79">
@@ -13307,22 +13307,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G80">
@@ -13470,22 +13470,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G81">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G82">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G84">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G85">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G87">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G89">
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G90">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-09-20 09:45:00</t>
+          <t>2026-09-20 09:30:00</t>
         </is>
       </c>
     </row>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G91">
@@ -15258,12 +15258,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="G92">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-09-20 10:00:00</t>
+          <t>2026-09-20 09:45:00</t>
         </is>
       </c>
     </row>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G93">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G96">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G99">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G100">
@@ -16730,22 +16730,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G101">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G102">
@@ -17056,22 +17056,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G103">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G105">
@@ -17545,22 +17545,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,22 +18034,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G112">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G114">
@@ -19007,12 +19007,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G115">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-09-20 10:30:00</t>
+          <t>2026-09-20 10:00:00</t>
         </is>
       </c>
     </row>
@@ -19170,27 +19170,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G116">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-09-20 11:00:00</t>
+          <t>2026-09-20 10:30:00</t>
         </is>
       </c>
     </row>
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,22 +19664,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G119">
@@ -19827,22 +19827,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,22 +19990,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G121">
@@ -20028,7 +20028,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N121">
@@ -20153,22 +20153,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G122">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N122">
@@ -20316,22 +20316,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,22 +20479,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Excelsior Virton</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Excelsior Virton</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,22 +21457,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G130">
@@ -21620,22 +21620,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G131">
@@ -21778,12 +21778,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G132">
@@ -21929,7 +21929,7 @@
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>2026-09-20 11:15:00</t>
+          <t>2026-09-20 11:00:00</t>
         </is>
       </c>
     </row>
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G133">
@@ -22104,27 +22104,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G134">
@@ -22255,7 +22255,7 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>2026-09-20 11:30:00</t>
+          <t>2026-09-20 11:15:00</t>
         </is>
       </c>
     </row>
@@ -22272,22 +22272,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G136">
@@ -22598,7 +22598,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G137">
@@ -22761,22 +22761,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G139">
@@ -23087,22 +23087,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G141">
@@ -23413,7 +23413,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G142">
@@ -23571,12 +23571,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G143">
@@ -23722,7 +23722,7 @@
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>2026-09-20 11:45:00</t>
+          <t>2026-09-20 11:30:00</t>
         </is>
       </c>
     </row>
@@ -23739,7 +23739,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G144">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G145">
@@ -24065,7 +24065,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G146">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G147">
@@ -24386,12 +24386,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G148">
@@ -24537,7 +24537,7 @@
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>2026-09-20 12:00:00</t>
+          <t>2026-09-20 11:45:00</t>
         </is>
       </c>
     </row>
@@ -24554,7 +24554,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G149">
@@ -24717,7 +24717,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Arnedo</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G151">
@@ -25043,7 +25043,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Arnedo</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G152">
@@ -25206,22 +25206,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G155">
@@ -25695,22 +25695,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G156">
@@ -25858,7 +25858,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G157">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G158">
@@ -26184,22 +26184,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G159">
@@ -26347,22 +26347,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Atlético Tordesillas</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G160">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Atlético Tordesillas</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G161">
@@ -26673,7 +26673,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G162">
@@ -26836,7 +26836,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G164">
@@ -27162,22 +27162,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G167">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G170">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G171">
@@ -28298,27 +28298,27 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G172">
@@ -28449,7 +28449,7 @@
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>2026-09-20 12:15:00</t>
+          <t>2026-09-20 12:00:00</t>
         </is>
       </c>
     </row>
@@ -28466,7 +28466,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G173">
@@ -28624,12 +28624,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G174">
@@ -28775,7 +28775,7 @@
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>2026-09-20 12:30:00</t>
+          <t>2026-09-20 12:15:00</t>
         </is>
       </c>
     </row>
@@ -28792,7 +28792,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G175">
@@ -28955,7 +28955,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G176">
@@ -29118,7 +29118,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G177">
@@ -29281,7 +29281,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G178">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G179">
@@ -29607,7 +29607,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G180">
@@ -29770,7 +29770,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G181">
@@ -29933,7 +29933,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G182">
@@ -30096,7 +30096,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G183">
@@ -30259,7 +30259,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G184">
@@ -30417,27 +30417,27 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G185">
@@ -30568,7 +30568,7 @@
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>2026-09-20 13:00:00</t>
+          <t>2026-09-20 12:30:00</t>
         </is>
       </c>
     </row>
@@ -30585,22 +30585,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G186">
@@ -30748,7 +30748,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G187">
@@ -30911,22 +30911,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="G188">
@@ -31074,22 +31074,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G189">
@@ -31237,22 +31237,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G190">
@@ -31400,7 +31400,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G194">
@@ -32052,22 +32052,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G195">
@@ -32215,7 +32215,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>CD Badajoz</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G196">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>CD Badajoz</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G197">
@@ -32541,7 +32541,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="G198">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G199">
@@ -32867,7 +32867,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G200">
@@ -33030,7 +33030,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="G201">
@@ -33356,7 +33356,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G203">
@@ -33514,12 +33514,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G204">
@@ -33665,7 +33665,7 @@
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>2026-09-20 13:15:00</t>
+          <t>2026-09-20 13:00:00</t>
         </is>
       </c>
     </row>
@@ -33677,12 +33677,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G205">
@@ -33828,7 +33828,7 @@
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>2026-09-20 13:30:00</t>
+          <t>2026-09-20 13:15:00</t>
         </is>
       </c>
     </row>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G206">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G207">
@@ -34171,7 +34171,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G208">
@@ -34334,7 +34334,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G209">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G210">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G211">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G212">
@@ -34981,12 +34981,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G213">
@@ -35132,7 +35132,7 @@
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>2026-09-20 13:45:00</t>
+          <t>2026-09-20 13:30:00</t>
         </is>
       </c>
     </row>
@@ -35144,12 +35144,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G214">
@@ -35295,7 +35295,7 @@
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>2026-09-20 14:00:00</t>
+          <t>2026-09-20 13:45:00</t>
         </is>
       </c>
     </row>
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G215">
@@ -35475,7 +35475,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G216">
@@ -35638,7 +35638,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G217">
@@ -35801,7 +35801,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G218">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CD Don Benito</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="G219">
@@ -36127,7 +36127,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>CD Don Benito</t>
         </is>
       </c>
       <c r="G220">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G221">
@@ -36453,7 +36453,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G222">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G223">
@@ -36779,7 +36779,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G224">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G225">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G226">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G227">
@@ -37431,7 +37431,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G228">
@@ -37589,27 +37589,27 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G229">
@@ -37740,7 +37740,7 @@
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>2026-09-20 14:15:00</t>
+          <t>2026-09-20 14:00:00</t>
         </is>
       </c>
     </row>
@@ -37757,22 +37757,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G230">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G231">
@@ -38078,12 +38078,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G232">
@@ -38229,7 +38229,7 @@
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>2026-09-20 14:30:00</t>
+          <t>2026-09-20 14:15:00</t>
         </is>
       </c>
     </row>
@@ -38246,7 +38246,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G233">
@@ -38409,7 +38409,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G234">
@@ -38572,7 +38572,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G235">
@@ -38614,13 +38614,13 @@
         </is>
       </c>
       <c r="N235">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O235">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P235">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="Q235">
         <v>0</v>
@@ -38735,7 +38735,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G236">
@@ -38773,17 +38773,17 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N236">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O236">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P236">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="Q236">
         <v>0</v>
@@ -38898,7 +38898,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G237">
@@ -38936,7 +38936,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N237">
@@ -39056,27 +39056,27 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G238">
@@ -39207,7 +39207,7 @@
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>2026-09-20 15:00:00</t>
+          <t>2026-09-20 14:30:00</t>
         </is>
       </c>
     </row>
@@ -39224,22 +39224,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G239">
@@ -39387,22 +39387,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G240">
@@ -39550,22 +39550,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G241">
@@ -39708,12 +39708,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G242">
@@ -39859,7 +39859,7 @@
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>2026-09-20 15:15:00</t>
+          <t>2026-09-20 15:00:00</t>
         </is>
       </c>
     </row>
@@ -39876,7 +39876,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G243">
@@ -40034,12 +40034,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G244">
@@ -40185,7 +40185,7 @@
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>2026-09-20 15:30:00</t>
+          <t>2026-09-20 15:15:00</t>
         </is>
       </c>
     </row>
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G245">
@@ -40365,22 +40365,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G246">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G247">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G248">
@@ -40854,22 +40854,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G249">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G250">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G251">
@@ -41338,12 +41338,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G252">
@@ -41489,7 +41489,7 @@
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>2026-09-20 15:45:00</t>
+          <t>2026-09-20 15:30:00</t>
         </is>
       </c>
     </row>
@@ -41506,7 +41506,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G253">
@@ -41664,27 +41664,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G254">
@@ -41815,7 +41815,7 @@
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>2026-09-20 16:00:00</t>
+          <t>2026-09-20 15:45:00</t>
         </is>
       </c>
     </row>
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G255">
@@ -41995,7 +41995,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G256">
@@ -42158,7 +42158,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G257">
@@ -42321,22 +42321,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G258">
@@ -42484,22 +42484,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G259">
@@ -42647,22 +42647,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G260">
@@ -42810,22 +42810,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G261">
@@ -42968,12 +42968,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G262">
@@ -43119,7 +43119,7 @@
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>2026-09-20 16:30:00</t>
+          <t>2026-09-20 16:00:00</t>
         </is>
       </c>
     </row>
@@ -43136,22 +43136,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G263">
@@ -43294,27 +43294,27 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G264">
@@ -43445,7 +43445,7 @@
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>2026-09-20 17:00:00</t>
+          <t>2026-09-20 16:30:00</t>
         </is>
       </c>
     </row>
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G265">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G266">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G267">
@@ -43946,27 +43946,27 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G268">
@@ -44097,7 +44097,7 @@
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>2026-09-20 17:30:00</t>
+          <t>2026-09-20 17:00:00</t>
         </is>
       </c>
     </row>
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G269">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G270">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G271">
@@ -44598,27 +44598,27 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G272">
@@ -44749,7 +44749,7 @@
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>2026-09-20 18:00:00</t>
+          <t>2026-09-20 17:30:00</t>
         </is>
       </c>
     </row>
@@ -44766,7 +44766,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G273">
@@ -44924,12 +44924,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G274">
@@ -45075,7 +45075,7 @@
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>2026-09-20 18:30:00</t>
+          <t>2026-09-20 18:00:00</t>
         </is>
       </c>
     </row>
@@ -45092,7 +45092,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G275">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G276">
@@ -45418,7 +45418,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G277">
@@ -45576,12 +45576,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G278">
@@ -45727,7 +45727,7 @@
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>2026-09-20 19:30:00</t>
+          <t>2026-09-20 18:30:00</t>
         </is>
       </c>
     </row>
@@ -45739,12 +45739,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G279">
@@ -45890,7 +45890,7 @@
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>2026-09-20 20:00:00</t>
+          <t>2026-09-20 19:30:00</t>
         </is>
       </c>
     </row>
@@ -45907,7 +45907,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G280">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G281">
@@ -46233,151 +46233,314 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Utah Royals</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Angel City</t>
+        </is>
+      </c>
+      <c r="G282">
+        <v>0</v>
+      </c>
+      <c r="H282">
+        <v>0</v>
+      </c>
+      <c r="I282">
+        <v>0</v>
+      </c>
+      <c r="J282">
+        <v>0</v>
+      </c>
+      <c r="K282">
+        <v>0</v>
+      </c>
+      <c r="L282">
+        <v>0</v>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N282">
+        <v>0</v>
+      </c>
+      <c r="O282">
+        <v>0</v>
+      </c>
+      <c r="P282">
+        <v>0</v>
+      </c>
+      <c r="Q282">
+        <v>0</v>
+      </c>
+      <c r="R282">
+        <v>0</v>
+      </c>
+      <c r="S282">
+        <v>0</v>
+      </c>
+      <c r="T282">
+        <v>0</v>
+      </c>
+      <c r="U282">
+        <v>0</v>
+      </c>
+      <c r="V282">
+        <v>0</v>
+      </c>
+      <c r="W282">
+        <v>0</v>
+      </c>
+      <c r="X282">
+        <v>0</v>
+      </c>
+      <c r="Y282">
+        <v>0</v>
+      </c>
+      <c r="Z282">
+        <v>0</v>
+      </c>
+      <c r="AA282">
+        <v>0</v>
+      </c>
+      <c r="AB282">
+        <v>0</v>
+      </c>
+      <c r="AC282">
+        <v>0</v>
+      </c>
+      <c r="AD282">
+        <v>0</v>
+      </c>
+      <c r="AE282">
+        <v>0</v>
+      </c>
+      <c r="AF282">
+        <v>0</v>
+      </c>
+      <c r="AG282">
+        <v>0</v>
+      </c>
+      <c r="AH282" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI282" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ282">
+        <v>0</v>
+      </c>
+      <c r="AK282">
+        <v>0</v>
+      </c>
+      <c r="AL282">
+        <v>0</v>
+      </c>
+      <c r="AM282">
+        <v>-1</v>
+      </c>
+      <c r="AN282">
+        <v>-1</v>
+      </c>
+      <c r="AO282">
+        <v>-1</v>
+      </c>
+      <c r="AP282">
+        <v>-1</v>
+      </c>
+      <c r="AQ282">
+        <v>0</v>
+      </c>
+      <c r="AR282">
+        <v>0</v>
+      </c>
+      <c r="AS282">
+        <v>0</v>
+      </c>
+      <c r="AT282">
+        <v>0</v>
+      </c>
+      <c r="AU282" t="inlineStr">
+        <is>
+          <t>2026-09-20 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr">
+      <c r="D283" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr">
+      <c r="E283" t="inlineStr">
         <is>
           <t>Inter Miami</t>
         </is>
       </c>
-      <c r="F282" t="inlineStr">
+      <c r="F283" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="G282">
-        <v>0</v>
-      </c>
-      <c r="H282">
-        <v>0</v>
-      </c>
-      <c r="I282">
-        <v>0</v>
-      </c>
-      <c r="J282">
-        <v>0</v>
-      </c>
-      <c r="K282">
-        <v>0</v>
-      </c>
-      <c r="L282">
-        <v>0</v>
-      </c>
-      <c r="M282" t="inlineStr">
+      <c r="G283">
+        <v>0</v>
+      </c>
+      <c r="H283">
+        <v>0</v>
+      </c>
+      <c r="I283">
+        <v>0</v>
+      </c>
+      <c r="J283">
+        <v>0</v>
+      </c>
+      <c r="K283">
+        <v>0</v>
+      </c>
+      <c r="L283">
+        <v>0</v>
+      </c>
+      <c r="M283" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N282">
-        <v>0</v>
-      </c>
-      <c r="O282">
-        <v>0</v>
-      </c>
-      <c r="P282">
-        <v>0</v>
-      </c>
-      <c r="Q282">
-        <v>0</v>
-      </c>
-      <c r="R282">
-        <v>0</v>
-      </c>
-      <c r="S282">
-        <v>0</v>
-      </c>
-      <c r="T282">
-        <v>0</v>
-      </c>
-      <c r="U282">
-        <v>0</v>
-      </c>
-      <c r="V282">
-        <v>0</v>
-      </c>
-      <c r="W282">
-        <v>0</v>
-      </c>
-      <c r="X282">
-        <v>0</v>
-      </c>
-      <c r="Y282">
-        <v>0</v>
-      </c>
-      <c r="Z282">
-        <v>0</v>
-      </c>
-      <c r="AA282">
-        <v>0</v>
-      </c>
-      <c r="AB282">
-        <v>0</v>
-      </c>
-      <c r="AC282">
-        <v>0</v>
-      </c>
-      <c r="AD282">
-        <v>0</v>
-      </c>
-      <c r="AE282">
-        <v>0</v>
-      </c>
-      <c r="AF282">
-        <v>0</v>
-      </c>
-      <c r="AG282">
-        <v>0</v>
-      </c>
-      <c r="AH282" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI282" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ282">
-        <v>0</v>
-      </c>
-      <c r="AK282">
-        <v>0</v>
-      </c>
-      <c r="AL282">
-        <v>0</v>
-      </c>
-      <c r="AM282">
-        <v>-1</v>
-      </c>
-      <c r="AN282">
-        <v>-1</v>
-      </c>
-      <c r="AO282">
-        <v>-1</v>
-      </c>
-      <c r="AP282">
-        <v>-1</v>
-      </c>
-      <c r="AQ282">
-        <v>0</v>
-      </c>
-      <c r="AR282">
-        <v>0</v>
-      </c>
-      <c r="AS282">
-        <v>0</v>
-      </c>
-      <c r="AT282">
-        <v>0</v>
-      </c>
-      <c r="AU282" t="inlineStr">
+      <c r="N283">
+        <v>0</v>
+      </c>
+      <c r="O283">
+        <v>0</v>
+      </c>
+      <c r="P283">
+        <v>0</v>
+      </c>
+      <c r="Q283">
+        <v>0</v>
+      </c>
+      <c r="R283">
+        <v>0</v>
+      </c>
+      <c r="S283">
+        <v>0</v>
+      </c>
+      <c r="T283">
+        <v>0</v>
+      </c>
+      <c r="U283">
+        <v>0</v>
+      </c>
+      <c r="V283">
+        <v>0</v>
+      </c>
+      <c r="W283">
+        <v>0</v>
+      </c>
+      <c r="X283">
+        <v>0</v>
+      </c>
+      <c r="Y283">
+        <v>0</v>
+      </c>
+      <c r="Z283">
+        <v>0</v>
+      </c>
+      <c r="AA283">
+        <v>0</v>
+      </c>
+      <c r="AB283">
+        <v>0</v>
+      </c>
+      <c r="AC283">
+        <v>0</v>
+      </c>
+      <c r="AD283">
+        <v>0</v>
+      </c>
+      <c r="AE283">
+        <v>0</v>
+      </c>
+      <c r="AF283">
+        <v>0</v>
+      </c>
+      <c r="AG283">
+        <v>0</v>
+      </c>
+      <c r="AH283" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI283" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ283">
+        <v>0</v>
+      </c>
+      <c r="AK283">
+        <v>0</v>
+      </c>
+      <c r="AL283">
+        <v>0</v>
+      </c>
+      <c r="AM283">
+        <v>-1</v>
+      </c>
+      <c r="AN283">
+        <v>-1</v>
+      </c>
+      <c r="AO283">
+        <v>-1</v>
+      </c>
+      <c r="AP283">
+        <v>-1</v>
+      </c>
+      <c r="AQ283">
+        <v>0</v>
+      </c>
+      <c r="AR283">
+        <v>0</v>
+      </c>
+      <c r="AS283">
+        <v>0</v>
+      </c>
+      <c r="AT283">
+        <v>0</v>
+      </c>
+      <c r="AU283" t="inlineStr">
         <is>
           <t>2026-09-20 20:00:00</t>
         </is>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G16">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G28">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G113">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G195">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G210">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G211">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G215">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G216">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G221">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G222">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G265">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G267">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G281">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G282">

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU283"/>
+  <dimension ref="A1:AU287"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G24">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G33">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G90">
@@ -16241,22 +16241,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G100">
@@ -16730,7 +16730,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G101">
@@ -16893,22 +16893,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G102">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G103">
@@ -17219,22 +17219,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G104">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,22 +17708,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,22 +18197,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G110">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G113">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G114">
@@ -19170,12 +19170,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G116">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-09-20 10:30:00</t>
+          <t>2026-09-20 10:00:00</t>
         </is>
       </c>
     </row>
@@ -19333,27 +19333,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G117">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-09-20 11:00:00</t>
+          <t>2026-09-20 10:30:00</t>
         </is>
       </c>
     </row>
@@ -19501,22 +19501,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G119">
@@ -19827,22 +19827,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,22 +19990,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G121">
@@ -20153,22 +20153,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G122">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N122">
@@ -20316,22 +20316,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G123">
@@ -20354,7 +20354,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N123">
@@ -20479,22 +20479,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,22 +20642,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G125">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Excelsior Virton</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Excelsior Virton</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G130">
@@ -21620,22 +21620,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G131">
@@ -21783,22 +21783,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G132">
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G133">
@@ -22092,7 +22092,7 @@
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>2026-09-20 11:15:00</t>
+          <t>2026-09-20 11:00:00</t>
         </is>
       </c>
     </row>
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G134">
@@ -22267,27 +22267,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G135">
@@ -22418,7 +22418,7 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>2026-09-20 11:30:00</t>
+          <t>2026-09-20 11:15:00</t>
         </is>
       </c>
     </row>
@@ -22435,22 +22435,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G137">
@@ -22761,7 +22761,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G138">
@@ -22924,22 +22924,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G140">
@@ -23250,22 +23250,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G142">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G143">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G144">
@@ -23885,7 +23885,7 @@
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>2026-09-20 11:45:00</t>
+          <t>2026-09-20 11:30:00</t>
         </is>
       </c>
     </row>
@@ -23902,7 +23902,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G145">
@@ -24065,7 +24065,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G146">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G147">
@@ -24391,7 +24391,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G148">
@@ -24549,12 +24549,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G149">
@@ -24700,7 +24700,7 @@
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>2026-09-20 12:00:00</t>
+          <t>2026-09-20 11:45:00</t>
         </is>
       </c>
     </row>
@@ -24717,7 +24717,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G150">
@@ -24880,7 +24880,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G151">
@@ -25206,7 +25206,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G153">
@@ -25369,22 +25369,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G156">
@@ -25858,22 +25858,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G157">
@@ -26021,7 +26021,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G158">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G159">
@@ -26222,68 +26222,68 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N159">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O159">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P159">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q159">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R159">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S159">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T159">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U159">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V159">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W159">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X159">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y159">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z159">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA159">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB159">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC159">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AD159">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE159">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF159">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AG159">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK159">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26347,22 +26347,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G160">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Atlético Tordesillas</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G161">
@@ -26673,22 +26673,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G162">
@@ -26836,7 +26836,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Atlético Tordesillas</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G163">
@@ -26999,7 +26999,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G164">
@@ -27162,7 +27162,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G165">
@@ -27325,22 +27325,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G166">
@@ -27488,22 +27488,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="G167">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G170">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G171">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G172">
@@ -28461,27 +28461,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G173">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>2026-09-20 12:15:00</t>
+          <t>2026-09-20 12:00:00</t>
         </is>
       </c>
     </row>
@@ -28624,27 +28624,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G174">
@@ -28775,7 +28775,7 @@
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>2026-09-20 12:15:00</t>
+          <t>2026-09-20 12:00:00</t>
         </is>
       </c>
     </row>
@@ -28787,12 +28787,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G175">
@@ -28938,7 +28938,7 @@
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>2026-09-20 12:30:00</t>
+          <t>2026-09-20 12:15:00</t>
         </is>
       </c>
     </row>
@@ -28950,12 +28950,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G176">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>2026-09-20 12:30:00</t>
+          <t>2026-09-20 12:15:00</t>
         </is>
       </c>
     </row>
@@ -29118,7 +29118,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G177">
@@ -29281,7 +29281,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G178">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G179">
@@ -29607,7 +29607,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G180">
@@ -29770,7 +29770,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G181">
@@ -29933,7 +29933,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G182">
@@ -30096,7 +30096,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G183">
@@ -30259,7 +30259,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G184">
@@ -30422,7 +30422,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G185">
@@ -30580,27 +30580,27 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G186">
@@ -30731,7 +30731,7 @@
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>2026-09-20 13:00:00</t>
+          <t>2026-09-20 12:30:00</t>
         </is>
       </c>
     </row>
@@ -30743,12 +30743,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G187">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>2026-09-20 13:00:00</t>
+          <t>2026-09-20 12:30:00</t>
         </is>
       </c>
     </row>
@@ -30911,22 +30911,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G188">
@@ -31074,22 +31074,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G189">
@@ -31237,7 +31237,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="G190">
@@ -31400,7 +31400,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G191">
@@ -31563,22 +31563,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G192">
@@ -31726,7 +31726,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G195">
@@ -32215,22 +32215,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G196">
@@ -32378,22 +32378,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>CD Badajoz</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G197">
@@ -32541,7 +32541,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G198">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="G199">
@@ -32867,7 +32867,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>CD Badajoz</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G200">
@@ -33030,7 +33030,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G201">
@@ -33193,7 +33193,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G202">
@@ -33356,7 +33356,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="G203">
@@ -33519,7 +33519,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="G204">
@@ -33677,12 +33677,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G205">
@@ -33828,7 +33828,7 @@
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>2026-09-20 13:15:00</t>
+          <t>2026-09-20 13:00:00</t>
         </is>
       </c>
     </row>
@@ -33840,12 +33840,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G206">
@@ -33991,7 +33991,7 @@
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>2026-09-20 13:30:00</t>
+          <t>2026-09-20 13:00:00</t>
         </is>
       </c>
     </row>
@@ -34003,12 +34003,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G207">
@@ -34154,7 +34154,7 @@
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>2026-09-20 13:30:00</t>
+          <t>2026-09-20 13:15:00</t>
         </is>
       </c>
     </row>
@@ -34171,7 +34171,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G208">
@@ -34334,7 +34334,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G209">
@@ -34497,7 +34497,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G210">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G211">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G212">
@@ -34986,7 +34986,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G213">
@@ -35144,12 +35144,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G214">
@@ -35295,7 +35295,7 @@
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>2026-09-20 13:45:00</t>
+          <t>2026-09-20 13:30:00</t>
         </is>
       </c>
     </row>
@@ -35307,12 +35307,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G215">
@@ -35458,7 +35458,7 @@
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>2026-09-20 14:00:00</t>
+          <t>2026-09-20 13:30:00</t>
         </is>
       </c>
     </row>
@@ -35470,12 +35470,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G216">
@@ -35621,7 +35621,7 @@
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>2026-09-20 14:00:00</t>
+          <t>2026-09-20 13:45:00</t>
         </is>
       </c>
     </row>
@@ -35638,7 +35638,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G217">
@@ -35801,7 +35801,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G218">
@@ -35964,7 +35964,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G219">
@@ -36127,7 +36127,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>CD Don Benito</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G220">
@@ -36290,7 +36290,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="G221">
@@ -36453,7 +36453,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>CD Don Benito</t>
         </is>
       </c>
       <c r="G222">
@@ -36616,7 +36616,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G223">
@@ -36779,7 +36779,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G224">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G225">
@@ -37105,7 +37105,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G226">
@@ -37268,7 +37268,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G227">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G228">
@@ -37594,7 +37594,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G229">
@@ -37752,27 +37752,27 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G230">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>2026-09-20 14:15:00</t>
+          <t>2026-09-20 14:00:00</t>
         </is>
       </c>
     </row>
@@ -37915,12 +37915,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G231">
@@ -38066,7 +38066,7 @@
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>2026-09-20 14:15:00</t>
+          <t>2026-09-20 14:00:00</t>
         </is>
       </c>
     </row>
@@ -38083,22 +38083,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G232">
@@ -38241,12 +38241,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G233">
@@ -38392,7 +38392,7 @@
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>2026-09-20 14:30:00</t>
+          <t>2026-09-20 14:15:00</t>
         </is>
       </c>
     </row>
@@ -38404,12 +38404,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G234">
@@ -38555,7 +38555,7 @@
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>2026-09-20 14:30:00</t>
+          <t>2026-09-20 14:15:00</t>
         </is>
       </c>
     </row>
@@ -38572,7 +38572,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G235">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,13 +38777,13 @@
         </is>
       </c>
       <c r="N236">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O236">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P236">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="Q236">
         <v>0</v>
@@ -38898,7 +38898,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G237">
@@ -38936,7 +38936,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N237">
@@ -39061,7 +39061,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,13 +39103,13 @@
         </is>
       </c>
       <c r="N238">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O238">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P238">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="Q238">
         <v>0</v>
@@ -39219,27 +39219,27 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G239">
@@ -39262,7 +39262,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N239">
@@ -39370,7 +39370,7 @@
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>2026-09-20 15:00:00</t>
+          <t>2026-09-20 14:30:00</t>
         </is>
       </c>
     </row>
@@ -39382,12 +39382,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G240">
@@ -39533,7 +39533,7 @@
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>2026-09-20 15:00:00</t>
+          <t>2026-09-20 14:30:00</t>
         </is>
       </c>
     </row>
@@ -39550,7 +39550,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G241">
@@ -39592,64 +39592,64 @@
         </is>
       </c>
       <c r="N241">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O241">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P241">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q241">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R241">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S241">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T241">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U241">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V241">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W241">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X241">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y241">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z241">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA241">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB241">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC241">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="AD241">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE241">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF241">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AG241">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH241" t="inlineStr">
         <is>
@@ -39662,10 +39662,10 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK241">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -39713,22 +39713,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G242">
@@ -39871,27 +39871,27 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G243">
@@ -40022,7 +40022,7 @@
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>2026-09-20 15:15:00</t>
+          <t>2026-09-20 15:00:00</t>
         </is>
       </c>
     </row>
@@ -40034,12 +40034,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G244">
@@ -40185,7 +40185,7 @@
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>2026-09-20 15:15:00</t>
+          <t>2026-09-20 15:00:00</t>
         </is>
       </c>
     </row>
@@ -40197,27 +40197,27 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G245">
@@ -40348,7 +40348,7 @@
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>2026-09-20 15:30:00</t>
+          <t>2026-09-20 15:00:00</t>
         </is>
       </c>
     </row>
@@ -40360,12 +40360,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G246">
@@ -40511,7 +40511,7 @@
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>2026-09-20 15:30:00</t>
+          <t>2026-09-20 15:00:00</t>
         </is>
       </c>
     </row>
@@ -40523,27 +40523,27 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G247">
@@ -40674,7 +40674,7 @@
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>2026-09-20 15:30:00</t>
+          <t>2026-09-20 15:15:00</t>
         </is>
       </c>
     </row>
@@ -40686,27 +40686,27 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G248">
@@ -40837,7 +40837,7 @@
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>2026-09-20 15:30:00</t>
+          <t>2026-09-20 15:15:00</t>
         </is>
       </c>
     </row>
@@ -40854,22 +40854,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G249">
@@ -41017,7 +41017,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G250">
@@ -41180,22 +41180,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G251">
@@ -41343,22 +41343,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G252">
@@ -41501,12 +41501,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G253">
@@ -41652,7 +41652,7 @@
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>2026-09-20 15:45:00</t>
+          <t>2026-09-20 15:30:00</t>
         </is>
       </c>
     </row>
@@ -41664,12 +41664,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G254">
@@ -41815,7 +41815,7 @@
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>2026-09-20 15:45:00</t>
+          <t>2026-09-20 15:30:00</t>
         </is>
       </c>
     </row>
@@ -41827,27 +41827,27 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G255">
@@ -41978,7 +41978,7 @@
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>2026-09-20 16:00:00</t>
+          <t>2026-09-20 15:30:00</t>
         </is>
       </c>
     </row>
@@ -41990,27 +41990,27 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G256">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>2026-09-20 16:00:00</t>
+          <t>2026-09-20 15:45:00</t>
         </is>
       </c>
     </row>
@@ -42153,27 +42153,27 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G257">
@@ -42304,7 +42304,7 @@
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>2026-09-20 16:00:00</t>
+          <t>2026-09-20 15:45:00</t>
         </is>
       </c>
     </row>
@@ -42321,7 +42321,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G258">
@@ -42484,22 +42484,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G259">
@@ -42647,7 +42647,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G260">
@@ -42810,22 +42810,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G261">
@@ -42973,22 +42973,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G262">
@@ -43131,12 +43131,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G263">
@@ -43282,7 +43282,7 @@
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>2026-09-20 16:30:00</t>
+          <t>2026-09-20 16:00:00</t>
         </is>
       </c>
     </row>
@@ -43294,12 +43294,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G264">
@@ -43445,7 +43445,7 @@
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>2026-09-20 16:30:00</t>
+          <t>2026-09-20 16:00:00</t>
         </is>
       </c>
     </row>
@@ -43457,12 +43457,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G265">
@@ -43608,7 +43608,7 @@
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>2026-09-20 17:00:00</t>
+          <t>2026-09-20 16:00:00</t>
         </is>
       </c>
     </row>
@@ -43620,7 +43620,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G266">
@@ -43771,7 +43771,7 @@
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>2026-09-20 17:00:00</t>
+          <t>2026-09-20 16:30:00</t>
         </is>
       </c>
     </row>
@@ -43783,27 +43783,27 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G267">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>2026-09-20 17:00:00</t>
+          <t>2026-09-20 16:30:00</t>
         </is>
       </c>
     </row>
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G268">
@@ -44109,27 +44109,27 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G269">
@@ -44260,7 +44260,7 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>2026-09-20 17:30:00</t>
+          <t>2026-09-20 17:00:00</t>
         </is>
       </c>
     </row>
@@ -44272,27 +44272,27 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G270">
@@ -44423,7 +44423,7 @@
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>2026-09-20 17:30:00</t>
+          <t>2026-09-20 17:00:00</t>
         </is>
       </c>
     </row>
@@ -44435,27 +44435,27 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G271">
@@ -44586,7 +44586,7 @@
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>2026-09-20 17:30:00</t>
+          <t>2026-09-20 17:00:00</t>
         </is>
       </c>
     </row>
@@ -44598,27 +44598,27 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O272">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P272">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q272">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R272">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S272">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T272">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U272">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V272">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W272">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X272">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y272">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z272">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AA272">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AB272">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC272">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="AD272">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE272">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF272">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG272">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK272">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44749,7 +44749,7 @@
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>2026-09-20 17:30:00</t>
+          <t>2026-09-20 17:00:00</t>
         </is>
       </c>
     </row>
@@ -44761,27 +44761,27 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G273">
@@ -44912,7 +44912,7 @@
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>2026-09-20 18:00:00</t>
+          <t>2026-09-20 17:30:00</t>
         </is>
       </c>
     </row>
@@ -44924,27 +44924,27 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G274">
@@ -45075,7 +45075,7 @@
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>2026-09-20 18:00:00</t>
+          <t>2026-09-20 17:30:00</t>
         </is>
       </c>
     </row>
@@ -45087,27 +45087,27 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G275">
@@ -45238,7 +45238,7 @@
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>2026-09-20 18:30:00</t>
+          <t>2026-09-20 17:30:00</t>
         </is>
       </c>
     </row>
@@ -45250,27 +45250,27 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G276">
@@ -45401,7 +45401,7 @@
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>2026-09-20 18:30:00</t>
+          <t>2026-09-20 17:30:00</t>
         </is>
       </c>
     </row>
@@ -45413,12 +45413,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G277">
@@ -45564,7 +45564,7 @@
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>2026-09-20 18:30:00</t>
+          <t>2026-09-20 18:00:00</t>
         </is>
       </c>
     </row>
@@ -45576,12 +45576,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G278">
@@ -45727,7 +45727,7 @@
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>2026-09-20 18:30:00</t>
+          <t>2026-09-20 18:00:00</t>
         </is>
       </c>
     </row>
@@ -45739,7 +45739,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G279">
@@ -45890,7 +45890,7 @@
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>2026-09-20 19:30:00</t>
+          <t>2026-09-20 18:30:00</t>
         </is>
       </c>
     </row>
@@ -45902,12 +45902,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G280">
@@ -46053,7 +46053,7 @@
       </c>
       <c r="AU280" t="inlineStr">
         <is>
-          <t>2026-09-20 20:00:00</t>
+          <t>2026-09-20 18:30:00</t>
         </is>
       </c>
     </row>
@@ -46065,12 +46065,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G281">
@@ -46216,7 +46216,7 @@
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>2026-09-20 20:00:00</t>
+          <t>2026-09-20 18:30:00</t>
         </is>
       </c>
     </row>
@@ -46228,12 +46228,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G282">
@@ -46379,7 +46379,7 @@
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>2026-09-20 20:00:00</t>
+          <t>2026-09-20 18:30:00</t>
         </is>
       </c>
     </row>
@@ -46391,156 +46391,808 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="G283">
+        <v>0</v>
+      </c>
+      <c r="H283">
+        <v>0</v>
+      </c>
+      <c r="I283">
+        <v>0</v>
+      </c>
+      <c r="J283">
+        <v>0</v>
+      </c>
+      <c r="K283">
+        <v>0</v>
+      </c>
+      <c r="L283">
+        <v>0</v>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N283">
+        <v>0</v>
+      </c>
+      <c r="O283">
+        <v>0</v>
+      </c>
+      <c r="P283">
+        <v>0</v>
+      </c>
+      <c r="Q283">
+        <v>0</v>
+      </c>
+      <c r="R283">
+        <v>0</v>
+      </c>
+      <c r="S283">
+        <v>0</v>
+      </c>
+      <c r="T283">
+        <v>0</v>
+      </c>
+      <c r="U283">
+        <v>0</v>
+      </c>
+      <c r="V283">
+        <v>0</v>
+      </c>
+      <c r="W283">
+        <v>0</v>
+      </c>
+      <c r="X283">
+        <v>0</v>
+      </c>
+      <c r="Y283">
+        <v>0</v>
+      </c>
+      <c r="Z283">
+        <v>0</v>
+      </c>
+      <c r="AA283">
+        <v>0</v>
+      </c>
+      <c r="AB283">
+        <v>0</v>
+      </c>
+      <c r="AC283">
+        <v>0</v>
+      </c>
+      <c r="AD283">
+        <v>0</v>
+      </c>
+      <c r="AE283">
+        <v>0</v>
+      </c>
+      <c r="AF283">
+        <v>0</v>
+      </c>
+      <c r="AG283">
+        <v>0</v>
+      </c>
+      <c r="AH283" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI283" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ283">
+        <v>0</v>
+      </c>
+      <c r="AK283">
+        <v>0</v>
+      </c>
+      <c r="AL283">
+        <v>0</v>
+      </c>
+      <c r="AM283">
+        <v>-1</v>
+      </c>
+      <c r="AN283">
+        <v>-1</v>
+      </c>
+      <c r="AO283">
+        <v>-1</v>
+      </c>
+      <c r="AP283">
+        <v>-1</v>
+      </c>
+      <c r="AQ283">
+        <v>0</v>
+      </c>
+      <c r="AR283">
+        <v>0</v>
+      </c>
+      <c r="AS283">
+        <v>0</v>
+      </c>
+      <c r="AT283">
+        <v>0</v>
+      </c>
+      <c r="AU283" t="inlineStr">
+        <is>
+          <t>2026-09-20 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="G284">
+        <v>0</v>
+      </c>
+      <c r="H284">
+        <v>0</v>
+      </c>
+      <c r="I284">
+        <v>0</v>
+      </c>
+      <c r="J284">
+        <v>0</v>
+      </c>
+      <c r="K284">
+        <v>0</v>
+      </c>
+      <c r="L284">
+        <v>0</v>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N284">
+        <v>0</v>
+      </c>
+      <c r="O284">
+        <v>0</v>
+      </c>
+      <c r="P284">
+        <v>0</v>
+      </c>
+      <c r="Q284">
+        <v>0</v>
+      </c>
+      <c r="R284">
+        <v>0</v>
+      </c>
+      <c r="S284">
+        <v>0</v>
+      </c>
+      <c r="T284">
+        <v>0</v>
+      </c>
+      <c r="U284">
+        <v>0</v>
+      </c>
+      <c r="V284">
+        <v>0</v>
+      </c>
+      <c r="W284">
+        <v>0</v>
+      </c>
+      <c r="X284">
+        <v>0</v>
+      </c>
+      <c r="Y284">
+        <v>0</v>
+      </c>
+      <c r="Z284">
+        <v>0</v>
+      </c>
+      <c r="AA284">
+        <v>0</v>
+      </c>
+      <c r="AB284">
+        <v>0</v>
+      </c>
+      <c r="AC284">
+        <v>0</v>
+      </c>
+      <c r="AD284">
+        <v>0</v>
+      </c>
+      <c r="AE284">
+        <v>0</v>
+      </c>
+      <c r="AF284">
+        <v>0</v>
+      </c>
+      <c r="AG284">
+        <v>0</v>
+      </c>
+      <c r="AH284" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI284" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ284">
+        <v>0</v>
+      </c>
+      <c r="AK284">
+        <v>0</v>
+      </c>
+      <c r="AL284">
+        <v>0</v>
+      </c>
+      <c r="AM284">
+        <v>-1</v>
+      </c>
+      <c r="AN284">
+        <v>-1</v>
+      </c>
+      <c r="AO284">
+        <v>-1</v>
+      </c>
+      <c r="AP284">
+        <v>-1</v>
+      </c>
+      <c r="AQ284">
+        <v>0</v>
+      </c>
+      <c r="AR284">
+        <v>0</v>
+      </c>
+      <c r="AS284">
+        <v>0</v>
+      </c>
+      <c r="AT284">
+        <v>0</v>
+      </c>
+      <c r="AU284" t="inlineStr">
+        <is>
+          <t>2026-09-20 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Utah Royals</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Angel City</t>
+        </is>
+      </c>
+      <c r="G285">
+        <v>0</v>
+      </c>
+      <c r="H285">
+        <v>0</v>
+      </c>
+      <c r="I285">
+        <v>0</v>
+      </c>
+      <c r="J285">
+        <v>0</v>
+      </c>
+      <c r="K285">
+        <v>0</v>
+      </c>
+      <c r="L285">
+        <v>0</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N285">
+        <v>0</v>
+      </c>
+      <c r="O285">
+        <v>0</v>
+      </c>
+      <c r="P285">
+        <v>0</v>
+      </c>
+      <c r="Q285">
+        <v>0</v>
+      </c>
+      <c r="R285">
+        <v>0</v>
+      </c>
+      <c r="S285">
+        <v>0</v>
+      </c>
+      <c r="T285">
+        <v>0</v>
+      </c>
+      <c r="U285">
+        <v>0</v>
+      </c>
+      <c r="V285">
+        <v>0</v>
+      </c>
+      <c r="W285">
+        <v>0</v>
+      </c>
+      <c r="X285">
+        <v>0</v>
+      </c>
+      <c r="Y285">
+        <v>0</v>
+      </c>
+      <c r="Z285">
+        <v>0</v>
+      </c>
+      <c r="AA285">
+        <v>0</v>
+      </c>
+      <c r="AB285">
+        <v>0</v>
+      </c>
+      <c r="AC285">
+        <v>0</v>
+      </c>
+      <c r="AD285">
+        <v>0</v>
+      </c>
+      <c r="AE285">
+        <v>0</v>
+      </c>
+      <c r="AF285">
+        <v>0</v>
+      </c>
+      <c r="AG285">
+        <v>0</v>
+      </c>
+      <c r="AH285" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI285" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ285">
+        <v>0</v>
+      </c>
+      <c r="AK285">
+        <v>0</v>
+      </c>
+      <c r="AL285">
+        <v>0</v>
+      </c>
+      <c r="AM285">
+        <v>-1</v>
+      </c>
+      <c r="AN285">
+        <v>-1</v>
+      </c>
+      <c r="AO285">
+        <v>-1</v>
+      </c>
+      <c r="AP285">
+        <v>-1</v>
+      </c>
+      <c r="AQ285">
+        <v>0</v>
+      </c>
+      <c r="AR285">
+        <v>0</v>
+      </c>
+      <c r="AS285">
+        <v>0</v>
+      </c>
+      <c r="AT285">
+        <v>0</v>
+      </c>
+      <c r="AU285" t="inlineStr">
+        <is>
+          <t>2026-09-20 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Bay</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Racing Louisville</t>
+        </is>
+      </c>
+      <c r="G286">
+        <v>0</v>
+      </c>
+      <c r="H286">
+        <v>0</v>
+      </c>
+      <c r="I286">
+        <v>0</v>
+      </c>
+      <c r="J286">
+        <v>0</v>
+      </c>
+      <c r="K286">
+        <v>0</v>
+      </c>
+      <c r="L286">
+        <v>0</v>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N286">
+        <v>0</v>
+      </c>
+      <c r="O286">
+        <v>0</v>
+      </c>
+      <c r="P286">
+        <v>0</v>
+      </c>
+      <c r="Q286">
+        <v>0</v>
+      </c>
+      <c r="R286">
+        <v>0</v>
+      </c>
+      <c r="S286">
+        <v>0</v>
+      </c>
+      <c r="T286">
+        <v>0</v>
+      </c>
+      <c r="U286">
+        <v>0</v>
+      </c>
+      <c r="V286">
+        <v>0</v>
+      </c>
+      <c r="W286">
+        <v>0</v>
+      </c>
+      <c r="X286">
+        <v>0</v>
+      </c>
+      <c r="Y286">
+        <v>0</v>
+      </c>
+      <c r="Z286">
+        <v>0</v>
+      </c>
+      <c r="AA286">
+        <v>0</v>
+      </c>
+      <c r="AB286">
+        <v>0</v>
+      </c>
+      <c r="AC286">
+        <v>0</v>
+      </c>
+      <c r="AD286">
+        <v>0</v>
+      </c>
+      <c r="AE286">
+        <v>0</v>
+      </c>
+      <c r="AF286">
+        <v>0</v>
+      </c>
+      <c r="AG286">
+        <v>0</v>
+      </c>
+      <c r="AH286" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI286" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ286">
+        <v>0</v>
+      </c>
+      <c r="AK286">
+        <v>0</v>
+      </c>
+      <c r="AL286">
+        <v>0</v>
+      </c>
+      <c r="AM286">
+        <v>-1</v>
+      </c>
+      <c r="AN286">
+        <v>-1</v>
+      </c>
+      <c r="AO286">
+        <v>-1</v>
+      </c>
+      <c r="AP286">
+        <v>-1</v>
+      </c>
+      <c r="AQ286">
+        <v>0</v>
+      </c>
+      <c r="AR286">
+        <v>0</v>
+      </c>
+      <c r="AS286">
+        <v>0</v>
+      </c>
+      <c r="AT286">
+        <v>0</v>
+      </c>
+      <c r="AU286" t="inlineStr">
+        <is>
+          <t>2026-09-20 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr">
+      <c r="D287" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr">
+      <c r="E287" t="inlineStr">
         <is>
           <t>Inter Miami</t>
         </is>
       </c>
-      <c r="F283" t="inlineStr">
+      <c r="F287" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="G283">
-        <v>0</v>
-      </c>
-      <c r="H283">
-        <v>0</v>
-      </c>
-      <c r="I283">
-        <v>0</v>
-      </c>
-      <c r="J283">
-        <v>0</v>
-      </c>
-      <c r="K283">
-        <v>0</v>
-      </c>
-      <c r="L283">
-        <v>0</v>
-      </c>
-      <c r="M283" t="inlineStr">
+      <c r="G287">
+        <v>0</v>
+      </c>
+      <c r="H287">
+        <v>0</v>
+      </c>
+      <c r="I287">
+        <v>0</v>
+      </c>
+      <c r="J287">
+        <v>0</v>
+      </c>
+      <c r="K287">
+        <v>0</v>
+      </c>
+      <c r="L287">
+        <v>0</v>
+      </c>
+      <c r="M287" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N283">
-        <v>0</v>
-      </c>
-      <c r="O283">
-        <v>0</v>
-      </c>
-      <c r="P283">
-        <v>0</v>
-      </c>
-      <c r="Q283">
-        <v>0</v>
-      </c>
-      <c r="R283">
-        <v>0</v>
-      </c>
-      <c r="S283">
-        <v>0</v>
-      </c>
-      <c r="T283">
-        <v>0</v>
-      </c>
-      <c r="U283">
-        <v>0</v>
-      </c>
-      <c r="V283">
-        <v>0</v>
-      </c>
-      <c r="W283">
-        <v>0</v>
-      </c>
-      <c r="X283">
-        <v>0</v>
-      </c>
-      <c r="Y283">
-        <v>0</v>
-      </c>
-      <c r="Z283">
-        <v>0</v>
-      </c>
-      <c r="AA283">
-        <v>0</v>
-      </c>
-      <c r="AB283">
-        <v>0</v>
-      </c>
-      <c r="AC283">
-        <v>0</v>
-      </c>
-      <c r="AD283">
-        <v>0</v>
-      </c>
-      <c r="AE283">
-        <v>0</v>
-      </c>
-      <c r="AF283">
-        <v>0</v>
-      </c>
-      <c r="AG283">
-        <v>0</v>
-      </c>
-      <c r="AH283" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI283" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ283">
-        <v>0</v>
-      </c>
-      <c r="AK283">
-        <v>0</v>
-      </c>
-      <c r="AL283">
-        <v>0</v>
-      </c>
-      <c r="AM283">
-        <v>-1</v>
-      </c>
-      <c r="AN283">
-        <v>-1</v>
-      </c>
-      <c r="AO283">
-        <v>-1</v>
-      </c>
-      <c r="AP283">
-        <v>-1</v>
-      </c>
-      <c r="AQ283">
-        <v>0</v>
-      </c>
-      <c r="AR283">
-        <v>0</v>
-      </c>
-      <c r="AS283">
-        <v>0</v>
-      </c>
-      <c r="AT283">
-        <v>0</v>
-      </c>
-      <c r="AU283" t="inlineStr">
+      <c r="N287">
+        <v>0</v>
+      </c>
+      <c r="O287">
+        <v>0</v>
+      </c>
+      <c r="P287">
+        <v>0</v>
+      </c>
+      <c r="Q287">
+        <v>0</v>
+      </c>
+      <c r="R287">
+        <v>0</v>
+      </c>
+      <c r="S287">
+        <v>0</v>
+      </c>
+      <c r="T287">
+        <v>0</v>
+      </c>
+      <c r="U287">
+        <v>0</v>
+      </c>
+      <c r="V287">
+        <v>0</v>
+      </c>
+      <c r="W287">
+        <v>0</v>
+      </c>
+      <c r="X287">
+        <v>0</v>
+      </c>
+      <c r="Y287">
+        <v>0</v>
+      </c>
+      <c r="Z287">
+        <v>0</v>
+      </c>
+      <c r="AA287">
+        <v>0</v>
+      </c>
+      <c r="AB287">
+        <v>0</v>
+      </c>
+      <c r="AC287">
+        <v>0</v>
+      </c>
+      <c r="AD287">
+        <v>0</v>
+      </c>
+      <c r="AE287">
+        <v>0</v>
+      </c>
+      <c r="AF287">
+        <v>0</v>
+      </c>
+      <c r="AG287">
+        <v>0</v>
+      </c>
+      <c r="AH287" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI287" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ287">
+        <v>0</v>
+      </c>
+      <c r="AK287">
+        <v>0</v>
+      </c>
+      <c r="AL287">
+        <v>0</v>
+      </c>
+      <c r="AM287">
+        <v>-1</v>
+      </c>
+      <c r="AN287">
+        <v>-1</v>
+      </c>
+      <c r="AO287">
+        <v>-1</v>
+      </c>
+      <c r="AP287">
+        <v>-1</v>
+      </c>
+      <c r="AQ287">
+        <v>0</v>
+      </c>
+      <c r="AR287">
+        <v>0</v>
+      </c>
+      <c r="AS287">
+        <v>0</v>
+      </c>
+      <c r="AT287">
+        <v>0</v>
+      </c>
+      <c r="AU287" t="inlineStr">
         <is>
           <t>2026-09-20 20:00:00</t>
         </is>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G19">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P21">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="Q21">
-        <v>3.3</v>
+        <v>5.22</v>
       </c>
       <c r="R21">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="S21">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="T21">
-        <v>2.99</v>
+        <v>2.57</v>
       </c>
       <c r="U21">
-        <v>2.87</v>
+        <v>3.14</v>
       </c>
       <c r="V21">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z21">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA21">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="AB21">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AC21">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AD21">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE21">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF21">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AG21">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.31</v>
+        <v>1.85</v>
       </c>
       <c r="AK21">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="O22">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>1.86</v>
+        <v>2.55</v>
       </c>
       <c r="Q22">
-        <v>5.22</v>
+        <v>3.3</v>
       </c>
       <c r="R22">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="S22">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T22">
-        <v>2.57</v>
+        <v>2.99</v>
       </c>
       <c r="U22">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="V22">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
+        <v>1.07</v>
+      </c>
+      <c r="X22">
         <v>1.03</v>
       </c>
-      <c r="X22">
-        <v>1.02</v>
-      </c>
       <c r="Y22">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z22">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA22">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AB22">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC22">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="AD22">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE22">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF22">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AG22">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.85</v>
+        <v>1.31</v>
       </c>
       <c r="AK22">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,80 +20847,80 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q126">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R126">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="S126">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="T126">
-        <v>2.61</v>
+        <v>3.12</v>
       </c>
       <c r="U126">
-        <v>2.73</v>
+        <v>2.29</v>
       </c>
       <c r="V126">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W126">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X126">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="Z126">
-        <v>2.97</v>
+        <v>4.55</v>
       </c>
       <c r="AA126">
-        <v>1.98</v>
+        <v>1.56</v>
       </c>
       <c r="AB126">
+        <v>2.22</v>
+      </c>
+      <c r="AC126">
+        <v>2.5</v>
+      </c>
+      <c r="AD126">
+        <v>1.46</v>
+      </c>
+      <c r="AE126">
+        <v>1.15</v>
+      </c>
+      <c r="AF126">
+        <v>1.5</v>
+      </c>
+      <c r="AG126">
+        <v>2.38</v>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ126">
+        <v>1.2</v>
+      </c>
+      <c r="AK126">
         <v>1.71</v>
-      </c>
-      <c r="AC126">
-        <v>3.34</v>
-      </c>
-      <c r="AD126">
-        <v>1.24</v>
-      </c>
-      <c r="AE126">
-        <v>1.05</v>
-      </c>
-      <c r="AF126">
-        <v>1.81</v>
-      </c>
-      <c r="AG126">
-        <v>1.85</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ126">
-        <v>1.22</v>
-      </c>
-      <c r="AK126">
-        <v>1.67</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O127">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P127">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q127">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R127">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="S127">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="T127">
-        <v>3.12</v>
+        <v>2.61</v>
       </c>
       <c r="U127">
-        <v>2.29</v>
+        <v>2.73</v>
       </c>
       <c r="V127">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W127">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X127">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y127">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="Z127">
-        <v>4.55</v>
+        <v>2.97</v>
       </c>
       <c r="AA127">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="AB127">
-        <v>2.22</v>
+        <v>1.71</v>
       </c>
       <c r="AC127">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD127">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="AE127">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AF127">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="AG127">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK127">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G273">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G274">

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="O2">
-        <v>3.15</v>
+        <v>4.21</v>
       </c>
       <c r="P2">
-        <v>3.21</v>
+        <v>7.3</v>
       </c>
       <c r="Q2">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="R2">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T2">
-        <v>2.71</v>
+        <v>3.24</v>
       </c>
       <c r="U2">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="Z2">
-        <v>2.92</v>
+        <v>4.25</v>
       </c>
       <c r="AA2">
-        <v>2.08</v>
+        <v>1.64</v>
       </c>
       <c r="AB2">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="AC2">
-        <v>3.58</v>
+        <v>2.71</v>
       </c>
       <c r="AD2">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AE2">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF2">
         <v>1.84</v>
       </c>
       <c r="AG2">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AK2">
-        <v>1.7</v>
+        <v>2.86</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="O3">
-        <v>4.21</v>
+        <v>3.15</v>
       </c>
       <c r="P3">
-        <v>7.3</v>
+        <v>3.21</v>
       </c>
       <c r="Q3">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="R3">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="S3">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T3">
-        <v>3.24</v>
+        <v>2.71</v>
       </c>
       <c r="U3">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="V3">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="Z3">
-        <v>4.25</v>
+        <v>2.92</v>
       </c>
       <c r="AA3">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="AB3">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="AC3">
-        <v>2.71</v>
+        <v>3.58</v>
       </c>
       <c r="AD3">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AE3">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
         <v>1.84</v>
       </c>
       <c r="AG3">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AK3">
-        <v>2.86</v>
+        <v>1.7</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="O56">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P56">
-        <v>3.3</v>
+        <v>2.09</v>
       </c>
       <c r="Q56">
-        <v>2.54</v>
+        <v>3.13</v>
       </c>
       <c r="R56">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S56">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T56">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U56">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="V56">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="W56">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X56">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z56">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA56">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB56">
-        <v>2.29</v>
+        <v>2.87</v>
       </c>
       <c r="AC56">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AD56">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AE56">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AF56">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AG56">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK56">
-        <v>1.72</v>
+        <v>1.32</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
       <c r="O57">
         <v>3.7</v>
       </c>
       <c r="P57">
-        <v>2.09</v>
+        <v>3.6</v>
       </c>
       <c r="Q57">
-        <v>3.13</v>
+        <v>2.27</v>
       </c>
       <c r="R57">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="S57">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="T57">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="U57">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V57">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="W57">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z57">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA57">
         <v>1.4</v>
       </c>
       <c r="AB57">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AC57">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AD57">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AE57">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AF57">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AG57">
-        <v>2.81</v>
+        <v>2.58</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>1.32</v>
+        <v>1.99</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,80 +9763,80 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="O58">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P58">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q58">
-        <v>2.27</v>
+        <v>2.54</v>
       </c>
       <c r="R58">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S58">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T58">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="U58">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="V58">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="W58">
         <v>1.14</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z58">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA58">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AB58">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="AC58">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="AD58">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AE58">
+        <v>1.18</v>
+      </c>
+      <c r="AF58">
+        <v>1.45</v>
+      </c>
+      <c r="AG58">
+        <v>2.55</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
         <v>1.25</v>
       </c>
-      <c r="AF58">
-        <v>1.43</v>
-      </c>
-      <c r="AG58">
-        <v>2.58</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>1.22</v>
-      </c>
       <c r="AK58">
-        <v>1.99</v>
+        <v>1.72</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O106">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P106">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q106">
-        <v>3.42</v>
+        <v>1.88</v>
       </c>
       <c r="R106">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="S106">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="T106">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="U106">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="V106">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="W106">
+        <v>1.05</v>
+      </c>
+      <c r="X106">
+        <v>1.03</v>
+      </c>
+      <c r="Y106">
+        <v>1.19</v>
+      </c>
+      <c r="Z106">
+        <v>3.75</v>
+      </c>
+      <c r="AA106">
+        <v>1.75</v>
+      </c>
+      <c r="AB106">
+        <v>1.99</v>
+      </c>
+      <c r="AC106">
+        <v>2.81</v>
+      </c>
+      <c r="AD106">
+        <v>1.33</v>
+      </c>
+      <c r="AE106">
         <v>1.09</v>
       </c>
-      <c r="X106">
-        <v>1.01</v>
-      </c>
-      <c r="Y106">
-        <v>1.16</v>
-      </c>
-      <c r="Z106">
-        <v>4.1</v>
-      </c>
-      <c r="AA106">
-        <v>1.67</v>
-      </c>
-      <c r="AB106">
-        <v>2.07</v>
-      </c>
-      <c r="AC106">
-        <v>2.62</v>
-      </c>
-      <c r="AD106">
-        <v>1.38</v>
-      </c>
-      <c r="AE106">
-        <v>1.11</v>
-      </c>
       <c r="AF106">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="AG106">
-        <v>2.26</v>
+        <v>1.7</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AK106">
-        <v>1.38</v>
+        <v>2.82</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q107">
-        <v>1.88</v>
+        <v>3.42</v>
       </c>
       <c r="R107">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="S107">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="T107">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="U107">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="V107">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="W107">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X107">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z107">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AA107">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB107">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="AC107">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AD107">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE107">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF107">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="AG107">
-        <v>1.7</v>
+        <v>2.26</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AK107">
-        <v>2.82</v>
+        <v>1.38</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O126">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P126">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q126">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R126">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="S126">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="T126">
-        <v>3.12</v>
+        <v>2.61</v>
       </c>
       <c r="U126">
-        <v>2.29</v>
+        <v>2.73</v>
       </c>
       <c r="V126">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W126">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X126">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y126">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="Z126">
-        <v>4.55</v>
+        <v>2.97</v>
       </c>
       <c r="AA126">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="AB126">
-        <v>2.22</v>
+        <v>1.71</v>
       </c>
       <c r="AC126">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD126">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="AE126">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AF126">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="AG126">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK126">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,80 +21010,80 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q127">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R127">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="S127">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="T127">
-        <v>2.61</v>
+        <v>3.12</v>
       </c>
       <c r="U127">
-        <v>2.73</v>
+        <v>2.29</v>
       </c>
       <c r="V127">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W127">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X127">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="Z127">
-        <v>2.97</v>
+        <v>4.55</v>
       </c>
       <c r="AA127">
-        <v>1.98</v>
+        <v>1.56</v>
       </c>
       <c r="AB127">
+        <v>2.22</v>
+      </c>
+      <c r="AC127">
+        <v>2.5</v>
+      </c>
+      <c r="AD127">
+        <v>1.46</v>
+      </c>
+      <c r="AE127">
+        <v>1.15</v>
+      </c>
+      <c r="AF127">
+        <v>1.5</v>
+      </c>
+      <c r="AG127">
+        <v>2.38</v>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ127">
+        <v>1.2</v>
+      </c>
+      <c r="AK127">
         <v>1.71</v>
-      </c>
-      <c r="AC127">
-        <v>3.34</v>
-      </c>
-      <c r="AD127">
-        <v>1.24</v>
-      </c>
-      <c r="AE127">
-        <v>1.05</v>
-      </c>
-      <c r="AF127">
-        <v>1.81</v>
-      </c>
-      <c r="AG127">
-        <v>1.85</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ127">
-        <v>1.22</v>
-      </c>
-      <c r="AK127">
-        <v>1.67</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,64 +33724,64 @@
         </is>
       </c>
       <c r="N205">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="O205">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P205">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q205">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R205">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S205">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="T205">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="U205">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V205">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W205">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X205">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y205">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z205">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AA205">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB205">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC205">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD205">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE205">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF205">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG205">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK205">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O206">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P206">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q206">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R206">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S206">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T206">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U206">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V206">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W206">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X206">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y206">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z206">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA206">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB206">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC206">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD206">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE206">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF206">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG206">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK206">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G277">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G278">

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,80 +9600,80 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="O57">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P57">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q57">
-        <v>2.27</v>
+        <v>2.54</v>
       </c>
       <c r="R57">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S57">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T57">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="U57">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="V57">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="W57">
         <v>1.14</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z57">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA57">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AB57">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="AC57">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="AD57">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AE57">
+        <v>1.18</v>
+      </c>
+      <c r="AF57">
+        <v>1.45</v>
+      </c>
+      <c r="AG57">
+        <v>2.55</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
         <v>1.25</v>
       </c>
-      <c r="AF57">
-        <v>1.43</v>
-      </c>
-      <c r="AG57">
-        <v>2.58</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ57">
-        <v>1.22</v>
-      </c>
       <c r="AK57">
-        <v>1.99</v>
+        <v>1.72</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="O58">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P58">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q58">
-        <v>2.54</v>
+        <v>2.27</v>
       </c>
       <c r="R58">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S58">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T58">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="U58">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="V58">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="W58">
         <v>1.14</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z58">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA58">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB58">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="AC58">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="AD58">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AE58">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF58">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AG58">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK58">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G100">
@@ -16618,55 +16618,55 @@
         <v>0</v>
       </c>
       <c r="Q100">
-        <v>9.449999999999999</v>
+        <v>4.81</v>
       </c>
       <c r="R100">
-        <v>2.39</v>
+        <v>1.91</v>
       </c>
       <c r="S100">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="T100">
-        <v>2.76</v>
+        <v>2.38</v>
       </c>
       <c r="U100">
-        <v>2.57</v>
+        <v>3.3</v>
       </c>
       <c r="V100">
+        <v>1.25</v>
+      </c>
+      <c r="W100">
+        <v>1.04</v>
+      </c>
+      <c r="X100">
+        <v>1.03</v>
+      </c>
+      <c r="Y100">
         <v>1.4</v>
       </c>
-      <c r="W100">
-        <v>1.05</v>
-      </c>
-      <c r="X100">
-        <v>1.02</v>
-      </c>
-      <c r="Y100">
-        <v>1.21</v>
-      </c>
       <c r="Z100">
-        <v>3.58</v>
+        <v>2.56</v>
       </c>
       <c r="AA100">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="AB100">
-        <v>1.9</v>
+        <v>1.52</v>
       </c>
       <c r="AC100">
-        <v>2.92</v>
+        <v>4.45</v>
       </c>
       <c r="AD100">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AE100">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF100">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="AG100">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="AK100">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G101">
@@ -16781,55 +16781,55 @@
         <v>0</v>
       </c>
       <c r="Q101">
-        <v>4.81</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="R101">
-        <v>1.91</v>
+        <v>2.39</v>
       </c>
       <c r="S101">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="T101">
-        <v>2.38</v>
+        <v>2.76</v>
       </c>
       <c r="U101">
-        <v>3.3</v>
+        <v>2.57</v>
       </c>
       <c r="V101">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="W101">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X101">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="Z101">
-        <v>2.56</v>
+        <v>3.58</v>
       </c>
       <c r="AA101">
-        <v>2.31</v>
+        <v>1.77</v>
       </c>
       <c r="AB101">
-        <v>1.52</v>
+        <v>1.9</v>
       </c>
       <c r="AC101">
-        <v>4.45</v>
+        <v>2.92</v>
       </c>
       <c r="AD101">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AE101">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF101">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="AG101">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="AK101">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q122">
         <v>3.74</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q124">
         <v>7.55</v>
@@ -21834,55 +21834,55 @@
         <v>0</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>7.33</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S132">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T132">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U132">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V132">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W132">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X132">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y132">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z132">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="AA132">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD132">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE132">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG132">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK132">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="O159">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P159">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q159">
         <v>7.41</v>
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O193">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q193">
         <v>2.85</v>
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="O212">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P212">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q212">
         <v>7.5</v>
@@ -35680,13 +35680,13 @@
         </is>
       </c>
       <c r="N217">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O217">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P217">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q217">
         <v>2.54</v>
@@ -38777,64 +38777,64 @@
         </is>
       </c>
       <c r="N236">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O236">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P236">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q236">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R236">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S236">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T236">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U236">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V236">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W236">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X236">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y236">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z236">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA236">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB236">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC236">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD236">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE236">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF236">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG236">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK236">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -39103,64 +39103,64 @@
         </is>
       </c>
       <c r="N238">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O238">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P238">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q238">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R238">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S238">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T238">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U238">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V238">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W238">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X238">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y238">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z238">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA238">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB238">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC238">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD238">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE238">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF238">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG238">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK238">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -40407,64 +40407,64 @@
         </is>
       </c>
       <c r="N246">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O246">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P246">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q246">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="R246">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S246">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T246">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U246">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V246">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W246">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X246">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y246">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z246">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA246">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB246">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC246">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD246">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE246">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF246">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG246">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -40477,10 +40477,10 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK246">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -43341,64 +43341,64 @@
         </is>
       </c>
       <c r="N264">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O264">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P264">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q264">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R264">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S264">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T264">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U264">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V264">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W264">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X264">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y264">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z264">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA264">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB264">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC264">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD264">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE264">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF264">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG264">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43411,10 +43411,10 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK264">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -43667,64 +43667,64 @@
         </is>
       </c>
       <c r="N266">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O266">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P266">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q266">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R266">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S266">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T266">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U266">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V266">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W266">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X266">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y266">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z266">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA266">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB266">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC266">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD266">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE266">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF266">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG266">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -43737,10 +43737,10 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK266">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -44156,64 +44156,64 @@
         </is>
       </c>
       <c r="N269">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O269">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P269">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q269">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R269">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S269">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T269">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="U269">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V269">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W269">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X269">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y269">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z269">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA269">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB269">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC269">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AD269">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE269">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF269">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG269">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK269">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -46601,64 +46601,64 @@
         </is>
       </c>
       <c r="N284">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O284">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P284">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q284">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R284">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S284">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T284">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U284">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V284">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W284">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X284">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y284">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z284">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AA284">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB284">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC284">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD284">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE284">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF284">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG284">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK284">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL284">
         <v>0</v>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU289"/>
+  <dimension ref="A1:AU292"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.31</v>
+        <v>1.83</v>
       </c>
       <c r="O96">
-        <v>5.75</v>
+        <v>3.75</v>
       </c>
       <c r="P96">
-        <v>9.4</v>
+        <v>4</v>
       </c>
       <c r="Q96">
-        <v>1.71</v>
+        <v>2.4</v>
       </c>
       <c r="R96">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="S96">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="T96">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="U96">
-        <v>2.38</v>
+        <v>2.59</v>
       </c>
       <c r="V96">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W96">
+        <v>1.08</v>
+      </c>
+      <c r="X96">
+        <v>1.01</v>
+      </c>
+      <c r="Y96">
+        <v>1.21</v>
+      </c>
+      <c r="Z96">
+        <v>3.84</v>
+      </c>
+      <c r="AA96">
+        <v>1.83</v>
+      </c>
+      <c r="AB96">
+        <v>2.07</v>
+      </c>
+      <c r="AC96">
+        <v>2.66</v>
+      </c>
+      <c r="AD96">
+        <v>1.38</v>
+      </c>
+      <c r="AE96">
         <v>1.11</v>
       </c>
-      <c r="X96">
-        <v>1.02</v>
-      </c>
-      <c r="Y96">
-        <v>1.12</v>
-      </c>
-      <c r="Z96">
-        <v>4.65</v>
-      </c>
-      <c r="AA96">
-        <v>1.53</v>
-      </c>
-      <c r="AB96">
-        <v>2.37</v>
-      </c>
-      <c r="AC96">
-        <v>2.52</v>
-      </c>
-      <c r="AD96">
-        <v>1.56</v>
-      </c>
-      <c r="AE96">
-        <v>1.18</v>
-      </c>
       <c r="AF96">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AG96">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK96">
-        <v>3.72</v>
+        <v>2.06</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.83</v>
+        <v>1.31</v>
       </c>
       <c r="O97">
-        <v>3.75</v>
+        <v>5.75</v>
       </c>
       <c r="P97">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="Q97">
-        <v>2.4</v>
+        <v>1.71</v>
       </c>
       <c r="R97">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="S97">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="T97">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="U97">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="V97">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W97">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X97">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="Z97">
-        <v>3.84</v>
+        <v>4.65</v>
       </c>
       <c r="AA97">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AB97">
-        <v>2.07</v>
+        <v>2.37</v>
       </c>
       <c r="AC97">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="AD97">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AE97">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF97">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AG97">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK97">
-        <v>2.06</v>
+        <v>3.72</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="O195">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="P195">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R195">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S195">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T195">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U195">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V195">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W195">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X195">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y195">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z195">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AC195">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD195">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE195">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF195">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AG195">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK195">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="O196">
-        <v>3.7</v>
+        <v>4.13</v>
       </c>
       <c r="P196">
-        <v>2.38</v>
+        <v>2.71</v>
       </c>
       <c r="Q196">
-        <v>2.96</v>
+        <v>2.56</v>
       </c>
       <c r="R196">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="S196">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T196">
-        <v>4</v>
+        <v>5.15</v>
       </c>
       <c r="U196">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="V196">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="W196">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="X196">
         <v>1.01</v>
       </c>
       <c r="Y196">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z196">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
       <c r="AA196">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AB196">
-        <v>2.92</v>
+        <v>3.34</v>
       </c>
       <c r="AC196">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="AD196">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AE196">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AF196">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AG196">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK196">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="O197">
-        <v>4.13</v>
+        <v>3.9</v>
       </c>
       <c r="P197">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="Q197">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R197">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S197">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T197">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U197">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V197">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W197">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X197">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y197">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z197">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AA197">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB197">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC197">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD197">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE197">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF197">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AG197">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AK197">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.19</v>
+        <v>3.15</v>
       </c>
       <c r="O198">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="P198">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="Q198">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="R198">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="S198">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="T198">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="U198">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V198">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="W198">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X198">
         <v>1.01</v>
       </c>
       <c r="Y198">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z198">
-        <v>6.65</v>
+        <v>6.8</v>
       </c>
       <c r="AA198">
+        <v>1.29</v>
+      </c>
+      <c r="AB198">
+        <v>3.04</v>
+      </c>
+      <c r="AC198">
+        <v>1.84</v>
+      </c>
+      <c r="AD198">
+        <v>1.91</v>
+      </c>
+      <c r="AE198">
         <v>1.4</v>
       </c>
-      <c r="AB198">
-        <v>2.97</v>
-      </c>
-      <c r="AC198">
-        <v>1.88</v>
-      </c>
-      <c r="AD198">
-        <v>1.86</v>
-      </c>
-      <c r="AE198">
-        <v>1.32</v>
-      </c>
       <c r="AF198">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AG198">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="AK198">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O209">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P209">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="Q209">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="R209">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="S209">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="T209">
-        <v>2.39</v>
+        <v>3.4</v>
       </c>
       <c r="U209">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="V209">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="W209">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="X209">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y209">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="Z209">
-        <v>2.92</v>
+        <v>4.65</v>
       </c>
       <c r="AA209">
-        <v>2.1</v>
+        <v>1.56</v>
       </c>
       <c r="AB209">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="AC209">
-        <v>3.9</v>
+        <v>2.37</v>
       </c>
       <c r="AD209">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="AE209">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF209">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG209">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK209">
-        <v>1.74</v>
+        <v>3.02</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,65 +34539,65 @@
         </is>
       </c>
       <c r="N210">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O210">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P210">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Q210">
+        <v>2.5</v>
+      </c>
+      <c r="R210">
+        <v>2.05</v>
+      </c>
+      <c r="S210">
+        <v>1.4</v>
+      </c>
+      <c r="T210">
+        <v>2.39</v>
+      </c>
+      <c r="U210">
+        <v>2.95</v>
+      </c>
+      <c r="V210">
+        <v>1.33</v>
+      </c>
+      <c r="W210">
+        <v>1.04</v>
+      </c>
+      <c r="X210">
+        <v>1.04</v>
+      </c>
+      <c r="Y210">
+        <v>1.31</v>
+      </c>
+      <c r="Z210">
+        <v>2.92</v>
+      </c>
+      <c r="AA210">
+        <v>2.1</v>
+      </c>
+      <c r="AB210">
+        <v>1.76</v>
+      </c>
+      <c r="AC210">
+        <v>3.9</v>
+      </c>
+      <c r="AD210">
+        <v>1.25</v>
+      </c>
+      <c r="AE210">
+        <v>1.06</v>
+      </c>
+      <c r="AF210">
+        <v>1.81</v>
+      </c>
+      <c r="AG210">
         <v>1.8</v>
       </c>
-      <c r="R210">
-        <v>2.56</v>
-      </c>
-      <c r="S210">
-        <v>1.22</v>
-      </c>
-      <c r="T210">
-        <v>3.4</v>
-      </c>
-      <c r="U210">
-        <v>2.25</v>
-      </c>
-      <c r="V210">
-        <v>1.63</v>
-      </c>
-      <c r="W210">
-        <v>1.15</v>
-      </c>
-      <c r="X210">
-        <v>1.03</v>
-      </c>
-      <c r="Y210">
-        <v>1.15</v>
-      </c>
-      <c r="Z210">
-        <v>4.65</v>
-      </c>
-      <c r="AA210">
-        <v>1.56</v>
-      </c>
-      <c r="AB210">
-        <v>2.33</v>
-      </c>
-      <c r="AC210">
-        <v>2.37</v>
-      </c>
-      <c r="AD210">
-        <v>1.51</v>
-      </c>
-      <c r="AE210">
-        <v>1.18</v>
-      </c>
-      <c r="AF210">
-        <v>1.85</v>
-      </c>
-      <c r="AG210">
-        <v>1.85</v>
-      </c>
       <c r="AH210" t="inlineStr">
         <is>
           <t>[]</t>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK210">
-        <v>3.02</v>
+        <v>1.74</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -41832,22 +41832,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G255">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G256">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G257">
@@ -42316,12 +42316,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G258">
@@ -42363,64 +42363,64 @@
         </is>
       </c>
       <c r="N258">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O258">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="P258">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q258">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R258">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S258">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T258">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U258">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="V258">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="W258">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X258">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y258">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z258">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AA258">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB258">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC258">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD258">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE258">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF258">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG258">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH258" t="inlineStr">
         <is>
@@ -42433,10 +42433,10 @@
         </is>
       </c>
       <c r="AJ258">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK258">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AL258">
         <v>0</v>
@@ -42467,7 +42467,7 @@
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>2026-09-20 15:45:00</t>
+          <t>2026-09-20 15:30:00</t>
         </is>
       </c>
     </row>
@@ -42484,7 +42484,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G259">
@@ -42526,80 +42526,80 @@
         </is>
       </c>
       <c r="N259">
+        <v>6</v>
+      </c>
+      <c r="O259">
+        <v>4.9</v>
+      </c>
+      <c r="P259">
+        <v>1.43</v>
+      </c>
+      <c r="Q259">
+        <v>5.75</v>
+      </c>
+      <c r="R259">
+        <v>2.66</v>
+      </c>
+      <c r="S259">
+        <v>1.2</v>
+      </c>
+      <c r="T259">
+        <v>4.2</v>
+      </c>
+      <c r="U259">
+        <v>2.04</v>
+      </c>
+      <c r="V259">
+        <v>1.78</v>
+      </c>
+      <c r="W259">
         <v>1.19</v>
-      </c>
-      <c r="O259">
-        <v>5.7</v>
-      </c>
-      <c r="P259">
-        <v>11</v>
-      </c>
-      <c r="Q259">
-        <v>1.7</v>
-      </c>
-      <c r="R259">
-        <v>2.43</v>
-      </c>
-      <c r="S259">
-        <v>1.31</v>
-      </c>
-      <c r="T259">
-        <v>3.26</v>
-      </c>
-      <c r="U259">
-        <v>2.43</v>
-      </c>
-      <c r="V259">
-        <v>1.52</v>
-      </c>
-      <c r="W259">
-        <v>1.1</v>
       </c>
       <c r="X259">
         <v>1.01</v>
       </c>
       <c r="Y259">
+        <v>1.06</v>
+      </c>
+      <c r="Z259">
+        <v>6.35</v>
+      </c>
+      <c r="AA259">
+        <v>1.36</v>
+      </c>
+      <c r="AB259">
+        <v>3.2</v>
+      </c>
+      <c r="AC259">
+        <v>1.87</v>
+      </c>
+      <c r="AD259">
+        <v>1.92</v>
+      </c>
+      <c r="AE259">
+        <v>1.32</v>
+      </c>
+      <c r="AF259">
+        <v>1.5</v>
+      </c>
+      <c r="AG259">
+        <v>2.45</v>
+      </c>
+      <c r="AH259" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI259" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ259">
         <v>1.18</v>
       </c>
-      <c r="Z259">
-        <v>4.2</v>
-      </c>
-      <c r="AA259">
-        <v>1.72</v>
-      </c>
-      <c r="AB259">
-        <v>2.31</v>
-      </c>
-      <c r="AC259">
-        <v>2.5</v>
-      </c>
-      <c r="AD259">
-        <v>1.46</v>
-      </c>
-      <c r="AE259">
-        <v>1.15</v>
-      </c>
-      <c r="AF259">
-        <v>2.16</v>
-      </c>
-      <c r="AG259">
-        <v>1.62</v>
-      </c>
-      <c r="AH259" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI259" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ259">
-        <v>1.04</v>
-      </c>
       <c r="AK259">
-        <v>3.92</v>
+        <v>1.13</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -42642,27 +42642,27 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,64 +42689,64 @@
         </is>
       </c>
       <c r="N260">
-        <v>2.11</v>
+        <v>1.19</v>
       </c>
       <c r="O260">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="P260">
-        <v>3.6</v>
+        <v>11</v>
       </c>
       <c r="Q260">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="R260">
-        <v>1.93</v>
+        <v>2.43</v>
       </c>
       <c r="S260">
+        <v>1.31</v>
+      </c>
+      <c r="T260">
+        <v>3.26</v>
+      </c>
+      <c r="U260">
+        <v>2.43</v>
+      </c>
+      <c r="V260">
         <v>1.52</v>
       </c>
-      <c r="T260">
-        <v>2.52</v>
-      </c>
-      <c r="U260">
-        <v>3.32</v>
-      </c>
-      <c r="V260">
-        <v>1.3</v>
-      </c>
       <c r="W260">
+        <v>1.1</v>
+      </c>
+      <c r="X260">
         <v>1.01</v>
       </c>
-      <c r="X260">
-        <v>1.06</v>
-      </c>
       <c r="Y260">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="Z260">
-        <v>2.49</v>
+        <v>4.2</v>
       </c>
       <c r="AA260">
+        <v>1.72</v>
+      </c>
+      <c r="AB260">
         <v>2.31</v>
       </c>
-      <c r="AB260">
-        <v>1.53</v>
-      </c>
       <c r="AC260">
-        <v>4.76</v>
+        <v>2.5</v>
       </c>
       <c r="AD260">
-        <v>1.14</v>
+        <v>1.46</v>
       </c>
       <c r="AE260">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AF260">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="AG260">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AK260">
-        <v>1.62</v>
+        <v>3.92</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42793,7 +42793,7 @@
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>2026-09-20 16:00:00</t>
+          <t>2026-09-20 15:45:00</t>
         </is>
       </c>
     </row>
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G261">
@@ -42852,80 +42852,80 @@
         </is>
       </c>
       <c r="N261">
-        <v>2.85</v>
+        <v>2.11</v>
       </c>
       <c r="O261">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P261">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="Q261">
-        <v>3.52</v>
+        <v>2.8</v>
       </c>
       <c r="R261">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S261">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="T261">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="U261">
-        <v>2.8</v>
+        <v>3.32</v>
       </c>
       <c r="V261">
+        <v>1.3</v>
+      </c>
+      <c r="W261">
+        <v>1.01</v>
+      </c>
+      <c r="X261">
+        <v>1.06</v>
+      </c>
+      <c r="Y261">
+        <v>1.42</v>
+      </c>
+      <c r="Z261">
+        <v>2.49</v>
+      </c>
+      <c r="AA261">
+        <v>2.31</v>
+      </c>
+      <c r="AB261">
+        <v>1.53</v>
+      </c>
+      <c r="AC261">
+        <v>4.76</v>
+      </c>
+      <c r="AD261">
+        <v>1.14</v>
+      </c>
+      <c r="AE261">
+        <v>1.03</v>
+      </c>
+      <c r="AF261">
+        <v>2.03</v>
+      </c>
+      <c r="AG261">
+        <v>1.67</v>
+      </c>
+      <c r="AH261" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI261" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ261">
         <v>1.36</v>
       </c>
-      <c r="W261">
-        <v>1.08</v>
-      </c>
-      <c r="X261">
-        <v>1.04</v>
-      </c>
-      <c r="Y261">
-        <v>1.28</v>
-      </c>
-      <c r="Z261">
-        <v>3.08</v>
-      </c>
-      <c r="AA261">
-        <v>2.06</v>
-      </c>
-      <c r="AB261">
-        <v>1.79</v>
-      </c>
-      <c r="AC261">
-        <v>3.42</v>
-      </c>
-      <c r="AD261">
-        <v>1.23</v>
-      </c>
-      <c r="AE261">
-        <v>1.04</v>
-      </c>
-      <c r="AF261">
-        <v>1.76</v>
-      </c>
-      <c r="AG261">
-        <v>1.96</v>
-      </c>
-      <c r="AH261" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI261" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ261">
-        <v>1.28</v>
-      </c>
       <c r="AK261">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -42973,7 +42973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G262">
@@ -43015,64 +43015,64 @@
         </is>
       </c>
       <c r="N262">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O262">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P262">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q262">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R262">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S262">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T262">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U262">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V262">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W262">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X262">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y262">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z262">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA262">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB262">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC262">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD262">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE262">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF262">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG262">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH262" t="inlineStr">
         <is>
@@ -43085,10 +43085,10 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK262">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -43136,7 +43136,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G263">
@@ -43299,22 +43299,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G264">
@@ -43341,64 +43341,64 @@
         </is>
       </c>
       <c r="N264">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O264">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P264">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q264">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R264">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S264">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T264">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U264">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="V264">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W264">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X264">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y264">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z264">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA264">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AB264">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC264">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD264">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE264">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF264">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG264">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43411,10 +43411,10 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK264">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -43462,22 +43462,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G265">
@@ -43504,64 +43504,64 @@
         </is>
       </c>
       <c r="N265">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O265">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P265">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q265">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R265">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S265">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T265">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U265">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V265">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W265">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X265">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y265">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z265">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA265">
-        <v>1.53</v>
+        <v>2.27</v>
       </c>
       <c r="AB265">
-        <v>2.37</v>
+        <v>1.66</v>
       </c>
       <c r="AC265">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD265">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE265">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF265">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG265">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH265" t="inlineStr">
         <is>
@@ -43574,10 +43574,10 @@
         </is>
       </c>
       <c r="AJ265">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK265">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43625,22 +43625,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G266">
@@ -43667,64 +43667,64 @@
         </is>
       </c>
       <c r="N266">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O266">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P266">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q266">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R266">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S266">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T266">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U266">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V266">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W266">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X266">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y266">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z266">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA266">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="AB266">
-        <v>1.9</v>
+        <v>2.37</v>
       </c>
       <c r="AC266">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD266">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE266">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF266">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG266">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -43737,10 +43737,10 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK266">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -43788,22 +43788,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G267">
@@ -43830,64 +43830,64 @@
         </is>
       </c>
       <c r="N267">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O267">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P267">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q267">
-        <v>2.54</v>
+        <v>3.2</v>
       </c>
       <c r="R267">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="S267">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T267">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="U267">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="V267">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="W267">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X267">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y267">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="Z267">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="AA267">
-        <v>2.33</v>
+        <v>1.92</v>
       </c>
       <c r="AB267">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AC267">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="AD267">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AE267">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AF267">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AG267">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AH267" t="inlineStr">
         <is>
@@ -43900,10 +43900,10 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK267">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -43946,12 +43946,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G268">
@@ -44002,55 +44002,55 @@
         <v>0</v>
       </c>
       <c r="Q268">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R268">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S268">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T268">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U268">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V268">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W268">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X268">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y268">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z268">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA268">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB268">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC268">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD268">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE268">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF268">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG268">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH268" t="inlineStr">
         <is>
@@ -44063,10 +44063,10 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK268">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL268">
         <v>0</v>
@@ -44097,7 +44097,7 @@
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>2026-09-20 16:30:00</t>
+          <t>2026-09-20 16:00:00</t>
         </is>
       </c>
     </row>
@@ -44114,22 +44114,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G269">
@@ -44156,64 +44156,64 @@
         </is>
       </c>
       <c r="N269">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O269">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P269">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q269">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R269">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S269">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T269">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="U269">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V269">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W269">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X269">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y269">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z269">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA269">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB269">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC269">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="AD269">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE269">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF269">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG269">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK269">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44272,27 +44272,27 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G270">
@@ -44319,64 +44319,64 @@
         </is>
       </c>
       <c r="N270">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O270">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P270">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q270">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R270">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S270">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T270">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="U270">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V270">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W270">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X270">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y270">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z270">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA270">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB270">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC270">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AD270">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE270">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF270">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG270">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK270">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -44423,7 +44423,7 @@
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>2026-09-20 17:00:00</t>
+          <t>2026-09-20 16:30:00</t>
         </is>
       </c>
     </row>
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G271">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O272">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P272">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q272">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R272">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S272">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T272">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U272">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V272">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W272">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X272">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y272">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z272">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AA272">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AB272">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC272">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="AD272">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE272">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF272">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG272">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK272">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,64 +44808,64 @@
         </is>
       </c>
       <c r="N273">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O273">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P273">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q273">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R273">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S273">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T273">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U273">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V273">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W273">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X273">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y273">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z273">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AA273">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AB273">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC273">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="AD273">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE273">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF273">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG273">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK273">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G274">
@@ -45087,27 +45087,27 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G275">
@@ -45238,7 +45238,7 @@
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>2026-09-20 17:30:00</t>
+          <t>2026-09-20 17:00:00</t>
         </is>
       </c>
     </row>
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G276">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G277">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G278">
@@ -45739,27 +45739,27 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G279">
@@ -45890,7 +45890,7 @@
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>2026-09-20 18:00:00</t>
+          <t>2026-09-20 17:30:00</t>
         </is>
       </c>
     </row>
@@ -45907,7 +45907,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,64 +45949,64 @@
         </is>
       </c>
       <c r="N280">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O280">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P280">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q280">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R280">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S280">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T280">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U280">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V280">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W280">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X280">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y280">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z280">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA280">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB280">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC280">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD280">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE280">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF280">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG280">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK280">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -46065,12 +46065,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G281">
@@ -46216,7 +46216,7 @@
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>2026-09-20 18:30:00</t>
+          <t>2026-09-20 18:00:00</t>
         </is>
       </c>
     </row>
@@ -46228,12 +46228,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G282">
@@ -46284,55 +46284,55 @@
         <v>0</v>
       </c>
       <c r="Q282">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="R282">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S282">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T282">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U282">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V282">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W282">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X282">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y282">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z282">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA282">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB282">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC282">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD282">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE282">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF282">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG282">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH282" t="inlineStr">
         <is>
@@ -46345,10 +46345,10 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK282">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -46379,7 +46379,7 @@
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>2026-09-20 18:30:00</t>
+          <t>2026-09-20 18:00:00</t>
         </is>
       </c>
     </row>
@@ -46396,7 +46396,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,64 +46438,64 @@
         </is>
       </c>
       <c r="N283">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O283">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P283">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q283">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R283">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S283">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T283">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U283">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V283">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W283">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X283">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y283">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z283">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA283">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB283">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC283">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD283">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE283">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF283">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG283">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK283">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46559,7 +46559,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G284">
@@ -46601,64 +46601,64 @@
         </is>
       </c>
       <c r="N284">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O284">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P284">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q284">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R284">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S284">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T284">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U284">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="V284">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W284">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X284">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y284">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z284">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AA284">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB284">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC284">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD284">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE284">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF284">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG284">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK284">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46717,12 +46717,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G285">
@@ -46868,7 +46868,7 @@
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>2026-09-20 19:30:00</t>
+          <t>2026-09-20 18:30:00</t>
         </is>
       </c>
     </row>
@@ -46880,12 +46880,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,64 +46927,64 @@
         </is>
       </c>
       <c r="N286">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O286">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P286">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q286">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R286">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S286">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T286">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U286">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V286">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W286">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X286">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y286">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z286">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AA286">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB286">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC286">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD286">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE286">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF286">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG286">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK286">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47031,7 +47031,7 @@
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>2026-09-20 20:00:00</t>
+          <t>2026-09-20 18:30:00</t>
         </is>
       </c>
     </row>
@@ -47043,12 +47043,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,64 +47090,64 @@
         </is>
       </c>
       <c r="N287">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O287">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P287">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q287">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R287">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S287">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T287">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="U287">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V287">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W287">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X287">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y287">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z287">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA287">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB287">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC287">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD287">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE287">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF287">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG287">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK287">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47194,7 +47194,7 @@
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>2026-09-20 20:00:00</t>
+          <t>2026-09-20 19:30:00</t>
         </is>
       </c>
     </row>
@@ -47211,7 +47211,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,64 +47253,64 @@
         </is>
       </c>
       <c r="N288">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O288">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P288">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q288">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R288">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S288">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T288">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U288">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V288">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W288">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X288">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y288">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z288">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AA288">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB288">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC288">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD288">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE288">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF288">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG288">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK288">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47374,153 +47374,642 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Utah Royals</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Angel City</t>
+        </is>
+      </c>
+      <c r="G289">
+        <v>0</v>
+      </c>
+      <c r="H289">
+        <v>0</v>
+      </c>
+      <c r="I289">
+        <v>0</v>
+      </c>
+      <c r="J289">
+        <v>0</v>
+      </c>
+      <c r="K289">
+        <v>0</v>
+      </c>
+      <c r="L289">
+        <v>0</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N289">
+        <v>0</v>
+      </c>
+      <c r="O289">
+        <v>0</v>
+      </c>
+      <c r="P289">
+        <v>0</v>
+      </c>
+      <c r="Q289">
+        <v>0</v>
+      </c>
+      <c r="R289">
+        <v>0</v>
+      </c>
+      <c r="S289">
+        <v>0</v>
+      </c>
+      <c r="T289">
+        <v>0</v>
+      </c>
+      <c r="U289">
+        <v>0</v>
+      </c>
+      <c r="V289">
+        <v>0</v>
+      </c>
+      <c r="W289">
+        <v>0</v>
+      </c>
+      <c r="X289">
+        <v>0</v>
+      </c>
+      <c r="Y289">
+        <v>0</v>
+      </c>
+      <c r="Z289">
+        <v>0</v>
+      </c>
+      <c r="AA289">
+        <v>0</v>
+      </c>
+      <c r="AB289">
+        <v>0</v>
+      </c>
+      <c r="AC289">
+        <v>0</v>
+      </c>
+      <c r="AD289">
+        <v>0</v>
+      </c>
+      <c r="AE289">
+        <v>0</v>
+      </c>
+      <c r="AF289">
+        <v>0</v>
+      </c>
+      <c r="AG289">
+        <v>0</v>
+      </c>
+      <c r="AH289" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI289" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ289">
+        <v>0</v>
+      </c>
+      <c r="AK289">
+        <v>0</v>
+      </c>
+      <c r="AL289">
+        <v>0</v>
+      </c>
+      <c r="AM289">
+        <v>-1</v>
+      </c>
+      <c r="AN289">
+        <v>-1</v>
+      </c>
+      <c r="AO289">
+        <v>-1</v>
+      </c>
+      <c r="AP289">
+        <v>-1</v>
+      </c>
+      <c r="AQ289">
+        <v>0</v>
+      </c>
+      <c r="AR289">
+        <v>0</v>
+      </c>
+      <c r="AS289">
+        <v>0</v>
+      </c>
+      <c r="AT289">
+        <v>0</v>
+      </c>
+      <c r="AU289" t="inlineStr">
+        <is>
+          <t>2026-09-20 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Bay</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Racing Louisville</t>
+        </is>
+      </c>
+      <c r="G290">
+        <v>0</v>
+      </c>
+      <c r="H290">
+        <v>0</v>
+      </c>
+      <c r="I290">
+        <v>0</v>
+      </c>
+      <c r="J290">
+        <v>0</v>
+      </c>
+      <c r="K290">
+        <v>0</v>
+      </c>
+      <c r="L290">
+        <v>0</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N290">
+        <v>0</v>
+      </c>
+      <c r="O290">
+        <v>0</v>
+      </c>
+      <c r="P290">
+        <v>0</v>
+      </c>
+      <c r="Q290">
+        <v>0</v>
+      </c>
+      <c r="R290">
+        <v>0</v>
+      </c>
+      <c r="S290">
+        <v>0</v>
+      </c>
+      <c r="T290">
+        <v>0</v>
+      </c>
+      <c r="U290">
+        <v>0</v>
+      </c>
+      <c r="V290">
+        <v>0</v>
+      </c>
+      <c r="W290">
+        <v>0</v>
+      </c>
+      <c r="X290">
+        <v>0</v>
+      </c>
+      <c r="Y290">
+        <v>0</v>
+      </c>
+      <c r="Z290">
+        <v>0</v>
+      </c>
+      <c r="AA290">
+        <v>0</v>
+      </c>
+      <c r="AB290">
+        <v>0</v>
+      </c>
+      <c r="AC290">
+        <v>0</v>
+      </c>
+      <c r="AD290">
+        <v>0</v>
+      </c>
+      <c r="AE290">
+        <v>0</v>
+      </c>
+      <c r="AF290">
+        <v>0</v>
+      </c>
+      <c r="AG290">
+        <v>0</v>
+      </c>
+      <c r="AH290" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI290" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ290">
+        <v>0</v>
+      </c>
+      <c r="AK290">
+        <v>0</v>
+      </c>
+      <c r="AL290">
+        <v>0</v>
+      </c>
+      <c r="AM290">
+        <v>-1</v>
+      </c>
+      <c r="AN290">
+        <v>-1</v>
+      </c>
+      <c r="AO290">
+        <v>-1</v>
+      </c>
+      <c r="AP290">
+        <v>-1</v>
+      </c>
+      <c r="AQ290">
+        <v>0</v>
+      </c>
+      <c r="AR290">
+        <v>0</v>
+      </c>
+      <c r="AS290">
+        <v>0</v>
+      </c>
+      <c r="AT290">
+        <v>0</v>
+      </c>
+      <c r="AU290" t="inlineStr">
+        <is>
+          <t>2026-09-20 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr">
+      <c r="D291" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr">
+      <c r="E291" t="inlineStr">
         <is>
           <t>Inter Miami</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr">
+      <c r="F291" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="G289">
-        <v>0</v>
-      </c>
-      <c r="H289">
-        <v>0</v>
-      </c>
-      <c r="I289">
-        <v>0</v>
-      </c>
-      <c r="J289">
-        <v>0</v>
-      </c>
-      <c r="K289">
-        <v>0</v>
-      </c>
-      <c r="L289">
-        <v>0</v>
-      </c>
-      <c r="M289" t="inlineStr">
+      <c r="G291">
+        <v>0</v>
+      </c>
+      <c r="H291">
+        <v>0</v>
+      </c>
+      <c r="I291">
+        <v>0</v>
+      </c>
+      <c r="J291">
+        <v>0</v>
+      </c>
+      <c r="K291">
+        <v>0</v>
+      </c>
+      <c r="L291">
+        <v>0</v>
+      </c>
+      <c r="M291" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N289">
-        <v>0</v>
-      </c>
-      <c r="O289">
-        <v>0</v>
-      </c>
-      <c r="P289">
-        <v>0</v>
-      </c>
-      <c r="Q289">
-        <v>0</v>
-      </c>
-      <c r="R289">
-        <v>0</v>
-      </c>
-      <c r="S289">
-        <v>0</v>
-      </c>
-      <c r="T289">
-        <v>0</v>
-      </c>
-      <c r="U289">
-        <v>0</v>
-      </c>
-      <c r="V289">
-        <v>0</v>
-      </c>
-      <c r="W289">
-        <v>0</v>
-      </c>
-      <c r="X289">
-        <v>0</v>
-      </c>
-      <c r="Y289">
-        <v>0</v>
-      </c>
-      <c r="Z289">
-        <v>0</v>
-      </c>
-      <c r="AA289">
-        <v>0</v>
-      </c>
-      <c r="AB289">
-        <v>0</v>
-      </c>
-      <c r="AC289">
-        <v>0</v>
-      </c>
-      <c r="AD289">
-        <v>0</v>
-      </c>
-      <c r="AE289">
-        <v>0</v>
-      </c>
-      <c r="AF289">
-        <v>0</v>
-      </c>
-      <c r="AG289">
-        <v>0</v>
-      </c>
-      <c r="AH289" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI289" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ289">
-        <v>0</v>
-      </c>
-      <c r="AK289">
-        <v>0</v>
-      </c>
-      <c r="AL289">
-        <v>0</v>
-      </c>
-      <c r="AM289">
-        <v>-1</v>
-      </c>
-      <c r="AN289">
-        <v>-1</v>
-      </c>
-      <c r="AO289">
-        <v>-1</v>
-      </c>
-      <c r="AP289">
-        <v>-1</v>
-      </c>
-      <c r="AQ289">
-        <v>0</v>
-      </c>
-      <c r="AR289">
-        <v>0</v>
-      </c>
-      <c r="AS289">
-        <v>0</v>
-      </c>
-      <c r="AT289">
-        <v>0</v>
-      </c>
-      <c r="AU289" t="inlineStr">
+      <c r="N291">
+        <v>0</v>
+      </c>
+      <c r="O291">
+        <v>0</v>
+      </c>
+      <c r="P291">
+        <v>0</v>
+      </c>
+      <c r="Q291">
+        <v>0</v>
+      </c>
+      <c r="R291">
+        <v>0</v>
+      </c>
+      <c r="S291">
+        <v>0</v>
+      </c>
+      <c r="T291">
+        <v>0</v>
+      </c>
+      <c r="U291">
+        <v>0</v>
+      </c>
+      <c r="V291">
+        <v>0</v>
+      </c>
+      <c r="W291">
+        <v>0</v>
+      </c>
+      <c r="X291">
+        <v>0</v>
+      </c>
+      <c r="Y291">
+        <v>0</v>
+      </c>
+      <c r="Z291">
+        <v>0</v>
+      </c>
+      <c r="AA291">
+        <v>0</v>
+      </c>
+      <c r="AB291">
+        <v>0</v>
+      </c>
+      <c r="AC291">
+        <v>0</v>
+      </c>
+      <c r="AD291">
+        <v>0</v>
+      </c>
+      <c r="AE291">
+        <v>0</v>
+      </c>
+      <c r="AF291">
+        <v>0</v>
+      </c>
+      <c r="AG291">
+        <v>0</v>
+      </c>
+      <c r="AH291" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI291" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ291">
+        <v>0</v>
+      </c>
+      <c r="AK291">
+        <v>0</v>
+      </c>
+      <c r="AL291">
+        <v>0</v>
+      </c>
+      <c r="AM291">
+        <v>-1</v>
+      </c>
+      <c r="AN291">
+        <v>-1</v>
+      </c>
+      <c r="AO291">
+        <v>-1</v>
+      </c>
+      <c r="AP291">
+        <v>-1</v>
+      </c>
+      <c r="AQ291">
+        <v>0</v>
+      </c>
+      <c r="AR291">
+        <v>0</v>
+      </c>
+      <c r="AS291">
+        <v>0</v>
+      </c>
+      <c r="AT291">
+        <v>0</v>
+      </c>
+      <c r="AU291" t="inlineStr">
         <is>
           <t>2026-09-20 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>LDU Quito</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>CD Universidad Católica</t>
+        </is>
+      </c>
+      <c r="G292">
+        <v>0</v>
+      </c>
+      <c r="H292">
+        <v>0</v>
+      </c>
+      <c r="I292">
+        <v>0</v>
+      </c>
+      <c r="J292">
+        <v>0</v>
+      </c>
+      <c r="K292">
+        <v>0</v>
+      </c>
+      <c r="L292">
+        <v>0</v>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N292">
+        <v>0</v>
+      </c>
+      <c r="O292">
+        <v>0</v>
+      </c>
+      <c r="P292">
+        <v>0</v>
+      </c>
+      <c r="Q292">
+        <v>0</v>
+      </c>
+      <c r="R292">
+        <v>0</v>
+      </c>
+      <c r="S292">
+        <v>0</v>
+      </c>
+      <c r="T292">
+        <v>0</v>
+      </c>
+      <c r="U292">
+        <v>0</v>
+      </c>
+      <c r="V292">
+        <v>0</v>
+      </c>
+      <c r="W292">
+        <v>0</v>
+      </c>
+      <c r="X292">
+        <v>0</v>
+      </c>
+      <c r="Y292">
+        <v>0</v>
+      </c>
+      <c r="Z292">
+        <v>0</v>
+      </c>
+      <c r="AA292">
+        <v>0</v>
+      </c>
+      <c r="AB292">
+        <v>0</v>
+      </c>
+      <c r="AC292">
+        <v>0</v>
+      </c>
+      <c r="AD292">
+        <v>0</v>
+      </c>
+      <c r="AE292">
+        <v>0</v>
+      </c>
+      <c r="AF292">
+        <v>0</v>
+      </c>
+      <c r="AG292">
+        <v>0</v>
+      </c>
+      <c r="AH292" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI292" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ292">
+        <v>0</v>
+      </c>
+      <c r="AK292">
+        <v>0</v>
+      </c>
+      <c r="AL292">
+        <v>0</v>
+      </c>
+      <c r="AM292">
+        <v>-1</v>
+      </c>
+      <c r="AN292">
+        <v>-1</v>
+      </c>
+      <c r="AO292">
+        <v>-1</v>
+      </c>
+      <c r="AP292">
+        <v>-1</v>
+      </c>
+      <c r="AQ292">
+        <v>0</v>
+      </c>
+      <c r="AR292">
+        <v>0</v>
+      </c>
+      <c r="AS292">
+        <v>0</v>
+      </c>
+      <c r="AT292">
+        <v>0</v>
+      </c>
+      <c r="AU292" t="inlineStr">
+        <is>
+          <t>2026-09-20 20:30:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="O2">
-        <v>4.21</v>
+        <v>3.15</v>
       </c>
       <c r="P2">
-        <v>7.3</v>
+        <v>3.21</v>
       </c>
       <c r="Q2">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="R2">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="S2">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
-        <v>3.24</v>
+        <v>2.71</v>
       </c>
       <c r="U2">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="V2">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="Z2">
-        <v>4.25</v>
+        <v>2.92</v>
       </c>
       <c r="AA2">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="AB2">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="AC2">
-        <v>2.71</v>
+        <v>3.58</v>
       </c>
       <c r="AD2">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AE2">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
         <v>1.84</v>
       </c>
       <c r="AG2">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AK2">
-        <v>2.86</v>
+        <v>1.7</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="O3">
-        <v>3.15</v>
+        <v>4.21</v>
       </c>
       <c r="P3">
-        <v>3.21</v>
+        <v>7.3</v>
       </c>
       <c r="Q3">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="R3">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="S3">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T3">
-        <v>2.71</v>
+        <v>3.24</v>
       </c>
       <c r="U3">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="Z3">
-        <v>2.92</v>
+        <v>4.25</v>
       </c>
       <c r="AA3">
-        <v>2.08</v>
+        <v>1.64</v>
       </c>
       <c r="AB3">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="AC3">
-        <v>3.58</v>
+        <v>2.71</v>
       </c>
       <c r="AD3">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AE3">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF3">
         <v>1.84</v>
       </c>
       <c r="AG3">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AK3">
-        <v>1.7</v>
+        <v>2.86</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G230">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G231">

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G26">
@@ -4556,55 +4556,55 @@
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G27">
@@ -4719,55 +4719,55 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="O57">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P57">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q57">
-        <v>2.54</v>
+        <v>2.27</v>
       </c>
       <c r="R57">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S57">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T57">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="U57">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="V57">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="W57">
         <v>1.14</v>
       </c>
       <c r="X57">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z57">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA57">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB57">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="AC57">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="AD57">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AE57">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF57">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AG57">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,80 +9763,80 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="O58">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P58">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q58">
-        <v>2.27</v>
+        <v>2.54</v>
       </c>
       <c r="R58">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S58">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T58">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="U58">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="V58">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="W58">
         <v>1.14</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z58">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA58">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AB58">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="AC58">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="AD58">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AE58">
+        <v>1.18</v>
+      </c>
+      <c r="AF58">
+        <v>1.45</v>
+      </c>
+      <c r="AG58">
+        <v>2.55</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
         <v>1.25</v>
       </c>
-      <c r="AF58">
-        <v>1.43</v>
-      </c>
-      <c r="AG58">
-        <v>2.58</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>1.22</v>
-      </c>
       <c r="AK58">
-        <v>1.99</v>
+        <v>1.72</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -11559,10 +11559,10 @@
         <v>2.19</v>
       </c>
       <c r="O69">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P69">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="Q69">
         <v>2.73</v>
@@ -11571,16 +11571,16 @@
         <v>2.5</v>
       </c>
       <c r="S69">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T69">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U69">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V69">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W69">
         <v>1.11</v>
@@ -11589,22 +11589,22 @@
         <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z69">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="AA69">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB69">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AC69">
         <v>2.17</v>
       </c>
       <c r="AD69">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AE69">
         <v>1.21</v>
@@ -11613,7 +11613,7 @@
         <v>1.41</v>
       </c>
       <c r="AG69">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>1.25</v>
       </c>
       <c r="AK69">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="O74">
         <v>3.85</v>
       </c>
       <c r="P74">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="Q74">
         <v>5.42</v>
@@ -12386,19 +12386,19 @@
         <v>2.1</v>
       </c>
       <c r="S74">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T74">
-        <v>2.61</v>
+        <v>2.84</v>
       </c>
       <c r="U74">
         <v>2.89</v>
       </c>
       <c r="V74">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W74">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X74">
         <v>1</v>
@@ -12425,7 +12425,7 @@
         <v>1.04</v>
       </c>
       <c r="AF74">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AG74">
         <v>1.65</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.32</v>
+        <v>2.03</v>
       </c>
       <c r="O83">
         <v>3.15</v>
       </c>
       <c r="P83">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="Q83">
         <v>2.87</v>
@@ -13856,16 +13856,16 @@
         <v>1.44</v>
       </c>
       <c r="T83">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="U83">
         <v>3.2</v>
       </c>
       <c r="V83">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W83">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X83">
         <v>1.04</v>
@@ -13880,7 +13880,7 @@
         <v>2.25</v>
       </c>
       <c r="AB83">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC83">
         <v>3.9</v>
@@ -13911,7 +13911,7 @@
         <v>1.27</v>
       </c>
       <c r="AK83">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.83</v>
+        <v>1.31</v>
       </c>
       <c r="O96">
-        <v>3.75</v>
+        <v>5.75</v>
       </c>
       <c r="P96">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="Q96">
-        <v>2.4</v>
+        <v>1.71</v>
       </c>
       <c r="R96">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="S96">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="T96">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="U96">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="V96">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W96">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X96">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="Z96">
-        <v>3.84</v>
+        <v>4.65</v>
       </c>
       <c r="AA96">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AB96">
-        <v>2.07</v>
+        <v>2.37</v>
       </c>
       <c r="AC96">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="AD96">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AE96">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF96">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AG96">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK96">
-        <v>2.06</v>
+        <v>3.72</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.31</v>
+        <v>1.83</v>
       </c>
       <c r="O97">
-        <v>5.75</v>
+        <v>3.75</v>
       </c>
       <c r="P97">
-        <v>9.4</v>
+        <v>4</v>
       </c>
       <c r="Q97">
-        <v>1.71</v>
+        <v>2.4</v>
       </c>
       <c r="R97">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="S97">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="T97">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="U97">
-        <v>2.38</v>
+        <v>2.59</v>
       </c>
       <c r="V97">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W97">
+        <v>1.08</v>
+      </c>
+      <c r="X97">
+        <v>1.01</v>
+      </c>
+      <c r="Y97">
+        <v>1.21</v>
+      </c>
+      <c r="Z97">
+        <v>3.84</v>
+      </c>
+      <c r="AA97">
+        <v>1.83</v>
+      </c>
+      <c r="AB97">
+        <v>2.07</v>
+      </c>
+      <c r="AC97">
+        <v>2.66</v>
+      </c>
+      <c r="AD97">
+        <v>1.38</v>
+      </c>
+      <c r="AE97">
         <v>1.11</v>
       </c>
-      <c r="X97">
-        <v>1.02</v>
-      </c>
-      <c r="Y97">
-        <v>1.12</v>
-      </c>
-      <c r="Z97">
-        <v>4.65</v>
-      </c>
-      <c r="AA97">
-        <v>1.53</v>
-      </c>
-      <c r="AB97">
-        <v>2.37</v>
-      </c>
-      <c r="AC97">
-        <v>2.52</v>
-      </c>
-      <c r="AD97">
-        <v>1.56</v>
-      </c>
-      <c r="AE97">
-        <v>1.18</v>
-      </c>
       <c r="AF97">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AG97">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK97">
-        <v>3.72</v>
+        <v>2.06</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -18402,16 +18402,16 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O111">
         <v>3.25</v>
       </c>
       <c r="P111">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="Q111">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="R111">
         <v>2</v>
@@ -18420,7 +18420,7 @@
         <v>1.37</v>
       </c>
       <c r="T111">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="U111">
         <v>2.77</v>
@@ -18441,7 +18441,7 @@
         <v>2.92</v>
       </c>
       <c r="AA111">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AB111">
         <v>1.72</v>
@@ -18459,7 +18459,7 @@
         <v>1.78</v>
       </c>
       <c r="AG111">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>1.26</v>
       </c>
       <c r="AK111">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18737,40 +18737,40 @@
         <v>0</v>
       </c>
       <c r="Q113">
-        <v>5.52</v>
+        <v>5</v>
       </c>
       <c r="R113">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="S113">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T113">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="U113">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="V113">
         <v>1.47</v>
       </c>
       <c r="W113">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X113">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y113">
         <v>1.18</v>
       </c>
       <c r="Z113">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="AA113">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB113">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AC113">
         <v>2.74</v>
@@ -20527,10 +20527,10 @@
         <v>4.2</v>
       </c>
       <c r="P124">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Q124">
-        <v>7.55</v>
+        <v>7.07</v>
       </c>
       <c r="R124">
         <v>2.16</v>
@@ -20539,13 +20539,13 @@
         <v>1.34</v>
       </c>
       <c r="T124">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="U124">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V124">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W124">
         <v>1.06</v>
@@ -20566,10 +20566,10 @@
         <v>1.95</v>
       </c>
       <c r="AC124">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AD124">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE124">
         <v>1.09</v>
@@ -20578,7 +20578,7 @@
         <v>1.95</v>
       </c>
       <c r="AG124">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -24146,10 +24146,10 @@
         <v>0</v>
       </c>
       <c r="AA146">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB146">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC146">
         <v>0</v>
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="O153">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P153">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25287,10 +25287,10 @@
         <v>0</v>
       </c>
       <c r="AA153">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB153">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC153">
         <v>0</v>
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O154">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P154">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25450,10 +25450,10 @@
         <v>0</v>
       </c>
       <c r="AA154">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB154">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC154">
         <v>0</v>
@@ -26235,7 +26235,7 @@
         <v>1.32</v>
       </c>
       <c r="Q159">
-        <v>7.41</v>
+        <v>7</v>
       </c>
       <c r="R159">
         <v>2.4</v>
@@ -26247,7 +26247,7 @@
         <v>3.08</v>
       </c>
       <c r="U159">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V159">
         <v>1.46</v>
@@ -26265,16 +26265,16 @@
         <v>3.78</v>
       </c>
       <c r="AA159">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB159">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AC159">
         <v>2.66</v>
       </c>
       <c r="AD159">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE159">
         <v>1.12</v>
@@ -26296,7 +26296,7 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.16</v>
+        <v>3</v>
       </c>
       <c r="AK159">
         <v>1.05</v>
@@ -26389,10 +26389,10 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="O160">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="P160">
         <v>5.25</v>
@@ -26404,13 +26404,13 @@
         <v>1.72</v>
       </c>
       <c r="S160">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="T160">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="U160">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="V160">
         <v>1.2</v>
@@ -26434,10 +26434,10 @@
         <v>1.3</v>
       </c>
       <c r="AC160">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="AD160">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AE160">
         <v>1.02</v>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AK160">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O164">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q164">
         <v>0</v>
@@ -27080,10 +27080,10 @@
         <v>0</v>
       </c>
       <c r="AA164">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB164">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC164">
         <v>0</v>
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O167">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27569,10 +27569,10 @@
         <v>0</v>
       </c>
       <c r="AA167">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB167">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC167">
         <v>0</v>
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O168">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27732,10 +27732,10 @@
         <v>0</v>
       </c>
       <c r="AA168">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB168">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC168">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,31 +27856,31 @@
         </is>
       </c>
       <c r="N169">
+        <v>1.37</v>
+      </c>
+      <c r="O169">
+        <v>5.2</v>
+      </c>
+      <c r="P169">
+        <v>5.8</v>
+      </c>
+      <c r="Q169">
         <v>1.75</v>
       </c>
-      <c r="O169">
-        <v>4.3</v>
-      </c>
-      <c r="P169">
-        <v>3.6</v>
-      </c>
-      <c r="Q169">
-        <v>2.15</v>
-      </c>
       <c r="R169">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="S169">
         <v>1.13</v>
       </c>
       <c r="T169">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="U169">
         <v>1.67</v>
       </c>
       <c r="V169">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="W169">
         <v>1.3</v>
@@ -27892,28 +27892,28 @@
         <v>1.02</v>
       </c>
       <c r="Z169">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA169">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AB169">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AC169">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AD169">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AE169">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AF169">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AG169">
-        <v>3.48</v>
+        <v>2.9</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK169">
-        <v>2</v>
+        <v>2.74</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,58 +28019,58 @@
         </is>
       </c>
       <c r="N170">
+        <v>1.68</v>
+      </c>
+      <c r="O170">
+        <v>4.2</v>
+      </c>
+      <c r="P170">
+        <v>3.85</v>
+      </c>
+      <c r="Q170">
+        <v>2.17</v>
+      </c>
+      <c r="R170">
+        <v>2.52</v>
+      </c>
+      <c r="S170">
+        <v>1.17</v>
+      </c>
+      <c r="T170">
+        <v>4.45</v>
+      </c>
+      <c r="U170">
+        <v>1.89</v>
+      </c>
+      <c r="V170">
+        <v>1.83</v>
+      </c>
+      <c r="W170">
+        <v>1.22</v>
+      </c>
+      <c r="X170">
+        <v>1.01</v>
+      </c>
+      <c r="Y170">
+        <v>1.06</v>
+      </c>
+      <c r="Z170">
+        <v>6.25</v>
+      </c>
+      <c r="AA170">
+        <v>1.33</v>
+      </c>
+      <c r="AB170">
+        <v>2.92</v>
+      </c>
+      <c r="AC170">
+        <v>1.88</v>
+      </c>
+      <c r="AD170">
+        <v>1.85</v>
+      </c>
+      <c r="AE170">
         <v>1.37</v>
-      </c>
-      <c r="O170">
-        <v>5.2</v>
-      </c>
-      <c r="P170">
-        <v>5.8</v>
-      </c>
-      <c r="Q170">
-        <v>1.75</v>
-      </c>
-      <c r="R170">
-        <v>2.86</v>
-      </c>
-      <c r="S170">
-        <v>1.13</v>
-      </c>
-      <c r="T170">
-        <v>5.45</v>
-      </c>
-      <c r="U170">
-        <v>1.67</v>
-      </c>
-      <c r="V170">
-        <v>2.03</v>
-      </c>
-      <c r="W170">
-        <v>1.3</v>
-      </c>
-      <c r="X170">
-        <v>1</v>
-      </c>
-      <c r="Y170">
-        <v>1.02</v>
-      </c>
-      <c r="Z170">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA170">
-        <v>1.24</v>
-      </c>
-      <c r="AB170">
-        <v>3.7</v>
-      </c>
-      <c r="AC170">
-        <v>1.62</v>
-      </c>
-      <c r="AD170">
-        <v>2.19</v>
-      </c>
-      <c r="AE170">
-        <v>1.49</v>
       </c>
       <c r="AF170">
         <v>1.36</v>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK170">
-        <v>2.74</v>
+        <v>2</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,77 +28182,77 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="O171">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="P171">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="Q171">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="R171">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="S171">
+        <v>1.13</v>
+      </c>
+      <c r="T171">
+        <v>5.4</v>
+      </c>
+      <c r="U171">
+        <v>1.67</v>
+      </c>
+      <c r="V171">
+        <v>2.06</v>
+      </c>
+      <c r="W171">
+        <v>1.3</v>
+      </c>
+      <c r="X171">
+        <v>1</v>
+      </c>
+      <c r="Y171">
+        <v>1.02</v>
+      </c>
+      <c r="Z171">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA171">
+        <v>1.25</v>
+      </c>
+      <c r="AB171">
+        <v>4</v>
+      </c>
+      <c r="AC171">
+        <v>1.61</v>
+      </c>
+      <c r="AD171">
+        <v>2.21</v>
+      </c>
+      <c r="AE171">
+        <v>1.5</v>
+      </c>
+      <c r="AF171">
+        <v>1.26</v>
+      </c>
+      <c r="AG171">
+        <v>3.48</v>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ171">
         <v>1.17</v>
-      </c>
-      <c r="T171">
-        <v>4.45</v>
-      </c>
-      <c r="U171">
-        <v>1.89</v>
-      </c>
-      <c r="V171">
-        <v>1.83</v>
-      </c>
-      <c r="W171">
-        <v>1.22</v>
-      </c>
-      <c r="X171">
-        <v>1.01</v>
-      </c>
-      <c r="Y171">
-        <v>1.06</v>
-      </c>
-      <c r="Z171">
-        <v>6.25</v>
-      </c>
-      <c r="AA171">
-        <v>1.33</v>
-      </c>
-      <c r="AB171">
-        <v>2.92</v>
-      </c>
-      <c r="AC171">
-        <v>1.88</v>
-      </c>
-      <c r="AD171">
-        <v>1.85</v>
-      </c>
-      <c r="AE171">
-        <v>1.37</v>
-      </c>
-      <c r="AF171">
-        <v>1.36</v>
-      </c>
-      <c r="AG171">
-        <v>2.9</v>
-      </c>
-      <c r="AH171" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI171" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ171">
-        <v>1.2</v>
       </c>
       <c r="AK171">
         <v>2</v>
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O183">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P183">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30473,55 +30473,55 @@
         <v>0</v>
       </c>
       <c r="Q185">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R185">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S185">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T185">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U185">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V185">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W185">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y185">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z185">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA185">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB185">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC185">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD185">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE185">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF185">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG185">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK185">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -31481,10 +31481,10 @@
         <v>0</v>
       </c>
       <c r="AA191">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB191">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC191">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.19</v>
+        <v>3.15</v>
       </c>
       <c r="O197">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="P197">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="Q197">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="R197">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="S197">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="T197">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="U197">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V197">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="W197">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X197">
         <v>1.01</v>
       </c>
       <c r="Y197">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z197">
-        <v>6.65</v>
+        <v>6.8</v>
       </c>
       <c r="AA197">
+        <v>1.29</v>
+      </c>
+      <c r="AB197">
+        <v>3.04</v>
+      </c>
+      <c r="AC197">
+        <v>1.84</v>
+      </c>
+      <c r="AD197">
+        <v>1.91</v>
+      </c>
+      <c r="AE197">
         <v>1.4</v>
       </c>
-      <c r="AB197">
-        <v>2.97</v>
-      </c>
-      <c r="AC197">
-        <v>1.88</v>
-      </c>
-      <c r="AD197">
-        <v>1.86</v>
-      </c>
-      <c r="AE197">
-        <v>1.32</v>
-      </c>
       <c r="AF197">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AG197">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="AK197">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>3.15</v>
+        <v>2.19</v>
       </c>
       <c r="O198">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="P198">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="Q198">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="R198">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="S198">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="T198">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="U198">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="V198">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="W198">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X198">
         <v>1.01</v>
       </c>
       <c r="Y198">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z198">
-        <v>6.8</v>
+        <v>6.65</v>
       </c>
       <c r="AA198">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AB198">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AC198">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AD198">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AE198">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AF198">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AG198">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AK198">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32948,10 +32948,10 @@
         <v>0</v>
       </c>
       <c r="AA200">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB200">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC200">
         <v>0</v>
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O204">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P204">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -33600,10 +33600,10 @@
         <v>0</v>
       </c>
       <c r="AA204">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB204">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC204">
         <v>0</v>
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O211">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P211">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -34741,10 +34741,10 @@
         <v>0</v>
       </c>
       <c r="AA211">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB211">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC211">
         <v>0</v>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O221">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P221">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36371,10 +36371,10 @@
         <v>0</v>
       </c>
       <c r="AA221">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB221">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC221">
         <v>0</v>
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O222">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P222">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -36534,10 +36534,10 @@
         <v>0</v>
       </c>
       <c r="AA222">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB222">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC222">
         <v>0</v>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G27">
@@ -4719,71 +4719,71 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="R27">
         <v>1.98</v>
       </c>
       <c r="S27">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T27">
-        <v>2.42</v>
+        <v>2.51</v>
       </c>
       <c r="U27">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="V27">
+        <v>1.3</v>
+      </c>
+      <c r="W27">
+        <v>1.04</v>
+      </c>
+      <c r="X27">
+        <v>1.03</v>
+      </c>
+      <c r="Y27">
+        <v>1.32</v>
+      </c>
+      <c r="Z27">
+        <v>2.88</v>
+      </c>
+      <c r="AA27">
+        <v>2.08</v>
+      </c>
+      <c r="AB27">
+        <v>1.64</v>
+      </c>
+      <c r="AC27">
+        <v>3.74</v>
+      </c>
+      <c r="AD27">
+        <v>1.19</v>
+      </c>
+      <c r="AE27">
+        <v>1.04</v>
+      </c>
+      <c r="AF27">
+        <v>1.84</v>
+      </c>
+      <c r="AG27">
+        <v>1.85</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.26</v>
       </c>
-      <c r="W27">
-        <v>1.03</v>
-      </c>
-      <c r="X27">
-        <v>1.05</v>
-      </c>
-      <c r="Y27">
-        <v>1.39</v>
-      </c>
-      <c r="Z27">
-        <v>2.59</v>
-      </c>
-      <c r="AA27">
-        <v>2.27</v>
-      </c>
-      <c r="AB27">
-        <v>1.54</v>
-      </c>
-      <c r="AC27">
-        <v>4.2</v>
-      </c>
-      <c r="AD27">
-        <v>1.16</v>
-      </c>
-      <c r="AE27">
-        <v>1.02</v>
-      </c>
-      <c r="AF27">
-        <v>2.03</v>
-      </c>
-      <c r="AG27">
-        <v>1.67</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.25</v>
-      </c>
       <c r="AK27">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G28">
@@ -4882,55 +4882,55 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="R28">
         <v>1.98</v>
       </c>
       <c r="S28">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T28">
-        <v>2.51</v>
+        <v>2.42</v>
       </c>
       <c r="U28">
-        <v>2.99</v>
+        <v>3.24</v>
       </c>
       <c r="V28">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W28">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Z28">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AA28">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="AB28">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="AC28">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AD28">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AE28">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF28">
-        <v>1.84</v>
+        <v>2.03</v>
       </c>
       <c r="AG28">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -10910,7 +10910,7 @@
         <v>3.1</v>
       </c>
       <c r="P65">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="Q65">
         <v>2.8</v>
@@ -10925,7 +10925,7 @@
         <v>2.4</v>
       </c>
       <c r="U65">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="V65">
         <v>1.25</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK65">
         <v>1.65</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,80 +15794,80 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.31</v>
+        <v>2.9</v>
       </c>
       <c r="O95">
-        <v>5.75</v>
+        <v>3.75</v>
       </c>
       <c r="P95">
-        <v>8.5</v>
+        <v>2.16</v>
       </c>
       <c r="Q95">
+        <v>3.3</v>
+      </c>
+      <c r="R95">
+        <v>2.4</v>
+      </c>
+      <c r="S95">
+        <v>1.23</v>
+      </c>
+      <c r="T95">
+        <v>4.1</v>
+      </c>
+      <c r="U95">
+        <v>2.1</v>
+      </c>
+      <c r="V95">
+        <v>1.7</v>
+      </c>
+      <c r="W95">
+        <v>1.19</v>
+      </c>
+      <c r="X95">
+        <v>1.01</v>
+      </c>
+      <c r="Y95">
+        <v>1.11</v>
+      </c>
+      <c r="Z95">
+        <v>5.1</v>
+      </c>
+      <c r="AA95">
+        <v>1.45</v>
+      </c>
+      <c r="AB95">
+        <v>2.55</v>
+      </c>
+      <c r="AC95">
+        <v>2.23</v>
+      </c>
+      <c r="AD95">
+        <v>1.64</v>
+      </c>
+      <c r="AE95">
+        <v>1.26</v>
+      </c>
+      <c r="AF95">
+        <v>1.44</v>
+      </c>
+      <c r="AG95">
+        <v>2.73</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ95">
         <v>1.67</v>
       </c>
-      <c r="R95">
-        <v>2.6</v>
-      </c>
-      <c r="S95">
-        <v>1.29</v>
-      </c>
-      <c r="T95">
-        <v>3.6</v>
-      </c>
-      <c r="U95">
-        <v>2.3</v>
-      </c>
-      <c r="V95">
-        <v>1.57</v>
-      </c>
-      <c r="W95">
-        <v>1.11</v>
-      </c>
-      <c r="X95">
-        <v>1.02</v>
-      </c>
-      <c r="Y95">
-        <v>1.13</v>
-      </c>
-      <c r="Z95">
-        <v>4.6</v>
-      </c>
-      <c r="AA95">
-        <v>1.54</v>
-      </c>
-      <c r="AB95">
-        <v>2.44</v>
-      </c>
-      <c r="AC95">
-        <v>2.49</v>
-      </c>
-      <c r="AD95">
-        <v>1.55</v>
-      </c>
-      <c r="AE95">
-        <v>1.17</v>
-      </c>
-      <c r="AF95">
-        <v>1.96</v>
-      </c>
-      <c r="AG95">
-        <v>1.75</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ95">
-        <v>1.04</v>
-      </c>
       <c r="AK95">
-        <v>3.64</v>
+        <v>1.39</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.9</v>
+        <v>1.31</v>
       </c>
       <c r="O97">
-        <v>3.75</v>
+        <v>5.75</v>
       </c>
       <c r="P97">
-        <v>2.16</v>
+        <v>8.5</v>
       </c>
       <c r="Q97">
-        <v>3.3</v>
+        <v>1.67</v>
       </c>
       <c r="R97">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S97">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="T97">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="U97">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="V97">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="W97">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="X97">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z97">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AA97">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AB97">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="AC97">
-        <v>2.23</v>
+        <v>2.49</v>
       </c>
       <c r="AD97">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AE97">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AF97">
-        <v>1.44</v>
+        <v>1.96</v>
       </c>
       <c r="AG97">
-        <v>2.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.67</v>
+        <v>1.04</v>
       </c>
       <c r="AK97">
-        <v>1.39</v>
+        <v>3.64</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -21834,10 +21834,10 @@
         <v>0</v>
       </c>
       <c r="Q132">
-        <v>8.050000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="R132">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="S132">
         <v>1.25</v>
@@ -21846,10 +21846,10 @@
         <v>3.5</v>
       </c>
       <c r="U132">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="V132">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W132">
         <v>1.11</v>
@@ -21879,10 +21879,10 @@
         <v>1.17</v>
       </c>
       <c r="AF132">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG132">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>3.75</v>
       </c>
       <c r="AK132">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22314,19 +22314,19 @@
         </is>
       </c>
       <c r="N135">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="O135">
         <v>3.8</v>
       </c>
       <c r="P135">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
       </c>
       <c r="R135">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S135">
         <v>1.22</v>
@@ -22335,7 +22335,7 @@
         <v>4.1</v>
       </c>
       <c r="U135">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="V135">
         <v>1.67</v>
@@ -22350,19 +22350,19 @@
         <v>1.1</v>
       </c>
       <c r="Z135">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="AA135">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB135">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AC135">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AD135">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AE135">
         <v>1.29</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,31 +27856,31 @@
         </is>
       </c>
       <c r="N169">
-        <v>1.76</v>
+        <v>1.37</v>
       </c>
       <c r="O169">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="P169">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="Q169">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="R169">
-        <v>2.65</v>
+        <v>2.86</v>
       </c>
       <c r="S169">
         <v>1.13</v>
       </c>
       <c r="T169">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="U169">
         <v>1.67</v>
       </c>
       <c r="V169">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="W169">
         <v>1.3</v>
@@ -27892,28 +27892,28 @@
         <v>1.02</v>
       </c>
       <c r="Z169">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA169">
         <v>1.24</v>
       </c>
       <c r="AB169">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AC169">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AD169">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AE169">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AF169">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AG169">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK169">
-        <v>1.99</v>
+        <v>2.67</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,31 +28182,31 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.37</v>
+        <v>1.76</v>
       </c>
       <c r="O171">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="P171">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q171">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="R171">
-        <v>2.86</v>
+        <v>2.65</v>
       </c>
       <c r="S171">
         <v>1.13</v>
       </c>
       <c r="T171">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="U171">
         <v>1.67</v>
       </c>
       <c r="V171">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="W171">
         <v>1.3</v>
@@ -28218,28 +28218,28 @@
         <v>1.02</v>
       </c>
       <c r="Z171">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA171">
         <v>1.24</v>
       </c>
       <c r="AB171">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AC171">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AD171">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AE171">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AF171">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AG171">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AK171">
-        <v>2.67</v>
+        <v>1.99</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -35037,55 +35037,55 @@
         <v>0</v>
       </c>
       <c r="Q213">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="R213">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="S213">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T213">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U213">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="V213">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W213">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X213">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y213">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z213">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA213">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AB213">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AC213">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="AD213">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE213">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF213">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG213">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>1.29</v>
       </c>
       <c r="AK213">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35191,16 +35191,16 @@
         </is>
       </c>
       <c r="N214">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="O214">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="P214">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="Q214">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="R214">
         <v>2.4</v>
@@ -35209,7 +35209,7 @@
         <v>1.27</v>
       </c>
       <c r="T214">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U214">
         <v>2.33</v>
@@ -35224,13 +35224,13 @@
         <v>1.02</v>
       </c>
       <c r="Y214">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z214">
         <v>4.85</v>
       </c>
       <c r="AA214">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AB214">
         <v>2.35</v>
@@ -35245,7 +35245,7 @@
         <v>1.19</v>
       </c>
       <c r="AF214">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG214">
         <v>2.2</v>
@@ -35264,7 +35264,7 @@
         <v>1.22</v>
       </c>
       <c r="AK214">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G218">
@@ -35843,64 +35843,64 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.27</v>
+        <v>3.94</v>
       </c>
       <c r="O218">
-        <v>3.45</v>
+        <v>3.72</v>
       </c>
       <c r="P218">
-        <v>2.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q218">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="R218">
+        <v>2.22</v>
+      </c>
+      <c r="S218">
+        <v>1.32</v>
+      </c>
+      <c r="T218">
+        <v>3.02</v>
+      </c>
+      <c r="U218">
+        <v>2.4</v>
+      </c>
+      <c r="V218">
+        <v>1.47</v>
+      </c>
+      <c r="W218">
+        <v>1.08</v>
+      </c>
+      <c r="X218">
+        <v>1.01</v>
+      </c>
+      <c r="Y218">
+        <v>1.18</v>
+      </c>
+      <c r="Z218">
+        <v>3.85</v>
+      </c>
+      <c r="AA218">
+        <v>1.66</v>
+      </c>
+      <c r="AB218">
         <v>2.15</v>
       </c>
-      <c r="S218">
-        <v>1.35</v>
-      </c>
-      <c r="T218">
-        <v>2.82</v>
-      </c>
-      <c r="U218">
-        <v>2.45</v>
-      </c>
-      <c r="V218">
-        <v>1.44</v>
-      </c>
-      <c r="W218">
-        <v>1.07</v>
-      </c>
-      <c r="X218">
-        <v>1.02</v>
-      </c>
-      <c r="Y218">
-        <v>1.21</v>
-      </c>
-      <c r="Z218">
-        <v>3.58</v>
-      </c>
-      <c r="AA218">
-        <v>1.76</v>
-      </c>
-      <c r="AB218">
-        <v>2.07</v>
-      </c>
       <c r="AC218">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AD218">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE218">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF218">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG218">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.35</v>
+        <v>1.94</v>
       </c>
       <c r="AK218">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G219">
@@ -36006,64 +36006,64 @@
         </is>
       </c>
       <c r="N219">
-        <v>3.94</v>
+        <v>2.27</v>
       </c>
       <c r="O219">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="P219">
-        <v>1.88</v>
+        <v>2.95</v>
       </c>
       <c r="Q219">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="R219">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="S219">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T219">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="U219">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V219">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W219">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X219">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y219">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z219">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="AA219">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AB219">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC219">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD219">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE219">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF219">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AG219">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.94</v>
+        <v>1.35</v>
       </c>
       <c r="AK219">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -44008,10 +44008,10 @@
         <v>2.25</v>
       </c>
       <c r="S268">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T268">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U268">
         <v>2.7</v>
@@ -44020,7 +44020,7 @@
         <v>1.44</v>
       </c>
       <c r="W268">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X268">
         <v>1.01</v>
@@ -44029,19 +44029,19 @@
         <v>1.27</v>
       </c>
       <c r="Z268">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AA268">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB268">
         <v>1.9</v>
       </c>
       <c r="AC268">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="AD268">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE268">
         <v>1.08</v>
@@ -44165,37 +44165,37 @@
         <v>0</v>
       </c>
       <c r="Q269">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="R269">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="S269">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="T269">
         <v>2.62</v>
       </c>
       <c r="U269">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V269">
         <v>1.29</v>
       </c>
       <c r="W269">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X269">
         <v>1.03</v>
       </c>
       <c r="Y269">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="Z269">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="AA269">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AB269">
         <v>1.55</v>
@@ -44204,10 +44204,10 @@
         <v>4.4</v>
       </c>
       <c r="AD269">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AE269">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF269">
         <v>2</v>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK269">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G272">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G273">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,64 +44971,64 @@
         </is>
       </c>
       <c r="N274">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O274">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P274">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q274">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R274">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S274">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T274">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U274">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V274">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W274">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X274">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y274">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z274">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AA274">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AB274">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC274">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="AD274">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE274">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF274">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG274">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,10 +45041,10 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK274">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,64 +45134,64 @@
         </is>
       </c>
       <c r="N275">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O275">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P275">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q275">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R275">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S275">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T275">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U275">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V275">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W275">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X275">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y275">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z275">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AA275">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AB275">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC275">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="AD275">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE275">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF275">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG275">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK275">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL275">
         <v>0</v>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.83</v>
+        <v>1.31</v>
       </c>
       <c r="O96">
-        <v>3.75</v>
+        <v>5.75</v>
       </c>
       <c r="P96">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="Q96">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="R96">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="S96">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T96">
-        <v>2.86</v>
+        <v>3.6</v>
       </c>
       <c r="U96">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="V96">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="W96">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X96">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="Z96">
-        <v>3.84</v>
+        <v>4.6</v>
       </c>
       <c r="AA96">
-        <v>1.79</v>
+        <v>1.54</v>
       </c>
       <c r="AB96">
-        <v>2.07</v>
+        <v>2.44</v>
       </c>
       <c r="AC96">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AD96">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AE96">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF96">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="AG96">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AK96">
-        <v>2.02</v>
+        <v>3.64</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.31</v>
+        <v>1.83</v>
       </c>
       <c r="O97">
-        <v>5.75</v>
+        <v>3.75</v>
       </c>
       <c r="P97">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="Q97">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="R97">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="S97">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T97">
-        <v>3.6</v>
+        <v>2.86</v>
       </c>
       <c r="U97">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="V97">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="W97">
+        <v>1.08</v>
+      </c>
+      <c r="X97">
+        <v>1.01</v>
+      </c>
+      <c r="Y97">
+        <v>1.21</v>
+      </c>
+      <c r="Z97">
+        <v>3.84</v>
+      </c>
+      <c r="AA97">
+        <v>1.79</v>
+      </c>
+      <c r="AB97">
+        <v>2.07</v>
+      </c>
+      <c r="AC97">
+        <v>2.66</v>
+      </c>
+      <c r="AD97">
+        <v>1.38</v>
+      </c>
+      <c r="AE97">
         <v>1.11</v>
       </c>
-      <c r="X97">
-        <v>1.02</v>
-      </c>
-      <c r="Y97">
-        <v>1.13</v>
-      </c>
-      <c r="Z97">
-        <v>4.6</v>
-      </c>
-      <c r="AA97">
-        <v>1.54</v>
-      </c>
-      <c r="AB97">
-        <v>2.44</v>
-      </c>
-      <c r="AC97">
-        <v>2.49</v>
-      </c>
-      <c r="AD97">
-        <v>1.55</v>
-      </c>
-      <c r="AE97">
-        <v>1.17</v>
-      </c>
       <c r="AF97">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="AG97">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="AK97">
-        <v>3.64</v>
+        <v>2.02</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -20032,61 +20032,61 @@
         </is>
       </c>
       <c r="N121">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="O121">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P121">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q121">
-        <v>4.1</v>
+        <v>4.45</v>
       </c>
       <c r="R121">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="S121">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T121">
         <v>2.88</v>
       </c>
       <c r="U121">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="V121">
         <v>1.36</v>
       </c>
       <c r="W121">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X121">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y121">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z121">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA121">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB121">
         <v>1.8</v>
       </c>
       <c r="AC121">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD121">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE121">
         <v>1.06</v>
       </c>
       <c r="AF121">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG121">
         <v>1.95</v>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.74</v>
+        <v>1.3</v>
       </c>
       <c r="AK121">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -21834,10 +21834,10 @@
         <v>0</v>
       </c>
       <c r="Q132">
-        <v>7.95</v>
+        <v>7.5</v>
       </c>
       <c r="R132">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="S132">
         <v>1.25</v>
@@ -21858,31 +21858,31 @@
         <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z132">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA132">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AB132">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AC132">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AD132">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE132">
         <v>1.17</v>
       </c>
       <c r="AF132">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AG132">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>3.75</v>
+        <v>3.36</v>
       </c>
       <c r="AK132">
         <v>1.06</v>
@@ -25094,16 +25094,16 @@
         <v>0</v>
       </c>
       <c r="Q152">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="R152">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S152">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T152">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U152">
         <v>3.2</v>
@@ -25118,10 +25118,10 @@
         <v>1.01</v>
       </c>
       <c r="Y152">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z152">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="AA152">
         <v>2.25</v>
@@ -25139,7 +25139,7 @@
         <v>1.03</v>
       </c>
       <c r="AF152">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AG152">
         <v>1.87</v>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AK152">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G218">
@@ -35843,64 +35843,64 @@
         </is>
       </c>
       <c r="N218">
-        <v>3.94</v>
+        <v>2.27</v>
       </c>
       <c r="O218">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="P218">
-        <v>1.88</v>
+        <v>2.95</v>
       </c>
       <c r="Q218">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="R218">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="S218">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T218">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="U218">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V218">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W218">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X218">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y218">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z218">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="AA218">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AB218">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC218">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD218">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE218">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF218">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AG218">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.94</v>
+        <v>1.35</v>
       </c>
       <c r="AK218">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G219">
@@ -36006,64 +36006,64 @@
         </is>
       </c>
       <c r="N219">
-        <v>2.27</v>
+        <v>3.94</v>
       </c>
       <c r="O219">
-        <v>3.45</v>
+        <v>3.72</v>
       </c>
       <c r="P219">
-        <v>2.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q219">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="R219">
+        <v>2.22</v>
+      </c>
+      <c r="S219">
+        <v>1.32</v>
+      </c>
+      <c r="T219">
+        <v>3.02</v>
+      </c>
+      <c r="U219">
+        <v>2.4</v>
+      </c>
+      <c r="V219">
+        <v>1.47</v>
+      </c>
+      <c r="W219">
+        <v>1.08</v>
+      </c>
+      <c r="X219">
+        <v>1.01</v>
+      </c>
+      <c r="Y219">
+        <v>1.18</v>
+      </c>
+      <c r="Z219">
+        <v>3.85</v>
+      </c>
+      <c r="AA219">
+        <v>1.66</v>
+      </c>
+      <c r="AB219">
         <v>2.15</v>
       </c>
-      <c r="S219">
-        <v>1.35</v>
-      </c>
-      <c r="T219">
-        <v>2.82</v>
-      </c>
-      <c r="U219">
-        <v>2.45</v>
-      </c>
-      <c r="V219">
-        <v>1.44</v>
-      </c>
-      <c r="W219">
-        <v>1.07</v>
-      </c>
-      <c r="X219">
-        <v>1.02</v>
-      </c>
-      <c r="Y219">
-        <v>1.21</v>
-      </c>
-      <c r="Z219">
-        <v>3.58</v>
-      </c>
-      <c r="AA219">
-        <v>1.76</v>
-      </c>
-      <c r="AB219">
-        <v>2.07</v>
-      </c>
       <c r="AC219">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AD219">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE219">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF219">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG219">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.35</v>
+        <v>1.94</v>
       </c>
       <c r="AK219">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36193,7 +36193,7 @@
         <v>1.95</v>
       </c>
       <c r="V220">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W220">
         <v>1.17</v>
@@ -36208,13 +36208,13 @@
         <v>8.949999999999999</v>
       </c>
       <c r="AA220">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB220">
         <v>3</v>
       </c>
       <c r="AC220">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AD220">
         <v>1.86</v>
@@ -36223,10 +36223,10 @@
         <v>1.38</v>
       </c>
       <c r="AF220">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AG220">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AK220">
-        <v>7.7</v>
+        <v>6</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -39927,10 +39927,10 @@
         <v>4.35</v>
       </c>
       <c r="Q243">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="R243">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S243">
         <v>1.31</v>
@@ -39939,7 +39939,7 @@
         <v>2.94</v>
       </c>
       <c r="U243">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="V243">
         <v>1.42</v>
@@ -39948,7 +39948,7 @@
         <v>1.07</v>
       </c>
       <c r="X243">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y243">
         <v>1.19</v>
@@ -39963,7 +39963,7 @@
         <v>1.95</v>
       </c>
       <c r="AC243">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="AD243">
         <v>1.38</v>
@@ -39972,10 +39972,10 @@
         <v>1.11</v>
       </c>
       <c r="AF243">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG243">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AH243" t="inlineStr">
         <is>
@@ -39988,10 +39988,10 @@
         </is>
       </c>
       <c r="AJ243">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK243">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G244">
@@ -40081,64 +40081,64 @@
         </is>
       </c>
       <c r="N244">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O244">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P244">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q244">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R244">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S244">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T244">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U244">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="V244">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W244">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X244">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y244">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z244">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AA244">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB244">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC244">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="AD244">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE244">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF244">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AG244">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK244">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G245">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G246">
@@ -40407,64 +40407,64 @@
         </is>
       </c>
       <c r="N246">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O246">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P246">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q246">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R246">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S246">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T246">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U246">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V246">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W246">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X246">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y246">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z246">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA246">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB246">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC246">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="AD246">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE246">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF246">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AG246">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -40477,10 +40477,10 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK246">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -43015,25 +43015,25 @@
         </is>
       </c>
       <c r="N262">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="O262">
         <v>3.1</v>
       </c>
       <c r="P262">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q262">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R262">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="S262">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="T262">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="U262">
         <v>3.32</v>
@@ -43042,7 +43042,7 @@
         <v>1.3</v>
       </c>
       <c r="W262">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X262">
         <v>1.06</v>
@@ -43054,13 +43054,13 @@
         <v>2.49</v>
       </c>
       <c r="AA262">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AB262">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC262">
-        <v>4.76</v>
+        <v>4.8</v>
       </c>
       <c r="AD262">
         <v>1.14</v>
@@ -43069,7 +43069,7 @@
         <v>1.03</v>
       </c>
       <c r="AF262">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AG262">
         <v>1.67</v>
@@ -43085,10 +43085,10 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK262">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -43178,13 +43178,13 @@
         </is>
       </c>
       <c r="N263">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O263">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P263">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q263">
         <v>3.52</v>
@@ -43196,16 +43196,16 @@
         <v>1.4</v>
       </c>
       <c r="T263">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="U263">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="V263">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W263">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X263">
         <v>1.04</v>
@@ -43217,16 +43217,16 @@
         <v>3.08</v>
       </c>
       <c r="AA263">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB263">
         <v>1.79</v>
       </c>
       <c r="AC263">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AD263">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE263">
         <v>1.04</v>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK263">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -44168,16 +44168,16 @@
         <v>2.5</v>
       </c>
       <c r="R269">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="S269">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T269">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U269">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="V269">
         <v>1.29</v>
@@ -44189,19 +44189,19 @@
         <v>1.03</v>
       </c>
       <c r="Y269">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Z269">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AA269">
         <v>2.35</v>
       </c>
       <c r="AB269">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AC269">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AD269">
         <v>1.19</v>
@@ -46130,13 +46130,13 @@
         <v>1.26</v>
       </c>
       <c r="T281">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="U281">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V281">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W281">
         <v>1.11</v>
@@ -46148,28 +46148,28 @@
         <v>1.19</v>
       </c>
       <c r="Z281">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AA281">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB281">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AC281">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AD281">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE281">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF281">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG281">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AH281" t="inlineStr">
         <is>
@@ -46185,7 +46185,7 @@
         <v>1.23</v>
       </c>
       <c r="AK281">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AL281">
         <v>0</v>
@@ -46613,7 +46613,7 @@
         <v>1.75</v>
       </c>
       <c r="R284">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="S284">
         <v>1.27</v>
@@ -46634,28 +46634,28 @@
         <v>1.02</v>
       </c>
       <c r="Y284">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z284">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AA284">
         <v>1.65</v>
       </c>
       <c r="AB284">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AC284">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="AD284">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE284">
         <v>1.19</v>
       </c>
       <c r="AF284">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AG284">
         <v>1.85</v>
@@ -46674,7 +46674,7 @@
         <v>1.18</v>
       </c>
       <c r="AK284">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -47102,13 +47102,13 @@
         <v>3.91</v>
       </c>
       <c r="R287">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="S287">
         <v>1.51</v>
       </c>
       <c r="T287">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="U287">
         <v>3.24</v>
@@ -47120,13 +47120,13 @@
         <v>1.02</v>
       </c>
       <c r="X287">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y287">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z287">
-        <v>2.77</v>
+        <v>2.53</v>
       </c>
       <c r="AA287">
         <v>2.31</v>
@@ -47135,19 +47135,19 @@
         <v>1.56</v>
       </c>
       <c r="AC287">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AD287">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE287">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF287">
         <v>1.95</v>
       </c>
       <c r="AG287">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK287">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47262,22 +47262,22 @@
         <v>3.3</v>
       </c>
       <c r="Q288">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="R288">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S288">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T288">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="U288">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="V288">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W288">
         <v>1.07</v>
@@ -47286,31 +47286,31 @@
         <v>1.03</v>
       </c>
       <c r="Y288">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z288">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AA288">
+        <v>1.89</v>
+      </c>
+      <c r="AB288">
         <v>1.85</v>
       </c>
-      <c r="AB288">
-        <v>1.89</v>
-      </c>
       <c r="AC288">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD288">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE288">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF288">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG288">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK288">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47422,7 +47422,7 @@
         <v>3.3</v>
       </c>
       <c r="P289">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="Q289">
         <v>2.4</v>
@@ -47440,7 +47440,7 @@
         <v>2.99</v>
       </c>
       <c r="V289">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W289">
         <v>1.06</v>
@@ -47458,7 +47458,7 @@
         <v>2.23</v>
       </c>
       <c r="AB289">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AC289">
         <v>3.78</v>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -1827,13 +1827,13 @@
         <v>1.55</v>
       </c>
       <c r="AE9">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF9">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG9">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB13">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -2630,7 +2630,7 @@
         <v>2.59</v>
       </c>
       <c r="AA14">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AB14">
         <v>1.54</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="O15">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="P15">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -3246,10 +3246,10 @@
         <v>1.88</v>
       </c>
       <c r="O18">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="P18">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="O19">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="P19">
-        <v>3.92</v>
+        <v>3.32</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK20">
         <v>1.72</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="O25">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P25">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AK26">
         <v>1.97</v>
@@ -4719,10 +4719,10 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R27">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="S27">
         <v>1.42</v>
@@ -4755,10 +4755,10 @@
         <v>1.64</v>
       </c>
       <c r="AC27">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AD27">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE27">
         <v>1.04</v>
@@ -4783,7 +4783,7 @@
         <v>1.26</v>
       </c>
       <c r="AK27">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,16 +4882,16 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R28">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S28">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T28">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="U28">
         <v>3.24</v>
@@ -4921,7 +4921,7 @@
         <v>4.2</v>
       </c>
       <c r="AD28">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE28">
         <v>1.02</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK28">
         <v>1.74</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="O32">
         <v>3.2</v>
       </c>
       <c r="P32">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O33">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="P33">
         <v>3.25</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="O34">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P34">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>6.5</v>
       </c>
       <c r="P38">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Q38">
         <v>1.6</v>
@@ -6521,7 +6521,7 @@
         <v>1.11</v>
       </c>
       <c r="T38">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="U38">
         <v>1.91</v>
@@ -6539,28 +6539,28 @@
         <v>1.03</v>
       </c>
       <c r="Z38">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="AA38">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB38">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AC38">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AD38">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AE38">
         <v>1.4</v>
       </c>
       <c r="AF38">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG38">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.08</v>
       </c>
       <c r="AK38">
-        <v>3.46</v>
+        <v>3.28</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6998,7 +6998,7 @@
         <v>3.42</v>
       </c>
       <c r="P41">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -7016,7 +7016,7 @@
         <v>2.77</v>
       </c>
       <c r="V41">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W41">
         <v>1.07</v>
@@ -7028,7 +7028,7 @@
         <v>1.26</v>
       </c>
       <c r="Z41">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="AA41">
         <v>1.91</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="Q43">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="R43">
         <v>2.34</v>
@@ -7336,13 +7336,13 @@
         <v>1.25</v>
       </c>
       <c r="T43">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="U43">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V43">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W43">
         <v>1.11</v>
@@ -7363,10 +7363,10 @@
         <v>2.33</v>
       </c>
       <c r="AC43">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AD43">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE43">
         <v>1.19</v>
@@ -7490,7 +7490,7 @@
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>4.11</v>
+        <v>3.75</v>
       </c>
       <c r="R44">
         <v>2.19</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.27</v>
+        <v>2.69</v>
       </c>
       <c r="O49">
         <v>3.12</v>
       </c>
       <c r="P49">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="O51">
         <v>3.22</v>
@@ -8634,7 +8634,7 @@
         <v>3.6</v>
       </c>
       <c r="R51">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S51">
         <v>1.34</v>
@@ -8664,7 +8664,7 @@
         <v>1.72</v>
       </c>
       <c r="AB51">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AC51">
         <v>2.7</v>
@@ -8695,7 +8695,7 @@
         <v>1.67</v>
       </c>
       <c r="AK51">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8963,7 +8963,7 @@
         <v>2.25</v>
       </c>
       <c r="S53">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T53">
         <v>3.2</v>
@@ -8978,7 +8978,7 @@
         <v>1.11</v>
       </c>
       <c r="X53">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
         <v>1.18</v>
@@ -8990,7 +8990,7 @@
         <v>1.69</v>
       </c>
       <c r="AB53">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AC53">
         <v>2.69</v>
@@ -9005,7 +9005,7 @@
         <v>1.56</v>
       </c>
       <c r="AG53">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>1.25</v>
       </c>
       <c r="T54">
-        <v>2.99</v>
+        <v>3.5</v>
       </c>
       <c r="U54">
         <v>2.38</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,80 +9600,80 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="O57">
         <v>3.7</v>
       </c>
       <c r="P57">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q57">
-        <v>2.23</v>
+        <v>2.54</v>
       </c>
       <c r="R57">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S57">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T57">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="U57">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V57">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="W57">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z57">
-        <v>5.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA57">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AB57">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="AC57">
-        <v>2.06</v>
+        <v>2.35</v>
       </c>
       <c r="AD57">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AE57">
+        <v>1.18</v>
+      </c>
+      <c r="AF57">
+        <v>1.45</v>
+      </c>
+      <c r="AG57">
+        <v>2.45</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
         <v>1.25</v>
       </c>
-      <c r="AF57">
-        <v>1.42</v>
-      </c>
-      <c r="AG57">
-        <v>2.61</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ57">
-        <v>1.17</v>
-      </c>
       <c r="AK57">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="O58">
         <v>3.7</v>
       </c>
       <c r="P58">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q58">
-        <v>2.54</v>
+        <v>2.23</v>
       </c>
       <c r="R58">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S58">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T58">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="U58">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V58">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="W58">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z58">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA58">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AB58">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="AC58">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="AD58">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AE58">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF58">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AG58">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK58">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10267,13 +10267,13 @@
         <v>2.11</v>
       </c>
       <c r="S61">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T61">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="U61">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V61">
         <v>1.44</v>
@@ -10288,7 +10288,7 @@
         <v>1.19</v>
       </c>
       <c r="Z61">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="AA61">
         <v>1.74</v>
@@ -10325,7 +10325,7 @@
         <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -11571,7 +11571,7 @@
         <v>2.5</v>
       </c>
       <c r="S69">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T69">
         <v>3.14</v>
@@ -11595,7 +11595,7 @@
         <v>4.95</v>
       </c>
       <c r="AA69">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB69">
         <v>2.35</v>
@@ -11882,7 +11882,7 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="O71">
         <v>3.4</v>
@@ -11900,13 +11900,13 @@
         <v>1.3</v>
       </c>
       <c r="T71">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U71">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="V71">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W71">
         <v>1.08</v>
@@ -12118,7 +12118,7 @@
         <v>1.25</v>
       </c>
       <c r="AK72">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="N74">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O74">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P74">
         <v>1.49</v>
@@ -12389,7 +12389,7 @@
         <v>1.4</v>
       </c>
       <c r="T74">
-        <v>2.84</v>
+        <v>2.61</v>
       </c>
       <c r="U74">
         <v>2.89</v>
@@ -12419,7 +12419,7 @@
         <v>3.5</v>
       </c>
       <c r="AD74">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE74">
         <v>1.04</v>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK74">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="O76">
         <v>3.3</v>
       </c>
       <c r="P76">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q76">
         <v>3.1</v>
@@ -12718,10 +12718,10 @@
         <v>3</v>
       </c>
       <c r="U76">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="V76">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W76">
         <v>1.06</v>
@@ -12730,28 +12730,28 @@
         <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z76">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA76">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AB76">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC76">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AD76">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE76">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF76">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG76">
         <v>2.05</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK76">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13352,7 +13352,7 @@
         <v>4.1</v>
       </c>
       <c r="O80">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="P80">
         <v>1.75</v>
@@ -13367,7 +13367,7 @@
         <v>1.33</v>
       </c>
       <c r="T80">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U80">
         <v>2.75</v>
@@ -13419,7 +13419,7 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.21</v>
+        <v>1.67</v>
       </c>
       <c r="AK80">
         <v>1.22</v>
@@ -13838,25 +13838,25 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="O83">
         <v>3.15</v>
       </c>
       <c r="P83">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="Q83">
-        <v>2.87</v>
+        <v>2.68</v>
       </c>
       <c r="R83">
         <v>1.94</v>
       </c>
       <c r="S83">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T83">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U83">
         <v>3.2</v>
@@ -13865,7 +13865,7 @@
         <v>1.3</v>
       </c>
       <c r="W83">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X83">
         <v>1.04</v>
@@ -13880,10 +13880,10 @@
         <v>2.25</v>
       </c>
       <c r="AB83">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC83">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AD83">
         <v>1.18</v>
@@ -13892,10 +13892,10 @@
         <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG83">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK83">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14384,7 +14384,7 @@
         <v>1.44</v>
       </c>
       <c r="AG86">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK86">
         <v>1.61</v>
@@ -14490,16 +14490,16 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O87">
         <v>4</v>
       </c>
       <c r="P87">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q87">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="R87">
         <v>2.75</v>
@@ -14508,13 +14508,13 @@
         <v>1.17</v>
       </c>
       <c r="T87">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="U87">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V87">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="W87">
         <v>1.25</v>
@@ -14526,7 +14526,7 @@
         <v>1.05</v>
       </c>
       <c r="Z87">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA87">
         <v>1.25</v>
@@ -14538,13 +14538,13 @@
         <v>1.74</v>
       </c>
       <c r="AD87">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AE87">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AF87">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AG87">
         <v>3.3</v>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AK87">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14680,7 +14680,7 @@
         <v>1.95</v>
       </c>
       <c r="W88">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X88">
         <v>1.01</v>
@@ -15471,10 +15471,10 @@
         <v>1.94</v>
       </c>
       <c r="O93">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P93">
-        <v>3.83</v>
+        <v>3.6</v>
       </c>
       <c r="Q93">
         <v>2.5</v>
@@ -15525,7 +15525,7 @@
         <v>1.65</v>
       </c>
       <c r="AG93">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK94">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.31</v>
+        <v>1.83</v>
       </c>
       <c r="O96">
-        <v>5.75</v>
+        <v>3.75</v>
       </c>
       <c r="P96">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="Q96">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="R96">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="S96">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T96">
-        <v>3.6</v>
+        <v>2.86</v>
       </c>
       <c r="U96">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="V96">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="W96">
+        <v>1.08</v>
+      </c>
+      <c r="X96">
+        <v>1.01</v>
+      </c>
+      <c r="Y96">
+        <v>1.21</v>
+      </c>
+      <c r="Z96">
+        <v>3.84</v>
+      </c>
+      <c r="AA96">
+        <v>1.79</v>
+      </c>
+      <c r="AB96">
+        <v>2.07</v>
+      </c>
+      <c r="AC96">
+        <v>2.66</v>
+      </c>
+      <c r="AD96">
+        <v>1.38</v>
+      </c>
+      <c r="AE96">
         <v>1.11</v>
       </c>
-      <c r="X96">
-        <v>1.02</v>
-      </c>
-      <c r="Y96">
-        <v>1.13</v>
-      </c>
-      <c r="Z96">
-        <v>4.6</v>
-      </c>
-      <c r="AA96">
-        <v>1.54</v>
-      </c>
-      <c r="AB96">
-        <v>2.44</v>
-      </c>
-      <c r="AC96">
-        <v>2.49</v>
-      </c>
-      <c r="AD96">
-        <v>1.55</v>
-      </c>
-      <c r="AE96">
-        <v>1.17</v>
-      </c>
       <c r="AF96">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="AG96">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="AK96">
-        <v>3.64</v>
+        <v>2.02</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.83</v>
+        <v>1.31</v>
       </c>
       <c r="O97">
-        <v>3.75</v>
+        <v>5.75</v>
       </c>
       <c r="P97">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="Q97">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="R97">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="S97">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T97">
-        <v>2.86</v>
+        <v>3.6</v>
       </c>
       <c r="U97">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="V97">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="W97">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X97">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="Z97">
-        <v>3.84</v>
+        <v>4.6</v>
       </c>
       <c r="AA97">
-        <v>1.79</v>
+        <v>1.54</v>
       </c>
       <c r="AB97">
-        <v>2.07</v>
+        <v>2.44</v>
       </c>
       <c r="AC97">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AD97">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AE97">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF97">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="AG97">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AK97">
-        <v>2.02</v>
+        <v>3.64</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16503,7 +16503,7 @@
         <v>2.09</v>
       </c>
       <c r="AG99">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O100">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P100">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q100">
         <v>4.86</v>
@@ -16627,7 +16627,7 @@
         <v>1.47</v>
       </c>
       <c r="T100">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U100">
         <v>3.25</v>
@@ -16648,7 +16648,7 @@
         <v>2.56</v>
       </c>
       <c r="AA100">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AB100">
         <v>1.51</v>
@@ -16772,10 +16772,10 @@
         </is>
       </c>
       <c r="N101">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="O101">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P101">
         <v>1.25</v>
@@ -16784,19 +16784,19 @@
         <v>9</v>
       </c>
       <c r="R101">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="S101">
         <v>1.3</v>
       </c>
       <c r="T101">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="U101">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="V101">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W101">
         <v>1.06</v>
@@ -16808,7 +16808,7 @@
         <v>1.2</v>
       </c>
       <c r="Z101">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AA101">
         <v>1.75</v>
@@ -16817,19 +16817,19 @@
         <v>1.95</v>
       </c>
       <c r="AC101">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AD101">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE101">
         <v>1.09</v>
       </c>
       <c r="AF101">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AG101">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -18402,16 +18402,16 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="O111">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P111">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q111">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="R111">
         <v>2</v>
@@ -18423,7 +18423,7 @@
         <v>2.75</v>
       </c>
       <c r="U111">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="V111">
         <v>1.35</v>
@@ -18475,7 +18475,7 @@
         <v>1.26</v>
       </c>
       <c r="AK111">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18764,13 +18764,13 @@
         <v>1.18</v>
       </c>
       <c r="Z113">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AA113">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB113">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AC113">
         <v>2.74</v>
@@ -18782,7 +18782,7 @@
         <v>1.1</v>
       </c>
       <c r="AF113">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG113">
         <v>2</v>
@@ -19075,10 +19075,10 @@
         <v>3.65</v>
       </c>
       <c r="U115">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="V115">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="W115">
         <v>1.18</v>
@@ -19093,7 +19093,7 @@
         <v>6</v>
       </c>
       <c r="AA115">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB115">
         <v>2.5</v>
@@ -19226,7 +19226,7 @@
         <v>2.45</v>
       </c>
       <c r="Q116">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="R116">
         <v>1.95</v>
@@ -19256,10 +19256,10 @@
         <v>2.7</v>
       </c>
       <c r="AA116">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AB116">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AC116">
         <v>5</v>
@@ -19268,7 +19268,7 @@
         <v>1.15</v>
       </c>
       <c r="AE116">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF116">
         <v>1.91</v>
@@ -19383,7 +19383,7 @@
         <v>2.02</v>
       </c>
       <c r="O117">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P117">
         <v>3.05</v>
@@ -19392,13 +19392,13 @@
         <v>2.44</v>
       </c>
       <c r="R117">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="S117">
         <v>1.19</v>
       </c>
       <c r="T117">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="U117">
         <v>1.96</v>
@@ -19437,7 +19437,7 @@
         <v>1.36</v>
       </c>
       <c r="AG117">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -20207,19 +20207,19 @@
         <v>3.72</v>
       </c>
       <c r="R122">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S122">
         <v>1.42</v>
       </c>
       <c r="T122">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="U122">
         <v>3.12</v>
       </c>
       <c r="V122">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W122">
         <v>1.02</v>
@@ -20234,10 +20234,10 @@
         <v>2.62</v>
       </c>
       <c r="AA122">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AB122">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AC122">
         <v>4.33</v>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
+        <v>1.28</v>
+      </c>
+      <c r="AK122">
         <v>1.33</v>
-      </c>
-      <c r="AK122">
-        <v>1.4</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20524,10 +20524,10 @@
         <v>7.25</v>
       </c>
       <c r="O124">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="P124">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Q124">
         <v>7.07</v>
@@ -20566,7 +20566,7 @@
         <v>1.95</v>
       </c>
       <c r="AC124">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AD124">
         <v>1.36</v>
@@ -20856,7 +20856,7 @@
         <v>0</v>
       </c>
       <c r="Q126">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="R126">
         <v>1.99</v>
@@ -21019,7 +21019,7 @@
         <v>3.45</v>
       </c>
       <c r="Q127">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R127">
         <v>2.25</v>
@@ -21037,7 +21037,7 @@
         <v>1.5</v>
       </c>
       <c r="W127">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X127">
         <v>1.01</v>
@@ -21067,7 +21067,7 @@
         <v>1.51</v>
       </c>
       <c r="AG127">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK127">
         <v>1.73</v>
@@ -21345,7 +21345,7 @@
         <v>1.85</v>
       </c>
       <c r="Q129">
-        <v>3.61</v>
+        <v>3.67</v>
       </c>
       <c r="R129">
         <v>2.25</v>
@@ -21393,7 +21393,7 @@
         <v>1.67</v>
       </c>
       <c r="AG129">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21514,10 +21514,10 @@
         <v>2.14</v>
       </c>
       <c r="S130">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T130">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U130">
         <v>2.6</v>
@@ -21526,7 +21526,7 @@
         <v>1.44</v>
       </c>
       <c r="W130">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X130">
         <v>1</v>
@@ -21701,7 +21701,7 @@
         <v>2.88</v>
       </c>
       <c r="AA131">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB131">
         <v>1.63</v>
@@ -21991,7 +21991,7 @@
         <v>1.68</v>
       </c>
       <c r="O133">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P133">
         <v>4.33</v>
@@ -23790,7 +23790,7 @@
         <v>0</v>
       </c>
       <c r="Q144">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="R144">
         <v>2.11</v>
@@ -23805,13 +23805,13 @@
         <v>2.5</v>
       </c>
       <c r="V144">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W144">
         <v>1.12</v>
       </c>
       <c r="X144">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y144">
         <v>1.17</v>
@@ -23851,7 +23851,7 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK144">
         <v>1.53</v>
@@ -24273,22 +24273,22 @@
         <v>6.4</v>
       </c>
       <c r="O147">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P147">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q147">
-        <v>6.78</v>
+        <v>6.84</v>
       </c>
       <c r="R147">
         <v>2.2</v>
       </c>
       <c r="S147">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T147">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="U147">
         <v>2.88</v>
@@ -24297,37 +24297,37 @@
         <v>1.36</v>
       </c>
       <c r="W147">
+        <v>1.03</v>
+      </c>
+      <c r="X147">
+        <v>1.02</v>
+      </c>
+      <c r="Y147">
+        <v>1.3</v>
+      </c>
+      <c r="Z147">
+        <v>2.97</v>
+      </c>
+      <c r="AA147">
+        <v>2.02</v>
+      </c>
+      <c r="AB147">
+        <v>1.73</v>
+      </c>
+      <c r="AC147">
+        <v>3.42</v>
+      </c>
+      <c r="AD147">
+        <v>1.23</v>
+      </c>
+      <c r="AE147">
         <v>1.04</v>
       </c>
-      <c r="X147">
-        <v>1.01</v>
-      </c>
-      <c r="Y147">
-        <v>1.27</v>
-      </c>
-      <c r="Z147">
-        <v>3.14</v>
-      </c>
-      <c r="AA147">
-        <v>2.01</v>
-      </c>
-      <c r="AB147">
-        <v>1.74</v>
-      </c>
-      <c r="AC147">
-        <v>3.28</v>
-      </c>
-      <c r="AD147">
-        <v>1.25</v>
-      </c>
-      <c r="AE147">
-        <v>1.05</v>
-      </c>
       <c r="AF147">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG147">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24448,16 +24448,16 @@
         <v>2.75</v>
       </c>
       <c r="S148">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T148">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="U148">
         <v>1.87</v>
       </c>
       <c r="V148">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="W148">
         <v>1.22</v>
@@ -24466,10 +24466,10 @@
         <v>1.01</v>
       </c>
       <c r="Y148">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z148">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA148">
         <v>1.33</v>
@@ -24481,13 +24481,13 @@
         <v>1.88</v>
       </c>
       <c r="AD148">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AE148">
         <v>1.39</v>
       </c>
       <c r="AF148">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AG148">
         <v>3.2</v>
@@ -24503,7 +24503,7 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK148">
         <v>1.95</v>
@@ -24653,7 +24653,7 @@
         <v>1.33</v>
       </c>
       <c r="AG149">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="O153">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P153">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25414,10 +25414,10 @@
         <v>2.3</v>
       </c>
       <c r="O154">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P154">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="O168">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P168">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -28997,34 +28997,34 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="O176">
         <v>3.3</v>
       </c>
       <c r="P176">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q176">
         <v>3.32</v>
       </c>
       <c r="R176">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S176">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T176">
         <v>2.83</v>
       </c>
       <c r="U176">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="V176">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W176">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X176">
         <v>1</v>
@@ -29033,19 +29033,19 @@
         <v>1.24</v>
       </c>
       <c r="Z176">
-        <v>3.34</v>
+        <v>3.43</v>
       </c>
       <c r="AA176">
         <v>1.95</v>
       </c>
       <c r="AB176">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC176">
         <v>3.08</v>
       </c>
       <c r="AD176">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE176">
         <v>1.07</v>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK176">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29658,37 +29658,37 @@
         <v>3.2</v>
       </c>
       <c r="Q180">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="R180">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="S180">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T180">
         <v>3.24</v>
       </c>
       <c r="U180">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="V180">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W180">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X180">
         <v>1.01</v>
       </c>
       <c r="Y180">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z180">
         <v>4.3</v>
       </c>
       <c r="AA180">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB180">
         <v>2.15</v>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK180">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29821,16 +29821,16 @@
         <v>3.2</v>
       </c>
       <c r="Q181">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="R181">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="S181">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="T181">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="U181">
         <v>3.3</v>
@@ -29845,31 +29845,31 @@
         <v>1.05</v>
       </c>
       <c r="Y181">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z181">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AA181">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AB181">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AC181">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AD181">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE181">
         <v>1</v>
       </c>
       <c r="AF181">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG181">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK181">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -30141,10 +30141,10 @@
         <v>2.89</v>
       </c>
       <c r="O183">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P183">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30627,22 +30627,22 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.19</v>
+        <v>1.91</v>
       </c>
       <c r="O186">
         <v>3.35</v>
       </c>
       <c r="P186">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="Q186">
-        <v>2.77</v>
+        <v>2.39</v>
       </c>
       <c r="R186">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="S186">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T186">
         <v>2.69</v>
@@ -30666,10 +30666,10 @@
         <v>2.97</v>
       </c>
       <c r="AA186">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB186">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC186">
         <v>3.42</v>
@@ -30681,10 +30681,10 @@
         <v>1.05</v>
       </c>
       <c r="AF186">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AG186">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK186">
-        <v>1.54</v>
+        <v>1.79</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30953,10 +30953,10 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="O188">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="P188">
         <v>2.85</v>
@@ -30965,52 +30965,52 @@
         <v>2.36</v>
       </c>
       <c r="R188">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="S188">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T188">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U188">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="V188">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="W188">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X188">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y188">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z188">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="AA188">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AB188">
+        <v>2.44</v>
+      </c>
+      <c r="AC188">
         <v>2.25</v>
-      </c>
-      <c r="AC188">
-        <v>2.35</v>
       </c>
       <c r="AD188">
         <v>1.66</v>
       </c>
       <c r="AE188">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF188">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG188">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK188">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31768,40 +31768,40 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="O193">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P193">
         <v>3.25</v>
       </c>
       <c r="Q193">
-        <v>2.85</v>
+        <v>2.61</v>
       </c>
       <c r="R193">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S193">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T193">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U193">
         <v>3.12</v>
       </c>
       <c r="V193">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W193">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X193">
         <v>1.03</v>
       </c>
       <c r="Y193">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z193">
         <v>2.7</v>
@@ -31813,7 +31813,7 @@
         <v>1.61</v>
       </c>
       <c r="AC193">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AD193">
         <v>1.18</v>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK193">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -33404,25 +33404,25 @@
         <v>3.5</v>
       </c>
       <c r="P203">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="Q203">
         <v>3</v>
       </c>
       <c r="R203">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="S203">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T203">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U203">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V203">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W203">
         <v>1.14</v>
@@ -33434,19 +33434,19 @@
         <v>1.1</v>
       </c>
       <c r="Z203">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AA203">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB203">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC203">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD203">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AE203">
         <v>1.29</v>
@@ -33455,7 +33455,7 @@
         <v>1.4</v>
       </c>
       <c r="AG203">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="O204">
         <v>3</v>
       </c>
       <c r="P204">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -33896,25 +33896,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Q206">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="R206">
         <v>2.62</v>
       </c>
       <c r="S206">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T206">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U206">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V206">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W206">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X206">
         <v>1</v>
@@ -33923,7 +33923,7 @@
         <v>1.11</v>
       </c>
       <c r="Z206">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA206">
         <v>1.44</v>
@@ -33941,10 +33941,10 @@
         <v>1.22</v>
       </c>
       <c r="AF206">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AG206">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK206">
-        <v>3.52</v>
+        <v>3.78</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34050,13 +34050,13 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="O207">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P207">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="Q207">
         <v>2.1</v>
@@ -34065,19 +34065,19 @@
         <v>2.3</v>
       </c>
       <c r="S207">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T207">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U207">
         <v>2.55</v>
       </c>
       <c r="V207">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W207">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X207">
         <v>1</v>
@@ -34089,25 +34089,25 @@
         <v>3.7</v>
       </c>
       <c r="AA207">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AB207">
         <v>2</v>
       </c>
       <c r="AC207">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="AD207">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE207">
         <v>1.1</v>
       </c>
       <c r="AF207">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG207">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK207">
         <v>2.17</v>
@@ -34213,7 +34213,7 @@
         </is>
       </c>
       <c r="N208">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O208">
         <v>3.1</v>
@@ -34225,7 +34225,7 @@
         <v>2.97</v>
       </c>
       <c r="R208">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="S208">
         <v>1.47</v>
@@ -34246,16 +34246,16 @@
         <v>1.04</v>
       </c>
       <c r="Y208">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z208">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AA208">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AB208">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AC208">
         <v>4.4</v>
@@ -34264,13 +34264,13 @@
         <v>1.14</v>
       </c>
       <c r="AE208">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF208">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AG208">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="O211">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P211">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -34868,55 +34868,55 @@
         <v>7.95</v>
       </c>
       <c r="O212">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P212">
         <v>1.33</v>
       </c>
       <c r="Q212">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="R212">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="S212">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T212">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="U212">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="V212">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W212">
         <v>1.07</v>
       </c>
       <c r="X212">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y212">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z212">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA212">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB212">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC212">
-        <v>3.09</v>
+        <v>2.81</v>
       </c>
       <c r="AD212">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE212">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF212">
         <v>2.05</v>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK212">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="O216">
-        <v>4.7</v>
+        <v>4.67</v>
       </c>
       <c r="P216">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="Q216">
         <v>0</v>
@@ -35689,22 +35689,22 @@
         <v>4.1</v>
       </c>
       <c r="Q217">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="R217">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="S217">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T217">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="U217">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="V217">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W217">
         <v>1.03</v>
@@ -35713,10 +35713,10 @@
         <v>1.02</v>
       </c>
       <c r="Y217">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z217">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AA217">
         <v>2.17</v>
@@ -35725,19 +35725,19 @@
         <v>1.59</v>
       </c>
       <c r="AC217">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AD217">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE217">
         <v>1.01</v>
       </c>
       <c r="AF217">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG217">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>1.24</v>
       </c>
       <c r="AK217">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="O221">
         <v>3.3</v>
       </c>
       <c r="P221">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36830,7 +36830,7 @@
         <v>0</v>
       </c>
       <c r="Q224">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R224">
         <v>2</v>
@@ -36857,28 +36857,28 @@
         <v>1.28</v>
       </c>
       <c r="Z224">
-        <v>3.08</v>
+        <v>3.36</v>
       </c>
       <c r="AA224">
         <v>1.94</v>
       </c>
       <c r="AB224">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AC224">
         <v>3.28</v>
       </c>
       <c r="AD224">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE224">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF224">
         <v>1.73</v>
       </c>
       <c r="AG224">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AK224">
         <v>1.44</v>
@@ -36990,25 +36990,25 @@
         <v>4</v>
       </c>
       <c r="P225">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="Q225">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="R225">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="S225">
         <v>1.26</v>
       </c>
       <c r="T225">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="U225">
         <v>2.34</v>
       </c>
       <c r="V225">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W225">
         <v>1.12</v>
@@ -37023,7 +37023,7 @@
         <v>4.07</v>
       </c>
       <c r="AA225">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB225">
         <v>2.05</v>
@@ -37032,7 +37032,7 @@
         <v>2.72</v>
       </c>
       <c r="AD225">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE225">
         <v>1.11</v>
@@ -37054,7 +37054,7 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK225">
         <v>2.22</v>
@@ -37482,25 +37482,25 @@
         <v>0</v>
       </c>
       <c r="Q228">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="R228">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S228">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T228">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U228">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V228">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W228">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X228">
         <v>1.01</v>
@@ -37512,10 +37512,10 @@
         <v>3.84</v>
       </c>
       <c r="AA228">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB228">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC228">
         <v>2.78</v>
@@ -37546,7 +37546,7 @@
         <v>1.22</v>
       </c>
       <c r="AK228">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -38137,7 +38137,7 @@
         <v>2.88</v>
       </c>
       <c r="R232">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="S232">
         <v>1.4</v>
@@ -38167,7 +38167,7 @@
         <v>2.1</v>
       </c>
       <c r="AB232">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC232">
         <v>3.5</v>
@@ -38777,10 +38777,10 @@
         </is>
       </c>
       <c r="N236">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="O236">
-        <v>3.55</v>
+        <v>3.39</v>
       </c>
       <c r="P236">
         <v>5.25</v>
@@ -38789,10 +38789,10 @@
         <v>2.2</v>
       </c>
       <c r="R236">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="S236">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T236">
         <v>2.97</v>
@@ -38801,7 +38801,7 @@
         <v>2.88</v>
       </c>
       <c r="V236">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W236">
         <v>1.08</v>
@@ -38816,16 +38816,16 @@
         <v>3.5</v>
       </c>
       <c r="AA236">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB236">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AC236">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD236">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE236">
         <v>1.09</v>
@@ -38850,7 +38850,7 @@
         <v>1.24</v>
       </c>
       <c r="AK236">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="O239">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P239">
-        <v>4.44</v>
+        <v>4.9</v>
       </c>
       <c r="Q239">
         <v>0</v>
@@ -39305,10 +39305,10 @@
         <v>0</v>
       </c>
       <c r="AA239">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB239">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC239">
         <v>0</v>
@@ -39438,25 +39438,25 @@
         <v>3.9</v>
       </c>
       <c r="Q240">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R240">
         <v>2.02</v>
       </c>
       <c r="S240">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T240">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="U240">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="V240">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W240">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X240">
         <v>1.01</v>
@@ -39468,16 +39468,16 @@
         <v>3.04</v>
       </c>
       <c r="AA240">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AB240">
         <v>1.72</v>
       </c>
       <c r="AC240">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="AD240">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE240">
         <v>1.03</v>
@@ -39486,7 +39486,7 @@
         <v>1.83</v>
       </c>
       <c r="AG240">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39592,10 +39592,10 @@
         </is>
       </c>
       <c r="N241">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="O241">
-        <v>4.44</v>
+        <v>4.2</v>
       </c>
       <c r="P241">
         <v>1.67</v>
@@ -39607,19 +39607,19 @@
         <v>2.6</v>
       </c>
       <c r="S241">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T241">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="U241">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="V241">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="W241">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X241">
         <v>1.01</v>
@@ -39631,25 +39631,25 @@
         <v>5.5</v>
       </c>
       <c r="AA241">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB241">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AC241">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AD241">
         <v>1.78</v>
       </c>
       <c r="AE241">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF241">
         <v>1.44</v>
       </c>
       <c r="AG241">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AH241" t="inlineStr">
         <is>
@@ -39662,10 +39662,10 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="AK241">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -40570,7 +40570,7 @@
         </is>
       </c>
       <c r="N247">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="O247">
         <v>3.9</v>
@@ -40597,7 +40597,7 @@
         <v>1.44</v>
       </c>
       <c r="W247">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X247">
         <v>1.01</v>
@@ -40606,10 +40606,10 @@
         <v>1.23</v>
       </c>
       <c r="Z247">
-        <v>3.74</v>
+        <v>3.42</v>
       </c>
       <c r="AA247">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AB247">
         <v>1.92</v>
@@ -40643,7 +40643,7 @@
         <v>1.25</v>
       </c>
       <c r="AK247">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -42852,10 +42852,10 @@
         </is>
       </c>
       <c r="N261">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="O261">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="P261">
         <v>11</v>
@@ -42864,13 +42864,13 @@
         <v>1.7</v>
       </c>
       <c r="R261">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="S261">
         <v>1.31</v>
       </c>
       <c r="T261">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="U261">
         <v>2.43</v>
@@ -42879,7 +42879,7 @@
         <v>1.52</v>
       </c>
       <c r="W261">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X261">
         <v>1.01</v>
@@ -42888,7 +42888,7 @@
         <v>1.18</v>
       </c>
       <c r="Z261">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="AA261">
         <v>1.72</v>
@@ -42897,7 +42897,7 @@
         <v>2.31</v>
       </c>
       <c r="AC261">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="AD261">
         <v>1.46</v>
@@ -42925,7 +42925,7 @@
         <v>1.04</v>
       </c>
       <c r="AK261">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -46447,22 +46447,22 @@
         <v>0</v>
       </c>
       <c r="Q283">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="R283">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S283">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T283">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U283">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V283">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W283">
         <v>1.14</v>
@@ -46471,25 +46471,25 @@
         <v>1.02</v>
       </c>
       <c r="Y283">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z283">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AA283">
         <v>1.5</v>
       </c>
       <c r="AB283">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AC283">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AD283">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AE283">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF283">
         <v>1.75</v>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -1302,28 +1302,28 @@
         <v>2.17</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U6">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z6">
-        <v>3.88</v>
+        <v>3.58</v>
       </c>
       <c r="AA6">
         <v>1.74</v>
@@ -1332,19 +1332,19 @@
         <v>2.08</v>
       </c>
       <c r="AC6">
-        <v>2.83</v>
+        <v>3.02</v>
       </c>
       <c r="AD6">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG6">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>1.3</v>
       </c>
       <c r="Z7">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA7">
         <v>2.05</v>
@@ -1686,7 +1686,7 @@
         <v>1.44</v>
       </c>
       <c r="AK8">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G27">
@@ -4719,55 +4719,55 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="R27">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="S27">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T27">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="U27">
-        <v>2.99</v>
+        <v>3.24</v>
       </c>
       <c r="V27">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Z27">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AA27">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="AB27">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="AC27">
-        <v>3.72</v>
+        <v>4.2</v>
       </c>
       <c r="AD27">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE27">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF27">
-        <v>1.84</v>
+        <v>2.03</v>
       </c>
       <c r="AG27">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK27">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G28">
@@ -4882,71 +4882,71 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="R28">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="S28">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T28">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="U28">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="V28">
+        <v>1.3</v>
+      </c>
+      <c r="W28">
+        <v>1.04</v>
+      </c>
+      <c r="X28">
+        <v>1.03</v>
+      </c>
+      <c r="Y28">
+        <v>1.32</v>
+      </c>
+      <c r="Z28">
+        <v>2.88</v>
+      </c>
+      <c r="AA28">
+        <v>2.08</v>
+      </c>
+      <c r="AB28">
+        <v>1.64</v>
+      </c>
+      <c r="AC28">
+        <v>3.72</v>
+      </c>
+      <c r="AD28">
+        <v>1.2</v>
+      </c>
+      <c r="AE28">
+        <v>1.04</v>
+      </c>
+      <c r="AF28">
+        <v>1.84</v>
+      </c>
+      <c r="AG28">
+        <v>1.85</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
         <v>1.26</v>
       </c>
-      <c r="W28">
-        <v>1.03</v>
-      </c>
-      <c r="X28">
-        <v>1.05</v>
-      </c>
-      <c r="Y28">
-        <v>1.39</v>
-      </c>
-      <c r="Z28">
-        <v>2.59</v>
-      </c>
-      <c r="AA28">
-        <v>2.27</v>
-      </c>
-      <c r="AB28">
-        <v>1.54</v>
-      </c>
-      <c r="AC28">
-        <v>4.2</v>
-      </c>
-      <c r="AD28">
-        <v>1.15</v>
-      </c>
-      <c r="AE28">
-        <v>1.02</v>
-      </c>
-      <c r="AF28">
-        <v>2.03</v>
-      </c>
-      <c r="AG28">
-        <v>1.67</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.24</v>
-      </c>
       <c r="AK28">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O37">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="P37">
         <v>2.85</v>
@@ -7656,7 +7656,7 @@
         <v>2.21</v>
       </c>
       <c r="R45">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="S45">
         <v>1.36</v>
@@ -7698,7 +7698,7 @@
         <v>1.08</v>
       </c>
       <c r="AF45">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG45">
         <v>1.91</v>
@@ -7717,7 +7717,7 @@
         <v>1.21</v>
       </c>
       <c r="AK45">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7988,13 +7988,13 @@
         <v>1.33</v>
       </c>
       <c r="T47">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="U47">
         <v>2.62</v>
       </c>
       <c r="V47">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W47">
         <v>1.07</v>
@@ -8006,7 +8006,7 @@
         <v>1.23</v>
       </c>
       <c r="Z47">
-        <v>3.42</v>
+        <v>3.67</v>
       </c>
       <c r="AA47">
         <v>1.83</v>
@@ -8027,7 +8027,7 @@
         <v>1.75</v>
       </c>
       <c r="AG47">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
         <v>0</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>1.14</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
         <v>1.15</v>
@@ -8513,10 +8513,10 @@
         <v>1.19</v>
       </c>
       <c r="AF50">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AG50">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -9274,25 +9274,25 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O55">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P55">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q55">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="R55">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S55">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T55">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="U55">
         <v>2.1</v>
@@ -9304,34 +9304,34 @@
         <v>1.17</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z55">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="AA55">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB55">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="AC55">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AD55">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AE55">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF55">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AG55">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.2</v>
       </c>
       <c r="AK55">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9446,46 +9446,46 @@
         <v>2.09</v>
       </c>
       <c r="Q56">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="R56">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="S56">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T56">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="U56">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="V56">
         <v>1.65</v>
       </c>
       <c r="W56">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X56">
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z56">
         <v>5.75</v>
       </c>
       <c r="AA56">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AB56">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="AC56">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AD56">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AE56">
         <v>1.32</v>
@@ -9494,7 +9494,7 @@
         <v>1.36</v>
       </c>
       <c r="AG56">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="AK56">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9606,10 +9606,10 @@
         <v>3.7</v>
       </c>
       <c r="P57">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q57">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R57">
         <v>2.4</v>
@@ -9657,7 +9657,7 @@
         <v>1.45</v>
       </c>
       <c r="AG57">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>3.6</v>
       </c>
       <c r="Q58">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="R58">
         <v>2.5</v>
@@ -9790,37 +9790,37 @@
         <v>1.67</v>
       </c>
       <c r="W58">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X58">
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z58">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA58">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB58">
         <v>2.7</v>
       </c>
       <c r="AC58">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="AD58">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AE58">
         <v>1.25</v>
       </c>
       <c r="AF58">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AG58">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK58">
         <v>1.95</v>
@@ -9935,7 +9935,7 @@
         <v>1.66</v>
       </c>
       <c r="Q59">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="R59">
         <v>2.27</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AK59">
         <v>1.17</v>
@@ -10418,16 +10418,16 @@
         <v>2.3</v>
       </c>
       <c r="O62">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P62">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q62">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R62">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="S62">
         <v>1.18</v>
@@ -10439,37 +10439,37 @@
         <v>1.85</v>
       </c>
       <c r="V62">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="W62">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z62">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
       <c r="AA62">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AB62">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AC62">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AD62">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AE62">
         <v>1.33</v>
       </c>
       <c r="AF62">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG62">
         <v>3.14</v>
@@ -10587,10 +10587,10 @@
         <v>3</v>
       </c>
       <c r="Q63">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="R63">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="S63">
         <v>1.5</v>
@@ -10614,7 +10614,7 @@
         <v>1.42</v>
       </c>
       <c r="Z63">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AA63">
         <v>2.6</v>
@@ -10623,19 +10623,19 @@
         <v>1.47</v>
       </c>
       <c r="AC63">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AD63">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE63">
         <v>1</v>
       </c>
       <c r="AF63">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AG63">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK63">
         <v>1.5</v>
@@ -10958,7 +10958,7 @@
         <v>1.01</v>
       </c>
       <c r="AF65">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AG65">
         <v>1.6</v>
@@ -11236,7 +11236,7 @@
         <v>4.3</v>
       </c>
       <c r="P67">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Q67">
         <v>2</v>
@@ -11260,7 +11260,7 @@
         <v>1.12</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
         <v>1.2</v>
@@ -11272,7 +11272,7 @@
         <v>1.63</v>
       </c>
       <c r="AB67">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="AC67">
         <v>2.6</v>
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="O68">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P68">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q68">
-        <v>4.03</v>
+        <v>3.72</v>
       </c>
       <c r="R68">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S68">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T68">
         <v>3.3</v>
       </c>
       <c r="U68">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V68">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W68">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X68">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z68">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA68">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB68">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC68">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="AD68">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE68">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF68">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG68">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AK68">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -13521,7 +13521,7 @@
         <v>3.86</v>
       </c>
       <c r="Q81">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="R81">
         <v>2.5</v>
@@ -13533,7 +13533,7 @@
         <v>4</v>
       </c>
       <c r="U81">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="V81">
         <v>1.63</v>
@@ -13554,7 +13554,7 @@
         <v>1.47</v>
       </c>
       <c r="AB81">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AC81">
         <v>2.32</v>
@@ -13696,7 +13696,7 @@
         <v>4</v>
       </c>
       <c r="U82">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="V82">
         <v>1.6</v>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK82">
         <v>2.4</v>
@@ -14010,10 +14010,10 @@
         <v>1.28</v>
       </c>
       <c r="Q84">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="R84">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="S84">
         <v>1.23</v>
@@ -14022,7 +14022,7 @@
         <v>4</v>
       </c>
       <c r="U84">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="V84">
         <v>1.64</v>
@@ -14034,7 +14034,7 @@
         <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z84">
         <v>5.2</v>
@@ -14049,7 +14049,7 @@
         <v>2.2</v>
       </c>
       <c r="AD84">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE84">
         <v>1.25</v>
@@ -15151,7 +15151,7 @@
         <v>2.8</v>
       </c>
       <c r="Q91">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="R91">
         <v>2.24</v>
@@ -15163,10 +15163,10 @@
         <v>2.74</v>
       </c>
       <c r="U91">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="V91">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W91">
         <v>1.05</v>
@@ -15311,7 +15311,7 @@
         <v>3.8</v>
       </c>
       <c r="P92">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="Q92">
         <v>2.55</v>
@@ -15378,7 +15378,7 @@
         <v>1.33</v>
       </c>
       <c r="AK92">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15800,7 +15800,7 @@
         <v>3.75</v>
       </c>
       <c r="P95">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="Q95">
         <v>3.3</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O96">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P96">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q96">
         <v>2.4</v>
@@ -15993,10 +15993,10 @@
         <v>1.21</v>
       </c>
       <c r="Z96">
-        <v>3.84</v>
+        <v>3.55</v>
       </c>
       <c r="AA96">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AB96">
         <v>2.07</v>
@@ -16030,7 +16030,7 @@
         <v>1.2</v>
       </c>
       <c r="AK96">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16123,7 +16123,7 @@
         <v>1.31</v>
       </c>
       <c r="O97">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="P97">
         <v>8.5</v>
@@ -16135,10 +16135,10 @@
         <v>2.6</v>
       </c>
       <c r="S97">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T97">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U97">
         <v>2.3</v>
@@ -16156,13 +16156,13 @@
         <v>1.13</v>
       </c>
       <c r="Z97">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AA97">
         <v>1.54</v>
       </c>
       <c r="AB97">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="AC97">
         <v>2.49</v>
@@ -16177,7 +16177,7 @@
         <v>1.96</v>
       </c>
       <c r="AG97">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
         <v>3.5</v>
       </c>
       <c r="P102">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="Q102">
         <v>3.36</v>
@@ -16953,7 +16953,7 @@
         <v>1.35</v>
       </c>
       <c r="T102">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U102">
         <v>2.44</v>
@@ -16974,7 +16974,7 @@
         <v>3.98</v>
       </c>
       <c r="AA102">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB102">
         <v>2.12</v>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="AK102">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17433,7 +17433,7 @@
         <v>1.89</v>
       </c>
       <c r="Q105">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="R105">
         <v>2.25</v>
@@ -17451,7 +17451,7 @@
         <v>1.41</v>
       </c>
       <c r="W105">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X105">
         <v>1.01</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AK105">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q106">
-        <v>1.87</v>
+        <v>3.3</v>
       </c>
       <c r="R106">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S106">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T106">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="U106">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="V106">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W106">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X106">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z106">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="AA106">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AB106">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AC106">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AD106">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE106">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF106">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="AG106">
-        <v>1.74</v>
+        <v>2.26</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AK106">
-        <v>2.62</v>
+        <v>1.34</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,80 +17750,80 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O107">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P107">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q107">
-        <v>3.3</v>
+        <v>1.91</v>
       </c>
       <c r="R107">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="S107">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T107">
-        <v>3.4</v>
+        <v>3.07</v>
       </c>
       <c r="U107">
-        <v>2.37</v>
+        <v>2.77</v>
       </c>
       <c r="V107">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W107">
+        <v>1.08</v>
+      </c>
+      <c r="X107">
+        <v>1.03</v>
+      </c>
+      <c r="Y107">
+        <v>1.2</v>
+      </c>
+      <c r="Z107">
+        <v>3.72</v>
+      </c>
+      <c r="AA107">
+        <v>1.8</v>
+      </c>
+      <c r="AB107">
+        <v>2</v>
+      </c>
+      <c r="AC107">
+        <v>2.83</v>
+      </c>
+      <c r="AD107">
+        <v>1.33</v>
+      </c>
+      <c r="AE107">
         <v>1.09</v>
       </c>
-      <c r="X107">
-        <v>1.01</v>
-      </c>
-      <c r="Y107">
-        <v>1.16</v>
-      </c>
-      <c r="Z107">
-        <v>4.1</v>
-      </c>
-      <c r="AA107">
-        <v>1.69</v>
-      </c>
-      <c r="AB107">
-        <v>2.11</v>
-      </c>
-      <c r="AC107">
+      <c r="AF107">
+        <v>1.95</v>
+      </c>
+      <c r="AG107">
+        <v>1.76</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ107">
+        <v>1.08</v>
+      </c>
+      <c r="AK107">
         <v>2.62</v>
-      </c>
-      <c r="AD107">
-        <v>1.4</v>
-      </c>
-      <c r="AE107">
-        <v>1.11</v>
-      </c>
-      <c r="AF107">
-        <v>1.57</v>
-      </c>
-      <c r="AG107">
-        <v>2.26</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ107">
-        <v>1.29</v>
-      </c>
-      <c r="AK107">
-        <v>1.34</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -19724,7 +19724,7 @@
         <v>1.37</v>
       </c>
       <c r="T119">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="U119">
         <v>2.75</v>
@@ -19736,7 +19736,7 @@
         <v>1.05</v>
       </c>
       <c r="X119">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y119">
         <v>1.3</v>
@@ -19869,7 +19869,7 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="O120">
         <v>6.9</v>
@@ -19905,7 +19905,7 @@
         <v>1.14</v>
       </c>
       <c r="Z120">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="AA120">
         <v>1.38</v>
@@ -19914,19 +19914,19 @@
         <v>2.62</v>
       </c>
       <c r="AC120">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AD120">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE120">
         <v>1.23</v>
       </c>
       <c r="AF120">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AG120">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -20693,10 +20693,10 @@
         <v>1.14</v>
       </c>
       <c r="Q125">
-        <v>11.25</v>
+        <v>11</v>
       </c>
       <c r="R125">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="S125">
         <v>1.14</v>
@@ -20717,10 +20717,10 @@
         <v>1.01</v>
       </c>
       <c r="Y125">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z125">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="AA125">
         <v>1.3</v>
@@ -20735,7 +20735,7 @@
         <v>1.95</v>
       </c>
       <c r="AE125">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AF125">
         <v>1.92</v>
@@ -21834,10 +21834,10 @@
         <v>0</v>
       </c>
       <c r="Q132">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="R132">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="S132">
         <v>1.25</v>
@@ -21846,37 +21846,37 @@
         <v>3.5</v>
       </c>
       <c r="U132">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V132">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W132">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X132">
         <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z132">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="AA132">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AB132">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC132">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AD132">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE132">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF132">
         <v>1.94</v>
@@ -21895,7 +21895,7 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="AK132">
         <v>1.06</v>
@@ -22154,22 +22154,22 @@
         <v>2.6</v>
       </c>
       <c r="O134">
-        <v>3.3</v>
+        <v>3.07</v>
       </c>
       <c r="P134">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="Q134">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R134">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="S134">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T134">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="U134">
         <v>2.75</v>
@@ -22184,31 +22184,31 @@
         <v>1.01</v>
       </c>
       <c r="Y134">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z134">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA134">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB134">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC134">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AD134">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE134">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF134">
         <v>1.73</v>
       </c>
       <c r="AG134">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>1.3</v>
       </c>
       <c r="AK134">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22323,10 +22323,10 @@
         <v>1.91</v>
       </c>
       <c r="Q135">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R135">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="S135">
         <v>1.22</v>
@@ -22341,7 +22341,7 @@
         <v>1.67</v>
       </c>
       <c r="W135">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X135">
         <v>1.01</v>
@@ -22350,7 +22350,7 @@
         <v>1.1</v>
       </c>
       <c r="Z135">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="AA135">
         <v>1.4</v>
@@ -22384,7 +22384,7 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK135">
         <v>1.25</v>
@@ -22649,49 +22649,49 @@
         <v>0</v>
       </c>
       <c r="Q137">
-        <v>4.26</v>
+        <v>4.04</v>
       </c>
       <c r="R137">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="S137">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T137">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="U137">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V137">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W137">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X137">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y137">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z137">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="AA137">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AB137">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AC137">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="AD137">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AE137">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF137">
         <v>1.56</v>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AK137">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22803,19 +22803,19 @@
         </is>
       </c>
       <c r="N138">
+        <v>2.51</v>
+      </c>
+      <c r="O138">
+        <v>3.8</v>
+      </c>
+      <c r="P138">
         <v>2.3</v>
       </c>
-      <c r="O138">
-        <v>3.86</v>
-      </c>
-      <c r="P138">
-        <v>2.62</v>
-      </c>
       <c r="Q138">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="R138">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="S138">
         <v>1.2</v>
@@ -22824,13 +22824,13 @@
         <v>4</v>
       </c>
       <c r="U138">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V138">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W138">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X138">
         <v>1.01</v>
@@ -22839,28 +22839,28 @@
         <v>1.07</v>
       </c>
       <c r="Z138">
-        <v>5.9</v>
+        <v>5.95</v>
       </c>
       <c r="AA138">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB138">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="AC138">
         <v>1.9</v>
       </c>
       <c r="AD138">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AE138">
         <v>1.3</v>
       </c>
       <c r="AF138">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AG138">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AK138">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="O139">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P139">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q139">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R139">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S139">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T139">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U139">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V139">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W139">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X139">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y139">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z139">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="AA139">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB139">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC139">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD139">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE139">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF139">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG139">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK139">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23129,7 +23129,7 @@
         </is>
       </c>
       <c r="N140">
-        <v>8.5</v>
+        <v>8.25</v>
       </c>
       <c r="O140">
         <v>5.25</v>
@@ -23144,7 +23144,7 @@
         <v>2.63</v>
       </c>
       <c r="S140">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T140">
         <v>3.8</v>
@@ -23159,7 +23159,7 @@
         <v>1.15</v>
       </c>
       <c r="X140">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y140">
         <v>1.13</v>
@@ -23292,19 +23292,19 @@
         </is>
       </c>
       <c r="N141">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="O141">
         <v>3.6</v>
       </c>
       <c r="P141">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="Q141">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R141">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S141">
         <v>1.29</v>
@@ -23313,43 +23313,43 @@
         <v>3.3</v>
       </c>
       <c r="U141">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="V141">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W141">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X141">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y141">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z141">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AA141">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AB141">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AC141">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="AD141">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AE141">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF141">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG141">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>1.28</v>
       </c>
       <c r="AK141">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23461,7 +23461,7 @@
         <v>3.3</v>
       </c>
       <c r="P142">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="Q142">
         <v>2.53</v>
@@ -23528,7 +23528,7 @@
         <v>1.31</v>
       </c>
       <c r="AK142">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23639,7 +23639,7 @@
         <v>2.94</v>
       </c>
       <c r="U143">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V143">
         <v>1.41</v>
@@ -25604,7 +25604,7 @@
         <v>1.12</v>
       </c>
       <c r="X155">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y155">
         <v>1.15</v>
@@ -25613,10 +25613,10 @@
         <v>4.25</v>
       </c>
       <c r="AA155">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB155">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AC155">
         <v>2.5</v>
@@ -25767,10 +25767,10 @@
         <v>1.12</v>
       </c>
       <c r="X156">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y156">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z156">
         <v>4.3</v>
@@ -25930,13 +25930,13 @@
         <v>1.12</v>
       </c>
       <c r="X157">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y157">
         <v>1.17</v>
       </c>
       <c r="Z157">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AA157">
         <v>1.64</v>
@@ -25970,7 +25970,7 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK157">
         <v>1.81</v>
@@ -26136,7 +26136,7 @@
         <v>1.16</v>
       </c>
       <c r="AK158">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O163">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P163">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q163">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R163">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S163">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T163">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U163">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V163">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W163">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X163">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y163">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z163">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA163">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB163">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC163">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD163">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE163">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF163">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG163">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK163">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27249,16 +27249,16 @@
         <v>1.89</v>
       </c>
       <c r="AC165">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="AD165">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE165">
         <v>1.08</v>
       </c>
       <c r="AF165">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG165">
         <v>2</v>
@@ -27277,7 +27277,7 @@
         <v>1.27</v>
       </c>
       <c r="AK165">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27373,7 +27373,7 @@
         <v>4</v>
       </c>
       <c r="P166">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="Q166">
         <v>2.03</v>
@@ -27385,46 +27385,46 @@
         <v>1.2</v>
       </c>
       <c r="T166">
-        <v>3.88</v>
+        <v>3.98</v>
       </c>
       <c r="U166">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="V166">
         <v>1.73</v>
       </c>
       <c r="W166">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X166">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y166">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z166">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA166">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AB166">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AC166">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="AD166">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AE166">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF166">
         <v>1.4</v>
       </c>
       <c r="AG166">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK166">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,80 +27856,80 @@
         </is>
       </c>
       <c r="N169">
+        <v>1.68</v>
+      </c>
+      <c r="O169">
+        <v>4.2</v>
+      </c>
+      <c r="P169">
+        <v>3.85</v>
+      </c>
+      <c r="Q169">
+        <v>2.17</v>
+      </c>
+      <c r="R169">
+        <v>2.52</v>
+      </c>
+      <c r="S169">
+        <v>1.17</v>
+      </c>
+      <c r="T169">
+        <v>4.5</v>
+      </c>
+      <c r="U169">
+        <v>1.89</v>
+      </c>
+      <c r="V169">
+        <v>1.83</v>
+      </c>
+      <c r="W169">
+        <v>1.22</v>
+      </c>
+      <c r="X169">
+        <v>1.01</v>
+      </c>
+      <c r="Y169">
+        <v>1.06</v>
+      </c>
+      <c r="Z169">
+        <v>6.25</v>
+      </c>
+      <c r="AA169">
+        <v>1.32</v>
+      </c>
+      <c r="AB169">
+        <v>2.88</v>
+      </c>
+      <c r="AC169">
+        <v>1.89</v>
+      </c>
+      <c r="AD169">
+        <v>1.84</v>
+      </c>
+      <c r="AE169">
         <v>1.37</v>
       </c>
-      <c r="O169">
-        <v>5.2</v>
-      </c>
-      <c r="P169">
-        <v>5.6</v>
-      </c>
-      <c r="Q169">
-        <v>1.75</v>
-      </c>
-      <c r="R169">
-        <v>2.86</v>
-      </c>
-      <c r="S169">
-        <v>1.13</v>
-      </c>
-      <c r="T169">
-        <v>5.45</v>
-      </c>
-      <c r="U169">
-        <v>1.67</v>
-      </c>
-      <c r="V169">
+      <c r="AF169">
+        <v>1.37</v>
+      </c>
+      <c r="AG169">
+        <v>2.8</v>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ169">
+        <v>1.2</v>
+      </c>
+      <c r="AK169">
         <v>2.03</v>
-      </c>
-      <c r="W169">
-        <v>1.3</v>
-      </c>
-      <c r="X169">
-        <v>1</v>
-      </c>
-      <c r="Y169">
-        <v>1.02</v>
-      </c>
-      <c r="Z169">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA169">
-        <v>1.24</v>
-      </c>
-      <c r="AB169">
-        <v>3.7</v>
-      </c>
-      <c r="AC169">
-        <v>1.63</v>
-      </c>
-      <c r="AD169">
-        <v>2.19</v>
-      </c>
-      <c r="AE169">
-        <v>1.49</v>
-      </c>
-      <c r="AF169">
-        <v>1.36</v>
-      </c>
-      <c r="AG169">
-        <v>2.9</v>
-      </c>
-      <c r="AH169" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI169" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ169">
-        <v>1.11</v>
-      </c>
-      <c r="AK169">
-        <v>2.67</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.68</v>
+        <v>1.37</v>
       </c>
       <c r="O170">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="P170">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="Q170">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="R170">
-        <v>2.49</v>
+        <v>2.86</v>
       </c>
       <c r="S170">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T170">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="U170">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="V170">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="W170">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X170">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y170">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Z170">
-        <v>6.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA170">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AB170">
-        <v>2.92</v>
+        <v>3.7</v>
       </c>
       <c r="AC170">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AD170">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AE170">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AF170">
         <v>1.36</v>
       </c>
       <c r="AG170">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK170">
-        <v>2.02</v>
+        <v>2.67</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28182,7 +28182,7 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="O171">
         <v>4</v>
@@ -28233,7 +28233,7 @@
         <v>2.21</v>
       </c>
       <c r="AE171">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF171">
         <v>1.26</v>
@@ -28348,16 +28348,16 @@
         <v>7</v>
       </c>
       <c r="O172">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="P172">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Q172">
         <v>5.22</v>
       </c>
       <c r="R172">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="S172">
         <v>1.14</v>
@@ -28381,7 +28381,7 @@
         <v>1.04</v>
       </c>
       <c r="Z172">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="AA172">
         <v>1.25</v>
@@ -28390,10 +28390,10 @@
         <v>3.28</v>
       </c>
       <c r="AC172">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AD172">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AE172">
         <v>1.47</v>
@@ -28544,7 +28544,7 @@
         <v>1.01</v>
       </c>
       <c r="Z173">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA173">
         <v>1.19</v>
@@ -28553,13 +28553,13 @@
         <v>4.2</v>
       </c>
       <c r="AC173">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AD173">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="AE173">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AF173">
         <v>1.44</v>
@@ -28695,7 +28695,7 @@
         <v>1.74</v>
       </c>
       <c r="V174">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="W174">
         <v>1.28</v>
@@ -28840,7 +28840,7 @@
         <v>3.55</v>
       </c>
       <c r="P175">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="Q175">
         <v>2.42</v>
@@ -28879,7 +28879,7 @@
         <v>2.46</v>
       </c>
       <c r="AC175">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AD175">
         <v>1.65</v>
@@ -29160,25 +29160,25 @@
         </is>
       </c>
       <c r="N177">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="O177">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="P177">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="Q177">
-        <v>4.25</v>
+        <v>4.26</v>
       </c>
       <c r="R177">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S177">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T177">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U177">
         <v>2.83</v>
@@ -29187,7 +29187,7 @@
         <v>1.41</v>
       </c>
       <c r="W177">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X177">
         <v>1.01</v>
@@ -29199,10 +29199,10 @@
         <v>3.2</v>
       </c>
       <c r="AA177">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB177">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC177">
         <v>3.14</v>
@@ -29217,7 +29217,7 @@
         <v>1.73</v>
       </c>
       <c r="AG177">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AK177">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29486,34 +29486,34 @@
         </is>
       </c>
       <c r="N179">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O179">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P179">
         <v>1.95</v>
       </c>
       <c r="Q179">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="R179">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="S179">
         <v>1.25</v>
       </c>
       <c r="T179">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U179">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="V179">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W179">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X179">
         <v>1.02</v>
@@ -29528,19 +29528,19 @@
         <v>1.64</v>
       </c>
       <c r="AB179">
-        <v>2.37</v>
+        <v>2.46</v>
       </c>
       <c r="AC179">
         <v>2.45</v>
       </c>
       <c r="AD179">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AE179">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF179">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AG179">
         <v>2.48</v>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK179">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29975,31 +29975,31 @@
         </is>
       </c>
       <c r="N182">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="O182">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P182">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q182">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="R182">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="S182">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T182">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="U182">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="V182">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W182">
         <v>1.11</v>
@@ -30008,31 +30008,31 @@
         <v>1.01</v>
       </c>
       <c r="Y182">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z182">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="AA182">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AB182">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AC182">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="AD182">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE182">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF182">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG182">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK182">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30301,25 +30301,25 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="O184">
-        <v>3.38</v>
+        <v>3.55</v>
       </c>
       <c r="P184">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="Q184">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="R184">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="S184">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T184">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="U184">
         <v>2.52</v>
@@ -30328,7 +30328,7 @@
         <v>1.44</v>
       </c>
       <c r="W184">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X184">
         <v>1.02</v>
@@ -30340,10 +30340,10 @@
         <v>4.22</v>
       </c>
       <c r="AA184">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB184">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC184">
         <v>2.69</v>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK184">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -31279,64 +31279,64 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="O190">
         <v>3.85</v>
       </c>
       <c r="P190">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q190">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R190">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="S190">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T190">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="U190">
         <v>2.4</v>
       </c>
       <c r="V190">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W190">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X190">
         <v>1.01</v>
       </c>
       <c r="Y190">
+        <v>1.15</v>
+      </c>
+      <c r="Z190">
+        <v>4.44</v>
+      </c>
+      <c r="AA190">
+        <v>1.66</v>
+      </c>
+      <c r="AB190">
+        <v>2.25</v>
+      </c>
+      <c r="AC190">
+        <v>2.38</v>
+      </c>
+      <c r="AD190">
+        <v>1.46</v>
+      </c>
+      <c r="AE190">
         <v>1.16</v>
       </c>
-      <c r="Z190">
-        <v>4.15</v>
-      </c>
-      <c r="AA190">
+      <c r="AF190">
         <v>1.61</v>
       </c>
-      <c r="AB190">
-        <v>2.21</v>
-      </c>
-      <c r="AC190">
-        <v>2.43</v>
-      </c>
-      <c r="AD190">
-        <v>1.44</v>
-      </c>
-      <c r="AE190">
-        <v>1.15</v>
-      </c>
-      <c r="AF190">
-        <v>1.63</v>
-      </c>
       <c r="AG190">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK190">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31940,25 +31940,25 @@
         <v>5</v>
       </c>
       <c r="Q194">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="R194">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="S194">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T194">
         <v>4.2</v>
       </c>
       <c r="U194">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="V194">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="W194">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X194">
         <v>1</v>
@@ -31970,7 +31970,7 @@
         <v>6.4</v>
       </c>
       <c r="AA194">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AB194">
         <v>3</v>
@@ -31985,10 +31985,10 @@
         <v>1.32</v>
       </c>
       <c r="AF194">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG194">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK194">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32100,19 +32100,19 @@
         <v>3.7</v>
       </c>
       <c r="P195">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="Q195">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="R195">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="S195">
         <v>1.18</v>
       </c>
       <c r="T195">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="U195">
         <v>1.92</v>
@@ -32127,16 +32127,16 @@
         <v>1.01</v>
       </c>
       <c r="Y195">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z195">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="AA195">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AB195">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AC195">
         <v>1.88</v>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK195">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32257,25 +32257,25 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="O196">
-        <v>4.13</v>
+        <v>4</v>
       </c>
       <c r="P196">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="Q196">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="R196">
         <v>2.8</v>
       </c>
       <c r="S196">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="T196">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="U196">
         <v>1.8</v>
@@ -32293,22 +32293,22 @@
         <v>1.03</v>
       </c>
       <c r="Z196">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="AA196">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AB196">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AC196">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AD196">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AE196">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AF196">
         <v>1.27</v>
@@ -32327,7 +32327,7 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK196">
         <v>1.63</v>
@@ -32420,22 +32420,22 @@
         </is>
       </c>
       <c r="N197">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="O197">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="P197">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="Q197">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="R197">
-        <v>2.69</v>
+        <v>2.47</v>
       </c>
       <c r="S197">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T197">
         <v>4.25</v>
@@ -32468,13 +32468,13 @@
         <v>1.84</v>
       </c>
       <c r="AD197">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AE197">
         <v>1.4</v>
       </c>
       <c r="AF197">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AG197">
         <v>3.14</v>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK197">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32583,10 +32583,10 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="O198">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P198">
         <v>2.7</v>
@@ -32595,7 +32595,7 @@
         <v>2.5</v>
       </c>
       <c r="R198">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="S198">
         <v>1.13</v>
@@ -32604,7 +32604,7 @@
         <v>4.6</v>
       </c>
       <c r="U198">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="V198">
         <v>1.84</v>
@@ -32619,10 +32619,10 @@
         <v>1.05</v>
       </c>
       <c r="Z198">
-        <v>6.65</v>
+        <v>6.7</v>
       </c>
       <c r="AA198">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB198">
         <v>2.97</v>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AK198">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -34385,49 +34385,49 @@
         <v>0</v>
       </c>
       <c r="Q209">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="R209">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="S209">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T209">
         <v>3.4</v>
       </c>
       <c r="U209">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V209">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W209">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X209">
         <v>1.03</v>
       </c>
       <c r="Y209">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z209">
-        <v>4.65</v>
+        <v>4.45</v>
       </c>
       <c r="AA209">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AB209">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="AC209">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AD209">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AE209">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF209">
         <v>1.85</v>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK209">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34545,25 +34545,25 @@
         <v>2.85</v>
       </c>
       <c r="P210">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="Q210">
         <v>2.5</v>
       </c>
       <c r="R210">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S210">
         <v>1.4</v>
       </c>
       <c r="T210">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="U210">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="V210">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W210">
         <v>1.04</v>
@@ -34572,16 +34572,16 @@
         <v>1.04</v>
       </c>
       <c r="Y210">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z210">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA210">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AB210">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AC210">
         <v>3.9</v>
@@ -34590,10 +34590,10 @@
         <v>1.25</v>
       </c>
       <c r="AE210">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF210">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG210">
         <v>1.8</v>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK210">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -35037,7 +35037,7 @@
         <v>0</v>
       </c>
       <c r="Q213">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="R213">
         <v>2.08</v>
@@ -35049,7 +35049,7 @@
         <v>2.88</v>
       </c>
       <c r="U213">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V213">
         <v>1.4</v>
@@ -35073,7 +35073,7 @@
         <v>1.83</v>
       </c>
       <c r="AC213">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="AD213">
         <v>1.32</v>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK213">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35224,25 +35224,25 @@
         <v>1.02</v>
       </c>
       <c r="Y214">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z214">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="AA214">
         <v>1.53</v>
       </c>
       <c r="AB214">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC214">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AD214">
         <v>1.65</v>
       </c>
       <c r="AE214">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF214">
         <v>1.65</v>
@@ -35264,7 +35264,7 @@
         <v>1.22</v>
       </c>
       <c r="AK214">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35843,10 +35843,10 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="O218">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P218">
         <v>2.95</v>
@@ -35867,7 +35867,7 @@
         <v>2.45</v>
       </c>
       <c r="V218">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W218">
         <v>1.07</v>
@@ -35882,22 +35882,22 @@
         <v>3.58</v>
       </c>
       <c r="AA218">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AB218">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC218">
         <v>2.69</v>
       </c>
       <c r="AD218">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE218">
         <v>1.11</v>
       </c>
       <c r="AF218">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG218">
         <v>2.25</v>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AK218">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36006,34 +36006,34 @@
         </is>
       </c>
       <c r="N219">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="O219">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="P219">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="Q219">
         <v>4</v>
       </c>
       <c r="R219">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="S219">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T219">
-        <v>3.02</v>
+        <v>3.12</v>
       </c>
       <c r="U219">
         <v>2.4</v>
       </c>
       <c r="V219">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W219">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X219">
         <v>1.01</v>
@@ -36042,28 +36042,28 @@
         <v>1.18</v>
       </c>
       <c r="Z219">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="AA219">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AB219">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC219">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD219">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE219">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF219">
         <v>1.62</v>
       </c>
       <c r="AG219">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.94</v>
+        <v>1.28</v>
       </c>
       <c r="AK219">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36193,7 +36193,7 @@
         <v>1.95</v>
       </c>
       <c r="V220">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W220">
         <v>1.17</v>
@@ -36211,7 +36211,7 @@
         <v>1.33</v>
       </c>
       <c r="AB220">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AC220">
         <v>1.81</v>
@@ -37156,19 +37156,19 @@
         <v>2.1</v>
       </c>
       <c r="Q226">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="R226">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S226">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T226">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U226">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V226">
         <v>1.29</v>
@@ -37177,34 +37177,34 @@
         <v>1.03</v>
       </c>
       <c r="X226">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y226">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Z226">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="AA226">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AB226">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AC226">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AD226">
         <v>1.14</v>
       </c>
       <c r="AE226">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF226">
         <v>2</v>
       </c>
       <c r="AG226">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AK226">
         <v>1.22</v>
@@ -37313,13 +37313,13 @@
         <v>1.8</v>
       </c>
       <c r="O227">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P227">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="Q227">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R227">
         <v>2.15</v>
@@ -37328,13 +37328,13 @@
         <v>1.38</v>
       </c>
       <c r="T227">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="U227">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="V227">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W227">
         <v>1.05</v>
@@ -37343,22 +37343,22 @@
         <v>1.01</v>
       </c>
       <c r="Y227">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z227">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA227">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB227">
         <v>1.85</v>
       </c>
       <c r="AC227">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AD227">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE227">
         <v>1.07</v>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK227">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -38457,7 +38457,7 @@
         <v>3.65</v>
       </c>
       <c r="P234">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q234">
         <v>2.4</v>
@@ -38466,10 +38466,10 @@
         <v>2.2</v>
       </c>
       <c r="S234">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T234">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U234">
         <v>2.51</v>
@@ -38481,19 +38481,19 @@
         <v>1.08</v>
       </c>
       <c r="X234">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y234">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z234">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AA234">
         <v>1.93</v>
       </c>
       <c r="AB234">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AC234">
         <v>3.05</v>
@@ -38505,10 +38505,10 @@
         <v>1.08</v>
       </c>
       <c r="AF234">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG234">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AK234">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38946,28 +38946,28 @@
         <v>3.9</v>
       </c>
       <c r="P237">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="Q237">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="R237">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S237">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T237">
         <v>3.46</v>
       </c>
       <c r="U237">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="V237">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W237">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X237">
         <v>1.03</v>
@@ -38976,28 +38976,28 @@
         <v>1.14</v>
       </c>
       <c r="Z237">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA237">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB237">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AC237">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AD237">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE237">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF237">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG237">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>1.17</v>
+        <v>1.87</v>
       </c>
       <c r="AK237">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39103,64 +39103,64 @@
         </is>
       </c>
       <c r="N238">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="O238">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P238">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q238">
-        <v>3.82</v>
+        <v>3.64</v>
       </c>
       <c r="R238">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S238">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T238">
-        <v>3.3</v>
+        <v>3.17</v>
       </c>
       <c r="U238">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="V238">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W238">
+        <v>1.11</v>
+      </c>
+      <c r="X238">
+        <v>1</v>
+      </c>
+      <c r="Y238">
+        <v>1.21</v>
+      </c>
+      <c r="Z238">
+        <v>3.58</v>
+      </c>
+      <c r="AA238">
+        <v>1.74</v>
+      </c>
+      <c r="AB238">
+        <v>1.94</v>
+      </c>
+      <c r="AC238">
+        <v>2.81</v>
+      </c>
+      <c r="AD238">
+        <v>1.33</v>
+      </c>
+      <c r="AE238">
         <v>1.1</v>
       </c>
-      <c r="X238">
-        <v>1.01</v>
-      </c>
-      <c r="Y238">
-        <v>1.14</v>
-      </c>
-      <c r="Z238">
-        <v>4.45</v>
-      </c>
-      <c r="AA238">
-        <v>1.55</v>
-      </c>
-      <c r="AB238">
-        <v>2.24</v>
-      </c>
-      <c r="AC238">
-        <v>2.35</v>
-      </c>
-      <c r="AD238">
-        <v>1.47</v>
-      </c>
-      <c r="AE238">
-        <v>1.16</v>
-      </c>
       <c r="AF238">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG238">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AK238">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39776,13 +39776,13 @@
         <v>2.63</v>
       </c>
       <c r="U242">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V242">
         <v>1.3</v>
       </c>
       <c r="W242">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X242">
         <v>1.05</v>
@@ -39794,7 +39794,7 @@
         <v>2.66</v>
       </c>
       <c r="AA242">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB242">
         <v>1.57</v>
@@ -39988,10 +39988,10 @@
         </is>
       </c>
       <c r="AJ243">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK243">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -40896,43 +40896,43 @@
         </is>
       </c>
       <c r="N249">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="O249">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="P249">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q249">
         <v>1.55</v>
       </c>
       <c r="R249">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="S249">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T249">
         <v>4.55</v>
       </c>
       <c r="U249">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="V249">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="W249">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X249">
         <v>1.01</v>
       </c>
       <c r="Y249">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z249">
-        <v>6.35</v>
+        <v>6.4</v>
       </c>
       <c r="AA249">
         <v>1.3</v>
@@ -40941,19 +40941,19 @@
         <v>2.97</v>
       </c>
       <c r="AC249">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AD249">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AE249">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF249">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG249">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>1.06</v>
       </c>
       <c r="AK249">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AL249">
         <v>0</v>
@@ -41068,55 +41068,55 @@
         <v>3.25</v>
       </c>
       <c r="Q250">
+        <v>2.64</v>
+      </c>
+      <c r="R250">
+        <v>2.1</v>
+      </c>
+      <c r="S250">
+        <v>1.33</v>
+      </c>
+      <c r="T250">
+        <v>3.19</v>
+      </c>
+      <c r="U250">
         <v>2.66</v>
       </c>
-      <c r="R250">
-        <v>2.11</v>
-      </c>
-      <c r="S250">
-        <v>1.32</v>
-      </c>
-      <c r="T250">
-        <v>3.26</v>
-      </c>
-      <c r="U250">
-        <v>2.6</v>
-      </c>
       <c r="V250">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W250">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X250">
         <v>1.02</v>
       </c>
       <c r="Y250">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z250">
-        <v>3.82</v>
+        <v>3.74</v>
       </c>
       <c r="AA250">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB250">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC250">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AD250">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE250">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF250">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG250">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41129,10 +41129,10 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK250">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41222,64 +41222,64 @@
         </is>
       </c>
       <c r="N251">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O251">
-        <v>5.75</v>
+        <v>5.1</v>
       </c>
       <c r="P251">
-        <v>8.9</v>
+        <v>7</v>
       </c>
       <c r="Q251">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="R251">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="S251">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T251">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="U251">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V251">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="W251">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X251">
         <v>1.01</v>
       </c>
       <c r="Y251">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z251">
-        <v>6.42</v>
+        <v>6.57</v>
       </c>
       <c r="AA251">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB251">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AC251">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AD251">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AE251">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF251">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG251">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41295,7 +41295,7 @@
         <v>1.05</v>
       </c>
       <c r="AK251">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -42037,64 +42037,64 @@
         </is>
       </c>
       <c r="N256">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="O256">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="P256">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="Q256">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R256">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S256">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T256">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U256">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V256">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W256">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X256">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y256">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z256">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA256">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB256">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC256">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD256">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE256">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF256">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG256">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42107,10 +42107,10 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK256">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42695,28 +42695,28 @@
         <v>4.9</v>
       </c>
       <c r="P260">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q260">
         <v>5.75</v>
       </c>
       <c r="R260">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="S260">
         <v>1.2</v>
       </c>
       <c r="T260">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="U260">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="V260">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="W260">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X260">
         <v>1.01</v>
@@ -42725,28 +42725,28 @@
         <v>1.06</v>
       </c>
       <c r="Z260">
-        <v>6.35</v>
+        <v>6.3</v>
       </c>
       <c r="AA260">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB260">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AC260">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AD260">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AE260">
         <v>1.32</v>
       </c>
       <c r="AF260">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG260">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>3.18</v>
       </c>
       <c r="V266">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W266">
         <v>1.03</v>
@@ -43703,19 +43703,19 @@
         <v>1.4</v>
       </c>
       <c r="Z266">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="AA266">
         <v>2.27</v>
       </c>
       <c r="AB266">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AC266">
         <v>3.9</v>
       </c>
       <c r="AD266">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE266">
         <v>1.02</v>
@@ -43724,7 +43724,7 @@
         <v>2.05</v>
       </c>
       <c r="AG266">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -43737,7 +43737,7 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AK266">
         <v>1.82</v>
@@ -44044,7 +44044,7 @@
         <v>1.34</v>
       </c>
       <c r="AE268">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF268">
         <v>1.69</v>
@@ -44494,13 +44494,13 @@
         <v>2.9</v>
       </c>
       <c r="R271">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="S271">
         <v>1.36</v>
       </c>
       <c r="T271">
-        <v>3.11</v>
+        <v>2.82</v>
       </c>
       <c r="U271">
         <v>2.76</v>
@@ -44524,7 +44524,7 @@
         <v>1.8</v>
       </c>
       <c r="AB271">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC271">
         <v>3.13</v>
@@ -46275,64 +46275,64 @@
         </is>
       </c>
       <c r="N282">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="O282">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="P282">
+        <v>3</v>
+      </c>
+      <c r="Q282">
+        <v>2.98</v>
+      </c>
+      <c r="R282">
+        <v>2.02</v>
+      </c>
+      <c r="S282">
+        <v>1.44</v>
+      </c>
+      <c r="T282">
+        <v>2.4</v>
+      </c>
+      <c r="U282">
         <v>3.06</v>
       </c>
-      <c r="Q282">
-        <v>0</v>
-      </c>
-      <c r="R282">
-        <v>0</v>
-      </c>
-      <c r="S282">
-        <v>0</v>
-      </c>
-      <c r="T282">
-        <v>0</v>
-      </c>
-      <c r="U282">
-        <v>0</v>
-      </c>
       <c r="V282">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W282">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X282">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y282">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z282">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA282">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB282">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC282">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="AD282">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE282">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF282">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG282">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH282" t="inlineStr">
         <is>
@@ -46345,10 +46345,10 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK282">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -46447,7 +46447,7 @@
         <v>0</v>
       </c>
       <c r="Q283">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="R283">
         <v>2.62</v>
@@ -47102,7 +47102,7 @@
         <v>3.91</v>
       </c>
       <c r="R287">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="S287">
         <v>1.51</v>
@@ -47135,7 +47135,7 @@
         <v>1.56</v>
       </c>
       <c r="AC287">
-        <v>4.15</v>
+        <v>4.75</v>
       </c>
       <c r="AD287">
         <v>1.16</v>
@@ -47147,7 +47147,7 @@
         <v>1.95</v>
       </c>
       <c r="AG287">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47588,55 +47588,55 @@
         <v>0</v>
       </c>
       <c r="Q290">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R290">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S290">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T290">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U290">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V290">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W290">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X290">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y290">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z290">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA290">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB290">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC290">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD290">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE290">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF290">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG290">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK290">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47751,55 +47751,55 @@
         <v>0</v>
       </c>
       <c r="Q291">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R291">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S291">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T291">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U291">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V291">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W291">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X291">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y291">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z291">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA291">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB291">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC291">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD291">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE291">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF291">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG291">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK291">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -48068,64 +48068,64 @@
         </is>
       </c>
       <c r="N293">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="O293">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P293">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q293">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R293">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S293">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T293">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U293">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V293">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W293">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X293">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y293">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z293">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA293">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB293">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC293">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD293">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE293">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF293">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG293">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK293">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL293">
         <v>0</v>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU293"/>
+  <dimension ref="A1:AU291"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="O2">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="P2">
-        <v>3.35</v>
+        <v>7.3</v>
       </c>
       <c r="Q2">
-        <v>2.73</v>
+        <v>1.8</v>
       </c>
       <c r="R2">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="S2">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="U2">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="Z2">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="AA2">
-        <v>2.08</v>
+        <v>1.64</v>
       </c>
       <c r="AB2">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="AC2">
-        <v>3.84</v>
+        <v>2.52</v>
       </c>
       <c r="AD2">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AE2">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AF2">
         <v>1.84</v>
       </c>
       <c r="AG2">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AK2">
-        <v>1.7</v>
+        <v>2.88</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.36</v>
+        <v>2.11</v>
       </c>
       <c r="O3">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="P3">
-        <v>7.3</v>
+        <v>2.94</v>
       </c>
       <c r="Q3">
-        <v>1.8</v>
+        <v>2.71</v>
       </c>
       <c r="R3">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="U3">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="V3">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="Z3">
-        <v>4.2</v>
+        <v>2.92</v>
       </c>
       <c r="AA3">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="AB3">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="AC3">
-        <v>2.52</v>
+        <v>3.84</v>
       </c>
       <c r="AD3">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AE3">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
         <v>1.84</v>
       </c>
       <c r="AG3">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>2.88</v>
+        <v>1.7</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -985,10 +985,10 @@
         <v>2.8</v>
       </c>
       <c r="V4">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
         <v>1.02</v>
@@ -1009,7 +1009,7 @@
         <v>3.28</v>
       </c>
       <c r="AD4">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE4">
         <v>1.1</v>
@@ -1157,7 +1157,7 @@
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z5">
         <v>3.2</v>
@@ -1175,7 +1175,7 @@
         <v>1.24</v>
       </c>
       <c r="AE5">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF5">
         <v>1.75</v>
@@ -1197,7 +1197,7 @@
         <v>1.33</v>
       </c>
       <c r="AK5">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -3774,13 +3774,13 @@
         <v>2.05</v>
       </c>
       <c r="AB21">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC21">
         <v>3.42</v>
       </c>
       <c r="AD21">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE21">
         <v>1.04</v>
@@ -4103,7 +4103,7 @@
         <v>1.69</v>
       </c>
       <c r="AC23">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AD23">
         <v>1.23</v>
@@ -4131,7 +4131,7 @@
         <v>1.4</v>
       </c>
       <c r="AK23">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4239,7 +4239,7 @@
         <v>1.4</v>
       </c>
       <c r="T24">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="U24">
         <v>2.8</v>
@@ -4257,7 +4257,7 @@
         <v>1.31</v>
       </c>
       <c r="Z24">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA24">
         <v>2.07</v>
@@ -4275,7 +4275,7 @@
         <v>1.05</v>
       </c>
       <c r="AF24">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG24">
         <v>1.95</v>
@@ -7819,7 +7819,7 @@
         <v>3.75</v>
       </c>
       <c r="R46">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S46">
         <v>1.29</v>
@@ -7837,10 +7837,10 @@
         <v>1.07</v>
       </c>
       <c r="X46">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z46">
         <v>4.21</v>
@@ -7864,7 +7864,7 @@
         <v>1.6</v>
       </c>
       <c r="AG46">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
         <v>1.3</v>
@@ -8842,7 +8842,7 @@
         <v>1.82</v>
       </c>
       <c r="AG52">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="N74">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="O74">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P74">
         <v>1.49</v>
@@ -12383,7 +12383,7 @@
         <v>5.42</v>
       </c>
       <c r="R74">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S74">
         <v>1.4</v>
@@ -12419,16 +12419,16 @@
         <v>3.5</v>
       </c>
       <c r="AD74">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE74">
         <v>1.04</v>
       </c>
       <c r="AF74">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AG74">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK74">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="O96">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="P96">
-        <v>4.2</v>
+        <v>8.5</v>
       </c>
       <c r="Q96">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="R96">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="S96">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T96">
-        <v>2.86</v>
+        <v>3.7</v>
       </c>
       <c r="U96">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="V96">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="W96">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X96">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="Z96">
-        <v>3.55</v>
+        <v>4.65</v>
       </c>
       <c r="AA96">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="AB96">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="AC96">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AD96">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AE96">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF96">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="AG96">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AK96">
-        <v>2.04</v>
+        <v>3.64</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.31</v>
+        <v>1.8</v>
       </c>
       <c r="O97">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="P97">
-        <v>8.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q97">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="R97">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="S97">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T97">
-        <v>3.7</v>
+        <v>2.86</v>
       </c>
       <c r="U97">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="V97">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="W97">
+        <v>1.08</v>
+      </c>
+      <c r="X97">
+        <v>1.01</v>
+      </c>
+      <c r="Y97">
+        <v>1.21</v>
+      </c>
+      <c r="Z97">
+        <v>3.55</v>
+      </c>
+      <c r="AA97">
+        <v>1.72</v>
+      </c>
+      <c r="AB97">
+        <v>2.07</v>
+      </c>
+      <c r="AC97">
+        <v>2.66</v>
+      </c>
+      <c r="AD97">
+        <v>1.38</v>
+      </c>
+      <c r="AE97">
         <v>1.11</v>
       </c>
-      <c r="X97">
-        <v>1.02</v>
-      </c>
-      <c r="Y97">
-        <v>1.13</v>
-      </c>
-      <c r="Z97">
-        <v>4.65</v>
-      </c>
-      <c r="AA97">
-        <v>1.54</v>
-      </c>
-      <c r="AB97">
-        <v>2.38</v>
-      </c>
-      <c r="AC97">
-        <v>2.49</v>
-      </c>
-      <c r="AD97">
-        <v>1.55</v>
-      </c>
-      <c r="AE97">
-        <v>1.17</v>
-      </c>
       <c r="AF97">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="AG97">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="AK97">
-        <v>3.64</v>
+        <v>2.04</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,80 +17587,80 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O106">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P106">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q106">
-        <v>3.3</v>
+        <v>1.91</v>
       </c>
       <c r="R106">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="S106">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T106">
-        <v>3.4</v>
+        <v>3.07</v>
       </c>
       <c r="U106">
-        <v>2.61</v>
+        <v>2.77</v>
       </c>
       <c r="V106">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W106">
+        <v>1.08</v>
+      </c>
+      <c r="X106">
+        <v>1.03</v>
+      </c>
+      <c r="Y106">
+        <v>1.2</v>
+      </c>
+      <c r="Z106">
+        <v>3.72</v>
+      </c>
+      <c r="AA106">
+        <v>1.8</v>
+      </c>
+      <c r="AB106">
+        <v>2</v>
+      </c>
+      <c r="AC106">
+        <v>2.83</v>
+      </c>
+      <c r="AD106">
+        <v>1.33</v>
+      </c>
+      <c r="AE106">
         <v>1.09</v>
       </c>
-      <c r="X106">
-        <v>1.01</v>
-      </c>
-      <c r="Y106">
-        <v>1.16</v>
-      </c>
-      <c r="Z106">
-        <v>4.1</v>
-      </c>
-      <c r="AA106">
-        <v>1.69</v>
-      </c>
-      <c r="AB106">
-        <v>2.11</v>
-      </c>
-      <c r="AC106">
+      <c r="AF106">
+        <v>1.95</v>
+      </c>
+      <c r="AG106">
+        <v>1.76</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ106">
+        <v>1.08</v>
+      </c>
+      <c r="AK106">
         <v>2.62</v>
-      </c>
-      <c r="AD106">
-        <v>1.4</v>
-      </c>
-      <c r="AE106">
-        <v>1.11</v>
-      </c>
-      <c r="AF106">
-        <v>1.55</v>
-      </c>
-      <c r="AG106">
-        <v>2.26</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ106">
-        <v>1.29</v>
-      </c>
-      <c r="AK106">
-        <v>1.34</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q107">
-        <v>1.91</v>
+        <v>3.3</v>
       </c>
       <c r="R107">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="S107">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T107">
-        <v>3.07</v>
+        <v>3.4</v>
       </c>
       <c r="U107">
-        <v>2.77</v>
+        <v>2.61</v>
       </c>
       <c r="V107">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W107">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X107">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z107">
-        <v>3.72</v>
+        <v>4.1</v>
       </c>
       <c r="AA107">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AB107">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AC107">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AD107">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE107">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF107">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AG107">
-        <v>1.76</v>
+        <v>2.26</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AK107">
-        <v>2.62</v>
+        <v>1.34</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,22 +17913,22 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="O108">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="P108">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="Q108">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="R108">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S108">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T108">
         <v>3.18</v>
@@ -17955,7 +17955,7 @@
         <v>1.62</v>
       </c>
       <c r="AB108">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AC108">
         <v>2.43</v>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK108">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -38297,10 +38297,10 @@
         <v>1.63</v>
       </c>
       <c r="Q233">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="R233">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="S233">
         <v>1.15</v>
@@ -38309,13 +38309,13 @@
         <v>4.3</v>
       </c>
       <c r="U233">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V233">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="W233">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X233">
         <v>1.01</v>
@@ -38324,22 +38324,22 @@
         <v>1.05</v>
       </c>
       <c r="Z233">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="AA233">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB233">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AC233">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AD233">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AE233">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AF233">
         <v>1.36</v>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK233">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -40081,64 +40081,64 @@
         </is>
       </c>
       <c r="N244">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O244">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P244">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q244">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R244">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S244">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T244">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U244">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="V244">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W244">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X244">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y244">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z244">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA244">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB244">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC244">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AD244">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE244">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF244">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG244">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK244">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G245">
@@ -40244,64 +40244,64 @@
         </is>
       </c>
       <c r="N245">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O245">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P245">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q245">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R245">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S245">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T245">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U245">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V245">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W245">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X245">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y245">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z245">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA245">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB245">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC245">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AD245">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE245">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF245">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG245">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40314,10 +40314,10 @@
         </is>
       </c>
       <c r="AJ245">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK245">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G246">
@@ -40407,64 +40407,64 @@
         </is>
       </c>
       <c r="N246">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="O246">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="P246">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q246">
-        <v>2.8</v>
+        <v>3.57</v>
       </c>
       <c r="R246">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S246">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="T246">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="U246">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="V246">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W246">
         <v>1.03</v>
       </c>
       <c r="X246">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y246">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Z246">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AA246">
         <v>2.87</v>
       </c>
       <c r="AB246">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC246">
-        <v>5.68</v>
+        <v>5.25</v>
       </c>
       <c r="AD246">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AE246">
         <v>1.03</v>
       </c>
       <c r="AF246">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AG246">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -40477,10 +40477,10 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK246">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -41669,7 +41669,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G254">
@@ -41711,64 +41711,64 @@
         </is>
       </c>
       <c r="N254">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O254">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P254">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q254">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R254">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S254">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T254">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U254">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V254">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W254">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X254">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y254">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z254">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA254">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB254">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC254">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD254">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE254">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF254">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG254">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -41781,10 +41781,10 @@
         </is>
       </c>
       <c r="AJ254">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK254">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL254">
         <v>0</v>
@@ -41832,22 +41832,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G255">
@@ -41995,22 +41995,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G256">
@@ -42037,64 +42037,64 @@
         </is>
       </c>
       <c r="N256">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O256">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P256">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q256">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="R256">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S256">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T256">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U256">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V256">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W256">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X256">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y256">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z256">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA256">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB256">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC256">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD256">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE256">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF256">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG256">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42107,10 +42107,10 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK256">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G257">
@@ -42316,12 +42316,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G258">
@@ -42363,64 +42363,64 @@
         </is>
       </c>
       <c r="N258">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O258">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P258">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q258">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R258">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S258">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T258">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U258">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V258">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W258">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X258">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y258">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z258">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA258">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB258">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC258">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD258">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE258">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF258">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG258">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH258" t="inlineStr">
         <is>
@@ -42433,10 +42433,10 @@
         </is>
       </c>
       <c r="AJ258">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK258">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL258">
         <v>0</v>
@@ -42467,7 +42467,7 @@
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>2026-09-20 15:30:00</t>
+          <t>2026-09-20 15:45:00</t>
         </is>
       </c>
     </row>
@@ -42479,12 +42479,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G259">
@@ -42526,64 +42526,64 @@
         </is>
       </c>
       <c r="N259">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O259">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P259">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q259">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R259">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S259">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T259">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U259">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V259">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W259">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X259">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y259">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z259">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA259">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB259">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC259">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD259">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE259">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF259">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG259">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK259">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -42630,7 +42630,7 @@
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>2026-09-20 15:30:00</t>
+          <t>2026-09-20 15:45:00</t>
         </is>
       </c>
     </row>
@@ -42642,27 +42642,27 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,64 +42689,64 @@
         </is>
       </c>
       <c r="N260">
-        <v>6</v>
+        <v>2.15</v>
       </c>
       <c r="O260">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="P260">
+        <v>3.5</v>
+      </c>
+      <c r="Q260">
+        <v>2.75</v>
+      </c>
+      <c r="R260">
+        <v>1.95</v>
+      </c>
+      <c r="S260">
+        <v>1.51</v>
+      </c>
+      <c r="T260">
+        <v>2.5</v>
+      </c>
+      <c r="U260">
+        <v>3.32</v>
+      </c>
+      <c r="V260">
+        <v>1.3</v>
+      </c>
+      <c r="W260">
+        <v>1.03</v>
+      </c>
+      <c r="X260">
+        <v>1.06</v>
+      </c>
+      <c r="Y260">
         <v>1.42</v>
       </c>
-      <c r="Q260">
-        <v>5.75</v>
-      </c>
-      <c r="R260">
-        <v>2.7</v>
-      </c>
-      <c r="S260">
-        <v>1.2</v>
-      </c>
-      <c r="T260">
-        <v>4.15</v>
-      </c>
-      <c r="U260">
-        <v>1.95</v>
-      </c>
-      <c r="V260">
-        <v>1.75</v>
-      </c>
-      <c r="W260">
-        <v>1.18</v>
-      </c>
-      <c r="X260">
-        <v>1.01</v>
-      </c>
-      <c r="Y260">
-        <v>1.06</v>
-      </c>
       <c r="Z260">
-        <v>6.3</v>
+        <v>2.49</v>
       </c>
       <c r="AA260">
-        <v>1.37</v>
+        <v>2.3</v>
       </c>
       <c r="AB260">
-        <v>2.8</v>
+        <v>1.55</v>
       </c>
       <c r="AC260">
-        <v>1.88</v>
+        <v>4.8</v>
       </c>
       <c r="AD260">
-        <v>1.91</v>
+        <v>1.14</v>
       </c>
       <c r="AE260">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AF260">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AG260">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK260">
-        <v>1.13</v>
+        <v>1.65</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42793,7 +42793,7 @@
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>2026-09-20 15:45:00</t>
+          <t>2026-09-20 16:00:00</t>
         </is>
       </c>
     </row>
@@ -42805,27 +42805,27 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G261">
@@ -42852,64 +42852,64 @@
         </is>
       </c>
       <c r="N261">
+        <v>2.8</v>
+      </c>
+      <c r="O261">
+        <v>3.25</v>
+      </c>
+      <c r="P261">
+        <v>2.5</v>
+      </c>
+      <c r="Q261">
+        <v>3.52</v>
+      </c>
+      <c r="R261">
+        <v>2</v>
+      </c>
+      <c r="S261">
+        <v>1.4</v>
+      </c>
+      <c r="T261">
+        <v>2.88</v>
+      </c>
+      <c r="U261">
+        <v>2.76</v>
+      </c>
+      <c r="V261">
+        <v>1.37</v>
+      </c>
+      <c r="W261">
+        <v>1.03</v>
+      </c>
+      <c r="X261">
+        <v>1.04</v>
+      </c>
+      <c r="Y261">
+        <v>1.28</v>
+      </c>
+      <c r="Z261">
+        <v>3.08</v>
+      </c>
+      <c r="AA261">
+        <v>2.05</v>
+      </c>
+      <c r="AB261">
+        <v>1.79</v>
+      </c>
+      <c r="AC261">
+        <v>3.6</v>
+      </c>
+      <c r="AD261">
         <v>1.25</v>
       </c>
-      <c r="O261">
-        <v>5.5</v>
-      </c>
-      <c r="P261">
-        <v>11</v>
-      </c>
-      <c r="Q261">
-        <v>1.7</v>
-      </c>
-      <c r="R261">
-        <v>2.47</v>
-      </c>
-      <c r="S261">
-        <v>1.31</v>
-      </c>
-      <c r="T261">
-        <v>3.6</v>
-      </c>
-      <c r="U261">
-        <v>2.43</v>
-      </c>
-      <c r="V261">
-        <v>1.52</v>
-      </c>
-      <c r="W261">
-        <v>1.12</v>
-      </c>
-      <c r="X261">
-        <v>1.01</v>
-      </c>
-      <c r="Y261">
-        <v>1.18</v>
-      </c>
-      <c r="Z261">
-        <v>3.88</v>
-      </c>
-      <c r="AA261">
-        <v>1.72</v>
-      </c>
-      <c r="AB261">
-        <v>2.31</v>
-      </c>
-      <c r="AC261">
-        <v>2.66</v>
-      </c>
-      <c r="AD261">
-        <v>1.46</v>
-      </c>
       <c r="AE261">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AF261">
-        <v>2.16</v>
+        <v>1.76</v>
       </c>
       <c r="AG261">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -42922,10 +42922,10 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="AK261">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -42956,7 +42956,7 @@
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>2026-09-20 15:45:00</t>
+          <t>2026-09-20 16:00:00</t>
         </is>
       </c>
     </row>
@@ -42973,7 +42973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G262">
@@ -43015,64 +43015,64 @@
         </is>
       </c>
       <c r="N262">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O262">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P262">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q262">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R262">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S262">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T262">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U262">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="V262">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W262">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X262">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y262">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z262">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AA262">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB262">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC262">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD262">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE262">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF262">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG262">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH262" t="inlineStr">
         <is>
@@ -43085,10 +43085,10 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK262">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -43136,7 +43136,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G263">
@@ -43178,64 +43178,64 @@
         </is>
       </c>
       <c r="N263">
-        <v>2.8</v>
+        <v>1.64</v>
       </c>
       <c r="O263">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P263">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="Q263">
-        <v>3.52</v>
+        <v>2.24</v>
       </c>
       <c r="R263">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S263">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T263">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="U263">
-        <v>2.76</v>
+        <v>3.4</v>
       </c>
       <c r="V263">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="W263">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X263">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y263">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="Z263">
-        <v>3.08</v>
+        <v>2.49</v>
       </c>
       <c r="AA263">
-        <v>2.05</v>
+        <v>2.51</v>
       </c>
       <c r="AB263">
-        <v>1.79</v>
+        <v>1.46</v>
       </c>
       <c r="AC263">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="AD263">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AE263">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF263">
-        <v>1.76</v>
+        <v>2.25</v>
       </c>
       <c r="AG263">
-        <v>1.96</v>
+        <v>1.6</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>1.3</v>
       </c>
       <c r="AK263">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43299,22 +43299,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G264">
@@ -43341,64 +43341,64 @@
         </is>
       </c>
       <c r="N264">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O264">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P264">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q264">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R264">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S264">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T264">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U264">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V264">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W264">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X264">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y264">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z264">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AA264">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB264">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC264">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD264">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE264">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF264">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG264">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43411,10 +43411,10 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK264">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -43462,7 +43462,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G265">
@@ -43543,10 +43543,10 @@
         <v>0</v>
       </c>
       <c r="AA265">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB265">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC265">
         <v>0</v>
@@ -43625,7 +43625,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G266">
@@ -43667,64 +43667,64 @@
         </is>
       </c>
       <c r="N266">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="O266">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="P266">
-        <v>4.04</v>
+        <v>2.5</v>
       </c>
       <c r="Q266">
+        <v>3.2</v>
+      </c>
+      <c r="R266">
+        <v>2.25</v>
+      </c>
+      <c r="S266">
+        <v>1.4</v>
+      </c>
+      <c r="T266">
+        <v>2.88</v>
+      </c>
+      <c r="U266">
         <v>2.7</v>
       </c>
-      <c r="R266">
-        <v>1.95</v>
-      </c>
-      <c r="S266">
-        <v>1.49</v>
-      </c>
-      <c r="T266">
-        <v>2.58</v>
-      </c>
-      <c r="U266">
-        <v>3.18</v>
-      </c>
       <c r="V266">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="W266">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X266">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y266">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="Z266">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="AA266">
-        <v>2.27</v>
+        <v>1.93</v>
       </c>
       <c r="AB266">
-        <v>1.59</v>
+        <v>1.9</v>
       </c>
       <c r="AC266">
-        <v>3.9</v>
+        <v>2.98</v>
       </c>
       <c r="AD266">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AE266">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF266">
+        <v>1.69</v>
+      </c>
+      <c r="AG266">
         <v>2.05</v>
-      </c>
-      <c r="AG266">
-        <v>1.75</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>1.34</v>
       </c>
       <c r="AK266">
-        <v>1.82</v>
+        <v>1.47</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -43788,7 +43788,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G267">
@@ -43839,55 +43839,55 @@
         <v>0</v>
       </c>
       <c r="Q267">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R267">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S267">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T267">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U267">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V267">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W267">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X267">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y267">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z267">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA267">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="AB267">
-        <v>2.37</v>
+        <v>1.54</v>
       </c>
       <c r="AC267">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD267">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE267">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF267">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG267">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH267" t="inlineStr">
         <is>
@@ -43900,10 +43900,10 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK267">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -43946,27 +43946,27 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G268">
@@ -43993,64 +43993,64 @@
         </is>
       </c>
       <c r="N268">
-        <v>2.7</v>
+        <v>1.97</v>
       </c>
       <c r="O268">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P268">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q268">
-        <v>3.2</v>
+        <v>2.57</v>
       </c>
       <c r="R268">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S268">
         <v>1.4</v>
       </c>
       <c r="T268">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U268">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="V268">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W268">
         <v>1.07</v>
       </c>
       <c r="X268">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y268">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="Z268">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="AA268">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AB268">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC268">
-        <v>2.98</v>
+        <v>4.03</v>
       </c>
       <c r="AD268">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AE268">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF268">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="AG268">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AH268" t="inlineStr">
         <is>
@@ -44063,10 +44063,10 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AK268">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AL268">
         <v>0</v>
@@ -44097,7 +44097,7 @@
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>2026-09-20 16:00:00</t>
+          <t>2026-09-20 16:30:00</t>
         </is>
       </c>
     </row>
@@ -44109,12 +44109,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G269">
@@ -44156,64 +44156,64 @@
         </is>
       </c>
       <c r="N269">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O269">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P269">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q269">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="R269">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="S269">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="T269">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="U269">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="V269">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="W269">
         <v>1.03</v>
       </c>
       <c r="X269">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="Y269">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="Z269">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="AA269">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="AB269">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AC269">
-        <v>4.45</v>
+        <v>5.9</v>
       </c>
       <c r="AD269">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AE269">
         <v>1.03</v>
       </c>
       <c r="AF269">
-        <v>2</v>
+        <v>2.57</v>
       </c>
       <c r="AG269">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK269">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44260,7 +44260,7 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>2026-09-20 16:00:00</t>
+          <t>2026-09-20 16:30:00</t>
         </is>
       </c>
     </row>
@@ -44277,22 +44277,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G270">
@@ -44319,64 +44319,64 @@
         </is>
       </c>
       <c r="N270">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O270">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P270">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q270">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R270">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S270">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T270">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U270">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V270">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W270">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X270">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y270">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z270">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA270">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB270">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC270">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AD270">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE270">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF270">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG270">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK270">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -44435,27 +44435,27 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G271">
@@ -44482,64 +44482,64 @@
         </is>
       </c>
       <c r="N271">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="O271">
+        <v>2.75</v>
+      </c>
+      <c r="P271">
         <v>3.5</v>
       </c>
-      <c r="P271">
-        <v>2.65</v>
-      </c>
       <c r="Q271">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R271">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S271">
+        <v>0</v>
+      </c>
+      <c r="T271">
+        <v>0</v>
+      </c>
+      <c r="U271">
+        <v>0</v>
+      </c>
+      <c r="V271">
+        <v>0</v>
+      </c>
+      <c r="W271">
+        <v>0</v>
+      </c>
+      <c r="X271">
+        <v>0</v>
+      </c>
+      <c r="Y271">
+        <v>0</v>
+      </c>
+      <c r="Z271">
+        <v>0</v>
+      </c>
+      <c r="AA271">
+        <v>3.1</v>
+      </c>
+      <c r="AB271">
         <v>1.36</v>
       </c>
-      <c r="T271">
-        <v>2.82</v>
-      </c>
-      <c r="U271">
-        <v>2.76</v>
-      </c>
-      <c r="V271">
-        <v>1.43</v>
-      </c>
-      <c r="W271">
-        <v>1.04</v>
-      </c>
-      <c r="X271">
-        <v>1.01</v>
-      </c>
-      <c r="Y271">
-        <v>1.25</v>
-      </c>
-      <c r="Z271">
-        <v>3.6</v>
-      </c>
-      <c r="AA271">
-        <v>1.8</v>
-      </c>
-      <c r="AB271">
-        <v>1.94</v>
-      </c>
       <c r="AC271">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="AD271">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE271">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF271">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG271">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK271">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44586,7 +44586,7 @@
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>2026-09-20 16:30:00</t>
+          <t>2026-09-20 17:00:00</t>
         </is>
       </c>
     </row>
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O272">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P272">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q272">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R272">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S272">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T272">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U272">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V272">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W272">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X272">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y272">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z272">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA272">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB272">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC272">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AD272">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE272">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF272">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG272">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK272">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,64 +44808,64 @@
         </is>
       </c>
       <c r="N273">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O273">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P273">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q273">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R273">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S273">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T273">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U273">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V273">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W273">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X273">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y273">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z273">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA273">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB273">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC273">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AD273">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE273">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF273">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AG273">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK273">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,64 +44971,64 @@
         </is>
       </c>
       <c r="N274">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O274">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="P274">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q274">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R274">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S274">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T274">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U274">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V274">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W274">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X274">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y274">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z274">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA274">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB274">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC274">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="AD274">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE274">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF274">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG274">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,10 +45041,10 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK274">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45087,27 +45087,27 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,64 +45134,64 @@
         </is>
       </c>
       <c r="N275">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O275">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P275">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q275">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R275">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S275">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T275">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U275">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V275">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W275">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X275">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y275">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z275">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AA275">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AB275">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC275">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="AD275">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE275">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF275">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG275">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK275">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45238,7 +45238,7 @@
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>2026-09-20 17:00:00</t>
+          <t>2026-09-20 17:30:00</t>
         </is>
       </c>
     </row>
@@ -45250,27 +45250,27 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G276">
@@ -45401,7 +45401,7 @@
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>2026-09-20 17:00:00</t>
+          <t>2026-09-20 17:30:00</t>
         </is>
       </c>
     </row>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G277">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G278">
@@ -45739,27 +45739,27 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O279">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P279">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q279">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R279">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S279">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T279">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U279">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V279">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W279">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X279">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y279">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z279">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA279">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB279">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC279">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD279">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE279">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF279">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG279">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK279">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45890,7 +45890,7 @@
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>2026-09-20 17:30:00</t>
+          <t>2026-09-20 18:00:00</t>
         </is>
       </c>
     </row>
@@ -45902,27 +45902,27 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,64 +45949,64 @@
         </is>
       </c>
       <c r="N280">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O280">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P280">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q280">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R280">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S280">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T280">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U280">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V280">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W280">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X280">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y280">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z280">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA280">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB280">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC280">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="AD280">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE280">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF280">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG280">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK280">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -46053,7 +46053,7 @@
       </c>
       <c r="AU280" t="inlineStr">
         <is>
-          <t>2026-09-20 17:30:00</t>
+          <t>2026-09-20 18:00:00</t>
         </is>
       </c>
     </row>
@@ -46070,7 +46070,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G281">
@@ -46112,64 +46112,64 @@
         </is>
       </c>
       <c r="N281">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O281">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P281">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q281">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="R281">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="S281">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T281">
-        <v>3.24</v>
+        <v>3.8</v>
       </c>
       <c r="U281">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="V281">
+        <v>1.58</v>
+      </c>
+      <c r="W281">
+        <v>1.14</v>
+      </c>
+      <c r="X281">
+        <v>1.02</v>
+      </c>
+      <c r="Y281">
+        <v>1.13</v>
+      </c>
+      <c r="Z281">
+        <v>4.8</v>
+      </c>
+      <c r="AA281">
         <v>1.5</v>
       </c>
-      <c r="W281">
-        <v>1.11</v>
-      </c>
-      <c r="X281">
-        <v>1</v>
-      </c>
-      <c r="Y281">
-        <v>1.19</v>
-      </c>
-      <c r="Z281">
-        <v>3.8</v>
-      </c>
-      <c r="AA281">
-        <v>1.68</v>
-      </c>
       <c r="AB281">
-        <v>2.02</v>
+        <v>2.47</v>
       </c>
       <c r="AC281">
-        <v>2.66</v>
+        <v>2.31</v>
       </c>
       <c r="AD281">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="AE281">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF281">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG281">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AH281" t="inlineStr">
         <is>
@@ -46182,10 +46182,10 @@
         </is>
       </c>
       <c r="AJ281">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AK281">
-        <v>1.71</v>
+        <v>1.08</v>
       </c>
       <c r="AL281">
         <v>0</v>
@@ -46228,12 +46228,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G282">
@@ -46275,81 +46275,81 @@
         </is>
       </c>
       <c r="N282">
-        <v>2.2</v>
+        <v>1.39</v>
       </c>
       <c r="O282">
+        <v>5</v>
+      </c>
+      <c r="P282">
+        <v>7.5</v>
+      </c>
+      <c r="Q282">
+        <v>1.75</v>
+      </c>
+      <c r="R282">
+        <v>2.47</v>
+      </c>
+      <c r="S282">
+        <v>1.27</v>
+      </c>
+      <c r="T282">
+        <v>3.32</v>
+      </c>
+      <c r="U282">
+        <v>2.4</v>
+      </c>
+      <c r="V282">
+        <v>1.5</v>
+      </c>
+      <c r="W282">
+        <v>1.08</v>
+      </c>
+      <c r="X282">
+        <v>1.02</v>
+      </c>
+      <c r="Y282">
+        <v>1.14</v>
+      </c>
+      <c r="Z282">
+        <v>4.33</v>
+      </c>
+      <c r="AA282">
+        <v>1.65</v>
+      </c>
+      <c r="AB282">
+        <v>2.22</v>
+      </c>
+      <c r="AC282">
+        <v>2.6</v>
+      </c>
+      <c r="AD282">
+        <v>1.43</v>
+      </c>
+      <c r="AE282">
+        <v>1.19</v>
+      </c>
+      <c r="AF282">
+        <v>1.87</v>
+      </c>
+      <c r="AG282">
+        <v>1.85</v>
+      </c>
+      <c r="AH282" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI282" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ282">
+        <v>1.18</v>
+      </c>
+      <c r="AK282">
         <v>2.9</v>
       </c>
-      <c r="P282">
-        <v>3</v>
-      </c>
-      <c r="Q282">
-        <v>2.98</v>
-      </c>
-      <c r="R282">
-        <v>2.02</v>
-      </c>
-      <c r="S282">
-        <v>1.44</v>
-      </c>
-      <c r="T282">
-        <v>2.4</v>
-      </c>
-      <c r="U282">
-        <v>3.06</v>
-      </c>
-      <c r="V282">
-        <v>1.29</v>
-      </c>
-      <c r="W282">
-        <v>1.05</v>
-      </c>
-      <c r="X282">
-        <v>1.04</v>
-      </c>
-      <c r="Y282">
-        <v>1.4</v>
-      </c>
-      <c r="Z282">
-        <v>2.62</v>
-      </c>
-      <c r="AA282">
-        <v>2.37</v>
-      </c>
-      <c r="AB282">
-        <v>1.56</v>
-      </c>
-      <c r="AC282">
-        <v>4.29</v>
-      </c>
-      <c r="AD282">
-        <v>1.16</v>
-      </c>
-      <c r="AE282">
-        <v>1.01</v>
-      </c>
-      <c r="AF282">
-        <v>1.95</v>
-      </c>
-      <c r="AG282">
-        <v>1.74</v>
-      </c>
-      <c r="AH282" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI282" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ282">
-        <v>1.29</v>
-      </c>
-      <c r="AK282">
-        <v>1.52</v>
-      </c>
       <c r="AL282">
         <v>0</v>
       </c>
@@ -46379,7 +46379,7 @@
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>2026-09-20 18:00:00</t>
+          <t>2026-09-20 18:30:00</t>
         </is>
       </c>
     </row>
@@ -46391,12 +46391,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G283">
@@ -46447,55 +46447,55 @@
         <v>0</v>
       </c>
       <c r="Q283">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R283">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S283">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T283">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U283">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V283">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W283">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X283">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y283">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z283">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA283">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB283">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AC283">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AD283">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE283">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF283">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG283">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK283">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46542,7 +46542,7 @@
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>2026-09-20 18:00:00</t>
+          <t>2026-09-20 18:30:00</t>
         </is>
       </c>
     </row>
@@ -46559,7 +46559,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G284">
@@ -46601,64 +46601,64 @@
         </is>
       </c>
       <c r="N284">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O284">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P284">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Q284">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="R284">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S284">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T284">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="U284">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V284">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W284">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X284">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y284">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z284">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA284">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB284">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AC284">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD284">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE284">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF284">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG284">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK284">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46722,7 +46722,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G285">
@@ -46764,64 +46764,64 @@
         </is>
       </c>
       <c r="N285">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O285">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P285">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q285">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R285">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S285">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T285">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U285">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V285">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W285">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X285">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y285">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z285">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AA285">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB285">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC285">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD285">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE285">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF285">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG285">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK285">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -46880,12 +46880,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,64 +46927,64 @@
         </is>
       </c>
       <c r="N286">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O286">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P286">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q286">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R286">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S286">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T286">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U286">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V286">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W286">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X286">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y286">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z286">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA286">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB286">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC286">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD286">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE286">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF286">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG286">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK286">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47031,7 +47031,7 @@
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>2026-09-20 18:30:00</t>
+          <t>2026-09-20 19:30:00</t>
         </is>
       </c>
     </row>
@@ -47043,12 +47043,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,55 +47090,55 @@
         </is>
       </c>
       <c r="N287">
-        <v>2.87</v>
+        <v>1.84</v>
       </c>
       <c r="O287">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P287">
-        <v>2.3</v>
+        <v>3.95</v>
       </c>
       <c r="Q287">
-        <v>3.91</v>
+        <v>2.4</v>
       </c>
       <c r="R287">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S287">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="T287">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="U287">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="V287">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W287">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X287">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y287">
         <v>1.4</v>
       </c>
       <c r="Z287">
-        <v>2.53</v>
+        <v>2.82</v>
       </c>
       <c r="AA287">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="AB287">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AC287">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD287">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AE287">
         <v>1.03</v>
@@ -47147,7 +47147,7 @@
         <v>1.95</v>
       </c>
       <c r="AG287">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK287">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47194,7 +47194,7 @@
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>2026-09-20 18:30:00</t>
+          <t>2026-09-20 20:00:00</t>
         </is>
       </c>
     </row>
@@ -47206,12 +47206,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,64 +47253,64 @@
         </is>
       </c>
       <c r="N288">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O288">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P288">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q288">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="R288">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S288">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T288">
-        <v>3.01</v>
+        <v>3.12</v>
       </c>
       <c r="U288">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="V288">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W288">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X288">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y288">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z288">
-        <v>3.28</v>
+        <v>3.92</v>
       </c>
       <c r="AA288">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="AB288">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AC288">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="AD288">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE288">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF288">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AG288">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AK288">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47357,7 +47357,7 @@
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>2026-09-20 19:30:00</t>
+          <t>2026-09-20 20:00:00</t>
         </is>
       </c>
     </row>
@@ -47374,7 +47374,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,64 +47416,64 @@
         </is>
       </c>
       <c r="N289">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O289">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P289">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Q289">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="R289">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="S289">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T289">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="U289">
-        <v>2.99</v>
+        <v>2.18</v>
       </c>
       <c r="V289">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="W289">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X289">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y289">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="Z289">
-        <v>2.82</v>
+        <v>4.7</v>
       </c>
       <c r="AA289">
-        <v>2.23</v>
+        <v>1.48</v>
       </c>
       <c r="AB289">
-        <v>1.72</v>
+        <v>2.33</v>
       </c>
       <c r="AC289">
-        <v>3.78</v>
+        <v>2.29</v>
       </c>
       <c r="AD289">
-        <v>1.19</v>
+        <v>1.53</v>
       </c>
       <c r="AE289">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AF289">
-        <v>1.95</v>
+        <v>1.46</v>
       </c>
       <c r="AG289">
-        <v>1.76</v>
+        <v>2.41</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>1.17</v>
       </c>
       <c r="AK289">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47537,7 +47537,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G290">
@@ -47588,55 +47588,55 @@
         <v>0</v>
       </c>
       <c r="Q290">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R290">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S290">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T290">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U290">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V290">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W290">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X290">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y290">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z290">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AA290">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB290">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC290">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD290">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE290">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF290">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG290">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK290">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47695,12 +47695,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,64 +47742,64 @@
         </is>
       </c>
       <c r="N291">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O291">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P291">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q291">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="R291">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="S291">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T291">
-        <v>3.6</v>
+        <v>2.72</v>
       </c>
       <c r="U291">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="V291">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="W291">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X291">
         <v>1.02</v>
       </c>
       <c r="Y291">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="Z291">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="AA291">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="AB291">
-        <v>2.33</v>
+        <v>1.88</v>
       </c>
       <c r="AC291">
-        <v>2.29</v>
+        <v>3.18</v>
       </c>
       <c r="AD291">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AE291">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF291">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AG291">
-        <v>2.41</v>
+        <v>2.04</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK291">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47845,332 +47845,6 @@
         <v>0</v>
       </c>
       <c r="AU291" t="inlineStr">
-        <is>
-          <t>2026-09-20 20:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>Inter Miami</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
-      <c r="G292">
-        <v>0</v>
-      </c>
-      <c r="H292">
-        <v>0</v>
-      </c>
-      <c r="I292">
-        <v>0</v>
-      </c>
-      <c r="J292">
-        <v>0</v>
-      </c>
-      <c r="K292">
-        <v>0</v>
-      </c>
-      <c r="L292">
-        <v>0</v>
-      </c>
-      <c r="M292" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N292">
-        <v>0</v>
-      </c>
-      <c r="O292">
-        <v>0</v>
-      </c>
-      <c r="P292">
-        <v>0</v>
-      </c>
-      <c r="Q292">
-        <v>0</v>
-      </c>
-      <c r="R292">
-        <v>0</v>
-      </c>
-      <c r="S292">
-        <v>0</v>
-      </c>
-      <c r="T292">
-        <v>0</v>
-      </c>
-      <c r="U292">
-        <v>0</v>
-      </c>
-      <c r="V292">
-        <v>0</v>
-      </c>
-      <c r="W292">
-        <v>0</v>
-      </c>
-      <c r="X292">
-        <v>0</v>
-      </c>
-      <c r="Y292">
-        <v>0</v>
-      </c>
-      <c r="Z292">
-        <v>0</v>
-      </c>
-      <c r="AA292">
-        <v>0</v>
-      </c>
-      <c r="AB292">
-        <v>0</v>
-      </c>
-      <c r="AC292">
-        <v>0</v>
-      </c>
-      <c r="AD292">
-        <v>0</v>
-      </c>
-      <c r="AE292">
-        <v>0</v>
-      </c>
-      <c r="AF292">
-        <v>0</v>
-      </c>
-      <c r="AG292">
-        <v>0</v>
-      </c>
-      <c r="AH292" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI292" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ292">
-        <v>0</v>
-      </c>
-      <c r="AK292">
-        <v>0</v>
-      </c>
-      <c r="AL292">
-        <v>0</v>
-      </c>
-      <c r="AM292">
-        <v>-1</v>
-      </c>
-      <c r="AN292">
-        <v>-1</v>
-      </c>
-      <c r="AO292">
-        <v>-1</v>
-      </c>
-      <c r="AP292">
-        <v>-1</v>
-      </c>
-      <c r="AQ292">
-        <v>0</v>
-      </c>
-      <c r="AR292">
-        <v>0</v>
-      </c>
-      <c r="AS292">
-        <v>0</v>
-      </c>
-      <c r="AT292">
-        <v>0</v>
-      </c>
-      <c r="AU292" t="inlineStr">
-        <is>
-          <t>2026-09-20 20:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>LDU Quito</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>CD Universidad Católica</t>
-        </is>
-      </c>
-      <c r="G293">
-        <v>0</v>
-      </c>
-      <c r="H293">
-        <v>0</v>
-      </c>
-      <c r="I293">
-        <v>0</v>
-      </c>
-      <c r="J293">
-        <v>0</v>
-      </c>
-      <c r="K293">
-        <v>0</v>
-      </c>
-      <c r="L293">
-        <v>0</v>
-      </c>
-      <c r="M293" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N293">
-        <v>2.1</v>
-      </c>
-      <c r="O293">
-        <v>3.2</v>
-      </c>
-      <c r="P293">
-        <v>3</v>
-      </c>
-      <c r="Q293">
-        <v>2.75</v>
-      </c>
-      <c r="R293">
-        <v>2.04</v>
-      </c>
-      <c r="S293">
-        <v>1.36</v>
-      </c>
-      <c r="T293">
-        <v>2.72</v>
-      </c>
-      <c r="U293">
-        <v>2.62</v>
-      </c>
-      <c r="V293">
-        <v>1.4</v>
-      </c>
-      <c r="W293">
-        <v>1.08</v>
-      </c>
-      <c r="X293">
-        <v>1.02</v>
-      </c>
-      <c r="Y293">
-        <v>1.27</v>
-      </c>
-      <c r="Z293">
-        <v>3.55</v>
-      </c>
-      <c r="AA293">
-        <v>1.9</v>
-      </c>
-      <c r="AB293">
-        <v>1.88</v>
-      </c>
-      <c r="AC293">
-        <v>3.18</v>
-      </c>
-      <c r="AD293">
-        <v>1.31</v>
-      </c>
-      <c r="AE293">
-        <v>1.12</v>
-      </c>
-      <c r="AF293">
-        <v>1.68</v>
-      </c>
-      <c r="AG293">
-        <v>2.04</v>
-      </c>
-      <c r="AH293" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI293" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ293">
-        <v>1.29</v>
-      </c>
-      <c r="AK293">
-        <v>1.62</v>
-      </c>
-      <c r="AL293">
-        <v>0</v>
-      </c>
-      <c r="AM293">
-        <v>-1</v>
-      </c>
-      <c r="AN293">
-        <v>-1</v>
-      </c>
-      <c r="AO293">
-        <v>-1</v>
-      </c>
-      <c r="AP293">
-        <v>-1</v>
-      </c>
-      <c r="AQ293">
-        <v>0</v>
-      </c>
-      <c r="AR293">
-        <v>0</v>
-      </c>
-      <c r="AS293">
-        <v>0</v>
-      </c>
-      <c r="AT293">
-        <v>0</v>
-      </c>
-      <c r="AU293" t="inlineStr">
         <is>
           <t>2026-09-20 20:30:00</t>
         </is>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,80 +3732,80 @@
         </is>
       </c>
       <c r="N21">
-        <v>4.4</v>
+        <v>2.53</v>
       </c>
       <c r="O21">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="P21">
-        <v>1.86</v>
+        <v>2.31</v>
       </c>
       <c r="Q21">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="R21">
         <v>2.01</v>
       </c>
       <c r="S21">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T21">
-        <v>2.57</v>
+        <v>2.99</v>
       </c>
       <c r="U21">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="V21">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W21">
+        <v>1.06</v>
+      </c>
+      <c r="X21">
+        <v>1.03</v>
+      </c>
+      <c r="Y21">
+        <v>1.26</v>
+      </c>
+      <c r="Z21">
+        <v>3.2</v>
+      </c>
+      <c r="AA21">
+        <v>1.96</v>
+      </c>
+      <c r="AB21">
+        <v>1.85</v>
+      </c>
+      <c r="AC21">
+        <v>3.14</v>
+      </c>
+      <c r="AD21">
+        <v>1.27</v>
+      </c>
+      <c r="AE21">
         <v>1.07</v>
       </c>
-      <c r="X21">
-        <v>1.02</v>
-      </c>
-      <c r="Y21">
+      <c r="AF21">
+        <v>1.7</v>
+      </c>
+      <c r="AG21">
+        <v>2</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
         <v>1.3</v>
       </c>
-      <c r="Z21">
-        <v>2.97</v>
-      </c>
-      <c r="AA21">
-        <v>2.05</v>
-      </c>
-      <c r="AB21">
-        <v>1.8</v>
-      </c>
-      <c r="AC21">
-        <v>3.42</v>
-      </c>
-      <c r="AD21">
-        <v>1.26</v>
-      </c>
-      <c r="AE21">
-        <v>1.04</v>
-      </c>
-      <c r="AF21">
-        <v>1.91</v>
-      </c>
-      <c r="AG21">
-        <v>1.83</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.85</v>
-      </c>
       <c r="AK21">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.53</v>
+        <v>4.4</v>
       </c>
       <c r="O22">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="P22">
-        <v>2.31</v>
+        <v>1.86</v>
       </c>
       <c r="Q22">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="R22">
         <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="T22">
-        <v>2.99</v>
+        <v>2.57</v>
       </c>
       <c r="U22">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="V22">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W22">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
+        <v>1.3</v>
+      </c>
+      <c r="Z22">
+        <v>2.97</v>
+      </c>
+      <c r="AA22">
+        <v>2.05</v>
+      </c>
+      <c r="AB22">
+        <v>1.8</v>
+      </c>
+      <c r="AC22">
+        <v>3.42</v>
+      </c>
+      <c r="AD22">
         <v>1.26</v>
       </c>
-      <c r="Z22">
-        <v>3.2</v>
-      </c>
-      <c r="AA22">
-        <v>1.96</v>
-      </c>
-      <c r="AB22">
+      <c r="AE22">
+        <v>1.04</v>
+      </c>
+      <c r="AF22">
+        <v>1.91</v>
+      </c>
+      <c r="AG22">
+        <v>1.83</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
         <v>1.85</v>
       </c>
-      <c r="AC22">
-        <v>3.14</v>
-      </c>
-      <c r="AD22">
-        <v>1.27</v>
-      </c>
-      <c r="AE22">
-        <v>1.07</v>
-      </c>
-      <c r="AF22">
-        <v>1.7</v>
-      </c>
-      <c r="AG22">
-        <v>2</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.3</v>
-      </c>
       <c r="AK22">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G27">
@@ -4719,71 +4719,71 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="R27">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="S27">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T27">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="U27">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="V27">
+        <v>1.3</v>
+      </c>
+      <c r="W27">
+        <v>1.04</v>
+      </c>
+      <c r="X27">
+        <v>1.03</v>
+      </c>
+      <c r="Y27">
+        <v>1.32</v>
+      </c>
+      <c r="Z27">
+        <v>2.88</v>
+      </c>
+      <c r="AA27">
+        <v>2.08</v>
+      </c>
+      <c r="AB27">
+        <v>1.64</v>
+      </c>
+      <c r="AC27">
+        <v>3.72</v>
+      </c>
+      <c r="AD27">
+        <v>1.2</v>
+      </c>
+      <c r="AE27">
+        <v>1.04</v>
+      </c>
+      <c r="AF27">
+        <v>1.84</v>
+      </c>
+      <c r="AG27">
+        <v>1.85</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.26</v>
       </c>
-      <c r="W27">
-        <v>1.03</v>
-      </c>
-      <c r="X27">
-        <v>1.05</v>
-      </c>
-      <c r="Y27">
-        <v>1.39</v>
-      </c>
-      <c r="Z27">
-        <v>2.59</v>
-      </c>
-      <c r="AA27">
-        <v>2.27</v>
-      </c>
-      <c r="AB27">
-        <v>1.54</v>
-      </c>
-      <c r="AC27">
-        <v>4.2</v>
-      </c>
-      <c r="AD27">
-        <v>1.15</v>
-      </c>
-      <c r="AE27">
-        <v>1.02</v>
-      </c>
-      <c r="AF27">
-        <v>2.03</v>
-      </c>
-      <c r="AG27">
-        <v>1.67</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.24</v>
-      </c>
       <c r="AK27">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G28">
@@ -4882,55 +4882,55 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="R28">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="S28">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T28">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="U28">
-        <v>2.99</v>
+        <v>3.24</v>
       </c>
       <c r="V28">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W28">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Z28">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AA28">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="AB28">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="AC28">
-        <v>3.72</v>
+        <v>4.2</v>
       </c>
       <c r="AD28">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE28">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF28">
-        <v>1.84</v>
+        <v>2.03</v>
       </c>
       <c r="AG28">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK28">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="O57">
         <v>3.7</v>
       </c>
       <c r="P57">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q57">
-        <v>2.52</v>
+        <v>2.24</v>
       </c>
       <c r="R57">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S57">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T57">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="U57">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V57">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="W57">
         <v>1.14</v>
       </c>
       <c r="X57">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z57">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA57">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB57">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="AC57">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="AD57">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AE57">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF57">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AG57">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK57">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,80 +9763,80 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="O58">
         <v>3.7</v>
       </c>
       <c r="P58">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="Q58">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="R58">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S58">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T58">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="U58">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V58">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="W58">
         <v>1.14</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z58">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA58">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AB58">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="AC58">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="AD58">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AE58">
+        <v>1.18</v>
+      </c>
+      <c r="AF58">
+        <v>1.45</v>
+      </c>
+      <c r="AG58">
+        <v>2.55</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
         <v>1.25</v>
       </c>
-      <c r="AF58">
-        <v>1.43</v>
-      </c>
-      <c r="AG58">
-        <v>2.58</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>1.16</v>
-      </c>
       <c r="AK58">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G218">
@@ -35843,65 +35843,65 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="O218">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P218">
-        <v>2.95</v>
+        <v>1.83</v>
       </c>
       <c r="Q218">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="R218">
+        <v>2.26</v>
+      </c>
+      <c r="S218">
+        <v>1.25</v>
+      </c>
+      <c r="T218">
+        <v>3.12</v>
+      </c>
+      <c r="U218">
+        <v>2.4</v>
+      </c>
+      <c r="V218">
+        <v>1.5</v>
+      </c>
+      <c r="W218">
+        <v>1.1</v>
+      </c>
+      <c r="X218">
+        <v>1.01</v>
+      </c>
+      <c r="Y218">
+        <v>1.18</v>
+      </c>
+      <c r="Z218">
+        <v>4.4</v>
+      </c>
+      <c r="AA218">
+        <v>1.64</v>
+      </c>
+      <c r="AB218">
+        <v>2.25</v>
+      </c>
+      <c r="AC218">
+        <v>2.63</v>
+      </c>
+      <c r="AD218">
+        <v>1.43</v>
+      </c>
+      <c r="AE218">
+        <v>1.14</v>
+      </c>
+      <c r="AF218">
+        <v>1.62</v>
+      </c>
+      <c r="AG218">
         <v>2.15</v>
       </c>
-      <c r="S218">
-        <v>1.35</v>
-      </c>
-      <c r="T218">
-        <v>2.82</v>
-      </c>
-      <c r="U218">
-        <v>2.45</v>
-      </c>
-      <c r="V218">
-        <v>1.47</v>
-      </c>
-      <c r="W218">
-        <v>1.07</v>
-      </c>
-      <c r="X218">
-        <v>1.02</v>
-      </c>
-      <c r="Y218">
-        <v>1.21</v>
-      </c>
-      <c r="Z218">
-        <v>3.58</v>
-      </c>
-      <c r="AA218">
-        <v>1.81</v>
-      </c>
-      <c r="AB218">
-        <v>2.08</v>
-      </c>
-      <c r="AC218">
-        <v>2.69</v>
-      </c>
-      <c r="AD218">
-        <v>1.41</v>
-      </c>
-      <c r="AE218">
-        <v>1.11</v>
-      </c>
-      <c r="AF218">
-        <v>1.6</v>
-      </c>
-      <c r="AG218">
-        <v>2.25</v>
-      </c>
       <c r="AH218" t="inlineStr">
         <is>
           <t>[]</t>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AK218">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G219">
@@ -36006,65 +36006,65 @@
         </is>
       </c>
       <c r="N219">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="O219">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P219">
-        <v>1.83</v>
+        <v>2.95</v>
       </c>
       <c r="Q219">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="R219">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="S219">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T219">
-        <v>3.12</v>
+        <v>2.82</v>
       </c>
       <c r="U219">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V219">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W219">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X219">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y219">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z219">
-        <v>4.4</v>
+        <v>3.58</v>
       </c>
       <c r="AA219">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AB219">
+        <v>2.08</v>
+      </c>
+      <c r="AC219">
+        <v>2.69</v>
+      </c>
+      <c r="AD219">
+        <v>1.41</v>
+      </c>
+      <c r="AE219">
+        <v>1.11</v>
+      </c>
+      <c r="AF219">
+        <v>1.6</v>
+      </c>
+      <c r="AG219">
         <v>2.25</v>
       </c>
-      <c r="AC219">
-        <v>2.63</v>
-      </c>
-      <c r="AD219">
-        <v>1.43</v>
-      </c>
-      <c r="AE219">
-        <v>1.14</v>
-      </c>
-      <c r="AF219">
-        <v>1.62</v>
-      </c>
-      <c r="AG219">
-        <v>2.15</v>
-      </c>
       <c r="AH219" t="inlineStr">
         <is>
           <t>[]</t>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK219">
-        <v>1.22</v>
+        <v>1.54</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,64 +42689,64 @@
         </is>
       </c>
       <c r="N260">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="O260">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P260">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q260">
-        <v>2.75</v>
+        <v>3.52</v>
       </c>
       <c r="R260">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S260">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="T260">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="U260">
-        <v>3.32</v>
+        <v>2.76</v>
       </c>
       <c r="V260">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="W260">
         <v>1.03</v>
       </c>
       <c r="X260">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y260">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="Z260">
-        <v>2.49</v>
+        <v>3.08</v>
       </c>
       <c r="AA260">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AB260">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="AC260">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD260">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AE260">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF260">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AG260">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK260">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G261">
@@ -42852,64 +42852,64 @@
         </is>
       </c>
       <c r="N261">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="O261">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P261">
+        <v>3.5</v>
+      </c>
+      <c r="Q261">
+        <v>2.75</v>
+      </c>
+      <c r="R261">
+        <v>1.95</v>
+      </c>
+      <c r="S261">
+        <v>1.51</v>
+      </c>
+      <c r="T261">
         <v>2.5</v>
       </c>
-      <c r="Q261">
-        <v>3.52</v>
-      </c>
-      <c r="R261">
-        <v>2</v>
-      </c>
-      <c r="S261">
-        <v>1.4</v>
-      </c>
-      <c r="T261">
-        <v>2.88</v>
-      </c>
       <c r="U261">
-        <v>2.76</v>
+        <v>3.32</v>
       </c>
       <c r="V261">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W261">
         <v>1.03</v>
       </c>
       <c r="X261">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y261">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="Z261">
-        <v>3.08</v>
+        <v>2.49</v>
       </c>
       <c r="AA261">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB261">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="AC261">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="AD261">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AE261">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF261">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AG261">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -42922,10 +42922,10 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK261">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="O272">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P272">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="Q272">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="R272">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="S272">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="T272">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U272">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="V272">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W272">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X272">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Y272">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="Z272">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AA272">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="AB272">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC272">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="AD272">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AE272">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF272">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AG272">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK272">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,64 +44808,64 @@
         </is>
       </c>
       <c r="N273">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="O273">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P273">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="Q273">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="R273">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="S273">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="T273">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U273">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="V273">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W273">
+        <v>1.04</v>
+      </c>
+      <c r="X273">
+        <v>1.09</v>
+      </c>
+      <c r="Y273">
+        <v>1.6</v>
+      </c>
+      <c r="Z273">
+        <v>2.15</v>
+      </c>
+      <c r="AA273">
+        <v>2.83</v>
+      </c>
+      <c r="AB273">
+        <v>1.36</v>
+      </c>
+      <c r="AC273">
+        <v>5.8</v>
+      </c>
+      <c r="AD273">
+        <v>1.07</v>
+      </c>
+      <c r="AE273">
         <v>1.03</v>
       </c>
-      <c r="X273">
-        <v>1.15</v>
-      </c>
-      <c r="Y273">
-        <v>1.67</v>
-      </c>
-      <c r="Z273">
-        <v>2.04</v>
-      </c>
-      <c r="AA273">
-        <v>3.08</v>
-      </c>
-      <c r="AB273">
-        <v>1.32</v>
-      </c>
-      <c r="AC273">
-        <v>6.7</v>
-      </c>
-      <c r="AD273">
-        <v>1.05</v>
-      </c>
-      <c r="AE273">
-        <v>1.02</v>
-      </c>
       <c r="AF273">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AG273">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK273">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G277">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G278">

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.36</v>
+        <v>2.11</v>
       </c>
       <c r="O2">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>7.3</v>
+        <v>2.94</v>
       </c>
       <c r="Q2">
-        <v>1.8</v>
+        <v>2.71</v>
       </c>
       <c r="R2">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="S2">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="U2">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="V2">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="Z2">
-        <v>4.2</v>
+        <v>2.92</v>
       </c>
       <c r="AA2">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="AB2">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="AC2">
-        <v>2.52</v>
+        <v>3.84</v>
       </c>
       <c r="AD2">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AE2">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
         <v>1.84</v>
       </c>
       <c r="AG2">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AK2">
-        <v>2.88</v>
+        <v>1.7</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.11</v>
+        <v>1.36</v>
       </c>
       <c r="O3">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="P3">
-        <v>2.94</v>
+        <v>7.3</v>
       </c>
       <c r="Q3">
-        <v>2.71</v>
+        <v>1.8</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="S3">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="U3">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="Z3">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="AA3">
-        <v>2.08</v>
+        <v>1.64</v>
       </c>
       <c r="AB3">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="AC3">
-        <v>3.84</v>
+        <v>2.52</v>
       </c>
       <c r="AD3">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AE3">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AF3">
         <v>1.84</v>
       </c>
       <c r="AG3">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AK3">
-        <v>1.7</v>
+        <v>2.88</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G4">
@@ -961,34 +961,34 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q4">
-        <v>4.39</v>
+        <v>2.91</v>
       </c>
       <c r="R4">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="S4">
         <v>1.36</v>
       </c>
       <c r="T4">
-        <v>2.64</v>
+        <v>2.71</v>
       </c>
       <c r="U4">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="V4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
         <v>1.02</v>
@@ -1000,25 +1000,25 @@
         <v>3.2</v>
       </c>
       <c r="AA4">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB4">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC4">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD4">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE4">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF4">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG4">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="AK4">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,34 +1124,34 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.91</v>
+        <v>4.39</v>
       </c>
       <c r="R5">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="S5">
         <v>1.36</v>
       </c>
       <c r="T5">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="U5">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="V5">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
         <v>1.02</v>
@@ -1163,25 +1163,25 @@
         <v>3.2</v>
       </c>
       <c r="AA5">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB5">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AC5">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD5">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE5">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG5">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AK5">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="O13">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="P13">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2591,31 +2591,31 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q14">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="R14">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S14">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="T14">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="U14">
-        <v>3.06</v>
+        <v>3.25</v>
       </c>
       <c r="V14">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W14">
         <v>1.03</v>
@@ -2624,31 +2624,31 @@
         <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z14">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AA14">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AB14">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AC14">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AD14">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE14">
         <v>1.02</v>
       </c>
       <c r="AF14">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AG14">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AK14">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="O15">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P15">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="O16">
         <v>3.25</v>
       </c>
       <c r="P16">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.07</v>
+        <v>2.39</v>
       </c>
       <c r="O17">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="P17">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="O18">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="P18">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="O19">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>3.32</v>
+        <v>4.3</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,80 +3732,80 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.53</v>
+        <v>4.4</v>
       </c>
       <c r="O21">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="P21">
-        <v>2.31</v>
+        <v>1.86</v>
       </c>
       <c r="Q21">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="R21">
         <v>2.01</v>
       </c>
       <c r="S21">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="T21">
-        <v>2.99</v>
+        <v>2.57</v>
       </c>
       <c r="U21">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="V21">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W21">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
+        <v>1.3</v>
+      </c>
+      <c r="Z21">
+        <v>2.97</v>
+      </c>
+      <c r="AA21">
+        <v>2.05</v>
+      </c>
+      <c r="AB21">
+        <v>1.8</v>
+      </c>
+      <c r="AC21">
+        <v>3.42</v>
+      </c>
+      <c r="AD21">
         <v>1.26</v>
       </c>
-      <c r="Z21">
-        <v>3.2</v>
-      </c>
-      <c r="AA21">
-        <v>1.96</v>
-      </c>
-      <c r="AB21">
+      <c r="AE21">
+        <v>1.04</v>
+      </c>
+      <c r="AF21">
+        <v>1.91</v>
+      </c>
+      <c r="AG21">
+        <v>1.83</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
         <v>1.85</v>
       </c>
-      <c r="AC21">
-        <v>3.14</v>
-      </c>
-      <c r="AD21">
-        <v>1.27</v>
-      </c>
-      <c r="AE21">
-        <v>1.07</v>
-      </c>
-      <c r="AF21">
-        <v>1.7</v>
-      </c>
-      <c r="AG21">
-        <v>2</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.3</v>
-      </c>
       <c r="AK21">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>4.4</v>
+        <v>2.53</v>
       </c>
       <c r="O22">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="P22">
-        <v>1.86</v>
+        <v>2.31</v>
       </c>
       <c r="Q22">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="R22">
         <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T22">
-        <v>2.57</v>
+        <v>2.99</v>
       </c>
       <c r="U22">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="V22">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
+        <v>1.06</v>
+      </c>
+      <c r="X22">
+        <v>1.03</v>
+      </c>
+      <c r="Y22">
+        <v>1.26</v>
+      </c>
+      <c r="Z22">
+        <v>3.2</v>
+      </c>
+      <c r="AA22">
+        <v>1.96</v>
+      </c>
+      <c r="AB22">
+        <v>1.85</v>
+      </c>
+      <c r="AC22">
+        <v>3.14</v>
+      </c>
+      <c r="AD22">
+        <v>1.27</v>
+      </c>
+      <c r="AE22">
         <v>1.07</v>
       </c>
-      <c r="X22">
-        <v>1.02</v>
-      </c>
-      <c r="Y22">
+      <c r="AF22">
+        <v>1.7</v>
+      </c>
+      <c r="AG22">
+        <v>2</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
         <v>1.3</v>
       </c>
-      <c r="Z22">
-        <v>2.97</v>
-      </c>
-      <c r="AA22">
-        <v>2.05</v>
-      </c>
-      <c r="AB22">
-        <v>1.8</v>
-      </c>
-      <c r="AC22">
-        <v>3.42</v>
-      </c>
-      <c r="AD22">
-        <v>1.26</v>
-      </c>
-      <c r="AE22">
-        <v>1.04</v>
-      </c>
-      <c r="AF22">
-        <v>1.91</v>
-      </c>
-      <c r="AG22">
-        <v>1.83</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.85</v>
-      </c>
       <c r="AK22">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.28</v>
+        <v>3.6</v>
       </c>
       <c r="O25">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
-        <v>2.82</v>
+        <v>1.85</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q26">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="R26">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="S26">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T26">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="U26">
         <v>3.3</v>
       </c>
       <c r="V26">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W26">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
+        <v>1.07</v>
+      </c>
+      <c r="Y26">
+        <v>1.46</v>
+      </c>
+      <c r="Z26">
+        <v>2.56</v>
+      </c>
+      <c r="AA26">
+        <v>2.38</v>
+      </c>
+      <c r="AB26">
+        <v>1.49</v>
+      </c>
+      <c r="AC26">
+        <v>4.6</v>
+      </c>
+      <c r="AD26">
+        <v>1.13</v>
+      </c>
+      <c r="AE26">
         <v>1.05</v>
       </c>
-      <c r="Y26">
-        <v>1.38</v>
-      </c>
-      <c r="Z26">
-        <v>2.62</v>
-      </c>
-      <c r="AA26">
-        <v>2.27</v>
-      </c>
-      <c r="AB26">
-        <v>1.54</v>
-      </c>
-      <c r="AC26">
-        <v>4.3</v>
-      </c>
-      <c r="AD26">
-        <v>1.15</v>
-      </c>
-      <c r="AE26">
-        <v>1.02</v>
-      </c>
       <c r="AF26">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AG26">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AK26">
-        <v>1.97</v>
+        <v>1.71</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,55 +4719,55 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="R27">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="S27">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="T27">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="U27">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="V27">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
+        <v>1.05</v>
+      </c>
+      <c r="Y27">
+        <v>1.36</v>
+      </c>
+      <c r="Z27">
+        <v>2.7</v>
+      </c>
+      <c r="AA27">
+        <v>2.27</v>
+      </c>
+      <c r="AB27">
+        <v>1.6</v>
+      </c>
+      <c r="AC27">
+        <v>3.94</v>
+      </c>
+      <c r="AD27">
+        <v>1.17</v>
+      </c>
+      <c r="AE27">
         <v>1.03</v>
       </c>
-      <c r="Y27">
-        <v>1.32</v>
-      </c>
-      <c r="Z27">
-        <v>2.88</v>
-      </c>
-      <c r="AA27">
-        <v>2.08</v>
-      </c>
-      <c r="AB27">
-        <v>1.64</v>
-      </c>
-      <c r="AC27">
-        <v>3.72</v>
-      </c>
-      <c r="AD27">
-        <v>1.2</v>
-      </c>
-      <c r="AE27">
-        <v>1.04</v>
-      </c>
       <c r="AF27">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AG27">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK27">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,46 +4873,46 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q28">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="R28">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="S28">
         <v>1.44</v>
       </c>
       <c r="T28">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U28">
         <v>3.24</v>
       </c>
       <c r="V28">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W28">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
         <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z28">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AA28">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AB28">
         <v>1.54</v>
@@ -4927,10 +4927,10 @@
         <v>1.02</v>
       </c>
       <c r="AF28">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AG28">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK28">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>4.06</v>
+        <v>3.77</v>
       </c>
       <c r="O29">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P29">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.56</v>
+        <v>2.19</v>
       </c>
       <c r="O32">
         <v>3.2</v>
       </c>
       <c r="P32">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="O33">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="P33">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O34">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="P34">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.57</v>
+        <v>2.85</v>
       </c>
       <c r="O35">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="P35">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="O49">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="P49">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8839,10 +8839,10 @@
         <v>1.06</v>
       </c>
       <c r="AF52">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG52">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,80 +9600,80 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="O57">
         <v>3.7</v>
       </c>
       <c r="P57">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="Q57">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="R57">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S57">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T57">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="U57">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V57">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="W57">
         <v>1.14</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z57">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA57">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AB57">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="AC57">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="AD57">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AE57">
+        <v>1.18</v>
+      </c>
+      <c r="AF57">
+        <v>1.45</v>
+      </c>
+      <c r="AG57">
+        <v>2.55</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
         <v>1.25</v>
       </c>
-      <c r="AF57">
-        <v>1.43</v>
-      </c>
-      <c r="AG57">
-        <v>2.58</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ57">
-        <v>1.16</v>
-      </c>
       <c r="AK57">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="O58">
         <v>3.7</v>
       </c>
       <c r="P58">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q58">
-        <v>2.52</v>
+        <v>2.24</v>
       </c>
       <c r="R58">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S58">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T58">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="U58">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V58">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="W58">
         <v>1.14</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z58">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA58">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB58">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="AC58">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="AD58">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AE58">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF58">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AG58">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK58">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -12374,7 +12374,7 @@
         <v>6.8</v>
       </c>
       <c r="O74">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P74">
         <v>1.49</v>
@@ -12386,10 +12386,10 @@
         <v>2.08</v>
       </c>
       <c r="S74">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T74">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="U74">
         <v>2.89</v>
@@ -12398,7 +12398,7 @@
         <v>1.36</v>
       </c>
       <c r="W74">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X74">
         <v>1</v>
@@ -12410,25 +12410,25 @@
         <v>3.08</v>
       </c>
       <c r="AA74">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB74">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC74">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AD74">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE74">
         <v>1.04</v>
       </c>
       <c r="AF74">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AG74">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q106">
-        <v>1.91</v>
+        <v>3.3</v>
       </c>
       <c r="R106">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="S106">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T106">
-        <v>3.07</v>
+        <v>3.4</v>
       </c>
       <c r="U106">
-        <v>2.77</v>
+        <v>2.61</v>
       </c>
       <c r="V106">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W106">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X106">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z106">
-        <v>3.72</v>
+        <v>4.1</v>
       </c>
       <c r="AA106">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AB106">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AC106">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AD106">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE106">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF106">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AG106">
-        <v>1.76</v>
+        <v>2.26</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AK106">
-        <v>2.62</v>
+        <v>1.34</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,80 +17750,80 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O107">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P107">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q107">
-        <v>3.3</v>
+        <v>1.91</v>
       </c>
       <c r="R107">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="S107">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T107">
-        <v>3.4</v>
+        <v>3.07</v>
       </c>
       <c r="U107">
-        <v>2.61</v>
+        <v>2.77</v>
       </c>
       <c r="V107">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W107">
+        <v>1.08</v>
+      </c>
+      <c r="X107">
+        <v>1.03</v>
+      </c>
+      <c r="Y107">
+        <v>1.2</v>
+      </c>
+      <c r="Z107">
+        <v>3.72</v>
+      </c>
+      <c r="AA107">
+        <v>1.8</v>
+      </c>
+      <c r="AB107">
+        <v>2</v>
+      </c>
+      <c r="AC107">
+        <v>2.83</v>
+      </c>
+      <c r="AD107">
+        <v>1.33</v>
+      </c>
+      <c r="AE107">
         <v>1.09</v>
       </c>
-      <c r="X107">
-        <v>1.01</v>
-      </c>
-      <c r="Y107">
-        <v>1.16</v>
-      </c>
-      <c r="Z107">
-        <v>4.1</v>
-      </c>
-      <c r="AA107">
-        <v>1.69</v>
-      </c>
-      <c r="AB107">
-        <v>2.11</v>
-      </c>
-      <c r="AC107">
+      <c r="AF107">
+        <v>1.95</v>
+      </c>
+      <c r="AG107">
+        <v>1.76</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ107">
+        <v>1.08</v>
+      </c>
+      <c r="AK107">
         <v>2.62</v>
-      </c>
-      <c r="AD107">
-        <v>1.4</v>
-      </c>
-      <c r="AE107">
-        <v>1.11</v>
-      </c>
-      <c r="AF107">
-        <v>1.55</v>
-      </c>
-      <c r="AG107">
-        <v>2.26</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ107">
-        <v>1.29</v>
-      </c>
-      <c r="AK107">
-        <v>1.34</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="O153">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P153">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="O154">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="P154">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="O164">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P164">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Q164">
         <v>0</v>
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="O167">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P167">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27693,10 +27693,10 @@
         </is>
       </c>
       <c r="N168">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="O168">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P168">
         <v>2.4</v>
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.89</v>
+        <v>4.2</v>
       </c>
       <c r="O183">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="P183">
-        <v>2.26</v>
+        <v>1.73</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30473,55 +30473,55 @@
         <v>0</v>
       </c>
       <c r="Q185">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="R185">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="S185">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T185">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="U185">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="V185">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W185">
         <v>1.07</v>
       </c>
       <c r="X185">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y185">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z185">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AA185">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB185">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AC185">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD185">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE185">
         <v>1.08</v>
       </c>
       <c r="AF185">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG185">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK185">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="O204">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P204">
-        <v>3.3</v>
+        <v>3.49</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="O206">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="P206">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="Q206">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="R206">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="S206">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T206">
         <v>3.75</v>
       </c>
       <c r="U206">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V206">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="W206">
         <v>1.14</v>
       </c>
       <c r="X206">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y206">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z206">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA206">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AB206">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AC206">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AD206">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AE206">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF206">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG206">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AK206">
-        <v>3.78</v>
+        <v>3.24</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.73</v>
+        <v>2.01</v>
       </c>
       <c r="O211">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P211">
-        <v>4.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G218">
@@ -35843,65 +35843,65 @@
         </is>
       </c>
       <c r="N218">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="O218">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P218">
-        <v>1.83</v>
+        <v>2.95</v>
       </c>
       <c r="Q218">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="R218">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="S218">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T218">
-        <v>3.12</v>
+        <v>2.82</v>
       </c>
       <c r="U218">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V218">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W218">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X218">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y218">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z218">
-        <v>4.4</v>
+        <v>3.58</v>
       </c>
       <c r="AA218">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AB218">
+        <v>2.08</v>
+      </c>
+      <c r="AC218">
+        <v>2.69</v>
+      </c>
+      <c r="AD218">
+        <v>1.41</v>
+      </c>
+      <c r="AE218">
+        <v>1.11</v>
+      </c>
+      <c r="AF218">
+        <v>1.6</v>
+      </c>
+      <c r="AG218">
         <v>2.25</v>
       </c>
-      <c r="AC218">
-        <v>2.63</v>
-      </c>
-      <c r="AD218">
-        <v>1.43</v>
-      </c>
-      <c r="AE218">
-        <v>1.14</v>
-      </c>
-      <c r="AF218">
-        <v>1.62</v>
-      </c>
-      <c r="AG218">
-        <v>2.15</v>
-      </c>
       <c r="AH218" t="inlineStr">
         <is>
           <t>[]</t>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK218">
-        <v>1.22</v>
+        <v>1.54</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G219">
@@ -36006,65 +36006,65 @@
         </is>
       </c>
       <c r="N219">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="O219">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P219">
-        <v>2.95</v>
+        <v>1.83</v>
       </c>
       <c r="Q219">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="R219">
+        <v>2.26</v>
+      </c>
+      <c r="S219">
+        <v>1.25</v>
+      </c>
+      <c r="T219">
+        <v>3.12</v>
+      </c>
+      <c r="U219">
+        <v>2.4</v>
+      </c>
+      <c r="V219">
+        <v>1.5</v>
+      </c>
+      <c r="W219">
+        <v>1.1</v>
+      </c>
+      <c r="X219">
+        <v>1.01</v>
+      </c>
+      <c r="Y219">
+        <v>1.18</v>
+      </c>
+      <c r="Z219">
+        <v>4.4</v>
+      </c>
+      <c r="AA219">
+        <v>1.64</v>
+      </c>
+      <c r="AB219">
+        <v>2.25</v>
+      </c>
+      <c r="AC219">
+        <v>2.63</v>
+      </c>
+      <c r="AD219">
+        <v>1.43</v>
+      </c>
+      <c r="AE219">
+        <v>1.14</v>
+      </c>
+      <c r="AF219">
+        <v>1.62</v>
+      </c>
+      <c r="AG219">
         <v>2.15</v>
       </c>
-      <c r="S219">
-        <v>1.35</v>
-      </c>
-      <c r="T219">
-        <v>2.82</v>
-      </c>
-      <c r="U219">
-        <v>2.45</v>
-      </c>
-      <c r="V219">
-        <v>1.47</v>
-      </c>
-      <c r="W219">
-        <v>1.07</v>
-      </c>
-      <c r="X219">
-        <v>1.02</v>
-      </c>
-      <c r="Y219">
-        <v>1.21</v>
-      </c>
-      <c r="Z219">
-        <v>3.58</v>
-      </c>
-      <c r="AA219">
-        <v>1.81</v>
-      </c>
-      <c r="AB219">
-        <v>2.08</v>
-      </c>
-      <c r="AC219">
-        <v>2.69</v>
-      </c>
-      <c r="AD219">
-        <v>1.41</v>
-      </c>
-      <c r="AE219">
-        <v>1.11</v>
-      </c>
-      <c r="AF219">
-        <v>1.6</v>
-      </c>
-      <c r="AG219">
-        <v>2.25</v>
-      </c>
       <c r="AH219" t="inlineStr">
         <is>
           <t>[]</t>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AK219">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="O221">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="P221">
-        <v>3.75</v>
+        <v>5.01</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="O222">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P222">
-        <v>3.57</v>
+        <v>4.71</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -38125,28 +38125,28 @@
         </is>
       </c>
       <c r="N232">
-        <v>2.28</v>
+        <v>2.49</v>
       </c>
       <c r="O232">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P232">
-        <v>3.1</v>
+        <v>2.58</v>
       </c>
       <c r="Q232">
+        <v>3.3</v>
+      </c>
+      <c r="R232">
+        <v>2.02</v>
+      </c>
+      <c r="S232">
+        <v>1.38</v>
+      </c>
+      <c r="T232">
         <v>2.88</v>
       </c>
-      <c r="R232">
-        <v>1.98</v>
-      </c>
-      <c r="S232">
-        <v>1.4</v>
-      </c>
-      <c r="T232">
-        <v>2.75</v>
-      </c>
       <c r="U232">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="V232">
         <v>1.36</v>
@@ -38158,16 +38158,16 @@
         <v>1.02</v>
       </c>
       <c r="Y232">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z232">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA232">
         <v>2.1</v>
       </c>
       <c r="AB232">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC232">
         <v>3.5</v>
@@ -38179,10 +38179,10 @@
         <v>1.04</v>
       </c>
       <c r="AF232">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AG232">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK232">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G245">
@@ -40244,64 +40244,64 @@
         </is>
       </c>
       <c r="N245">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O245">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="P245">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q245">
-        <v>2.89</v>
+        <v>3.57</v>
       </c>
       <c r="R245">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="S245">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="T245">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="U245">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="V245">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W245">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X245">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y245">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Z245">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AA245">
         <v>2.87</v>
       </c>
       <c r="AB245">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC245">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AD245">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AE245">
         <v>1.03</v>
       </c>
       <c r="AF245">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AG245">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40314,10 +40314,10 @@
         </is>
       </c>
       <c r="AJ245">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AK245">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G246">
@@ -40407,64 +40407,64 @@
         </is>
       </c>
       <c r="N246">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O246">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="P246">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q246">
-        <v>3.57</v>
+        <v>2.89</v>
       </c>
       <c r="R246">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="S246">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="T246">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="U246">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="V246">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W246">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X246">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Y246">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Z246">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AA246">
         <v>2.87</v>
       </c>
       <c r="AB246">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AC246">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AD246">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AE246">
         <v>1.03</v>
       </c>
       <c r="AF246">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG246">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -40477,10 +40477,10 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK246">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,64 +42689,64 @@
         </is>
       </c>
       <c r="N260">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="O260">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P260">
+        <v>3.5</v>
+      </c>
+      <c r="Q260">
+        <v>2.75</v>
+      </c>
+      <c r="R260">
+        <v>1.95</v>
+      </c>
+      <c r="S260">
+        <v>1.51</v>
+      </c>
+      <c r="T260">
         <v>2.5</v>
       </c>
-      <c r="Q260">
-        <v>3.52</v>
-      </c>
-      <c r="R260">
-        <v>2</v>
-      </c>
-      <c r="S260">
-        <v>1.4</v>
-      </c>
-      <c r="T260">
-        <v>2.88</v>
-      </c>
       <c r="U260">
-        <v>2.76</v>
+        <v>3.32</v>
       </c>
       <c r="V260">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W260">
         <v>1.03</v>
       </c>
       <c r="X260">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y260">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="Z260">
-        <v>3.08</v>
+        <v>2.49</v>
       </c>
       <c r="AA260">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB260">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="AC260">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="AD260">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AE260">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF260">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AG260">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK260">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G261">
@@ -42852,64 +42852,64 @@
         </is>
       </c>
       <c r="N261">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="O261">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P261">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q261">
-        <v>2.75</v>
+        <v>3.52</v>
       </c>
       <c r="R261">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S261">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="T261">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="U261">
-        <v>3.32</v>
+        <v>2.76</v>
       </c>
       <c r="V261">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="W261">
         <v>1.03</v>
       </c>
       <c r="X261">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y261">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="Z261">
-        <v>2.49</v>
+        <v>3.08</v>
       </c>
       <c r="AA261">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AB261">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="AC261">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD261">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AE261">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF261">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AG261">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -42922,10 +42922,10 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK261">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,28 +44808,28 @@
         </is>
       </c>
       <c r="N273">
-        <v>1.8</v>
+        <v>2.78</v>
       </c>
       <c r="O273">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P273">
-        <v>5.2</v>
+        <v>2.42</v>
       </c>
       <c r="Q273">
-        <v>2.5</v>
+        <v>3.96</v>
       </c>
       <c r="R273">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="S273">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="T273">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="U273">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="V273">
         <v>1.2</v>
@@ -44838,50 +44838,50 @@
         <v>1.04</v>
       </c>
       <c r="X273">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y273">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="Z273">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AA273">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AB273">
+        <v>1.4</v>
+      </c>
+      <c r="AC273">
+        <v>5.36</v>
+      </c>
+      <c r="AD273">
+        <v>1.1</v>
+      </c>
+      <c r="AE273">
+        <v>1.01</v>
+      </c>
+      <c r="AF273">
+        <v>2.12</v>
+      </c>
+      <c r="AG273">
+        <v>1.63</v>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ273">
+        <v>1.44</v>
+      </c>
+      <c r="AK273">
         <v>1.36</v>
-      </c>
-      <c r="AC273">
-        <v>5.8</v>
-      </c>
-      <c r="AD273">
-        <v>1.07</v>
-      </c>
-      <c r="AE273">
-        <v>1.03</v>
-      </c>
-      <c r="AF273">
-        <v>2.5</v>
-      </c>
-      <c r="AG273">
-        <v>1.46</v>
-      </c>
-      <c r="AH273" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI273" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ273">
-        <v>1.33</v>
-      </c>
-      <c r="AK273">
-        <v>1.79</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,28 +44971,28 @@
         </is>
       </c>
       <c r="N274">
-        <v>2.78</v>
+        <v>1.8</v>
       </c>
       <c r="O274">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P274">
-        <v>2.42</v>
+        <v>5.2</v>
       </c>
       <c r="Q274">
-        <v>3.96</v>
+        <v>2.5</v>
       </c>
       <c r="R274">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="S274">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="T274">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="U274">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="V274">
         <v>1.2</v>
@@ -45001,34 +45001,34 @@
         <v>1.04</v>
       </c>
       <c r="X274">
+        <v>1.09</v>
+      </c>
+      <c r="Y274">
+        <v>1.6</v>
+      </c>
+      <c r="Z274">
+        <v>2.15</v>
+      </c>
+      <c r="AA274">
+        <v>2.83</v>
+      </c>
+      <c r="AB274">
+        <v>1.36</v>
+      </c>
+      <c r="AC274">
+        <v>5.8</v>
+      </c>
+      <c r="AD274">
         <v>1.07</v>
       </c>
-      <c r="Y274">
-        <v>1.51</v>
-      </c>
-      <c r="Z274">
-        <v>2.33</v>
-      </c>
-      <c r="AA274">
-        <v>2.7</v>
-      </c>
-      <c r="AB274">
-        <v>1.4</v>
-      </c>
-      <c r="AC274">
-        <v>5.36</v>
-      </c>
-      <c r="AD274">
-        <v>1.1</v>
-      </c>
       <c r="AE274">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF274">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AG274">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,10 +45041,10 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AK274">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="AL274">
         <v>0</v>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G4">
@@ -961,65 +961,65 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q4">
-        <v>4.39</v>
+        <v>2.91</v>
       </c>
       <c r="R4">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="S4">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
-        <v>2.64</v>
+        <v>2.71</v>
       </c>
       <c r="U4">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="V4">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
         <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z4">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AA4">
+        <v>1.93</v>
+      </c>
+      <c r="AB4">
+        <v>1.75</v>
+      </c>
+      <c r="AC4">
+        <v>3.34</v>
+      </c>
+      <c r="AD4">
+        <v>1.24</v>
+      </c>
+      <c r="AE4">
+        <v>1.04</v>
+      </c>
+      <c r="AF4">
+        <v>1.73</v>
+      </c>
+      <c r="AG4">
         <v>1.98</v>
       </c>
-      <c r="AB4">
-        <v>1.77</v>
-      </c>
-      <c r="AC4">
-        <v>3.4</v>
-      </c>
-      <c r="AD4">
-        <v>1.29</v>
-      </c>
-      <c r="AE4">
-        <v>1.05</v>
-      </c>
-      <c r="AF4">
-        <v>1.8</v>
-      </c>
-      <c r="AG4">
-        <v>1.91</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="AK4">
-        <v>1.19</v>
+        <v>1.57</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.91</v>
+        <v>4.39</v>
       </c>
       <c r="R5">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T5">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="U5">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="V5">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W5">
         <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z5">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AA5">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AB5">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC5">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AD5">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE5">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF5">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG5">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.31</v>
+        <v>1.8</v>
       </c>
       <c r="AK5">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,31 +4710,31 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q27">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="R27">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="S27">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T27">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U27">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="V27">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W27">
         <v>1.06</v>
@@ -4743,31 +4743,31 @@
         <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z27">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AA27">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AB27">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AC27">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="AD27">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE27">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF27">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="AG27">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK27">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="R28">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="S28">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T28">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U28">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="V28">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W28">
         <v>1.06</v>
@@ -4906,31 +4906,31 @@
         <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z28">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AA28">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AB28">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AC28">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="AD28">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE28">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF28">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="AG28">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6847,7 +6847,7 @@
         <v>1.45</v>
       </c>
       <c r="T40">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="U40">
         <v>3.06</v>
@@ -6856,7 +6856,7 @@
         <v>1.29</v>
       </c>
       <c r="W40">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X40">
         <v>1.04</v>
@@ -6868,10 +6868,10 @@
         <v>2.59</v>
       </c>
       <c r="AA40">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AB40">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC40">
         <v>4.25</v>
@@ -6886,7 +6886,7 @@
         <v>1.93</v>
       </c>
       <c r="AG40">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK40">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7816,10 +7816,10 @@
         <v>1.95</v>
       </c>
       <c r="Q46">
-        <v>3.75</v>
+        <v>4.18</v>
       </c>
       <c r="R46">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S46">
         <v>1.29</v>
@@ -7828,37 +7828,37 @@
         <v>3.3</v>
       </c>
       <c r="U46">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V46">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W46">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
         <v>1.17</v>
       </c>
       <c r="Z46">
-        <v>4.21</v>
+        <v>4.25</v>
       </c>
       <c r="AA46">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB46">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC46">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="AD46">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE46">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF46">
         <v>1.6</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.25</v>
+        <v>1.82</v>
       </c>
       <c r="AK46">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -13512,34 +13512,34 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="O81">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="P81">
-        <v>3.86</v>
+        <v>3.68</v>
       </c>
       <c r="Q81">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R81">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S81">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T81">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U81">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="V81">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W81">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X81">
         <v>1.02</v>
@@ -13554,22 +13554,22 @@
         <v>1.47</v>
       </c>
       <c r="AB81">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AC81">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="AD81">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE81">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF81">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG81">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK81">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.87</v>
+        <v>1.29</v>
       </c>
       <c r="O95">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="P95">
-        <v>2.15</v>
+        <v>8.5</v>
       </c>
       <c r="Q95">
-        <v>3.3</v>
+        <v>1.62</v>
       </c>
       <c r="R95">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="S95">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T95">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="U95">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="V95">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W95">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="X95">
         <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z95">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AA95">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AB95">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AC95">
-        <v>2.23</v>
+        <v>2.49</v>
       </c>
       <c r="AD95">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AE95">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AF95">
-        <v>1.41</v>
+        <v>1.9</v>
       </c>
       <c r="AG95">
-        <v>2.73</v>
+        <v>1.76</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.67</v>
+        <v>1.04</v>
       </c>
       <c r="AK95">
-        <v>1.39</v>
+        <v>3.5</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.29</v>
+        <v>2.87</v>
       </c>
       <c r="O97">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="P97">
-        <v>8.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q97">
-        <v>1.62</v>
+        <v>3.3</v>
       </c>
       <c r="R97">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="S97">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T97">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="U97">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="V97">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W97">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="X97">
         <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z97">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AA97">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AB97">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AC97">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="AD97">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AE97">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AF97">
-        <v>1.9</v>
+        <v>1.41</v>
       </c>
       <c r="AG97">
-        <v>1.76</v>
+        <v>2.73</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="AK97">
-        <v>3.5</v>
+        <v>1.39</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -17913,19 +17913,19 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="O108">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="P108">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q108">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R108">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="S108">
         <v>1.29</v>
@@ -17970,7 +17970,7 @@
         <v>1.53</v>
       </c>
       <c r="AG108">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AK108">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -20032,61 +20032,61 @@
         </is>
       </c>
       <c r="N121">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="O121">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P121">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q121">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="R121">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S121">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T121">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U121">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="V121">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W121">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X121">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y121">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z121">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="AA121">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AB121">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC121">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AD121">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE121">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF121">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG121">
         <v>1.95</v>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK121">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -22498,10 +22498,10 @@
         <v>4.1</v>
       </c>
       <c r="U136">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="V136">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W136">
         <v>1.19</v>
@@ -25903,10 +25903,10 @@
         <v>1.5</v>
       </c>
       <c r="O157">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="P157">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="Q157">
         <v>1.95</v>
@@ -25915,7 +25915,7 @@
         <v>2.6</v>
       </c>
       <c r="S157">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T157">
         <v>3.6</v>
@@ -25933,7 +25933,7 @@
         <v>1.02</v>
       </c>
       <c r="Y157">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z157">
         <v>4.3</v>
@@ -25948,7 +25948,7 @@
         <v>2.58</v>
       </c>
       <c r="AD157">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AE157">
         <v>1.15</v>
@@ -26063,7 +26063,7 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="O158">
         <v>3.54</v>
@@ -26078,10 +26078,10 @@
         <v>2.46</v>
       </c>
       <c r="S158">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T158">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U158">
         <v>2.29</v>
@@ -26105,7 +26105,7 @@
         <v>1.64</v>
       </c>
       <c r="AB158">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="AC158">
         <v>2.55</v>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK158">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26226,7 +26226,7 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="O159">
         <v>5.1</v>
@@ -26235,7 +26235,7 @@
         <v>6</v>
       </c>
       <c r="Q159">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R159">
         <v>2.8</v>
@@ -26262,16 +26262,16 @@
         <v>1.05</v>
       </c>
       <c r="Z159">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="AA159">
         <v>1.29</v>
       </c>
       <c r="AB159">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AC159">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AD159">
         <v>2.01</v>
@@ -26280,7 +26280,7 @@
         <v>1.4</v>
       </c>
       <c r="AF159">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG159">
         <v>2.62</v>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AK159">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O188">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q188">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R188">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S188">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T188">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U188">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V188">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W188">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X188">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y188">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z188">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA188">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB188">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC188">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD188">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE188">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF188">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG188">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK188">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -35200,16 +35200,16 @@
         <v>0</v>
       </c>
       <c r="Q214">
-        <v>3.55</v>
+        <v>3.82</v>
       </c>
       <c r="R214">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S214">
         <v>1.4</v>
       </c>
       <c r="T214">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="U214">
         <v>2.8</v>
@@ -35218,7 +35218,7 @@
         <v>1.4</v>
       </c>
       <c r="W214">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X214">
         <v>1.03</v>
@@ -35227,16 +35227,16 @@
         <v>1.25</v>
       </c>
       <c r="Z214">
-        <v>3.78</v>
+        <v>3.81</v>
       </c>
       <c r="AA214">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AB214">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC214">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD214">
         <v>1.33</v>
@@ -35245,7 +35245,7 @@
         <v>1.06</v>
       </c>
       <c r="AF214">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG214">
         <v>2.05</v>
@@ -35264,7 +35264,7 @@
         <v>1.27</v>
       </c>
       <c r="AK214">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35366,19 +35366,19 @@
         <v>1.95</v>
       </c>
       <c r="R215">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="S215">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T215">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="U215">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="V215">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W215">
         <v>1.14</v>
@@ -35390,7 +35390,7 @@
         <v>1.1</v>
       </c>
       <c r="Z215">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="AA215">
         <v>1.53</v>
@@ -35405,7 +35405,7 @@
         <v>1.59</v>
       </c>
       <c r="AE215">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF215">
         <v>1.57</v>
@@ -38297,7 +38297,7 @@
         <v>1.63</v>
       </c>
       <c r="Q233">
-        <v>4.4</v>
+        <v>3.88</v>
       </c>
       <c r="R233">
         <v>2.63</v>
@@ -38306,13 +38306,13 @@
         <v>1.15</v>
       </c>
       <c r="T233">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="U233">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="V233">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="W233">
         <v>1.2</v>
@@ -38321,22 +38321,22 @@
         <v>1.01</v>
       </c>
       <c r="Y233">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z233">
-        <v>6.7</v>
+        <v>6.75</v>
       </c>
       <c r="AA233">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB233">
         <v>3.2</v>
       </c>
       <c r="AC233">
+        <v>1.78</v>
+      </c>
+      <c r="AD233">
         <v>1.89</v>
-      </c>
-      <c r="AD233">
-        <v>1.93</v>
       </c>
       <c r="AE233">
         <v>1.42</v>
@@ -38345,7 +38345,7 @@
         <v>1.36</v>
       </c>
       <c r="AG233">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,7 +38358,7 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK233">
         <v>1.2</v>
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G252">
@@ -41385,64 +41385,64 @@
         </is>
       </c>
       <c r="N252">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="O252">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="P252">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q252">
-        <v>3.7</v>
+        <v>2.63</v>
       </c>
       <c r="R252">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="S252">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T252">
-        <v>2.44</v>
+        <v>2.94</v>
       </c>
       <c r="U252">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="V252">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W252">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X252">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y252">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z252">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA252">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB252">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC252">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AD252">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE252">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF252">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG252">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK252">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,65 +41548,65 @@
         </is>
       </c>
       <c r="N253">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="O253">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="P253">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q253">
-        <v>2.63</v>
+        <v>3.7</v>
       </c>
       <c r="R253">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="S253">
+        <v>1.44</v>
+      </c>
+      <c r="T253">
+        <v>2.44</v>
+      </c>
+      <c r="U253">
+        <v>2.71</v>
+      </c>
+      <c r="V253">
         <v>1.36</v>
       </c>
-      <c r="T253">
-        <v>2.94</v>
-      </c>
-      <c r="U253">
-        <v>2.75</v>
-      </c>
-      <c r="V253">
-        <v>1.4</v>
-      </c>
       <c r="W253">
+        <v>1.05</v>
+      </c>
+      <c r="X253">
+        <v>1.04</v>
+      </c>
+      <c r="Y253">
+        <v>1.26</v>
+      </c>
+      <c r="Z253">
+        <v>3.2</v>
+      </c>
+      <c r="AA253">
+        <v>2.05</v>
+      </c>
+      <c r="AB253">
+        <v>1.75</v>
+      </c>
+      <c r="AC253">
+        <v>2.97</v>
+      </c>
+      <c r="AD253">
+        <v>1.3</v>
+      </c>
+      <c r="AE253">
         <v>1.08</v>
       </c>
-      <c r="X253">
-        <v>1.01</v>
-      </c>
-      <c r="Y253">
-        <v>1.23</v>
-      </c>
-      <c r="Z253">
-        <v>3.42</v>
-      </c>
-      <c r="AA253">
+      <c r="AF253">
+        <v>1.65</v>
+      </c>
+      <c r="AG253">
         <v>2.07</v>
       </c>
-      <c r="AB253">
-        <v>1.72</v>
-      </c>
-      <c r="AC253">
-        <v>3.08</v>
-      </c>
-      <c r="AD253">
-        <v>1.28</v>
-      </c>
-      <c r="AE253">
-        <v>1.06</v>
-      </c>
-      <c r="AF253">
-        <v>1.68</v>
-      </c>
-      <c r="AG253">
-        <v>2.02</v>
-      </c>
       <c r="AH253" t="inlineStr">
         <is>
           <t>[]</t>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK253">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O256">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P256">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -42200,13 +42200,13 @@
         </is>
       </c>
       <c r="N257">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O257">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P257">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q257">
         <v>0</v>
@@ -42698,10 +42698,10 @@
         <v>3.5</v>
       </c>
       <c r="Q260">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R260">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S260">
         <v>1.51</v>
@@ -42740,13 +42740,13 @@
         <v>1.14</v>
       </c>
       <c r="AE260">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF260">
         <v>2</v>
       </c>
       <c r="AG260">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>2.5</v>
       </c>
       <c r="Q261">
-        <v>3.52</v>
+        <v>3.13</v>
       </c>
       <c r="R261">
         <v>2</v>
@@ -42876,7 +42876,7 @@
         <v>2.76</v>
       </c>
       <c r="V261">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W261">
         <v>1.03</v>
@@ -42891,7 +42891,7 @@
         <v>3.08</v>
       </c>
       <c r="AA261">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AB261">
         <v>1.79</v>
@@ -42900,7 +42900,7 @@
         <v>3.6</v>
       </c>
       <c r="AD261">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE261">
         <v>1.04</v>
@@ -43688,10 +43688,10 @@
         <v>2.88</v>
       </c>
       <c r="U266">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V266">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W266">
         <v>1.1</v>
@@ -43740,7 +43740,7 @@
         <v>1.34</v>
       </c>
       <c r="AK266">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,64 +44808,64 @@
         </is>
       </c>
       <c r="N273">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="O273">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P273">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="Q273">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="R273">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="S273">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="T273">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U273">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="V273">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W273">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X273">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Y273">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="Z273">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AA273">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="AB273">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC273">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="AD273">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AE273">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF273">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AG273">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK273">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,64 +44971,64 @@
         </is>
       </c>
       <c r="N274">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="O274">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P274">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="Q274">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="R274">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="S274">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="T274">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U274">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="V274">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W274">
+        <v>1.04</v>
+      </c>
+      <c r="X274">
+        <v>1.09</v>
+      </c>
+      <c r="Y274">
+        <v>1.6</v>
+      </c>
+      <c r="Z274">
+        <v>2.15</v>
+      </c>
+      <c r="AA274">
+        <v>2.83</v>
+      </c>
+      <c r="AB274">
+        <v>1.36</v>
+      </c>
+      <c r="AC274">
+        <v>5.8</v>
+      </c>
+      <c r="AD274">
+        <v>1.07</v>
+      </c>
+      <c r="AE274">
         <v>1.03</v>
       </c>
-      <c r="X274">
-        <v>1.15</v>
-      </c>
-      <c r="Y274">
-        <v>1.67</v>
-      </c>
-      <c r="Z274">
-        <v>2.04</v>
-      </c>
-      <c r="AA274">
-        <v>3.08</v>
-      </c>
-      <c r="AB274">
-        <v>1.32</v>
-      </c>
-      <c r="AC274">
-        <v>6.7</v>
-      </c>
-      <c r="AD274">
-        <v>1.05</v>
-      </c>
-      <c r="AE274">
-        <v>1.02</v>
-      </c>
       <c r="AF274">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AG274">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,10 +45041,10 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK274">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45804,46 +45804,46 @@
         <v>1.26</v>
       </c>
       <c r="T279">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="U279">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V279">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W279">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X279">
         <v>1</v>
       </c>
       <c r="Y279">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z279">
-        <v>3.78</v>
+        <v>3.95</v>
       </c>
       <c r="AA279">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB279">
         <v>2.01</v>
       </c>
       <c r="AC279">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD279">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE279">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF279">
         <v>1.61</v>
       </c>
       <c r="AG279">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45859,7 +45859,7 @@
         <v>1.23</v>
       </c>
       <c r="AK279">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -46296,10 +46296,10 @@
         <v>3.32</v>
       </c>
       <c r="U282">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V282">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W282">
         <v>1.08</v>
@@ -46308,7 +46308,7 @@
         <v>1.02</v>
       </c>
       <c r="Y282">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z282">
         <v>4.33</v>
@@ -46348,7 +46348,7 @@
         <v>1.18</v>
       </c>
       <c r="AK282">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -46948,7 +46948,7 @@
         <v>3.01</v>
       </c>
       <c r="U286">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="V286">
         <v>1.39</v>
@@ -47096,13 +47096,13 @@
         <v>3.3</v>
       </c>
       <c r="P287">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="Q287">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R287">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S287">
         <v>1.4</v>
@@ -47114,25 +47114,25 @@
         <v>2.99</v>
       </c>
       <c r="V287">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W287">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X287">
         <v>1.03</v>
       </c>
       <c r="Y287">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z287">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="AA287">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AB287">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC287">
         <v>3.8</v>
@@ -47147,23 +47147,23 @@
         <v>1.95</v>
       </c>
       <c r="AG287">
+        <v>1.75</v>
+      </c>
+      <c r="AH287" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI287" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ287">
+        <v>1.2</v>
+      </c>
+      <c r="AK287">
         <v>1.76</v>
-      </c>
-      <c r="AH287" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI287" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ287">
-        <v>1.17</v>
-      </c>
-      <c r="AK287">
-        <v>1.83</v>
       </c>
       <c r="AL287">
         <v>0</v>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G2">
@@ -635,31 +635,31 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.11</v>
+        <v>1.44</v>
       </c>
       <c r="O2">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="P2">
-        <v>2.94</v>
+        <v>6.4</v>
       </c>
       <c r="Q2">
-        <v>2.71</v>
+        <v>1.88</v>
       </c>
       <c r="R2">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S2">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="U2">
-        <v>3.14</v>
+        <v>2.38</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
         <v>1.07</v>
@@ -668,31 +668,31 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="Z2">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="AA2">
-        <v>2.08</v>
+        <v>1.64</v>
       </c>
       <c r="AB2">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="AC2">
-        <v>3.84</v>
+        <v>2.52</v>
       </c>
       <c r="AD2">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="AE2">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AF2">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG2">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK2">
-        <v>1.7</v>
+        <v>2.69</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3">
@@ -798,31 +798,31 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.44</v>
+        <v>2.11</v>
       </c>
       <c r="O3">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="P3">
-        <v>6.4</v>
+        <v>2.94</v>
       </c>
       <c r="Q3">
-        <v>1.88</v>
+        <v>2.71</v>
       </c>
       <c r="R3">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="U3">
-        <v>2.38</v>
+        <v>3.14</v>
       </c>
       <c r="V3">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
         <v>1.07</v>
@@ -831,31 +831,31 @@
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="Z3">
-        <v>4.2</v>
+        <v>2.92</v>
       </c>
       <c r="AA3">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="AB3">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="AC3">
-        <v>2.52</v>
+        <v>3.84</v>
       </c>
       <c r="AD3">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="AE3">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG3">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>2.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.53</v>
+        <v>3.6</v>
       </c>
       <c r="O21">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="P21">
-        <v>2.31</v>
+        <v>1.86</v>
       </c>
       <c r="Q21">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="R21">
         <v>2.01</v>
       </c>
       <c r="S21">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="T21">
-        <v>2.99</v>
+        <v>2.57</v>
       </c>
       <c r="U21">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="V21">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W21">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z21">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA21">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB21">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AC21">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AD21">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE21">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF21">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AG21">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="AK21">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="O22">
-        <v>3.23</v>
+        <v>3.38</v>
       </c>
       <c r="P22">
-        <v>1.86</v>
+        <v>2.31</v>
       </c>
       <c r="Q22">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="R22">
         <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T22">
-        <v>2.57</v>
+        <v>2.99</v>
       </c>
       <c r="U22">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="V22">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
+        <v>1.06</v>
+      </c>
+      <c r="X22">
+        <v>1.03</v>
+      </c>
+      <c r="Y22">
+        <v>1.26</v>
+      </c>
+      <c r="Z22">
+        <v>3.2</v>
+      </c>
+      <c r="AA22">
+        <v>1.9</v>
+      </c>
+      <c r="AB22">
+        <v>1.87</v>
+      </c>
+      <c r="AC22">
+        <v>3.14</v>
+      </c>
+      <c r="AD22">
+        <v>1.27</v>
+      </c>
+      <c r="AE22">
         <v>1.07</v>
       </c>
-      <c r="X22">
-        <v>1.02</v>
-      </c>
-      <c r="Y22">
-        <v>1.3</v>
-      </c>
-      <c r="Z22">
-        <v>2.97</v>
-      </c>
-      <c r="AA22">
-        <v>2.05</v>
-      </c>
-      <c r="AB22">
+      <c r="AF22">
         <v>1.7</v>
       </c>
-      <c r="AC22">
-        <v>3.42</v>
-      </c>
-      <c r="AD22">
-        <v>1.23</v>
-      </c>
-      <c r="AE22">
-        <v>1.04</v>
-      </c>
-      <c r="AF22">
-        <v>1.91</v>
-      </c>
       <c r="AG22">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="AK22">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,31 +4710,31 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="R27">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="S27">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T27">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U27">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="V27">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
         <v>1.06</v>
@@ -4743,31 +4743,31 @@
         <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z27">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AA27">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AB27">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AC27">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="AD27">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF27">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="AG27">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK27">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q28">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="R28">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="S28">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T28">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U28">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="V28">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W28">
         <v>1.06</v>
@@ -4906,31 +4906,31 @@
         <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z28">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AA28">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AB28">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AC28">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="AD28">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE28">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF28">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="AG28">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK28">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,80 +9600,80 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="O57">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P57">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="Q57">
+        <v>2.55</v>
+      </c>
+      <c r="R57">
+        <v>2.3</v>
+      </c>
+      <c r="S57">
+        <v>1.22</v>
+      </c>
+      <c r="T57">
+        <v>3.8</v>
+      </c>
+      <c r="U57">
         <v>2.25</v>
       </c>
-      <c r="R57">
-        <v>2.5</v>
-      </c>
-      <c r="S57">
-        <v>1.21</v>
-      </c>
-      <c r="T57">
-        <v>3.64</v>
-      </c>
-      <c r="U57">
-        <v>2.1</v>
-      </c>
       <c r="V57">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="W57">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z57">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA57">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AB57">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="AC57">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="AD57">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AE57">
+        <v>1.18</v>
+      </c>
+      <c r="AF57">
+        <v>1.45</v>
+      </c>
+      <c r="AG57">
+        <v>2.55</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
         <v>1.25</v>
       </c>
-      <c r="AF57">
-        <v>1.43</v>
-      </c>
-      <c r="AG57">
-        <v>2.58</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ57">
-        <v>1.16</v>
-      </c>
       <c r="AK57">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
+        <v>1.75</v>
+      </c>
+      <c r="O58">
+        <v>3.7</v>
+      </c>
+      <c r="P58">
+        <v>3.6</v>
+      </c>
+      <c r="Q58">
+        <v>2.25</v>
+      </c>
+      <c r="R58">
+        <v>2.5</v>
+      </c>
+      <c r="S58">
+        <v>1.21</v>
+      </c>
+      <c r="T58">
+        <v>3.64</v>
+      </c>
+      <c r="U58">
         <v>2.1</v>
       </c>
-      <c r="O58">
-        <v>3.75</v>
-      </c>
-      <c r="P58">
-        <v>3</v>
-      </c>
-      <c r="Q58">
-        <v>2.55</v>
-      </c>
-      <c r="R58">
-        <v>2.3</v>
-      </c>
-      <c r="S58">
-        <v>1.22</v>
-      </c>
-      <c r="T58">
-        <v>3.8</v>
-      </c>
-      <c r="U58">
-        <v>2.25</v>
-      </c>
       <c r="V58">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="W58">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X58">
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z58">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA58">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AB58">
-        <v>2.27</v>
+        <v>2.7</v>
       </c>
       <c r="AC58">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="AD58">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="AE58">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF58">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AG58">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK58">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O106">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P106">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q106">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="R106">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S106">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="T106">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="U106">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="V106">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="W106">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X106">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z106">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA106">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AB106">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AC106">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AD106">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE106">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF106">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AG106">
-        <v>2.28</v>
+        <v>1.76</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AK106">
-        <v>1.4</v>
+        <v>2.62</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,65 +17750,65 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q107">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="R107">
+        <v>2.25</v>
+      </c>
+      <c r="S107">
+        <v>1.26</v>
+      </c>
+      <c r="T107">
+        <v>3.4</v>
+      </c>
+      <c r="U107">
+        <v>2.59</v>
+      </c>
+      <c r="V107">
+        <v>1.47</v>
+      </c>
+      <c r="W107">
+        <v>1.1</v>
+      </c>
+      <c r="X107">
+        <v>1.01</v>
+      </c>
+      <c r="Y107">
+        <v>1.16</v>
+      </c>
+      <c r="Z107">
+        <v>4.1</v>
+      </c>
+      <c r="AA107">
+        <v>1.69</v>
+      </c>
+      <c r="AB107">
+        <v>2.14</v>
+      </c>
+      <c r="AC107">
+        <v>2.59</v>
+      </c>
+      <c r="AD107">
+        <v>1.4</v>
+      </c>
+      <c r="AE107">
+        <v>1.12</v>
+      </c>
+      <c r="AF107">
+        <v>1.57</v>
+      </c>
+      <c r="AG107">
         <v>2.28</v>
       </c>
-      <c r="S107">
-        <v>1.33</v>
-      </c>
-      <c r="T107">
-        <v>2.96</v>
-      </c>
-      <c r="U107">
-        <v>2.75</v>
-      </c>
-      <c r="V107">
-        <v>1.42</v>
-      </c>
-      <c r="W107">
-        <v>1.05</v>
-      </c>
-      <c r="X107">
-        <v>1.03</v>
-      </c>
-      <c r="Y107">
-        <v>1.19</v>
-      </c>
-      <c r="Z107">
-        <v>3.74</v>
-      </c>
-      <c r="AA107">
-        <v>1.85</v>
-      </c>
-      <c r="AB107">
-        <v>1.95</v>
-      </c>
-      <c r="AC107">
-        <v>2.83</v>
-      </c>
-      <c r="AD107">
-        <v>1.33</v>
-      </c>
-      <c r="AE107">
-        <v>1.09</v>
-      </c>
-      <c r="AF107">
-        <v>1.95</v>
-      </c>
-      <c r="AG107">
-        <v>1.76</v>
-      </c>
       <c r="AH107" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AK107">
-        <v>2.62</v>
+        <v>1.4</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G252">
@@ -41385,65 +41385,65 @@
         </is>
       </c>
       <c r="N252">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="O252">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="P252">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q252">
-        <v>2.63</v>
+        <v>3.7</v>
       </c>
       <c r="R252">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="S252">
+        <v>1.44</v>
+      </c>
+      <c r="T252">
+        <v>2.44</v>
+      </c>
+      <c r="U252">
+        <v>2.71</v>
+      </c>
+      <c r="V252">
         <v>1.36</v>
       </c>
-      <c r="T252">
-        <v>2.94</v>
-      </c>
-      <c r="U252">
-        <v>2.75</v>
-      </c>
-      <c r="V252">
-        <v>1.4</v>
-      </c>
       <c r="W252">
+        <v>1.05</v>
+      </c>
+      <c r="X252">
+        <v>1.04</v>
+      </c>
+      <c r="Y252">
+        <v>1.26</v>
+      </c>
+      <c r="Z252">
+        <v>3.2</v>
+      </c>
+      <c r="AA252">
+        <v>2.05</v>
+      </c>
+      <c r="AB252">
+        <v>1.75</v>
+      </c>
+      <c r="AC252">
+        <v>2.97</v>
+      </c>
+      <c r="AD252">
+        <v>1.3</v>
+      </c>
+      <c r="AE252">
         <v>1.08</v>
       </c>
-      <c r="X252">
-        <v>1.01</v>
-      </c>
-      <c r="Y252">
-        <v>1.23</v>
-      </c>
-      <c r="Z252">
-        <v>3.42</v>
-      </c>
-      <c r="AA252">
+      <c r="AF252">
+        <v>1.65</v>
+      </c>
+      <c r="AG252">
         <v>2.07</v>
       </c>
-      <c r="AB252">
-        <v>1.72</v>
-      </c>
-      <c r="AC252">
-        <v>3.08</v>
-      </c>
-      <c r="AD252">
-        <v>1.28</v>
-      </c>
-      <c r="AE252">
-        <v>1.06</v>
-      </c>
-      <c r="AF252">
-        <v>1.68</v>
-      </c>
-      <c r="AG252">
-        <v>2.02</v>
-      </c>
       <c r="AH252" t="inlineStr">
         <is>
           <t>[]</t>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK252">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,64 +41548,64 @@
         </is>
       </c>
       <c r="N253">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="O253">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="P253">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q253">
-        <v>3.7</v>
+        <v>2.63</v>
       </c>
       <c r="R253">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="S253">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T253">
-        <v>2.44</v>
+        <v>2.94</v>
       </c>
       <c r="U253">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="V253">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W253">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X253">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y253">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z253">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA253">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB253">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC253">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AD253">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE253">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF253">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG253">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK253">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -45810,37 +45810,37 @@
         <v>2.4</v>
       </c>
       <c r="V279">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W279">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X279">
         <v>1</v>
       </c>
       <c r="Y279">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z279">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="AA279">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB279">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AC279">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD279">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE279">
         <v>1.16</v>
       </c>
       <c r="AF279">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG279">
         <v>2.2</v>
@@ -45859,7 +45859,7 @@
         <v>1.23</v>
       </c>
       <c r="AK279">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AL279">
         <v>0</v>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2">
@@ -635,31 +635,31 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.44</v>
+        <v>2.11</v>
       </c>
       <c r="O2">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>6.4</v>
+        <v>2.94</v>
       </c>
       <c r="Q2">
-        <v>1.88</v>
+        <v>2.71</v>
       </c>
       <c r="R2">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S2">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="U2">
-        <v>2.38</v>
+        <v>3.14</v>
       </c>
       <c r="V2">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
         <v>1.07</v>
@@ -668,31 +668,31 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>4.2</v>
+        <v>2.92</v>
       </c>
       <c r="AA2">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="AB2">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="AC2">
-        <v>2.52</v>
+        <v>3.84</v>
       </c>
       <c r="AD2">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="AE2">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG2">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>2.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G3">
@@ -798,31 +798,31 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.11</v>
+        <v>1.44</v>
       </c>
       <c r="O3">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="P3">
-        <v>2.94</v>
+        <v>6.4</v>
       </c>
       <c r="Q3">
-        <v>2.71</v>
+        <v>1.88</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S3">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="U3">
-        <v>3.14</v>
+        <v>2.38</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
         <v>1.07</v>
@@ -831,31 +831,31 @@
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="Z3">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="AA3">
-        <v>2.08</v>
+        <v>1.64</v>
       </c>
       <c r="AB3">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="AC3">
-        <v>3.84</v>
+        <v>2.52</v>
       </c>
       <c r="AD3">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="AE3">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AF3">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG3">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK3">
-        <v>1.7</v>
+        <v>2.69</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.91</v>
+        <v>4.39</v>
       </c>
       <c r="R4">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="S4">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T4">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="U4">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W4">
         <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z4">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AA4">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AB4">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC4">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AD4">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE4">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF4">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG4">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.31</v>
+        <v>1.8</v>
       </c>
       <c r="AK4">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,65 +1124,65 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q5">
-        <v>4.39</v>
+        <v>2.91</v>
       </c>
       <c r="R5">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="S5">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T5">
-        <v>2.64</v>
+        <v>2.71</v>
       </c>
       <c r="U5">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="V5">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
         <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z5">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AA5">
+        <v>1.93</v>
+      </c>
+      <c r="AB5">
+        <v>1.75</v>
+      </c>
+      <c r="AC5">
+        <v>3.34</v>
+      </c>
+      <c r="AD5">
+        <v>1.24</v>
+      </c>
+      <c r="AE5">
+        <v>1.04</v>
+      </c>
+      <c r="AF5">
+        <v>1.73</v>
+      </c>
+      <c r="AG5">
         <v>1.98</v>
       </c>
-      <c r="AB5">
-        <v>1.77</v>
-      </c>
-      <c r="AC5">
-        <v>3.4</v>
-      </c>
-      <c r="AD5">
-        <v>1.29</v>
-      </c>
-      <c r="AE5">
-        <v>1.05</v>
-      </c>
-      <c r="AF5">
-        <v>1.8</v>
-      </c>
-      <c r="AG5">
-        <v>1.91</v>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="AK5">
-        <v>1.19</v>
+        <v>1.57</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O13">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P13">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AB13">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="O14">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="Q14">
         <v>2.8</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="O16">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="O17">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="P17">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="O18">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P18">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="O21">
-        <v>3.23</v>
+        <v>3.38</v>
       </c>
       <c r="P21">
-        <v>1.86</v>
+        <v>2.31</v>
       </c>
       <c r="Q21">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="R21">
         <v>2.01</v>
       </c>
       <c r="S21">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T21">
-        <v>2.57</v>
+        <v>2.99</v>
       </c>
       <c r="U21">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="V21">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W21">
+        <v>1.06</v>
+      </c>
+      <c r="X21">
+        <v>1.03</v>
+      </c>
+      <c r="Y21">
+        <v>1.26</v>
+      </c>
+      <c r="Z21">
+        <v>3.2</v>
+      </c>
+      <c r="AA21">
+        <v>1.9</v>
+      </c>
+      <c r="AB21">
+        <v>1.87</v>
+      </c>
+      <c r="AC21">
+        <v>3.14</v>
+      </c>
+      <c r="AD21">
+        <v>1.27</v>
+      </c>
+      <c r="AE21">
         <v>1.07</v>
       </c>
-      <c r="X21">
-        <v>1.02</v>
-      </c>
-      <c r="Y21">
-        <v>1.3</v>
-      </c>
-      <c r="Z21">
-        <v>2.97</v>
-      </c>
-      <c r="AA21">
-        <v>2.05</v>
-      </c>
-      <c r="AB21">
+      <c r="AF21">
         <v>1.7</v>
       </c>
-      <c r="AC21">
-        <v>3.42</v>
-      </c>
-      <c r="AD21">
-        <v>1.23</v>
-      </c>
-      <c r="AE21">
-        <v>1.04</v>
-      </c>
-      <c r="AF21">
-        <v>1.91</v>
-      </c>
       <c r="AG21">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="AK21">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.53</v>
+        <v>3.6</v>
       </c>
       <c r="O22">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="P22">
-        <v>2.31</v>
+        <v>1.86</v>
       </c>
       <c r="Q22">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="R22">
         <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="T22">
-        <v>2.99</v>
+        <v>2.57</v>
       </c>
       <c r="U22">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="V22">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W22">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z22">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA22">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB22">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AC22">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AD22">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE22">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AG22">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="AK22">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4387,7 +4387,7 @@
         <v>3.6</v>
       </c>
       <c r="O25">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
         <v>1.85</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB25">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -4547,16 +4547,16 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="O26">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P26">
-        <v>4.9</v>
+        <v>3.65</v>
       </c>
       <c r="Q26">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="R26">
         <v>1.83</v>
@@ -4568,10 +4568,10 @@
         <v>2.45</v>
       </c>
       <c r="U26">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="V26">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="W26">
         <v>1.05</v>
@@ -4586,10 +4586,10 @@
         <v>2.56</v>
       </c>
       <c r="AA26">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AB26">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AC26">
         <v>4.6</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK26">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q27">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="R27">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="S27">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="T27">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="U27">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="V27">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
         <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z27">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="AA27">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AB27">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AC27">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="AD27">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE27">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF27">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="AG27">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK27">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="R28">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="S28">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T28">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U28">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="V28">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X28">
         <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z28">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AA28">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AB28">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AC28">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="AD28">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE28">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF28">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AG28">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK28">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.77</v>
+        <v>3.48</v>
       </c>
       <c r="O29">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB29">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="O32">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P32">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB32">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5691,10 +5691,10 @@
         <v>1.75</v>
       </c>
       <c r="O33">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="P33">
-        <v>4.33</v>
+        <v>4.54</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5854,10 +5854,10 @@
         <v>2.6</v>
       </c>
       <c r="O34">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="O40">
         <v>3</v>
@@ -6844,7 +6844,7 @@
         <v>1.89</v>
       </c>
       <c r="S40">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T40">
         <v>2.42</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="O49">
         <v>3.04</v>
       </c>
       <c r="P49">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB49">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
+        <v>1.75</v>
+      </c>
+      <c r="O57">
+        <v>3.7</v>
+      </c>
+      <c r="P57">
+        <v>3.6</v>
+      </c>
+      <c r="Q57">
+        <v>2.25</v>
+      </c>
+      <c r="R57">
+        <v>2.5</v>
+      </c>
+      <c r="S57">
+        <v>1.21</v>
+      </c>
+      <c r="T57">
+        <v>3.64</v>
+      </c>
+      <c r="U57">
         <v>2.1</v>
       </c>
-      <c r="O57">
-        <v>3.75</v>
-      </c>
-      <c r="P57">
-        <v>3</v>
-      </c>
-      <c r="Q57">
-        <v>2.55</v>
-      </c>
-      <c r="R57">
-        <v>2.3</v>
-      </c>
-      <c r="S57">
-        <v>1.22</v>
-      </c>
-      <c r="T57">
-        <v>3.8</v>
-      </c>
-      <c r="U57">
-        <v>2.25</v>
-      </c>
       <c r="V57">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="W57">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z57">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA57">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AB57">
-        <v>2.27</v>
+        <v>2.7</v>
       </c>
       <c r="AC57">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="AD57">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="AE57">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF57">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AG57">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK57">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,80 +9763,80 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="O58">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P58">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="Q58">
+        <v>2.55</v>
+      </c>
+      <c r="R58">
+        <v>2.3</v>
+      </c>
+      <c r="S58">
+        <v>1.22</v>
+      </c>
+      <c r="T58">
+        <v>3.8</v>
+      </c>
+      <c r="U58">
         <v>2.25</v>
       </c>
-      <c r="R58">
-        <v>2.5</v>
-      </c>
-      <c r="S58">
-        <v>1.21</v>
-      </c>
-      <c r="T58">
-        <v>3.64</v>
-      </c>
-      <c r="U58">
-        <v>2.1</v>
-      </c>
       <c r="V58">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="W58">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X58">
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z58">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA58">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AB58">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="AC58">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="AD58">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AE58">
+        <v>1.18</v>
+      </c>
+      <c r="AF58">
+        <v>1.45</v>
+      </c>
+      <c r="AG58">
+        <v>2.55</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
         <v>1.25</v>
       </c>
-      <c r="AF58">
-        <v>1.43</v>
-      </c>
-      <c r="AG58">
-        <v>2.58</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>1.16</v>
-      </c>
       <c r="AK58">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -12371,19 +12371,19 @@
         </is>
       </c>
       <c r="N74">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="O74">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P74">
         <v>1.49</v>
       </c>
       <c r="Q74">
-        <v>5.42</v>
+        <v>5.7</v>
       </c>
       <c r="R74">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S74">
         <v>1.39</v>
@@ -12392,13 +12392,13 @@
         <v>2.64</v>
       </c>
       <c r="U74">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="V74">
         <v>1.36</v>
       </c>
       <c r="W74">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X74">
         <v>1</v>
@@ -12419,7 +12419,7 @@
         <v>3.45</v>
       </c>
       <c r="AD74">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE74">
         <v>1.04</v>
@@ -14825,13 +14825,13 @@
         <v>2.37</v>
       </c>
       <c r="Q89">
-        <v>3.66</v>
+        <v>3.52</v>
       </c>
       <c r="R89">
         <v>1.96</v>
       </c>
       <c r="S89">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T89">
         <v>2.48</v>
@@ -14855,7 +14855,7 @@
         <v>2.74</v>
       </c>
       <c r="AA89">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB89">
         <v>1.6</v>
@@ -14889,7 +14889,7 @@
         <v>1.26</v>
       </c>
       <c r="AK89">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.29</v>
+        <v>2.87</v>
       </c>
       <c r="O95">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="P95">
-        <v>8.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q95">
-        <v>1.62</v>
+        <v>3.3</v>
       </c>
       <c r="R95">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="S95">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T95">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="U95">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="V95">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W95">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="X95">
         <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z95">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AA95">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AB95">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AC95">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="AD95">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AE95">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AF95">
-        <v>1.9</v>
+        <v>1.41</v>
       </c>
       <c r="AG95">
-        <v>1.76</v>
+        <v>2.73</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="AK95">
-        <v>3.5</v>
+        <v>1.39</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.87</v>
+        <v>1.29</v>
       </c>
       <c r="O97">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="P97">
-        <v>2.15</v>
+        <v>8.5</v>
       </c>
       <c r="Q97">
-        <v>3.3</v>
+        <v>1.62</v>
       </c>
       <c r="R97">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="S97">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T97">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="U97">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="V97">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W97">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="X97">
         <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z97">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AA97">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AB97">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AC97">
-        <v>2.23</v>
+        <v>2.49</v>
       </c>
       <c r="AD97">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AE97">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AF97">
-        <v>1.41</v>
+        <v>1.9</v>
       </c>
       <c r="AG97">
-        <v>2.73</v>
+        <v>1.76</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.67</v>
+        <v>1.04</v>
       </c>
       <c r="AK97">
-        <v>1.39</v>
+        <v>3.5</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,65 +17587,65 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q106">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="R106">
+        <v>2.25</v>
+      </c>
+      <c r="S106">
+        <v>1.26</v>
+      </c>
+      <c r="T106">
+        <v>3.4</v>
+      </c>
+      <c r="U106">
+        <v>2.59</v>
+      </c>
+      <c r="V106">
+        <v>1.47</v>
+      </c>
+      <c r="W106">
+        <v>1.1</v>
+      </c>
+      <c r="X106">
+        <v>1.01</v>
+      </c>
+      <c r="Y106">
+        <v>1.16</v>
+      </c>
+      <c r="Z106">
+        <v>4.1</v>
+      </c>
+      <c r="AA106">
+        <v>1.69</v>
+      </c>
+      <c r="AB106">
+        <v>2.14</v>
+      </c>
+      <c r="AC106">
+        <v>2.59</v>
+      </c>
+      <c r="AD106">
+        <v>1.4</v>
+      </c>
+      <c r="AE106">
+        <v>1.12</v>
+      </c>
+      <c r="AF106">
+        <v>1.57</v>
+      </c>
+      <c r="AG106">
         <v>2.28</v>
       </c>
-      <c r="S106">
-        <v>1.33</v>
-      </c>
-      <c r="T106">
-        <v>2.96</v>
-      </c>
-      <c r="U106">
-        <v>2.75</v>
-      </c>
-      <c r="V106">
-        <v>1.42</v>
-      </c>
-      <c r="W106">
-        <v>1.05</v>
-      </c>
-      <c r="X106">
-        <v>1.03</v>
-      </c>
-      <c r="Y106">
-        <v>1.19</v>
-      </c>
-      <c r="Z106">
-        <v>3.74</v>
-      </c>
-      <c r="AA106">
-        <v>1.85</v>
-      </c>
-      <c r="AB106">
-        <v>1.95</v>
-      </c>
-      <c r="AC106">
-        <v>2.83</v>
-      </c>
-      <c r="AD106">
-        <v>1.33</v>
-      </c>
-      <c r="AE106">
-        <v>1.09</v>
-      </c>
-      <c r="AF106">
-        <v>1.95</v>
-      </c>
-      <c r="AG106">
-        <v>1.76</v>
-      </c>
       <c r="AH106" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AK106">
-        <v>2.62</v>
+        <v>1.4</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O107">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P107">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q107">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="R107">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S107">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="T107">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="U107">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="V107">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="W107">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z107">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA107">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AB107">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AC107">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AD107">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE107">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF107">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AG107">
-        <v>2.28</v>
+        <v>1.76</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AK107">
-        <v>1.4</v>
+        <v>2.62</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -24309,10 +24309,10 @@
         <v>0</v>
       </c>
       <c r="AA147">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB147">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC147">
         <v>0</v>
@@ -25414,10 +25414,10 @@
         <v>4.55</v>
       </c>
       <c r="O154">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="P154">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -27696,10 +27696,10 @@
         <v>2.15</v>
       </c>
       <c r="O168">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P168">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27732,10 +27732,10 @@
         <v>0</v>
       </c>
       <c r="AA168">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB168">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC168">
         <v>0</v>
@@ -27856,10 +27856,10 @@
         </is>
       </c>
       <c r="N169">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O169">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="P169">
         <v>2.4</v>
@@ -27895,10 +27895,10 @@
         <v>0</v>
       </c>
       <c r="AA169">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AB169">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC169">
         <v>0</v>
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O186">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q186">
         <v>2.23</v>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK186">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30953,7 +30953,7 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="O188">
         <v>3</v>
@@ -30965,22 +30965,22 @@
         <v>3.1</v>
       </c>
       <c r="R188">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="S188">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="T188">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U188">
         <v>3.24</v>
       </c>
       <c r="V188">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W188">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X188">
         <v>1.04</v>
@@ -31026,7 +31026,7 @@
         <v>1.28</v>
       </c>
       <c r="AK188">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -33763,10 +33763,10 @@
         <v>0</v>
       </c>
       <c r="AA205">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AB205">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AC205">
         <v>0</v>
@@ -34059,7 +34059,7 @@
         <v>7.8</v>
       </c>
       <c r="Q207">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R207">
         <v>2.63</v>
@@ -34123,7 +34123,7 @@
         <v>1.07</v>
       </c>
       <c r="AK207">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="O212">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="P212">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q212">
         <v>0</v>
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O222">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="P222">
-        <v>5.01</v>
+        <v>5.26</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O223">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P223">
-        <v>4.71</v>
+        <v>4.78</v>
       </c>
       <c r="Q223">
         <v>0</v>
@@ -38131,7 +38131,7 @@
         <v>3.25</v>
       </c>
       <c r="P232">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="Q232">
         <v>3.3</v>
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G252">
@@ -41385,64 +41385,64 @@
         </is>
       </c>
       <c r="N252">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="O252">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="P252">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q252">
-        <v>3.7</v>
+        <v>2.63</v>
       </c>
       <c r="R252">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="S252">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T252">
-        <v>2.44</v>
+        <v>2.94</v>
       </c>
       <c r="U252">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="V252">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W252">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X252">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y252">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z252">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA252">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB252">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC252">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AD252">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE252">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF252">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG252">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK252">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,65 +41548,65 @@
         </is>
       </c>
       <c r="N253">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="O253">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="P253">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q253">
-        <v>2.63</v>
+        <v>3.7</v>
       </c>
       <c r="R253">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="S253">
+        <v>1.44</v>
+      </c>
+      <c r="T253">
+        <v>2.44</v>
+      </c>
+      <c r="U253">
+        <v>2.71</v>
+      </c>
+      <c r="V253">
         <v>1.36</v>
       </c>
-      <c r="T253">
-        <v>2.94</v>
-      </c>
-      <c r="U253">
-        <v>2.75</v>
-      </c>
-      <c r="V253">
-        <v>1.4</v>
-      </c>
       <c r="W253">
+        <v>1.05</v>
+      </c>
+      <c r="X253">
+        <v>1.04</v>
+      </c>
+      <c r="Y253">
+        <v>1.26</v>
+      </c>
+      <c r="Z253">
+        <v>3.2</v>
+      </c>
+      <c r="AA253">
+        <v>2.05</v>
+      </c>
+      <c r="AB253">
+        <v>1.75</v>
+      </c>
+      <c r="AC253">
+        <v>2.97</v>
+      </c>
+      <c r="AD253">
+        <v>1.3</v>
+      </c>
+      <c r="AE253">
         <v>1.08</v>
       </c>
-      <c r="X253">
-        <v>1.01</v>
-      </c>
-      <c r="Y253">
-        <v>1.23</v>
-      </c>
-      <c r="Z253">
-        <v>3.42</v>
-      </c>
-      <c r="AA253">
+      <c r="AF253">
+        <v>1.65</v>
+      </c>
+      <c r="AG253">
         <v>2.07</v>
       </c>
-      <c r="AB253">
-        <v>1.72</v>
-      </c>
-      <c r="AC253">
-        <v>3.08</v>
-      </c>
-      <c r="AD253">
-        <v>1.28</v>
-      </c>
-      <c r="AE253">
-        <v>1.06</v>
-      </c>
-      <c r="AF253">
-        <v>1.68</v>
-      </c>
-      <c r="AG253">
-        <v>2.02</v>
-      </c>
       <c r="AH253" t="inlineStr">
         <is>
           <t>[]</t>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK253">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -42040,7 +42040,7 @@
         <v>2.38</v>
       </c>
       <c r="O256">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P256">
         <v>3.05</v>
@@ -47262,10 +47262,10 @@
         <v>0</v>
       </c>
       <c r="Q288">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R288">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S288">
         <v>1.29</v>
@@ -47274,13 +47274,13 @@
         <v>3.3</v>
       </c>
       <c r="U288">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="V288">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W288">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X288">
         <v>1.04</v>
@@ -47326,7 +47326,7 @@
         <v>1.4</v>
       </c>
       <c r="AK288">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47449,10 +47449,10 @@
         <v>1.02</v>
       </c>
       <c r="Y289">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z289">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AA289">
         <v>1.54</v>
@@ -47464,13 +47464,13 @@
         <v>2.4</v>
       </c>
       <c r="AD289">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE289">
         <v>1.17</v>
       </c>
       <c r="AF289">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG289">
         <v>2.39</v>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -656,22 +656,22 @@
         <v>2.8</v>
       </c>
       <c r="U2">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z2">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AA2">
         <v>2.08</v>
@@ -686,10 +686,10 @@
         <v>1.21</v>
       </c>
       <c r="AE2">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG2">
         <v>1.85</v>
@@ -810,13 +810,13 @@
         <v>1.88</v>
       </c>
       <c r="R3">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S3">
         <v>1.3</v>
       </c>
       <c r="T3">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="U3">
         <v>2.38</v>
@@ -825,7 +825,7 @@
         <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X3">
         <v>1.02</v>
@@ -843,7 +843,7 @@
         <v>2.17</v>
       </c>
       <c r="AC3">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="AD3">
         <v>1.46</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G4">
@@ -961,65 +961,65 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q4">
-        <v>4.39</v>
+        <v>2.91</v>
       </c>
       <c r="R4">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="S4">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
-        <v>2.64</v>
+        <v>2.71</v>
       </c>
       <c r="U4">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="V4">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
         <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z4">
         <v>3.2</v>
       </c>
       <c r="AA4">
+        <v>1.93</v>
+      </c>
+      <c r="AB4">
+        <v>1.75</v>
+      </c>
+      <c r="AC4">
+        <v>3.34</v>
+      </c>
+      <c r="AD4">
+        <v>1.24</v>
+      </c>
+      <c r="AE4">
+        <v>1.04</v>
+      </c>
+      <c r="AF4">
+        <v>1.73</v>
+      </c>
+      <c r="AG4">
         <v>1.98</v>
       </c>
-      <c r="AB4">
-        <v>1.77</v>
-      </c>
-      <c r="AC4">
-        <v>3.4</v>
-      </c>
-      <c r="AD4">
-        <v>1.29</v>
-      </c>
-      <c r="AE4">
-        <v>1.05</v>
-      </c>
-      <c r="AF4">
-        <v>1.8</v>
-      </c>
-      <c r="AG4">
-        <v>1.91</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="AK4">
-        <v>1.19</v>
+        <v>1.57</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.91</v>
+        <v>4.39</v>
       </c>
       <c r="R5">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="S5">
         <v>1.36</v>
       </c>
       <c r="T5">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="U5">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="V5">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z5">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AA5">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB5">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC5">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AD5">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE5">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF5">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG5">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.31</v>
+        <v>1.8</v>
       </c>
       <c r="AK5">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1317,13 +1317,13 @@
         <v>1.09</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y6">
         <v>1.21</v>
       </c>
       <c r="Z6">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="AA6">
         <v>1.74</v>
@@ -1332,7 +1332,7 @@
         <v>2.08</v>
       </c>
       <c r="AC6">
-        <v>2.74</v>
+        <v>2.98</v>
       </c>
       <c r="AD6">
         <v>1.35</v>
@@ -1341,10 +1341,10 @@
         <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG6">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>4</v>
       </c>
       <c r="R7">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
         <v>1.36</v>
@@ -1625,7 +1625,7 @@
         <v>3.14</v>
       </c>
       <c r="R8">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="S8">
         <v>1.38</v>
@@ -1667,10 +1667,10 @@
         <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
         <v>2.1</v>
       </c>
       <c r="R9">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="S9">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T9">
         <v>3.5</v>
@@ -1800,7 +1800,7 @@
         <v>2.22</v>
       </c>
       <c r="V9">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="W9">
         <v>1.14</v>
@@ -1812,22 +1812,22 @@
         <v>1.13</v>
       </c>
       <c r="Z9">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AA9">
+        <v>1.51</v>
+      </c>
+      <c r="AB9">
+        <v>2.26</v>
+      </c>
+      <c r="AC9">
+        <v>2.36</v>
+      </c>
+      <c r="AD9">
         <v>1.5</v>
       </c>
-      <c r="AB9">
-        <v>2.28</v>
-      </c>
-      <c r="AC9">
-        <v>2.33</v>
-      </c>
-      <c r="AD9">
-        <v>1.51</v>
-      </c>
       <c r="AE9">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF9">
         <v>1.54</v>
@@ -1849,7 +1849,7 @@
         <v>1.17</v>
       </c>
       <c r="AK9">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -3578,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="Q20">
-        <v>2.96</v>
+        <v>3.04</v>
       </c>
       <c r="R20">
         <v>2.05</v>
@@ -3593,7 +3593,7 @@
         <v>3.18</v>
       </c>
       <c r="V20">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W20">
         <v>1.03</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.53</v>
+        <v>3.6</v>
       </c>
       <c r="O21">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="P21">
-        <v>2.31</v>
+        <v>1.86</v>
       </c>
       <c r="Q21">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="R21">
         <v>2.01</v>
       </c>
       <c r="S21">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="T21">
-        <v>2.99</v>
+        <v>2.57</v>
       </c>
       <c r="U21">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="V21">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W21">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z21">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AA21">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB21">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AC21">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AD21">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE21">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF21">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AG21">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="AK21">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="O22">
-        <v>3.23</v>
+        <v>3.38</v>
       </c>
       <c r="P22">
-        <v>1.86</v>
+        <v>2.31</v>
       </c>
       <c r="Q22">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="R22">
         <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T22">
-        <v>2.57</v>
+        <v>2.99</v>
       </c>
       <c r="U22">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="V22">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
+        <v>1.08</v>
+      </c>
+      <c r="X22">
+        <v>1.03</v>
+      </c>
+      <c r="Y22">
+        <v>1.26</v>
+      </c>
+      <c r="Z22">
+        <v>3.2</v>
+      </c>
+      <c r="AA22">
+        <v>1.9</v>
+      </c>
+      <c r="AB22">
+        <v>1.87</v>
+      </c>
+      <c r="AC22">
+        <v>3.14</v>
+      </c>
+      <c r="AD22">
+        <v>1.27</v>
+      </c>
+      <c r="AE22">
         <v>1.07</v>
       </c>
-      <c r="X22">
-        <v>1.02</v>
-      </c>
-      <c r="Y22">
-        <v>1.3</v>
-      </c>
-      <c r="Z22">
-        <v>2.97</v>
-      </c>
-      <c r="AA22">
-        <v>2.05</v>
-      </c>
-      <c r="AB22">
+      <c r="AF22">
         <v>1.7</v>
       </c>
-      <c r="AC22">
-        <v>3.42</v>
-      </c>
-      <c r="AD22">
-        <v>1.23</v>
-      </c>
-      <c r="AE22">
-        <v>1.04</v>
-      </c>
-      <c r="AF22">
-        <v>1.91</v>
-      </c>
       <c r="AG22">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="AK22">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4085,7 +4085,7 @@
         <v>1.32</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
         <v>1.02</v>
@@ -4254,16 +4254,16 @@
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z24">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="AA24">
         <v>2.07</v>
       </c>
       <c r="AB24">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC24">
         <v>3.42</v>
@@ -4294,7 +4294,7 @@
         <v>1.26</v>
       </c>
       <c r="AK24">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>1.3</v>
       </c>
       <c r="O38">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="P38">
         <v>9.199999999999999</v>
@@ -6545,13 +6545,13 @@
         <v>1.3</v>
       </c>
       <c r="AB38">
-        <v>3.37</v>
+        <v>3.14</v>
       </c>
       <c r="AC38">
         <v>1.82</v>
       </c>
       <c r="AD38">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AE38">
         <v>1.4</v>
@@ -6675,22 +6675,22 @@
         <v>0</v>
       </c>
       <c r="Q39">
-        <v>3.68</v>
+        <v>3.85</v>
       </c>
       <c r="R39">
         <v>2.21</v>
       </c>
       <c r="S39">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T39">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U39">
         <v>2.74</v>
       </c>
       <c r="V39">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W39">
         <v>1.08</v>
@@ -6705,13 +6705,13 @@
         <v>3.34</v>
       </c>
       <c r="AA39">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AB39">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC39">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AD39">
         <v>1.28</v>
@@ -6720,10 +6720,10 @@
         <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG39">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>1.39</v>
       </c>
       <c r="T41">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="U41">
         <v>2.73</v>
@@ -7022,19 +7022,19 @@
         <v>1.07</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z41">
-        <v>3.81</v>
+        <v>3.44</v>
       </c>
       <c r="AA41">
         <v>1.82</v>
       </c>
       <c r="AB41">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AC41">
         <v>2.95</v>
@@ -7363,10 +7363,10 @@
         <v>2.21</v>
       </c>
       <c r="AC43">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AD43">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AE43">
         <v>1.19</v>
@@ -7375,7 +7375,7 @@
         <v>1.62</v>
       </c>
       <c r="AG43">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>1.34</v>
       </c>
       <c r="T44">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U44">
         <v>2.5</v>
@@ -7554,7 +7554,7 @@
         <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7653,13 +7653,13 @@
         <v>4.4</v>
       </c>
       <c r="Q45">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="R45">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S45">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T45">
         <v>2.9</v>
@@ -7680,7 +7680,7 @@
         <v>1.29</v>
       </c>
       <c r="Z45">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AA45">
         <v>1.98</v>
@@ -7701,7 +7701,7 @@
         <v>1.83</v>
       </c>
       <c r="AG45">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK45">
         <v>1.89</v>
@@ -7816,7 +7816,7 @@
         <v>1.95</v>
       </c>
       <c r="Q46">
-        <v>4.18</v>
+        <v>4.21</v>
       </c>
       <c r="R46">
         <v>2.25</v>
@@ -7840,10 +7840,10 @@
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AA46">
         <v>1.7</v>
@@ -7864,7 +7864,7 @@
         <v>1.6</v>
       </c>
       <c r="AG46">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>1.35</v>
       </c>
       <c r="T47">
-        <v>3.07</v>
+        <v>2.92</v>
       </c>
       <c r="U47">
         <v>2.62</v>
@@ -8151,7 +8151,7 @@
         <v>1.28</v>
       </c>
       <c r="T48">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U48">
         <v>2.45</v>
@@ -8160,7 +8160,7 @@
         <v>1.44</v>
       </c>
       <c r="W48">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
         <v>1.03</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.01</v>
+        <v>2.14</v>
       </c>
       <c r="O50">
         <v>3.5</v>
@@ -8468,13 +8468,13 @@
         <v>3.5</v>
       </c>
       <c r="Q50">
-        <v>2.52</v>
+        <v>2.61</v>
       </c>
       <c r="R50">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="S50">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
         <v>3.75</v>
@@ -8495,10 +8495,10 @@
         <v>1.15</v>
       </c>
       <c r="Z50">
-        <v>5.44</v>
+        <v>5.43</v>
       </c>
       <c r="AA50">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB50">
         <v>2.5</v>
@@ -8516,7 +8516,7 @@
         <v>1.44</v>
       </c>
       <c r="AG50">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK50">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8640,10 +8640,10 @@
         <v>1.34</v>
       </c>
       <c r="T51">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U51">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="V51">
         <v>1.48</v>
@@ -8676,10 +8676,10 @@
         <v>1.11</v>
       </c>
       <c r="AF51">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG51">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8957,10 +8957,10 @@
         <v>3</v>
       </c>
       <c r="Q53">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="R53">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S53">
         <v>1.26</v>
@@ -8993,7 +8993,7 @@
         <v>2.12</v>
       </c>
       <c r="AC53">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="AD53">
         <v>1.47</v>
@@ -9005,7 +9005,7 @@
         <v>1.5</v>
       </c>
       <c r="AG53">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.35</v>
       </c>
       <c r="AK53">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9120,19 +9120,19 @@
         <v>0</v>
       </c>
       <c r="Q54">
-        <v>5.24</v>
+        <v>5.57</v>
       </c>
       <c r="R54">
         <v>2.41</v>
       </c>
       <c r="S54">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T54">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="U54">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V54">
         <v>1.5</v>
@@ -9141,19 +9141,19 @@
         <v>1.11</v>
       </c>
       <c r="X54">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
         <v>1.17</v>
       </c>
       <c r="Z54">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="AA54">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB54">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC54">
         <v>2.69</v>
@@ -9184,7 +9184,7 @@
         <v>1.16</v>
       </c>
       <c r="AK54">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9283,7 +9283,7 @@
         <v>2.9</v>
       </c>
       <c r="Q55">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R55">
         <v>2.3</v>
@@ -9295,13 +9295,13 @@
         <v>3.75</v>
       </c>
       <c r="U55">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V55">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W55">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X55">
         <v>1.02</v>
@@ -9328,7 +9328,7 @@
         <v>1.25</v>
       </c>
       <c r="AF55">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG55">
         <v>2.62</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>2.09</v>
       </c>
       <c r="Q56">
-        <v>3.01</v>
+        <v>2.92</v>
       </c>
       <c r="R56">
         <v>2.42</v>
@@ -9458,10 +9458,10 @@
         <v>4</v>
       </c>
       <c r="U56">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="V56">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W56">
         <v>1.14</v>
@@ -9473,22 +9473,22 @@
         <v>1.12</v>
       </c>
       <c r="Z56">
-        <v>6.27</v>
+        <v>6.23</v>
       </c>
       <c r="AA56">
         <v>1.43</v>
       </c>
       <c r="AB56">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="AC56">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AD56">
         <v>1.76</v>
       </c>
       <c r="AE56">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AF56">
         <v>1.36</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AK56">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK57">
         <v>1.95</v>
@@ -9787,10 +9787,10 @@
         <v>2.25</v>
       </c>
       <c r="V58">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W58">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X58">
         <v>1.02</v>
@@ -9805,13 +9805,13 @@
         <v>1.54</v>
       </c>
       <c r="AB58">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AC58">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AD58">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE58">
         <v>1.18</v>
@@ -9935,7 +9935,7 @@
         <v>1.67</v>
       </c>
       <c r="Q59">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="R59">
         <v>2.27</v>
@@ -9944,7 +9944,7 @@
         <v>1.24</v>
       </c>
       <c r="T59">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="U59">
         <v>2.22</v>
@@ -9980,10 +9980,10 @@
         <v>1.14</v>
       </c>
       <c r="AF59">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG59">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AK59">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10261,10 +10261,10 @@
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="R61">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="S61">
         <v>1.33</v>
@@ -10325,7 +10325,7 @@
         <v>1.18</v>
       </c>
       <c r="AK61">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O63">
         <v>2.95</v>
@@ -10587,16 +10587,16 @@
         <v>3</v>
       </c>
       <c r="Q63">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="R63">
         <v>1.87</v>
       </c>
       <c r="S63">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="T63">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U63">
         <v>3.9</v>
@@ -10614,7 +10614,7 @@
         <v>1.52</v>
       </c>
       <c r="Z63">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AA63">
         <v>2.7</v>
@@ -10623,7 +10623,7 @@
         <v>1.44</v>
       </c>
       <c r="AC63">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AD63">
         <v>1.13</v>
@@ -10635,7 +10635,7 @@
         <v>2.02</v>
       </c>
       <c r="AG63">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.36</v>
       </c>
       <c r="AK63">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10904,16 +10904,16 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O65">
         <v>3</v>
       </c>
       <c r="P65">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q65">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="R65">
         <v>1.91</v>
@@ -10934,22 +10934,22 @@
         <v>1.05</v>
       </c>
       <c r="X65">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y65">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="Z65">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AA65">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AB65">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AC65">
-        <v>4.85</v>
+        <v>4.95</v>
       </c>
       <c r="AD65">
         <v>1.11</v>
@@ -10958,7 +10958,7 @@
         <v>1.01</v>
       </c>
       <c r="AF65">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AG65">
         <v>1.62</v>
@@ -10977,7 +10977,7 @@
         <v>1.4</v>
       </c>
       <c r="AK65">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11073,7 +11073,7 @@
         <v>3.6</v>
       </c>
       <c r="P66">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q66">
         <v>3.16</v>
@@ -11266,13 +11266,13 @@
         <v>1.2</v>
       </c>
       <c r="Z67">
-        <v>4.3</v>
+        <v>4.42</v>
       </c>
       <c r="AA67">
         <v>1.63</v>
       </c>
       <c r="AB67">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AC67">
         <v>2.6</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O68">
         <v>3.5</v>
       </c>
       <c r="P68">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q68">
         <v>3.72</v>
@@ -11450,7 +11450,7 @@
         <v>1.53</v>
       </c>
       <c r="AG68">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>2.38</v>
       </c>
       <c r="S69">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="T69">
         <v>3.14</v>
@@ -11882,7 +11882,7 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O71">
         <v>3.4</v>
@@ -11897,13 +11897,13 @@
         <v>2.3</v>
       </c>
       <c r="S71">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T71">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U71">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="V71">
         <v>1.5</v>
@@ -11912,28 +11912,28 @@
         <v>1.08</v>
       </c>
       <c r="X71">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y71">
+        <v>1.18</v>
+      </c>
+      <c r="Z71">
+        <v>3.85</v>
+      </c>
+      <c r="AA71">
+        <v>1.72</v>
+      </c>
+      <c r="AB71">
+        <v>2.08</v>
+      </c>
+      <c r="AC71">
+        <v>2.75</v>
+      </c>
+      <c r="AD71">
+        <v>1.38</v>
+      </c>
+      <c r="AE71">
         <v>1.17</v>
-      </c>
-      <c r="Z71">
-        <v>3.96</v>
-      </c>
-      <c r="AA71">
-        <v>1.68</v>
-      </c>
-      <c r="AB71">
-        <v>2.13</v>
-      </c>
-      <c r="AC71">
-        <v>2.7</v>
-      </c>
-      <c r="AD71">
-        <v>1.41</v>
-      </c>
-      <c r="AE71">
-        <v>1.18</v>
       </c>
       <c r="AF71">
         <v>1.6</v>
@@ -11952,7 +11952,7 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK71">
         <v>1.36</v>
@@ -12054,7 +12054,7 @@
         <v>2.17</v>
       </c>
       <c r="Q72">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R72">
         <v>2.18</v>
@@ -12096,7 +12096,7 @@
         <v>1.43</v>
       </c>
       <c r="AE72">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF72">
         <v>1.53</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="O76">
         <v>3.25</v>
       </c>
       <c r="P76">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q76">
         <v>3.1</v>
@@ -12724,7 +12724,7 @@
         <v>1.42</v>
       </c>
       <c r="W76">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X76">
         <v>1.01</v>
@@ -12887,7 +12887,7 @@
         <v>1.33</v>
       </c>
       <c r="W77">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X77">
         <v>1.01</v>
@@ -13032,10 +13032,10 @@
         <v>1.91</v>
       </c>
       <c r="Q78">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="R78">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S78">
         <v>1.33</v>
@@ -13044,7 +13044,7 @@
         <v>3</v>
       </c>
       <c r="U78">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="V78">
         <v>1.4</v>
@@ -13056,16 +13056,16 @@
         <v>1</v>
       </c>
       <c r="Y78">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z78">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA78">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AB78">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AC78">
         <v>2.96</v>
@@ -13074,13 +13074,13 @@
         <v>1.36</v>
       </c>
       <c r="AE78">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF78">
         <v>1.67</v>
       </c>
       <c r="AG78">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>1.3</v>
       </c>
       <c r="AE80">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF80">
         <v>1.74</v>
@@ -13419,7 +13419,7 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.8</v>
+        <v>1.21</v>
       </c>
       <c r="AK80">
         <v>1.22</v>
@@ -13512,16 +13512,16 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O81">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="P81">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="Q81">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="R81">
         <v>2.4</v>
@@ -13554,13 +13554,13 @@
         <v>1.47</v>
       </c>
       <c r="AB81">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AC81">
         <v>2.27</v>
       </c>
       <c r="AD81">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE81">
         <v>1.19</v>
@@ -13585,7 +13585,7 @@
         <v>1.29</v>
       </c>
       <c r="AK81">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,7 +13675,7 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="O82">
         <v>4.5</v>
@@ -13687,7 +13687,7 @@
         <v>1.99</v>
       </c>
       <c r="R82">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="S82">
         <v>1.22</v>
@@ -13720,7 +13720,7 @@
         <v>2.33</v>
       </c>
       <c r="AC82">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="AD82">
         <v>1.56</v>
@@ -13847,7 +13847,7 @@
         <v>3.95</v>
       </c>
       <c r="Q83">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="R83">
         <v>2</v>
@@ -13895,7 +13895,7 @@
         <v>2.03</v>
       </c>
       <c r="AG83">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -14010,13 +14010,13 @@
         <v>1.28</v>
       </c>
       <c r="Q84">
-        <v>6.57</v>
+        <v>8</v>
       </c>
       <c r="R84">
         <v>2.66</v>
       </c>
       <c r="S84">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T84">
         <v>3.9</v>
@@ -14034,7 +14034,7 @@
         <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z84">
         <v>5.2</v>
@@ -14046,7 +14046,7 @@
         <v>2.6</v>
       </c>
       <c r="AC84">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AD84">
         <v>1.65</v>
@@ -14055,7 +14055,7 @@
         <v>1.22</v>
       </c>
       <c r="AF84">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG84">
         <v>1.95</v>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O85">
         <v>3.58</v>
@@ -14191,7 +14191,7 @@
         <v>1.48</v>
       </c>
       <c r="W85">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X85">
         <v>1.02</v>
@@ -14221,7 +14221,7 @@
         <v>1.57</v>
       </c>
       <c r="AG85">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK85">
         <v>1.81</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="O86">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P86">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q86">
         <v>2.7</v>
@@ -14354,7 +14354,7 @@
         <v>1.58</v>
       </c>
       <c r="W86">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X86">
         <v>1.01</v>
@@ -14381,7 +14381,7 @@
         <v>1.17</v>
       </c>
       <c r="AF86">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG86">
         <v>2.46</v>
@@ -14496,7 +14496,7 @@
         <v>4</v>
       </c>
       <c r="P87">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q87">
         <v>3.15</v>
@@ -14508,16 +14508,16 @@
         <v>1.17</v>
       </c>
       <c r="T87">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="U87">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V87">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="W87">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X87">
         <v>1.01</v>
@@ -14529,19 +14529,19 @@
         <v>8.5</v>
       </c>
       <c r="AA87">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB87">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AC87">
         <v>1.7</v>
       </c>
       <c r="AD87">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AE87">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AF87">
         <v>1.25</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="O88">
         <v>6.5</v>
       </c>
       <c r="P88">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Q88">
         <v>1.57</v>
@@ -14674,7 +14674,7 @@
         <v>5.2</v>
       </c>
       <c r="U88">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="V88">
         <v>1.95</v>
@@ -14689,7 +14689,7 @@
         <v>1.04</v>
       </c>
       <c r="Z88">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
       <c r="AA88">
         <v>1.28</v>
@@ -14701,16 +14701,16 @@
         <v>1.76</v>
       </c>
       <c r="AD88">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AE88">
         <v>1.45</v>
       </c>
       <c r="AF88">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG88">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK88">
-        <v>3.46</v>
+        <v>3.64</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -15151,10 +15151,10 @@
         <v>2.8</v>
       </c>
       <c r="Q91">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="R91">
-        <v>2.26</v>
+        <v>2.09</v>
       </c>
       <c r="S91">
         <v>1.35</v>
@@ -15332,7 +15332,7 @@
         <v>1.7</v>
       </c>
       <c r="W92">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X92">
         <v>1.01</v>
@@ -15468,19 +15468,19 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O93">
         <v>3.4</v>
       </c>
       <c r="P93">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q93">
         <v>2.4</v>
       </c>
       <c r="R93">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S93">
         <v>1.33</v>
@@ -15501,13 +15501,13 @@
         <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z93">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA93">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB93">
         <v>1.92</v>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK93">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15646,7 +15646,7 @@
         <v>2</v>
       </c>
       <c r="S94">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T94">
         <v>2.36</v>
@@ -15676,10 +15676,10 @@
         <v>1.62</v>
       </c>
       <c r="AC94">
-        <v>3.82</v>
+        <v>4.52</v>
       </c>
       <c r="AD94">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE94">
         <v>1.03</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.87</v>
+        <v>1.29</v>
       </c>
       <c r="O95">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="P95">
-        <v>2.15</v>
+        <v>8.5</v>
       </c>
       <c r="Q95">
-        <v>3.3</v>
+        <v>1.67</v>
       </c>
       <c r="R95">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="S95">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="T95">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="U95">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="V95">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W95">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="X95">
         <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z95">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AA95">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AB95">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="AC95">
-        <v>2.23</v>
+        <v>2.51</v>
       </c>
       <c r="AD95">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AE95">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AF95">
-        <v>1.41</v>
+        <v>1.9</v>
       </c>
       <c r="AG95">
-        <v>2.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.67</v>
+        <v>1.04</v>
       </c>
       <c r="AK95">
-        <v>1.39</v>
+        <v>3.4</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15981,10 +15981,10 @@
         <v>2.44</v>
       </c>
       <c r="V96">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W96">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X96">
         <v>1</v>
@@ -15993,7 +15993,7 @@
         <v>1.21</v>
       </c>
       <c r="Z96">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="AA96">
         <v>1.74</v>
@@ -16002,7 +16002,7 @@
         <v>2.09</v>
       </c>
       <c r="AC96">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="AD96">
         <v>1.39</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.29</v>
+        <v>2.87</v>
       </c>
       <c r="O97">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="P97">
-        <v>8.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q97">
-        <v>1.62</v>
+        <v>3.3</v>
       </c>
       <c r="R97">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S97">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T97">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="U97">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="V97">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W97">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="X97">
         <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z97">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AA97">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AB97">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AC97">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="AD97">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AE97">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AF97">
-        <v>1.9</v>
+        <v>1.41</v>
       </c>
       <c r="AG97">
-        <v>1.76</v>
+        <v>2.73</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="AK97">
-        <v>3.5</v>
+        <v>1.39</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16455,40 +16455,40 @@
         <v>0</v>
       </c>
       <c r="Q99">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="R99">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="S99">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="T99">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="U99">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="V99">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W99">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X99">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y99">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Z99">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="AA99">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="AB99">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AC99">
         <v>5.5</v>
@@ -16497,13 +16497,13 @@
         <v>1.11</v>
       </c>
       <c r="AE99">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF99">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AG99">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AK99">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16627,10 +16627,10 @@
         <v>1.5</v>
       </c>
       <c r="T100">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="U100">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="V100">
         <v>1.23</v>
@@ -16648,7 +16648,7 @@
         <v>2.46</v>
       </c>
       <c r="AA100">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="AB100">
         <v>1.48</v>
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="O101">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="P101">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Q101">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="R101">
-        <v>2.41</v>
+        <v>2.26</v>
       </c>
       <c r="S101">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T101">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="U101">
-        <v>2.51</v>
+        <v>2.72</v>
       </c>
       <c r="V101">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W101">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X101">
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z101">
-        <v>3.72</v>
+        <v>3.28</v>
       </c>
       <c r="AA101">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB101">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AC101">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="AD101">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AE101">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF101">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="AG101">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="AK101">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16935,19 +16935,19 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O102">
         <v>3.5</v>
       </c>
       <c r="P102">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="Q102">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R102">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S102">
         <v>1.35</v>
@@ -16977,7 +16977,7 @@
         <v>1.87</v>
       </c>
       <c r="AB102">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AC102">
         <v>2.8</v>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK102">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,10 +17098,10 @@
         </is>
       </c>
       <c r="N103">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="O103">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P103">
         <v>1.36</v>
@@ -17122,7 +17122,7 @@
         <v>2.25</v>
       </c>
       <c r="V103">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W103">
         <v>1.13</v>
@@ -17168,7 +17168,7 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK103">
         <v>1.06</v>
@@ -17427,7 +17427,7 @@
         <v>3.55</v>
       </c>
       <c r="O105">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P105">
         <v>1.97</v>
@@ -17608,7 +17608,7 @@
         <v>3.4</v>
       </c>
       <c r="U106">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="V106">
         <v>1.47</v>
@@ -17623,7 +17623,7 @@
         <v>1.16</v>
       </c>
       <c r="Z106">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA106">
         <v>1.69</v>
@@ -17762,7 +17762,7 @@
         <v>1.9</v>
       </c>
       <c r="R107">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="S107">
         <v>1.33</v>
@@ -17777,16 +17777,16 @@
         <v>1.42</v>
       </c>
       <c r="W107">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X107">
         <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z107">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AA107">
         <v>1.85</v>
@@ -17804,10 +17804,10 @@
         <v>1.09</v>
       </c>
       <c r="AF107">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG107">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>1.08</v>
       </c>
       <c r="AK107">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18281,7 +18281,7 @@
         <v>1.75</v>
       </c>
       <c r="AB110">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC110">
         <v>2.74</v>
@@ -18749,34 +18749,34 @@
         <v>3.12</v>
       </c>
       <c r="U113">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="V113">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W113">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X113">
         <v>1.04</v>
       </c>
       <c r="Y113">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z113">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA113">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB113">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AC113">
         <v>2.74</v>
       </c>
       <c r="AD113">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE113">
         <v>1.1</v>
@@ -18785,7 +18785,7 @@
         <v>1.75</v>
       </c>
       <c r="AG113">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK113">
         <v>1.08</v>
@@ -19096,13 +19096,13 @@
         <v>1.4</v>
       </c>
       <c r="AB115">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AC115">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AD115">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AE115">
         <v>1.26</v>
@@ -19124,7 +19124,7 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK115">
         <v>1.11</v>
@@ -19226,7 +19226,7 @@
         <v>2.45</v>
       </c>
       <c r="Q116">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="R116">
         <v>1.95</v>
@@ -19244,22 +19244,22 @@
         <v>1.3</v>
       </c>
       <c r="W116">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X116">
         <v>1.06</v>
       </c>
       <c r="Y116">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z116">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="AA116">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AB116">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AC116">
         <v>5</v>
@@ -19287,7 +19287,7 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AK116">
         <v>1.4</v>
@@ -19416,7 +19416,7 @@
         <v>1.06</v>
       </c>
       <c r="Z117">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="AA117">
         <v>1.32</v>
@@ -19739,16 +19739,16 @@
         <v>1.04</v>
       </c>
       <c r="Y119">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z119">
         <v>3.25</v>
       </c>
       <c r="AA119">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB119">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC119">
         <v>3.42</v>
@@ -19779,7 +19779,7 @@
         <v>1.3</v>
       </c>
       <c r="AK119">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19881,7 +19881,7 @@
         <v>1.46</v>
       </c>
       <c r="R120">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="S120">
         <v>1.14</v>
@@ -19893,7 +19893,7 @@
         <v>2.05</v>
       </c>
       <c r="V120">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="W120">
         <v>1.17</v>
@@ -19905,7 +19905,7 @@
         <v>1.13</v>
       </c>
       <c r="Z120">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="AA120">
         <v>1.38</v>
@@ -19917,16 +19917,16 @@
         <v>2.14</v>
       </c>
       <c r="AD120">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AE120">
         <v>1.24</v>
       </c>
       <c r="AF120">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG120">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>3.2</v>
       </c>
       <c r="Q122">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="R122">
         <v>2</v>
@@ -20228,10 +20228,10 @@
         <v>1.03</v>
       </c>
       <c r="Y122">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z122">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="AA122">
         <v>2.31</v>
@@ -20542,7 +20542,7 @@
         <v>2.96</v>
       </c>
       <c r="U124">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="V124">
         <v>1.42</v>
@@ -20566,7 +20566,7 @@
         <v>1.95</v>
       </c>
       <c r="AC124">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="AD124">
         <v>1.37</v>
@@ -20693,10 +20693,10 @@
         <v>1.13</v>
       </c>
       <c r="Q125">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R125">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="S125">
         <v>1.14</v>
@@ -20705,43 +20705,43 @@
         <v>5</v>
       </c>
       <c r="U125">
+        <v>1.85</v>
+      </c>
+      <c r="V125">
+        <v>1.82</v>
+      </c>
+      <c r="W125">
+        <v>1.22</v>
+      </c>
+      <c r="X125">
+        <v>1.01</v>
+      </c>
+      <c r="Y125">
+        <v>1.04</v>
+      </c>
+      <c r="Z125">
+        <v>6.9</v>
+      </c>
+      <c r="AA125">
+        <v>1.33</v>
+      </c>
+      <c r="AB125">
+        <v>3.25</v>
+      </c>
+      <c r="AC125">
         <v>1.8</v>
       </c>
-      <c r="V125">
-        <v>1.91</v>
-      </c>
-      <c r="W125">
-        <v>1.25</v>
-      </c>
-      <c r="X125">
-        <v>1</v>
-      </c>
-      <c r="Y125">
-        <v>1.03</v>
-      </c>
-      <c r="Z125">
-        <v>7.4</v>
-      </c>
-      <c r="AA125">
-        <v>1.28</v>
-      </c>
-      <c r="AB125">
-        <v>3.5</v>
-      </c>
-      <c r="AC125">
-        <v>1.72</v>
-      </c>
       <c r="AD125">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="AE125">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AF125">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG125">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AK125">
         <v>1.02</v>
@@ -20862,7 +20862,7 @@
         <v>2.1</v>
       </c>
       <c r="S126">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T126">
         <v>2.65</v>
@@ -20874,7 +20874,7 @@
         <v>1.36</v>
       </c>
       <c r="W126">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X126">
         <v>1.04</v>
@@ -20898,10 +20898,10 @@
         <v>1.25</v>
       </c>
       <c r="AE126">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF126">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG126">
         <v>1.85</v>
@@ -21016,7 +21016,7 @@
         <v>3.65</v>
       </c>
       <c r="P127">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q127">
         <v>2.4</v>
@@ -21037,7 +21037,7 @@
         <v>1.5</v>
       </c>
       <c r="W127">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X127">
         <v>1.01</v>
@@ -21052,7 +21052,7 @@
         <v>1.6</v>
       </c>
       <c r="AB127">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AC127">
         <v>2.5</v>
@@ -21339,7 +21339,7 @@
         <v>3.5</v>
       </c>
       <c r="O129">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P129">
         <v>1.85</v>
@@ -21387,7 +21387,7 @@
         <v>1.36</v>
       </c>
       <c r="AE129">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF129">
         <v>1.67</v>
@@ -21538,10 +21538,10 @@
         <v>3.5</v>
       </c>
       <c r="AA130">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB130">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC130">
         <v>2.83</v>
@@ -21701,7 +21701,7 @@
         <v>2.88</v>
       </c>
       <c r="AA131">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB131">
         <v>1.64</v>
@@ -21997,19 +21997,19 @@
         <v>0</v>
       </c>
       <c r="Q133">
-        <v>7.2</v>
+        <v>8.26</v>
       </c>
       <c r="R133">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="S133">
         <v>1.25</v>
       </c>
       <c r="T133">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="U133">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="V133">
         <v>1.57</v>
@@ -22024,19 +22024,19 @@
         <v>1.17</v>
       </c>
       <c r="Z133">
-        <v>4.96</v>
+        <v>4.99</v>
       </c>
       <c r="AA133">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB133">
-        <v>2.51</v>
+        <v>2.33</v>
       </c>
       <c r="AC133">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AD133">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE133">
         <v>1.2</v>
@@ -22045,7 +22045,7 @@
         <v>1.85</v>
       </c>
       <c r="AG133">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AK133">
         <v>1.07</v>
@@ -22154,10 +22154,10 @@
         <v>1.65</v>
       </c>
       <c r="O134">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P134">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -22314,7 +22314,7 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O135">
         <v>3.25</v>
@@ -22335,7 +22335,7 @@
         <v>2.89</v>
       </c>
       <c r="U135">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V135">
         <v>1.37</v>
@@ -22356,7 +22356,7 @@
         <v>1.96</v>
       </c>
       <c r="AB135">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC135">
         <v>3.14</v>
@@ -22498,7 +22498,7 @@
         <v>4.1</v>
       </c>
       <c r="U136">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="V136">
         <v>1.69</v>
@@ -22818,16 +22818,16 @@
         <v>2.3</v>
       </c>
       <c r="S138">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T138">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U138">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V138">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W138">
         <v>1.08</v>
@@ -22836,13 +22836,13 @@
         <v>1.01</v>
       </c>
       <c r="Y138">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z138">
-        <v>4.3</v>
+        <v>4.51</v>
       </c>
       <c r="AA138">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB138">
         <v>2.17</v>
@@ -22966,7 +22966,7 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O139">
         <v>3.8</v>
@@ -22999,7 +22999,7 @@
         <v>1.01</v>
       </c>
       <c r="Y139">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z139">
         <v>5.95</v>
@@ -23008,7 +23008,7 @@
         <v>1.4</v>
       </c>
       <c r="AB139">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="AC139">
         <v>1.94</v>
@@ -23150,13 +23150,13 @@
         <v>3.3</v>
       </c>
       <c r="U140">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="V140">
         <v>1.52</v>
       </c>
       <c r="W140">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X140">
         <v>1.01</v>
@@ -23171,16 +23171,16 @@
         <v>1.53</v>
       </c>
       <c r="AB140">
-        <v>2.24</v>
+        <v>2.45</v>
       </c>
       <c r="AC140">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AD140">
         <v>1.47</v>
       </c>
       <c r="AE140">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AF140">
         <v>1.48</v>
@@ -23292,16 +23292,16 @@
         </is>
       </c>
       <c r="N141">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="O141">
         <v>5.35</v>
       </c>
       <c r="P141">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Q141">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="R141">
         <v>2.63</v>
@@ -23310,7 +23310,7 @@
         <v>1.24</v>
       </c>
       <c r="T141">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U141">
         <v>2.32</v>
@@ -23331,7 +23331,7 @@
         <v>4.8</v>
       </c>
       <c r="AA141">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB141">
         <v>2.38</v>
@@ -23346,10 +23346,10 @@
         <v>1.17</v>
       </c>
       <c r="AF141">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG141">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>1.5</v>
       </c>
       <c r="W142">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X142">
         <v>1.03</v>
@@ -23497,7 +23497,7 @@
         <v>1.7</v>
       </c>
       <c r="AB142">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC142">
         <v>2.66</v>
@@ -23509,10 +23509,10 @@
         <v>1.1</v>
       </c>
       <c r="AF142">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG142">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23630,10 +23630,10 @@
         <v>2.81</v>
       </c>
       <c r="R143">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S143">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T143">
         <v>2.53</v>
@@ -23651,22 +23651,22 @@
         <v>1.03</v>
       </c>
       <c r="Y143">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z143">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA143">
         <v>2.08</v>
       </c>
       <c r="AB143">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC143">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD143">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE143">
         <v>1.05</v>
@@ -23784,16 +23784,16 @@
         <v>1.53</v>
       </c>
       <c r="O144">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P144">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Q144">
         <v>2</v>
       </c>
       <c r="R144">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="S144">
         <v>1.38</v>
@@ -23802,7 +23802,7 @@
         <v>2.94</v>
       </c>
       <c r="U144">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="V144">
         <v>1.38</v>
@@ -23817,7 +23817,7 @@
         <v>1.29</v>
       </c>
       <c r="Z144">
-        <v>3.39</v>
+        <v>3.28</v>
       </c>
       <c r="AA144">
         <v>1.89</v>
@@ -23854,7 +23854,7 @@
         <v>1.24</v>
       </c>
       <c r="AK144">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23998,10 +23998,10 @@
         <v>1.1</v>
       </c>
       <c r="AF145">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG145">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>1.24</v>
       </c>
       <c r="AK145">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24433,19 +24433,19 @@
         </is>
       </c>
       <c r="N148">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="O148">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P148">
         <v>1.48</v>
       </c>
       <c r="Q148">
-        <v>6.88</v>
+        <v>6</v>
       </c>
       <c r="R148">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S148">
         <v>1.4</v>
@@ -24469,19 +24469,19 @@
         <v>1.28</v>
       </c>
       <c r="Z148">
-        <v>3.33</v>
+        <v>3.08</v>
       </c>
       <c r="AA148">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AB148">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AC148">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD148">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE148">
         <v>1.05</v>
@@ -24596,16 +24596,16 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="O149">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="P149">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q149">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="R149">
         <v>2.73</v>
@@ -24614,13 +24614,13 @@
         <v>1.14</v>
       </c>
       <c r="T149">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="U149">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V149">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="W149">
         <v>1.22</v>
@@ -24635,22 +24635,22 @@
         <v>7.5</v>
       </c>
       <c r="AA149">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB149">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AC149">
         <v>1.89</v>
       </c>
       <c r="AD149">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AE149">
         <v>1.38</v>
       </c>
       <c r="AF149">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AG149">
         <v>3.2</v>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK149">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="O150">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="P150">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q150">
         <v>3.04</v>
@@ -24798,7 +24798,7 @@
         <v>6.6</v>
       </c>
       <c r="AA150">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AB150">
         <v>3.05</v>
@@ -24810,7 +24810,7 @@
         <v>1.95</v>
       </c>
       <c r="AE150">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AF150">
         <v>1.33</v>
@@ -24829,7 +24829,7 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK150">
         <v>1.33</v>
@@ -25094,19 +25094,19 @@
         <v>1.63</v>
       </c>
       <c r="Q152">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="R152">
         <v>2.15</v>
       </c>
       <c r="S152">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T152">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="U152">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="V152">
         <v>1.36</v>
@@ -25124,13 +25124,13 @@
         <v>3.05</v>
       </c>
       <c r="AA152">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AB152">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC152">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AD152">
         <v>1.22</v>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.3</v>
+        <v>2.25</v>
       </c>
       <c r="AK152">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25260,7 +25260,7 @@
         <v>3.3</v>
       </c>
       <c r="R153">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="S153">
         <v>1.45</v>
@@ -25299,7 +25299,7 @@
         <v>1.16</v>
       </c>
       <c r="AE153">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF153">
         <v>1.95</v>
@@ -25767,7 +25767,7 @@
         <v>1.12</v>
       </c>
       <c r="X156">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y156">
         <v>1.15</v>
@@ -25900,7 +25900,7 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="O157">
         <v>4</v>
@@ -25930,10 +25930,10 @@
         <v>1.12</v>
       </c>
       <c r="X157">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y157">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z157">
         <v>4.3</v>
@@ -25948,13 +25948,13 @@
         <v>2.58</v>
       </c>
       <c r="AD157">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE157">
         <v>1.15</v>
       </c>
       <c r="AF157">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG157">
         <v>2.05</v>
@@ -26093,7 +26093,7 @@
         <v>1.12</v>
       </c>
       <c r="X158">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y158">
         <v>1.17</v>
@@ -26133,7 +26133,7 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK158">
         <v>1.67</v>
@@ -26232,25 +26232,25 @@
         <v>5.1</v>
       </c>
       <c r="P159">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Q159">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="R159">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="S159">
         <v>1.18</v>
       </c>
       <c r="T159">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="U159">
         <v>1.91</v>
       </c>
       <c r="V159">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="W159">
         <v>1.22</v>
@@ -26262,25 +26262,25 @@
         <v>1.05</v>
       </c>
       <c r="Z159">
-        <v>6.6</v>
+        <v>6.65</v>
       </c>
       <c r="AA159">
         <v>1.29</v>
       </c>
       <c r="AB159">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AC159">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AD159">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AE159">
         <v>1.4</v>
       </c>
       <c r="AF159">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG159">
         <v>2.62</v>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK159">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26398,16 +26398,16 @@
         <v>1.32</v>
       </c>
       <c r="Q160">
-        <v>7.41</v>
+        <v>7.5</v>
       </c>
       <c r="R160">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="S160">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T160">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="U160">
         <v>2.4</v>
@@ -26425,28 +26425,28 @@
         <v>1.19</v>
       </c>
       <c r="Z160">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="AA160">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB160">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC160">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AD160">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE160">
         <v>1.12</v>
       </c>
       <c r="AF160">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AG160">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AK160">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -27062,7 +27062,7 @@
         <v>3.28</v>
       </c>
       <c r="U164">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="V164">
         <v>1.57</v>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.91</v>
+        <v>1.18</v>
       </c>
       <c r="AK164">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27391,7 +27391,7 @@
         <v>2.63</v>
       </c>
       <c r="V166">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W166">
         <v>1.06</v>
@@ -27409,7 +27409,7 @@
         <v>1.95</v>
       </c>
       <c r="AB166">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AC166">
         <v>3.4</v>
@@ -27530,25 +27530,25 @@
         </is>
       </c>
       <c r="N167">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="O167">
         <v>4</v>
       </c>
       <c r="P167">
-        <v>4.43</v>
+        <v>4.21</v>
       </c>
       <c r="Q167">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="R167">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S167">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T167">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="U167">
         <v>2.02</v>
@@ -27578,16 +27578,16 @@
         <v>2.04</v>
       </c>
       <c r="AD167">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AE167">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF167">
         <v>1.4</v>
       </c>
       <c r="AG167">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>1.17</v>
       </c>
       <c r="T170">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="U170">
         <v>1.89</v>
@@ -28206,7 +28206,7 @@
         <v>1.67</v>
       </c>
       <c r="V171">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W171">
         <v>1.3</v>
@@ -28224,10 +28224,10 @@
         <v>1.23</v>
       </c>
       <c r="AB171">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AC171">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AD171">
         <v>2.21</v>
@@ -28255,7 +28255,7 @@
         <v>1.14</v>
       </c>
       <c r="AK171">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28345,7 +28345,7 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="O172">
         <v>4.4</v>
@@ -28354,16 +28354,16 @@
         <v>3.65</v>
       </c>
       <c r="Q172">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="R172">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="S172">
         <v>1.13</v>
       </c>
       <c r="T172">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="U172">
         <v>1.67</v>
@@ -28372,28 +28372,28 @@
         <v>2.1</v>
       </c>
       <c r="W172">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="X172">
         <v>1</v>
       </c>
       <c r="Y172">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Z172">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AA172">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AB172">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AC172">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AD172">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="AE172">
         <v>1.57</v>
@@ -28402,7 +28402,7 @@
         <v>1.22</v>
       </c>
       <c r="AG172">
-        <v>3.56</v>
+        <v>3.75</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>1.22</v>
       </c>
       <c r="AK172">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28538,7 +28538,7 @@
         <v>1.29</v>
       </c>
       <c r="X173">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y173">
         <v>1.03</v>
@@ -28556,7 +28556,7 @@
         <v>1.65</v>
       </c>
       <c r="AD173">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AE173">
         <v>1.49</v>
@@ -28698,7 +28698,7 @@
         <v>1.95</v>
       </c>
       <c r="W174">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X174">
         <v>1.01</v>
@@ -28707,13 +28707,13 @@
         <v>1.04</v>
       </c>
       <c r="Z174">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="AA174">
         <v>1.24</v>
       </c>
       <c r="AB174">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AC174">
         <v>1.71</v>
@@ -28843,7 +28843,7 @@
         <v>7</v>
       </c>
       <c r="Q175">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="R175">
         <v>3.2</v>
@@ -28852,16 +28852,16 @@
         <v>1.15</v>
       </c>
       <c r="T175">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="U175">
         <v>1.73</v>
       </c>
       <c r="V175">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="W175">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X175">
         <v>1</v>
@@ -28870,25 +28870,25 @@
         <v>1.02</v>
       </c>
       <c r="Z175">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA175">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AB175">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="AC175">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AD175">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AE175">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AF175">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AG175">
         <v>2.62</v>
@@ -28907,7 +28907,7 @@
         <v>1.04</v>
       </c>
       <c r="AK175">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29054,7 +29054,7 @@
         <v>1.41</v>
       </c>
       <c r="AG176">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29178,16 +29178,16 @@
         <v>1.39</v>
       </c>
       <c r="T177">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="U177">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V177">
         <v>1.38</v>
       </c>
       <c r="W177">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X177">
         <v>1</v>
@@ -29196,16 +29196,16 @@
         <v>1.24</v>
       </c>
       <c r="Z177">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="AA177">
         <v>1.95</v>
       </c>
       <c r="AB177">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC177">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AD177">
         <v>1.3</v>
@@ -29217,7 +29217,7 @@
         <v>1.7</v>
       </c>
       <c r="AG177">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AK177">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29353,7 +29353,7 @@
         <v>1.06</v>
       </c>
       <c r="X178">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y178">
         <v>1.29</v>
@@ -29362,16 +29362,16 @@
         <v>3.2</v>
       </c>
       <c r="AA178">
+        <v>1.95</v>
+      </c>
+      <c r="AB178">
         <v>1.9</v>
-      </c>
-      <c r="AB178">
-        <v>1.85</v>
       </c>
       <c r="AC178">
         <v>3.14</v>
       </c>
       <c r="AD178">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE178">
         <v>1.06</v>
@@ -29492,19 +29492,19 @@
         <v>3.2</v>
       </c>
       <c r="P179">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q179">
-        <v>2.59</v>
+        <v>2.33</v>
       </c>
       <c r="R179">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="S179">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T179">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="U179">
         <v>3</v>
@@ -29513,7 +29513,7 @@
         <v>1.33</v>
       </c>
       <c r="W179">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X179">
         <v>1.02</v>
@@ -29525,25 +29525,25 @@
         <v>3.04</v>
       </c>
       <c r="AA179">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AB179">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC179">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD179">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE179">
         <v>1.06</v>
       </c>
       <c r="AF179">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG179">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK179">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29661,7 +29661,7 @@
         <v>3.75</v>
       </c>
       <c r="R180">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S180">
         <v>1.22</v>
@@ -29679,25 +29679,25 @@
         <v>1.15</v>
       </c>
       <c r="X180">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y180">
         <v>1.14</v>
       </c>
       <c r="Z180">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="AA180">
         <v>1.54</v>
       </c>
       <c r="AB180">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="AC180">
         <v>2.33</v>
       </c>
       <c r="AD180">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE180">
         <v>1.18</v>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK180">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29821,10 +29821,10 @@
         <v>3.1</v>
       </c>
       <c r="Q181">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="R181">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="S181">
         <v>1.26</v>
@@ -29836,13 +29836,13 @@
         <v>2.32</v>
       </c>
       <c r="V181">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W181">
         <v>1.12</v>
       </c>
       <c r="X181">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y181">
         <v>1.15</v>
@@ -29978,7 +29978,7 @@
         <v>2.15</v>
       </c>
       <c r="O182">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P182">
         <v>3.25</v>
@@ -30002,7 +30002,7 @@
         <v>1.23</v>
       </c>
       <c r="W182">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X182">
         <v>1.06</v>
@@ -30011,7 +30011,7 @@
         <v>1.45</v>
       </c>
       <c r="Z182">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AA182">
         <v>2.46</v>
@@ -30168,7 +30168,7 @@
         <v>1.1</v>
       </c>
       <c r="X183">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y183">
         <v>1.2</v>
@@ -30211,7 +30211,7 @@
         <v>1.2</v>
       </c>
       <c r="AK183">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30479,22 +30479,22 @@
         <v>2.13</v>
       </c>
       <c r="S185">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T185">
         <v>3.2</v>
       </c>
       <c r="U185">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="V185">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W185">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X185">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y185">
         <v>1.22</v>
@@ -30826,13 +30826,13 @@
         <v>1.3</v>
       </c>
       <c r="Z187">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA187">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AB187">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC187">
         <v>3.42</v>
@@ -31122,7 +31122,7 @@
         <v>3.75</v>
       </c>
       <c r="P189">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="Q189">
         <v>2.57</v>
@@ -31137,10 +31137,10 @@
         <v>3.8</v>
       </c>
       <c r="U189">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V189">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="W189">
         <v>1.17</v>
@@ -31158,22 +31158,22 @@
         <v>1.48</v>
       </c>
       <c r="AB189">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AC189">
         <v>2.27</v>
       </c>
       <c r="AD189">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE189">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF189">
         <v>1.44</v>
       </c>
       <c r="AG189">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31288,55 +31288,55 @@
         <v>2.9</v>
       </c>
       <c r="Q190">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R190">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S190">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T190">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U190">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V190">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W190">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y190">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z190">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA190">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB190">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC190">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD190">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE190">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF190">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG190">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK190">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31451,55 +31451,55 @@
         <v>4.6</v>
       </c>
       <c r="Q191">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R191">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S191">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T191">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="U191">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="V191">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W191">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X191">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y191">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z191">
-        <v>4.38</v>
+        <v>4.44</v>
       </c>
       <c r="AA191">
+        <v>1.65</v>
+      </c>
+      <c r="AB191">
+        <v>2.31</v>
+      </c>
+      <c r="AC191">
+        <v>2.3</v>
+      </c>
+      <c r="AD191">
+        <v>1.49</v>
+      </c>
+      <c r="AE191">
+        <v>1.17</v>
+      </c>
+      <c r="AF191">
         <v>1.66</v>
       </c>
-      <c r="AB191">
-        <v>2.23</v>
-      </c>
-      <c r="AC191">
-        <v>2.41</v>
-      </c>
-      <c r="AD191">
-        <v>1.45</v>
-      </c>
-      <c r="AE191">
-        <v>1.16</v>
-      </c>
-      <c r="AF191">
-        <v>1.61</v>
-      </c>
       <c r="AG191">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK191">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="O193">
         <v>3.6</v>
       </c>
       <c r="P193">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="O194">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P194">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q194">
         <v>2.61</v>
@@ -31946,10 +31946,10 @@
         <v>1.94</v>
       </c>
       <c r="S194">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T194">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="U194">
         <v>3.12</v>
@@ -32001,7 +32001,7 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK194">
         <v>1.62</v>
@@ -32094,31 +32094,31 @@
         </is>
       </c>
       <c r="N195">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="O195">
         <v>4.2</v>
       </c>
       <c r="P195">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q195">
         <v>1.93</v>
       </c>
       <c r="R195">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="S195">
         <v>1.2</v>
       </c>
       <c r="T195">
-        <v>3.98</v>
+        <v>3.85</v>
       </c>
       <c r="U195">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="V195">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W195">
         <v>1.18</v>
@@ -32130,25 +32130,25 @@
         <v>1.08</v>
       </c>
       <c r="Z195">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="AA195">
         <v>1.45</v>
       </c>
       <c r="AB195">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AC195">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AD195">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE195">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF195">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG195">
         <v>2.3</v>
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O196">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P196">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="Q196">
         <v>2.75</v>
@@ -32278,13 +32278,13 @@
         <v>4.4</v>
       </c>
       <c r="U196">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V196">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W196">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X196">
         <v>1.01</v>
@@ -32293,7 +32293,7 @@
         <v>1.05</v>
       </c>
       <c r="Z196">
-        <v>6.4</v>
+        <v>6.45</v>
       </c>
       <c r="AA196">
         <v>1.36</v>
@@ -32311,10 +32311,10 @@
         <v>1.39</v>
       </c>
       <c r="AF196">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AG196">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,7 +32327,7 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.2</v>
+        <v>1.51</v>
       </c>
       <c r="AK196">
         <v>1.5</v>
@@ -32474,10 +32474,10 @@
         <v>1.41</v>
       </c>
       <c r="AF197">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AG197">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32583,10 +32583,10 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="O198">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P198">
         <v>1.96</v>
@@ -32628,7 +32628,7 @@
         <v>3.04</v>
       </c>
       <c r="AC198">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AD198">
         <v>1.92</v>
@@ -32637,7 +32637,7 @@
         <v>1.34</v>
       </c>
       <c r="AF198">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AG198">
         <v>3.14</v>
@@ -32656,7 +32656,7 @@
         <v>1.25</v>
       </c>
       <c r="AK198">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32779,10 +32779,10 @@
         <v>1.01</v>
       </c>
       <c r="Y199">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z199">
-        <v>6.5</v>
+        <v>6.32</v>
       </c>
       <c r="AA199">
         <v>1.36</v>
@@ -32797,7 +32797,7 @@
         <v>1.83</v>
       </c>
       <c r="AE199">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AF199">
         <v>1.32</v>
@@ -33576,10 +33576,10 @@
         <v>2.38</v>
       </c>
       <c r="S204">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T204">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U204">
         <v>2.1</v>
@@ -33603,13 +33603,13 @@
         <v>1.53</v>
       </c>
       <c r="AB204">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="AC204">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="AD204">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE204">
         <v>1.26</v>
@@ -33618,7 +33618,7 @@
         <v>1.4</v>
       </c>
       <c r="AG204">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>2.55</v>
       </c>
       <c r="V208">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W208">
         <v>1.08</v>
@@ -34246,28 +34246,28 @@
         <v>1</v>
       </c>
       <c r="Y208">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z208">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="AA208">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB208">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AC208">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="AD208">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE208">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF208">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG208">
         <v>1.95</v>
@@ -34286,7 +34286,7 @@
         <v>1.29</v>
       </c>
       <c r="AK208">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34385,10 +34385,10 @@
         <v>3.5</v>
       </c>
       <c r="Q209">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="R209">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S209">
         <v>1.4</v>
@@ -34412,7 +34412,7 @@
         <v>1.38</v>
       </c>
       <c r="Z209">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="AA209">
         <v>2.24</v>
@@ -34430,10 +34430,10 @@
         <v>1.01</v>
       </c>
       <c r="AF209">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG209">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK209">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34557,13 +34557,13 @@
         <v>1.23</v>
       </c>
       <c r="T210">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U210">
         <v>2.38</v>
       </c>
       <c r="V210">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W210">
         <v>1.12</v>
@@ -34572,22 +34572,22 @@
         <v>1.03</v>
       </c>
       <c r="Y210">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z210">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA210">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AB210">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC210">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AD210">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AE210">
         <v>1.15</v>
@@ -34609,7 +34609,7 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK210">
         <v>2.91</v>
@@ -34702,7 +34702,7 @@
         </is>
       </c>
       <c r="N211">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O211">
         <v>3.1</v>
@@ -34714,16 +34714,16 @@
         <v>2.5</v>
       </c>
       <c r="R211">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S211">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T211">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U211">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="V211">
         <v>1.33</v>
@@ -34735,28 +34735,28 @@
         <v>1.04</v>
       </c>
       <c r="Y211">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z211">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA211">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="AB211">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AC211">
         <v>3.9</v>
       </c>
       <c r="AD211">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE211">
         <v>1.05</v>
       </c>
       <c r="AF211">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG211">
         <v>1.8</v>
@@ -34775,7 +34775,7 @@
         <v>1.25</v>
       </c>
       <c r="AK211">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -35031,61 +35031,61 @@
         <v>7</v>
       </c>
       <c r="O213">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="P213">
         <v>1.33</v>
       </c>
       <c r="Q213">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="R213">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="S213">
         <v>1.29</v>
       </c>
       <c r="T213">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="U213">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="V213">
         <v>1.45</v>
       </c>
       <c r="W213">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X213">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y213">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z213">
-        <v>3.78</v>
+        <v>3.88</v>
       </c>
       <c r="AA213">
         <v>1.86</v>
       </c>
       <c r="AB213">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AC213">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AD213">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE213">
         <v>1.09</v>
       </c>
       <c r="AF213">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AG213">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="AK213">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35200,16 +35200,16 @@
         <v>0</v>
       </c>
       <c r="Q214">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
       <c r="R214">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="S214">
         <v>1.4</v>
       </c>
       <c r="T214">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="U214">
         <v>2.8</v>
@@ -35221,34 +35221,34 @@
         <v>1.06</v>
       </c>
       <c r="X214">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y214">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z214">
         <v>3.81</v>
       </c>
       <c r="AA214">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AB214">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AC214">
-        <v>3.14</v>
+        <v>3.27</v>
       </c>
       <c r="AD214">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE214">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF214">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG214">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK214">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35354,31 +35354,31 @@
         </is>
       </c>
       <c r="N215">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="O215">
         <v>4.6</v>
       </c>
       <c r="P215">
-        <v>4.95</v>
+        <v>5.4</v>
       </c>
       <c r="Q215">
         <v>1.95</v>
       </c>
       <c r="R215">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="S215">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T215">
-        <v>3.65</v>
+        <v>3.74</v>
       </c>
       <c r="U215">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V215">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W215">
         <v>1.14</v>
@@ -35390,19 +35390,19 @@
         <v>1.1</v>
       </c>
       <c r="Z215">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AA215">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB215">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="AC215">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AD215">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="AE215">
         <v>1.22</v>
@@ -35680,13 +35680,13 @@
         </is>
       </c>
       <c r="N217">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="O217">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="P217">
-        <v>5.65</v>
+        <v>5</v>
       </c>
       <c r="Q217">
         <v>0</v>
@@ -35852,16 +35852,16 @@
         <v>3.6</v>
       </c>
       <c r="Q218">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="R218">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S218">
         <v>1.44</v>
       </c>
       <c r="T218">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="U218">
         <v>3.06</v>
@@ -35870,34 +35870,34 @@
         <v>1.33</v>
       </c>
       <c r="W218">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X218">
         <v>1.02</v>
       </c>
       <c r="Y218">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z218">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA218">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB218">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC218">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AD218">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE218">
         <v>1.02</v>
       </c>
       <c r="AF218">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG218">
         <v>1.8</v>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK218">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36006,7 +36006,7 @@
         </is>
       </c>
       <c r="N219">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O219">
         <v>3.5</v>
@@ -36027,10 +36027,10 @@
         <v>2.82</v>
       </c>
       <c r="U219">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V219">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W219">
         <v>1.11</v>
@@ -36039,10 +36039,10 @@
         <v>1.02</v>
       </c>
       <c r="Y219">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z219">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AA219">
         <v>1.81</v>
@@ -36051,16 +36051,16 @@
         <v>2.08</v>
       </c>
       <c r="AC219">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AD219">
         <v>1.36</v>
       </c>
       <c r="AE219">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF219">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG219">
         <v>2.25</v>
@@ -36175,13 +36175,13 @@
         <v>3.8</v>
       </c>
       <c r="P220">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q220">
         <v>4</v>
       </c>
       <c r="R220">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="S220">
         <v>1.25</v>
@@ -36196,10 +36196,10 @@
         <v>1.5</v>
       </c>
       <c r="W220">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X220">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y220">
         <v>1.18</v>
@@ -36208,25 +36208,25 @@
         <v>4.1</v>
       </c>
       <c r="AA220">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB220">
         <v>2.25</v>
       </c>
       <c r="AC220">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD220">
         <v>1.43</v>
       </c>
       <c r="AE220">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF220">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG220">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="O221">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P221">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q221">
         <v>1.44</v>
@@ -36350,7 +36350,7 @@
         <v>1.19</v>
       </c>
       <c r="T221">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="U221">
         <v>1.95</v>
@@ -36365,10 +36365,10 @@
         <v>1.01</v>
       </c>
       <c r="Y221">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z221">
-        <v>9.050000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AA221">
         <v>1.33</v>
@@ -36377,19 +36377,19 @@
         <v>3.3</v>
       </c>
       <c r="AC221">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AD221">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AE221">
         <v>1.38</v>
       </c>
       <c r="AF221">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AG221">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -37002,7 +37002,7 @@
         <v>1.36</v>
       </c>
       <c r="T225">
-        <v>2.91</v>
+        <v>2.57</v>
       </c>
       <c r="U225">
         <v>2.8</v>
@@ -37159,7 +37159,7 @@
         <v>2</v>
       </c>
       <c r="R226">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="S226">
         <v>1.26</v>
@@ -37177,7 +37177,7 @@
         <v>1.12</v>
       </c>
       <c r="X226">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y226">
         <v>1.22</v>
@@ -37192,7 +37192,7 @@
         <v>2.05</v>
       </c>
       <c r="AC226">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AD226">
         <v>1.37</v>
@@ -37313,10 +37313,10 @@
         <v>3.6</v>
       </c>
       <c r="O227">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P227">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q227">
         <v>4.33</v>
@@ -37343,10 +37343,10 @@
         <v>1.07</v>
       </c>
       <c r="Y227">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z227">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="AA227">
         <v>2.42</v>
@@ -37367,7 +37367,7 @@
         <v>2.05</v>
       </c>
       <c r="AG227">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>1.22</v>
       </c>
       <c r="AK228">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37636,22 +37636,22 @@
         </is>
       </c>
       <c r="N229">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O229">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P229">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q229">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R229">
         <v>2.2</v>
       </c>
       <c r="S229">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T229">
         <v>3.12</v>
@@ -37693,7 +37693,7 @@
         <v>1.59</v>
       </c>
       <c r="AG229">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -38297,7 +38297,7 @@
         <v>1.63</v>
       </c>
       <c r="Q233">
-        <v>3.88</v>
+        <v>4.2</v>
       </c>
       <c r="R233">
         <v>2.63</v>
@@ -38309,10 +38309,10 @@
         <v>4.33</v>
       </c>
       <c r="U233">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="V233">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="W233">
         <v>1.2</v>
@@ -38327,7 +38327,7 @@
         <v>6.75</v>
       </c>
       <c r="AA233">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AB233">
         <v>3.2</v>
@@ -38336,7 +38336,7 @@
         <v>1.78</v>
       </c>
       <c r="AD233">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="AE233">
         <v>1.42</v>
@@ -38358,7 +38358,7 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK233">
         <v>1.2</v>
@@ -38481,7 +38481,7 @@
         <v>1.08</v>
       </c>
       <c r="X234">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y234">
         <v>1.24</v>
@@ -38493,7 +38493,7 @@
         <v>1.93</v>
       </c>
       <c r="AB234">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AC234">
         <v>3.05</v>
@@ -38777,7 +38777,7 @@
         </is>
       </c>
       <c r="N236">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="O236">
         <v>3.6</v>
@@ -38786,10 +38786,10 @@
         <v>5.25</v>
       </c>
       <c r="Q236">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R236">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="S236">
         <v>1.35</v>
@@ -38946,10 +38946,10 @@
         <v>3.9</v>
       </c>
       <c r="P237">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="Q237">
-        <v>4.24</v>
+        <v>4.34</v>
       </c>
       <c r="R237">
         <v>2.25</v>
@@ -38958,16 +38958,16 @@
         <v>1.25</v>
       </c>
       <c r="T237">
-        <v>3.46</v>
+        <v>3.54</v>
       </c>
       <c r="U237">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="V237">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W237">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X237">
         <v>1.03</v>
@@ -38976,19 +38976,19 @@
         <v>1.14</v>
       </c>
       <c r="Z237">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA237">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB237">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AC237">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AD237">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE237">
         <v>1.15</v>
@@ -39115,13 +39115,13 @@
         <v>3.6</v>
       </c>
       <c r="R238">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="S238">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T238">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="U238">
         <v>2.54</v>
@@ -39176,7 +39176,7 @@
         <v>1.62</v>
       </c>
       <c r="AK238">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39429,10 +39429,10 @@
         </is>
       </c>
       <c r="N240">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="O240">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P240">
         <v>3.9</v>
@@ -39441,34 +39441,34 @@
         <v>2.63</v>
       </c>
       <c r="R240">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="S240">
         <v>1.4</v>
       </c>
       <c r="T240">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="U240">
         <v>2.83</v>
       </c>
       <c r="V240">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W240">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X240">
         <v>1.01</v>
       </c>
       <c r="Y240">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z240">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AA240">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB240">
         <v>1.72</v>
@@ -39499,10 +39499,10 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK240">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -39631,7 +39631,7 @@
         <v>7</v>
       </c>
       <c r="AA241">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB241">
         <v>2.72</v>
@@ -39764,40 +39764,40 @@
         <v>0</v>
       </c>
       <c r="Q242">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="R242">
         <v>2.15</v>
       </c>
       <c r="S242">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T242">
         <v>2.5</v>
       </c>
       <c r="U242">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="V242">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W242">
         <v>1.05</v>
       </c>
       <c r="X242">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y242">
         <v>1.39</v>
       </c>
       <c r="Z242">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AA242">
         <v>2.32</v>
       </c>
       <c r="AB242">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC242">
         <v>4.2</v>
@@ -39806,13 +39806,13 @@
         <v>1.15</v>
       </c>
       <c r="AE242">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF242">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AG242">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AH242" t="inlineStr">
         <is>
@@ -39825,7 +39825,7 @@
         </is>
       </c>
       <c r="AJ242">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AK242">
         <v>2.32</v>
@@ -39927,55 +39927,55 @@
         <v>4.35</v>
       </c>
       <c r="Q243">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="R243">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S243">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="T243">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="U243">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V243">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W243">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X243">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y243">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z243">
-        <v>3.76</v>
+        <v>4.2</v>
       </c>
       <c r="AA243">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AB243">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AC243">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="AD243">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AE243">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF243">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG243">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AH243" t="inlineStr">
         <is>
@@ -39988,10 +39988,10 @@
         </is>
       </c>
       <c r="AJ243">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK243">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -40570,16 +40570,16 @@
         </is>
       </c>
       <c r="N247">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="O247">
         <v>3.9</v>
       </c>
       <c r="P247">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q247">
-        <v>5.71</v>
+        <v>5.66</v>
       </c>
       <c r="R247">
         <v>2.15</v>
@@ -40588,7 +40588,7 @@
         <v>1.34</v>
       </c>
       <c r="T247">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="U247">
         <v>2.6</v>
@@ -40609,7 +40609,7 @@
         <v>3.42</v>
       </c>
       <c r="AA247">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB247">
         <v>1.92</v>
@@ -40911,46 +40911,46 @@
         <v>2.9</v>
       </c>
       <c r="S249">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T249">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="U249">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V249">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="W249">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="X249">
         <v>1.01</v>
       </c>
       <c r="Y249">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z249">
-        <v>6.4</v>
+        <v>6.05</v>
       </c>
       <c r="AA249">
+        <v>1.33</v>
+      </c>
+      <c r="AB249">
+        <v>2.83</v>
+      </c>
+      <c r="AC249">
+        <v>1.91</v>
+      </c>
+      <c r="AD249">
+        <v>1.73</v>
+      </c>
+      <c r="AE249">
         <v>1.3</v>
       </c>
-      <c r="AB249">
-        <v>2.97</v>
-      </c>
-      <c r="AC249">
+      <c r="AF249">
         <v>1.85</v>
-      </c>
-      <c r="AD249">
-        <v>1.88</v>
-      </c>
-      <c r="AE249">
-        <v>1.33</v>
-      </c>
-      <c r="AF249">
-        <v>1.8</v>
       </c>
       <c r="AG249">
         <v>1.85</v>
@@ -40969,7 +40969,7 @@
         <v>1</v>
       </c>
       <c r="AK249">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AL249">
         <v>0</v>
@@ -41089,10 +41089,10 @@
         <v>1.1</v>
       </c>
       <c r="X250">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y250">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z250">
         <v>3.58</v>
@@ -41129,7 +41129,7 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK250">
         <v>1.65</v>
@@ -41225,13 +41225,13 @@
         <v>1.31</v>
       </c>
       <c r="O251">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="P251">
         <v>7</v>
       </c>
       <c r="Q251">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="R251">
         <v>2.8</v>
@@ -41246,10 +41246,10 @@
         <v>1.96</v>
       </c>
       <c r="V251">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W251">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X251">
         <v>1.01</v>
@@ -41258,7 +41258,7 @@
         <v>1.05</v>
       </c>
       <c r="Z251">
-        <v>6.57</v>
+        <v>6.54</v>
       </c>
       <c r="AA251">
         <v>1.35</v>
@@ -41267,16 +41267,16 @@
         <v>2.92</v>
       </c>
       <c r="AC251">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AD251">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AE251">
         <v>1.31</v>
       </c>
       <c r="AF251">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG251">
         <v>2.15</v>
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G252">
@@ -41385,64 +41385,64 @@
         </is>
       </c>
       <c r="N252">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="O252">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P252">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q252">
-        <v>2.63</v>
+        <v>3.72</v>
       </c>
       <c r="R252">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="S252">
+        <v>1.44</v>
+      </c>
+      <c r="T252">
+        <v>2.44</v>
+      </c>
+      <c r="U252">
+        <v>2.72</v>
+      </c>
+      <c r="V252">
         <v>1.36</v>
       </c>
-      <c r="T252">
-        <v>2.94</v>
-      </c>
-      <c r="U252">
-        <v>2.75</v>
-      </c>
-      <c r="V252">
-        <v>1.4</v>
-      </c>
       <c r="W252">
+        <v>1.05</v>
+      </c>
+      <c r="X252">
+        <v>1.04</v>
+      </c>
+      <c r="Y252">
+        <v>1.26</v>
+      </c>
+      <c r="Z252">
+        <v>3.2</v>
+      </c>
+      <c r="AA252">
+        <v>1.88</v>
+      </c>
+      <c r="AB252">
+        <v>1.79</v>
+      </c>
+      <c r="AC252">
+        <v>2.97</v>
+      </c>
+      <c r="AD252">
+        <v>1.3</v>
+      </c>
+      <c r="AE252">
         <v>1.08</v>
       </c>
-      <c r="X252">
-        <v>1.01</v>
-      </c>
-      <c r="Y252">
-        <v>1.23</v>
-      </c>
-      <c r="Z252">
-        <v>3.42</v>
-      </c>
-      <c r="AA252">
-        <v>2.07</v>
-      </c>
-      <c r="AB252">
-        <v>1.72</v>
-      </c>
-      <c r="AC252">
-        <v>3.08</v>
-      </c>
-      <c r="AD252">
-        <v>1.28</v>
-      </c>
-      <c r="AE252">
-        <v>1.06</v>
-      </c>
       <c r="AF252">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AG252">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK252">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,64 +41548,64 @@
         </is>
       </c>
       <c r="N253">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="O253">
+        <v>3.25</v>
+      </c>
+      <c r="P253">
+        <v>3.25</v>
+      </c>
+      <c r="Q253">
+        <v>2.64</v>
+      </c>
+      <c r="R253">
+        <v>2.1</v>
+      </c>
+      <c r="S253">
+        <v>1.31</v>
+      </c>
+      <c r="T253">
         <v>2.95</v>
       </c>
-      <c r="P253">
-        <v>2.55</v>
-      </c>
-      <c r="Q253">
-        <v>3.7</v>
-      </c>
-      <c r="R253">
-        <v>1.87</v>
-      </c>
-      <c r="S253">
-        <v>1.44</v>
-      </c>
-      <c r="T253">
-        <v>2.44</v>
-      </c>
       <c r="U253">
-        <v>2.71</v>
+        <v>2.61</v>
       </c>
       <c r="V253">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W253">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X253">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y253">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z253">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA253">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB253">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC253">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="AD253">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE253">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF253">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG253">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK253">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41714,10 +41714,10 @@
         <v>2.1</v>
       </c>
       <c r="O254">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P254">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q254">
         <v>2.89</v>
@@ -41729,16 +41729,16 @@
         <v>1.44</v>
       </c>
       <c r="T254">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="U254">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="V254">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W254">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X254">
         <v>1.05</v>
@@ -41781,10 +41781,10 @@
         </is>
       </c>
       <c r="AJ254">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK254">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AL254">
         <v>0</v>
@@ -42363,13 +42363,13 @@
         </is>
       </c>
       <c r="N258">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="O258">
         <v>5.25</v>
       </c>
       <c r="P258">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Q258">
         <v>6</v>
@@ -42378,10 +42378,10 @@
         <v>2.7</v>
       </c>
       <c r="S258">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T258">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="U258">
         <v>1.95</v>
@@ -42390,37 +42390,37 @@
         <v>1.75</v>
       </c>
       <c r="W258">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X258">
         <v>1.01</v>
       </c>
       <c r="Y258">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z258">
-        <v>6.35</v>
+        <v>6.55</v>
       </c>
       <c r="AA258">
         <v>1.36</v>
       </c>
       <c r="AB258">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AC258">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AD258">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AE258">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF258">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG258">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AH258" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>1.18</v>
       </c>
       <c r="AK258">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AL258">
         <v>0</v>
@@ -42544,7 +42544,7 @@
         <v>1.29</v>
       </c>
       <c r="T259">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="U259">
         <v>2.43</v>
@@ -42568,7 +42568,7 @@
         <v>1.72</v>
       </c>
       <c r="AB259">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AC259">
         <v>2.66</v>
@@ -43015,64 +43015,64 @@
         </is>
       </c>
       <c r="N262">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O262">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P262">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q262">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R262">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S262">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T262">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U262">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V262">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W262">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X262">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y262">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z262">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA262">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AB262">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC262">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD262">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE262">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF262">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AG262">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH262" t="inlineStr">
         <is>
@@ -43085,10 +43085,10 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK262">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -43341,7 +43341,7 @@
         </is>
       </c>
       <c r="N264">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O264">
         <v>3.28</v>
@@ -43371,7 +43371,7 @@
         <v>1.03</v>
       </c>
       <c r="X264">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y264">
         <v>1.4</v>
@@ -43398,7 +43398,7 @@
         <v>2.05</v>
       </c>
       <c r="AG264">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43411,7 +43411,7 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AK264">
         <v>1.82</v>
@@ -43688,10 +43688,10 @@
         <v>2.88</v>
       </c>
       <c r="U266">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="V266">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W266">
         <v>1.1</v>
@@ -43700,22 +43700,22 @@
         <v>1.01</v>
       </c>
       <c r="Y266">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z266">
         <v>3.1</v>
       </c>
       <c r="AA266">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AB266">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC266">
         <v>3</v>
       </c>
       <c r="AD266">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE266">
         <v>1.07</v>
@@ -43737,7 +43737,7 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK266">
         <v>1.48</v>
@@ -43872,7 +43872,7 @@
         <v>2.29</v>
       </c>
       <c r="AB267">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC267">
         <v>4.45</v>
@@ -44319,7 +44319,7 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O270">
         <v>3.36</v>
@@ -44346,7 +44346,7 @@
         <v>1.44</v>
       </c>
       <c r="W270">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X270">
         <v>1.01</v>
@@ -44361,7 +44361,7 @@
         <v>1.8</v>
       </c>
       <c r="AB270">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC270">
         <v>3.13</v>
@@ -44370,7 +44370,7 @@
         <v>1.3</v>
       </c>
       <c r="AE270">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF270">
         <v>1.64</v>
@@ -44389,7 +44389,7 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK270">
         <v>1.44</v>
@@ -45949,64 +45949,64 @@
         </is>
       </c>
       <c r="N280">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="O280">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P280">
         <v>2.87</v>
       </c>
       <c r="Q280">
-        <v>3.16</v>
+        <v>3.23</v>
       </c>
       <c r="R280">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="S280">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="T280">
+        <v>2.45</v>
+      </c>
+      <c r="U280">
+        <v>3.22</v>
+      </c>
+      <c r="V280">
+        <v>1.26</v>
+      </c>
+      <c r="W280">
+        <v>1.03</v>
+      </c>
+      <c r="X280">
+        <v>1.05</v>
+      </c>
+      <c r="Y280">
+        <v>1.44</v>
+      </c>
+      <c r="Z280">
+        <v>2.57</v>
+      </c>
+      <c r="AA280">
         <v>2.52</v>
       </c>
-      <c r="U280">
-        <v>3.06</v>
-      </c>
-      <c r="V280">
-        <v>1.29</v>
-      </c>
-      <c r="W280">
-        <v>1.05</v>
-      </c>
-      <c r="X280">
-        <v>1.04</v>
-      </c>
-      <c r="Y280">
-        <v>1.4</v>
-      </c>
-      <c r="Z280">
-        <v>2.72</v>
-      </c>
-      <c r="AA280">
-        <v>2.39</v>
-      </c>
       <c r="AB280">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AC280">
-        <v>4.48</v>
+        <v>4.81</v>
       </c>
       <c r="AD280">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE280">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF280">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG280">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK280">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -46127,10 +46127,10 @@
         <v>2.62</v>
       </c>
       <c r="S281">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="T281">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U281">
         <v>2.17</v>
@@ -46438,64 +46438,64 @@
         </is>
       </c>
       <c r="N283">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O283">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P283">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q283">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R283">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S283">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T283">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U283">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V283">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W283">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X283">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y283">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z283">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AA283">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB283">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC283">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD283">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE283">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF283">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG283">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK283">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46601,64 +46601,64 @@
         </is>
       </c>
       <c r="N284">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O284">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P284">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q284">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R284">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S284">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T284">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U284">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="V284">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W284">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X284">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y284">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z284">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA284">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB284">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC284">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD284">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE284">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF284">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG284">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK284">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46767,22 +46767,22 @@
         <v>2.75</v>
       </c>
       <c r="O285">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="P285">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q285">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="R285">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="S285">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T285">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="U285">
         <v>3.24</v>
@@ -46797,19 +46797,19 @@
         <v>1.05</v>
       </c>
       <c r="Y285">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z285">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="AA285">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="AB285">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC285">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AD285">
         <v>1.16</v>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AK285">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -47262,10 +47262,10 @@
         <v>0</v>
       </c>
       <c r="Q288">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="R288">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="S288">
         <v>1.29</v>
@@ -47295,10 +47295,10 @@
         <v>1.68</v>
       </c>
       <c r="AB288">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AC288">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AD288">
         <v>1.36</v>
@@ -47307,7 +47307,7 @@
         <v>1.1</v>
       </c>
       <c r="AF288">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG288">
         <v>2.2</v>
@@ -47323,7 +47323,7 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AK288">
         <v>1.53</v>
@@ -47434,7 +47434,7 @@
         <v>1.25</v>
       </c>
       <c r="T289">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U289">
         <v>2.15</v>
@@ -47489,7 +47489,7 @@
         <v>1.22</v>
       </c>
       <c r="AK289">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47772,13 +47772,13 @@
         <v>1.08</v>
       </c>
       <c r="X291">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y291">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z291">
-        <v>3.44</v>
+        <v>3.56</v>
       </c>
       <c r="AA291">
         <v>1.9</v>
@@ -47787,13 +47787,13 @@
         <v>1.83</v>
       </c>
       <c r="AC291">
-        <v>3.11</v>
+        <v>3.18</v>
       </c>
       <c r="AD291">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE291">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF291">
         <v>1.68</v>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.11</v>
+        <v>1.44</v>
       </c>
       <c r="O2">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="P2">
-        <v>2.94</v>
+        <v>6.4</v>
       </c>
       <c r="Q2">
-        <v>2.71</v>
+        <v>1.88</v>
       </c>
       <c r="R2">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="S2">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>2.8</v>
+        <v>3.24</v>
       </c>
       <c r="U2">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="Z2">
-        <v>3.14</v>
+        <v>4.2</v>
       </c>
       <c r="AA2">
-        <v>2.08</v>
+        <v>1.64</v>
       </c>
       <c r="AB2">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="AC2">
-        <v>3.84</v>
+        <v>2.63</v>
       </c>
       <c r="AD2">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="AE2">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AF2">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG2">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK2">
-        <v>1.7</v>
+        <v>2.69</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.44</v>
+        <v>2.11</v>
       </c>
       <c r="O3">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="P3">
-        <v>6.4</v>
+        <v>2.94</v>
       </c>
       <c r="Q3">
-        <v>1.88</v>
+        <v>2.71</v>
       </c>
       <c r="R3">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
-        <v>3.24</v>
+        <v>2.8</v>
       </c>
       <c r="U3">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="V3">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="Z3">
-        <v>4.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA3">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="AB3">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="AC3">
-        <v>2.63</v>
+        <v>3.84</v>
       </c>
       <c r="AD3">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="AE3">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG3">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>2.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -2111,22 +2111,22 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.39</v>
+        <v>2.19</v>
       </c>
       <c r="R11">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="S11">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="T11">
-        <v>3.18</v>
+        <v>3.38</v>
       </c>
       <c r="U11">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="V11">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
         <v>1.09</v>
@@ -2135,16 +2135,16 @@
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z11">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="AA11">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB11">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AC11">
         <v>2.43</v>
@@ -2156,10 +2156,10 @@
         <v>1.14</v>
       </c>
       <c r="AF11">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG11">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AK11">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,31 +2265,31 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="O12">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="P12">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Q12">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R12">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
         <v>3.12</v>
       </c>
       <c r="U12">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W12">
         <v>1.08</v>
@@ -2298,31 +2298,31 @@
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z12">
-        <v>3.96</v>
+        <v>4.08</v>
       </c>
       <c r="AA12">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AB12">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AC12">
         <v>2.88</v>
       </c>
       <c r="AD12">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE12">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AG12">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AK12">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.53</v>
+        <v>3.6</v>
       </c>
       <c r="O21">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="P21">
-        <v>2.31</v>
+        <v>1.86</v>
       </c>
       <c r="Q21">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="R21">
         <v>2.01</v>
       </c>
       <c r="S21">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="T21">
-        <v>2.99</v>
+        <v>2.57</v>
       </c>
       <c r="U21">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="V21">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z21">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AA21">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB21">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AC21">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AD21">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE21">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF21">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AG21">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="AK21">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="O22">
-        <v>3.23</v>
+        <v>3.38</v>
       </c>
       <c r="P22">
-        <v>1.86</v>
+        <v>2.31</v>
       </c>
       <c r="Q22">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="R22">
         <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T22">
-        <v>2.57</v>
+        <v>2.99</v>
       </c>
       <c r="U22">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="V22">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
+        <v>1.08</v>
+      </c>
+      <c r="X22">
+        <v>1.03</v>
+      </c>
+      <c r="Y22">
+        <v>1.26</v>
+      </c>
+      <c r="Z22">
+        <v>3.2</v>
+      </c>
+      <c r="AA22">
+        <v>1.9</v>
+      </c>
+      <c r="AB22">
+        <v>1.87</v>
+      </c>
+      <c r="AC22">
+        <v>3.14</v>
+      </c>
+      <c r="AD22">
+        <v>1.27</v>
+      </c>
+      <c r="AE22">
         <v>1.07</v>
       </c>
-      <c r="X22">
-        <v>1.02</v>
-      </c>
-      <c r="Y22">
-        <v>1.3</v>
-      </c>
-      <c r="Z22">
-        <v>3.15</v>
-      </c>
-      <c r="AA22">
-        <v>2.05</v>
-      </c>
-      <c r="AB22">
-        <v>1.73</v>
-      </c>
-      <c r="AC22">
-        <v>3.42</v>
-      </c>
-      <c r="AD22">
-        <v>1.23</v>
-      </c>
-      <c r="AE22">
-        <v>1.05</v>
-      </c>
       <c r="AF22">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AG22">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="AK22">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,31 +4710,31 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="R27">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="S27">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="T27">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="U27">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="V27">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W27">
         <v>1.03</v>
@@ -4743,31 +4743,31 @@
         <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z27">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AA27">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AB27">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AC27">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="AD27">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF27">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AG27">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK27">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q28">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="R28">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="S28">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="T28">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="U28">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="V28">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W28">
         <v>1.03</v>
@@ -4906,31 +4906,31 @@
         <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z28">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="AA28">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AB28">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AC28">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="AD28">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE28">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF28">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AG28">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK28">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -12374,7 +12374,7 @@
         <v>6.6</v>
       </c>
       <c r="O74">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="P74">
         <v>1.49</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,80 +15957,80 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.8</v>
+        <v>2.87</v>
       </c>
       <c r="O96">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="P96">
-        <v>4.33</v>
+        <v>2.15</v>
       </c>
       <c r="Q96">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="R96">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="S96">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="T96">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="U96">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="V96">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="W96">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="X96">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="Z96">
-        <v>4.04</v>
+        <v>5.1</v>
       </c>
       <c r="AA96">
-        <v>1.74</v>
+        <v>1.45</v>
       </c>
       <c r="AB96">
-        <v>2.09</v>
+        <v>2.55</v>
       </c>
       <c r="AC96">
-        <v>2.64</v>
+        <v>2.23</v>
       </c>
       <c r="AD96">
+        <v>1.65</v>
+      </c>
+      <c r="AE96">
+        <v>1.26</v>
+      </c>
+      <c r="AF96">
+        <v>1.41</v>
+      </c>
+      <c r="AG96">
+        <v>2.73</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ96">
+        <v>1.67</v>
+      </c>
+      <c r="AK96">
         <v>1.39</v>
-      </c>
-      <c r="AE96">
-        <v>1.13</v>
-      </c>
-      <c r="AF96">
-        <v>1.67</v>
-      </c>
-      <c r="AG96">
-        <v>2.1</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ96">
-        <v>1.2</v>
-      </c>
-      <c r="AK96">
-        <v>2</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.87</v>
+        <v>1.8</v>
       </c>
       <c r="O97">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="P97">
-        <v>2.15</v>
+        <v>4.33</v>
       </c>
       <c r="Q97">
+        <v>2.4</v>
+      </c>
+      <c r="R97">
+        <v>2.22</v>
+      </c>
+      <c r="S97">
+        <v>1.35</v>
+      </c>
+      <c r="T97">
         <v>3.3</v>
       </c>
-      <c r="R97">
-        <v>2.5</v>
-      </c>
-      <c r="S97">
-        <v>1.23</v>
-      </c>
-      <c r="T97">
-        <v>4.1</v>
-      </c>
       <c r="U97">
-        <v>2.05</v>
+        <v>2.44</v>
       </c>
       <c r="V97">
+        <v>1.47</v>
+      </c>
+      <c r="W97">
+        <v>1.08</v>
+      </c>
+      <c r="X97">
+        <v>1</v>
+      </c>
+      <c r="Y97">
+        <v>1.21</v>
+      </c>
+      <c r="Z97">
+        <v>4.04</v>
+      </c>
+      <c r="AA97">
+        <v>1.74</v>
+      </c>
+      <c r="AB97">
+        <v>2.09</v>
+      </c>
+      <c r="AC97">
+        <v>2.64</v>
+      </c>
+      <c r="AD97">
+        <v>1.39</v>
+      </c>
+      <c r="AE97">
+        <v>1.13</v>
+      </c>
+      <c r="AF97">
         <v>1.67</v>
       </c>
-      <c r="W97">
-        <v>1.19</v>
-      </c>
-      <c r="X97">
-        <v>1.01</v>
-      </c>
-      <c r="Y97">
-        <v>1.11</v>
-      </c>
-      <c r="Z97">
-        <v>5.1</v>
-      </c>
-      <c r="AA97">
-        <v>1.45</v>
-      </c>
-      <c r="AB97">
-        <v>2.55</v>
-      </c>
-      <c r="AC97">
-        <v>2.23</v>
-      </c>
-      <c r="AD97">
-        <v>1.65</v>
-      </c>
-      <c r="AE97">
-        <v>1.26</v>
-      </c>
-      <c r="AF97">
-        <v>1.41</v>
-      </c>
       <c r="AG97">
-        <v>2.73</v>
+        <v>2.1</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AK97">
-        <v>1.39</v>
+        <v>2</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q106">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="R106">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S106">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="T106">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="U106">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="V106">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W106">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X106">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z106">
-        <v>3.72</v>
+        <v>4.2</v>
       </c>
       <c r="AA106">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AB106">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AC106">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="AD106">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE106">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF106">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="AG106">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AK106">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O107">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P107">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q107">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="R107">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S107">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="T107">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="U107">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="V107">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="W107">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z107">
-        <v>4.2</v>
+        <v>3.72</v>
       </c>
       <c r="AA107">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AB107">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AC107">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AD107">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE107">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF107">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="AG107">
-        <v>2.28</v>
+        <v>1.75</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AK107">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,80 +20684,80 @@
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q125">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="R125">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S125">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="T125">
-        <v>2.65</v>
+        <v>3.12</v>
       </c>
       <c r="U125">
-        <v>2.73</v>
+        <v>2.29</v>
       </c>
       <c r="V125">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W125">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X125">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y125">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="Z125">
-        <v>3.22</v>
+        <v>4.5</v>
       </c>
       <c r="AA125">
-        <v>1.97</v>
+        <v>1.6</v>
       </c>
       <c r="AB125">
+        <v>2.3</v>
+      </c>
+      <c r="AC125">
+        <v>2.5</v>
+      </c>
+      <c r="AD125">
+        <v>1.45</v>
+      </c>
+      <c r="AE125">
+        <v>1.14</v>
+      </c>
+      <c r="AF125">
+        <v>1.51</v>
+      </c>
+      <c r="AG125">
+        <v>2.36</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ125">
+        <v>1.25</v>
+      </c>
+      <c r="AK125">
         <v>1.72</v>
-      </c>
-      <c r="AC125">
-        <v>3.28</v>
-      </c>
-      <c r="AD125">
-        <v>1.25</v>
-      </c>
-      <c r="AE125">
-        <v>1.05</v>
-      </c>
-      <c r="AF125">
-        <v>1.83</v>
-      </c>
-      <c r="AG125">
-        <v>1.85</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ125">
-        <v>1.22</v>
-      </c>
-      <c r="AK125">
-        <v>1.73</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O126">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P126">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q126">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="R126">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S126">
+        <v>1.43</v>
+      </c>
+      <c r="T126">
+        <v>2.65</v>
+      </c>
+      <c r="U126">
+        <v>2.73</v>
+      </c>
+      <c r="V126">
+        <v>1.36</v>
+      </c>
+      <c r="W126">
+        <v>1.05</v>
+      </c>
+      <c r="X126">
+        <v>1.04</v>
+      </c>
+      <c r="Y126">
+        <v>1.32</v>
+      </c>
+      <c r="Z126">
+        <v>3.22</v>
+      </c>
+      <c r="AA126">
+        <v>1.97</v>
+      </c>
+      <c r="AB126">
+        <v>1.72</v>
+      </c>
+      <c r="AC126">
+        <v>3.28</v>
+      </c>
+      <c r="AD126">
         <v>1.25</v>
       </c>
-      <c r="T126">
-        <v>3.12</v>
-      </c>
-      <c r="U126">
-        <v>2.29</v>
-      </c>
-      <c r="V126">
-        <v>1.5</v>
-      </c>
-      <c r="W126">
-        <v>1.08</v>
-      </c>
-      <c r="X126">
-        <v>1.01</v>
-      </c>
-      <c r="Y126">
-        <v>1.13</v>
-      </c>
-      <c r="Z126">
-        <v>4.5</v>
-      </c>
-      <c r="AA126">
-        <v>1.6</v>
-      </c>
-      <c r="AB126">
-        <v>2.3</v>
-      </c>
-      <c r="AC126">
-        <v>2.5</v>
-      </c>
-      <c r="AD126">
-        <v>1.45</v>
-      </c>
       <c r="AE126">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF126">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="AG126">
-        <v>2.36</v>
+        <v>1.85</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK126">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
-        <v>2.78</v>
+        <v>1.95</v>
       </c>
       <c r="O272">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="P272">
-        <v>2.42</v>
+        <v>4</v>
       </c>
       <c r="Q272">
-        <v>3.96</v>
+        <v>2.82</v>
       </c>
       <c r="R272">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="S272">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="T272">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="U272">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="V272">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W272">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X272">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Y272">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="Z272">
-        <v>2.33</v>
+        <v>2.04</v>
       </c>
       <c r="AA272">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="AB272">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AC272">
-        <v>5.36</v>
+        <v>6.7</v>
       </c>
       <c r="AD272">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AE272">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF272">
-        <v>2.12</v>
+        <v>2.57</v>
       </c>
       <c r="AG272">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AK272">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,28 +44808,28 @@
         </is>
       </c>
       <c r="N273">
-        <v>1.8</v>
+        <v>2.78</v>
       </c>
       <c r="O273">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P273">
-        <v>5.2</v>
+        <v>2.42</v>
       </c>
       <c r="Q273">
-        <v>2.5</v>
+        <v>3.96</v>
       </c>
       <c r="R273">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="S273">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="T273">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="U273">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="V273">
         <v>1.2</v>
@@ -44838,50 +44838,50 @@
         <v>1.04</v>
       </c>
       <c r="X273">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y273">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="Z273">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AA273">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AB273">
+        <v>1.4</v>
+      </c>
+      <c r="AC273">
+        <v>5.36</v>
+      </c>
+      <c r="AD273">
+        <v>1.1</v>
+      </c>
+      <c r="AE273">
+        <v>1.01</v>
+      </c>
+      <c r="AF273">
+        <v>2.12</v>
+      </c>
+      <c r="AG273">
+        <v>1.63</v>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ273">
+        <v>1.44</v>
+      </c>
+      <c r="AK273">
         <v>1.36</v>
-      </c>
-      <c r="AC273">
-        <v>5.8</v>
-      </c>
-      <c r="AD273">
-        <v>1.07</v>
-      </c>
-      <c r="AE273">
-        <v>1.03</v>
-      </c>
-      <c r="AF273">
-        <v>2.5</v>
-      </c>
-      <c r="AG273">
-        <v>1.46</v>
-      </c>
-      <c r="AH273" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI273" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ273">
-        <v>1.33</v>
-      </c>
-      <c r="AK273">
-        <v>1.79</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,64 +44971,64 @@
         </is>
       </c>
       <c r="N274">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="O274">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P274">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="Q274">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="R274">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="S274">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="T274">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U274">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="V274">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W274">
+        <v>1.04</v>
+      </c>
+      <c r="X274">
+        <v>1.09</v>
+      </c>
+      <c r="Y274">
+        <v>1.6</v>
+      </c>
+      <c r="Z274">
+        <v>2.15</v>
+      </c>
+      <c r="AA274">
+        <v>2.83</v>
+      </c>
+      <c r="AB274">
+        <v>1.36</v>
+      </c>
+      <c r="AC274">
+        <v>5.8</v>
+      </c>
+      <c r="AD274">
+        <v>1.07</v>
+      </c>
+      <c r="AE274">
         <v>1.03</v>
       </c>
-      <c r="X274">
-        <v>1.15</v>
-      </c>
-      <c r="Y274">
-        <v>1.67</v>
-      </c>
-      <c r="Z274">
-        <v>2.04</v>
-      </c>
-      <c r="AA274">
-        <v>3.08</v>
-      </c>
-      <c r="AB274">
-        <v>1.32</v>
-      </c>
-      <c r="AC274">
-        <v>6.7</v>
-      </c>
-      <c r="AD274">
-        <v>1.05</v>
-      </c>
-      <c r="AE274">
-        <v>1.02</v>
-      </c>
       <c r="AF274">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AG274">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,10 +45041,10 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK274">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AL274">
         <v>0</v>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.44</v>
+        <v>2.11</v>
       </c>
       <c r="O2">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>6.4</v>
+        <v>2.94</v>
       </c>
       <c r="Q2">
-        <v>1.88</v>
+        <v>2.71</v>
       </c>
       <c r="R2">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S2">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>3.24</v>
+        <v>2.8</v>
       </c>
       <c r="U2">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="V2">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="Z2">
-        <v>4.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA2">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="AB2">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="AC2">
-        <v>2.63</v>
+        <v>3.84</v>
       </c>
       <c r="AD2">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="AE2">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG2">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>2.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.11</v>
+        <v>1.44</v>
       </c>
       <c r="O3">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="P3">
-        <v>2.94</v>
+        <v>6.4</v>
       </c>
       <c r="Q3">
-        <v>2.71</v>
+        <v>1.88</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="S3">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>2.8</v>
+        <v>3.24</v>
       </c>
       <c r="U3">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="Z3">
-        <v>3.14</v>
+        <v>4.2</v>
       </c>
       <c r="AA3">
-        <v>2.08</v>
+        <v>1.64</v>
       </c>
       <c r="AB3">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="AC3">
-        <v>3.84</v>
+        <v>2.63</v>
       </c>
       <c r="AD3">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="AE3">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AF3">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG3">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK3">
-        <v>1.7</v>
+        <v>2.69</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="O9">
         <v>4.2</v>
       </c>
       <c r="P9">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q9">
         <v>2.1</v>
@@ -1821,7 +1821,7 @@
         <v>2.26</v>
       </c>
       <c r="AC9">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AD9">
         <v>1.5</v>
@@ -2120,10 +2120,10 @@
         <v>1.24</v>
       </c>
       <c r="T11">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="U11">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="V11">
         <v>1.5</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
         <v>1.89</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="O12">
         <v>4.3</v>
@@ -2274,7 +2274,7 @@
         <v>5.5</v>
       </c>
       <c r="Q12">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="R12">
         <v>2.25</v>
@@ -2301,19 +2301,19 @@
         <v>1.2</v>
       </c>
       <c r="Z12">
-        <v>4.08</v>
+        <v>4.33</v>
       </c>
       <c r="AA12">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB12">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AC12">
         <v>2.88</v>
       </c>
       <c r="AD12">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE12">
         <v>1.14</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AK12">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.03</v>
+        <v>2.29</v>
       </c>
       <c r="O13">
         <v>3.15</v>
       </c>
       <c r="P13">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="O14">
         <v>3.1</v>
       </c>
       <c r="P14">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="Q14">
         <v>2.8</v>
@@ -2636,7 +2636,7 @@
         <v>1.52</v>
       </c>
       <c r="AC14">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AD14">
         <v>1.14</v>
@@ -2648,7 +2648,7 @@
         <v>2</v>
       </c>
       <c r="AG14">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK14">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="O15">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="P15">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
         <v>3.9</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="O17">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P17">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="O18">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P18">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="O19">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB19">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -3578,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="Q20">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="R20">
         <v>2.05</v>
@@ -3587,7 +3587,7 @@
         <v>1.48</v>
       </c>
       <c r="T20">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="U20">
         <v>3.18</v>
@@ -3608,13 +3608,13 @@
         <v>2.7</v>
       </c>
       <c r="AA20">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AB20">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC20">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AD20">
         <v>1.16</v>
@@ -3623,7 +3623,7 @@
         <v>1.01</v>
       </c>
       <c r="AF20">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AG20">
         <v>1.75</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="O21">
-        <v>3.23</v>
+        <v>3.38</v>
       </c>
       <c r="P21">
-        <v>1.86</v>
+        <v>2.31</v>
       </c>
       <c r="Q21">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="R21">
         <v>2.01</v>
       </c>
       <c r="S21">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T21">
-        <v>2.57</v>
+        <v>2.99</v>
       </c>
       <c r="U21">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="V21">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W21">
+        <v>1.08</v>
+      </c>
+      <c r="X21">
+        <v>1.03</v>
+      </c>
+      <c r="Y21">
+        <v>1.26</v>
+      </c>
+      <c r="Z21">
+        <v>3.2</v>
+      </c>
+      <c r="AA21">
+        <v>1.9</v>
+      </c>
+      <c r="AB21">
+        <v>1.87</v>
+      </c>
+      <c r="AC21">
+        <v>3.14</v>
+      </c>
+      <c r="AD21">
+        <v>1.27</v>
+      </c>
+      <c r="AE21">
         <v>1.07</v>
       </c>
-      <c r="X21">
-        <v>1.02</v>
-      </c>
-      <c r="Y21">
-        <v>1.3</v>
-      </c>
-      <c r="Z21">
-        <v>3.15</v>
-      </c>
-      <c r="AA21">
-        <v>2.05</v>
-      </c>
-      <c r="AB21">
-        <v>1.73</v>
-      </c>
-      <c r="AC21">
-        <v>3.42</v>
-      </c>
-      <c r="AD21">
-        <v>1.23</v>
-      </c>
-      <c r="AE21">
-        <v>1.05</v>
-      </c>
       <c r="AF21">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AG21">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="AK21">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.53</v>
+        <v>3.6</v>
       </c>
       <c r="O22">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="P22">
-        <v>2.31</v>
+        <v>1.86</v>
       </c>
       <c r="Q22">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="R22">
         <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="T22">
-        <v>2.99</v>
+        <v>2.57</v>
       </c>
       <c r="U22">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="V22">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W22">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z22">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AA22">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB22">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AC22">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AD22">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE22">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AG22">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="AK22">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="O26">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P26">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="Q26">
         <v>2.62</v>
       </c>
       <c r="R26">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S26">
         <v>1.44</v>
@@ -4574,7 +4574,7 @@
         <v>1.22</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X26">
         <v>1.07</v>
@@ -4586,10 +4586,10 @@
         <v>2.56</v>
       </c>
       <c r="AA26">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="AB26">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AC26">
         <v>4.6</v>
@@ -4620,7 +4620,7 @@
         <v>1.16</v>
       </c>
       <c r="AK26">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,31 +4710,31 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q27">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="R27">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="S27">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="T27">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="U27">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="V27">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W27">
         <v>1.03</v>
@@ -4743,47 +4743,47 @@
         <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z27">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AA27">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AB27">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC27">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="AD27">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE27">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF27">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AG27">
+        <v>1.66</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.15</v>
+      </c>
+      <c r="AK27">
         <v>1.75</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.29</v>
-      </c>
-      <c r="AK27">
-        <v>1.55</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="R28">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="S28">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="T28">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="U28">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="V28">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W28">
         <v>1.03</v>
@@ -4906,31 +4906,31 @@
         <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z28">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AA28">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AB28">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AC28">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="AD28">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE28">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF28">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AG28">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK28">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.48</v>
+        <v>3.21</v>
       </c>
       <c r="O29">
         <v>3.6</v>
       </c>
       <c r="P29">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB29">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="O32">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P32">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB33">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O34">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P34">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB34">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="O35">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="P35">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AB35">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="O37">
         <v>3.55</v>
@@ -6349,7 +6349,7 @@
         <v>2.85</v>
       </c>
       <c r="Q37">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="R37">
         <v>2.3</v>
@@ -6376,7 +6376,7 @@
         <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>4.41</v>
+        <v>3.96</v>
       </c>
       <c r="AA37">
         <v>1.66</v>
@@ -6391,7 +6391,7 @@
         <v>1.46</v>
       </c>
       <c r="AE37">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF37">
         <v>1.55</v>
@@ -6509,7 +6509,7 @@
         <v>6.25</v>
       </c>
       <c r="P38">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Q38">
         <v>1.6</v>
@@ -6536,19 +6536,19 @@
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z38">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AA38">
         <v>1.3</v>
       </c>
       <c r="AB38">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AC38">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AD38">
         <v>1.9</v>
@@ -6576,7 +6576,7 @@
         <v>1.08</v>
       </c>
       <c r="AK38">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6675,28 +6675,28 @@
         <v>0</v>
       </c>
       <c r="Q39">
-        <v>3.85</v>
+        <v>3.87</v>
       </c>
       <c r="R39">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="S39">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T39">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U39">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="V39">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W39">
         <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y39">
         <v>1.24</v>
@@ -6705,19 +6705,19 @@
         <v>3.34</v>
       </c>
       <c r="AA39">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AB39">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC39">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD39">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE39">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
         <v>1.69</v>
@@ -6739,7 +6739,7 @@
         <v>1.61</v>
       </c>
       <c r="AK39">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="O40">
+        <v>2.9</v>
+      </c>
+      <c r="P40">
+        <v>2.95</v>
+      </c>
+      <c r="Q40">
+        <v>2.93</v>
+      </c>
+      <c r="R40">
+        <v>1.88</v>
+      </c>
+      <c r="S40">
+        <v>1.46</v>
+      </c>
+      <c r="T40">
+        <v>2.58</v>
+      </c>
+      <c r="U40">
         <v>3</v>
       </c>
-      <c r="P40">
-        <v>3</v>
-      </c>
-      <c r="Q40">
-        <v>3</v>
-      </c>
-      <c r="R40">
-        <v>1.89</v>
-      </c>
-      <c r="S40">
-        <v>1.44</v>
-      </c>
-      <c r="T40">
-        <v>2.42</v>
-      </c>
-      <c r="U40">
-        <v>3.06</v>
-      </c>
       <c r="V40">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W40">
+        <v>1.04</v>
+      </c>
+      <c r="X40">
         <v>1.05</v>
       </c>
-      <c r="X40">
-        <v>1.04</v>
-      </c>
       <c r="Y40">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z40">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AA40">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AB40">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC40">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AD40">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE40">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF40">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AG40">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK40">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,37 +6992,37 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O41">
         <v>3.45</v>
       </c>
       <c r="P41">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="Q41">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R41">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S41">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T41">
         <v>2.85</v>
       </c>
       <c r="U41">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="V41">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W41">
         <v>1.07</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
         <v>1.25</v>
@@ -7031,22 +7031,22 @@
         <v>3.44</v>
       </c>
       <c r="AA41">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AB41">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AC41">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="AD41">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE41">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG41">
         <v>2.2</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>6.97</v>
+        <v>4.7</v>
       </c>
       <c r="O43">
-        <v>3.43</v>
+        <v>4.2</v>
       </c>
       <c r="P43">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="Q43">
         <v>5</v>
@@ -7339,13 +7339,13 @@
         <v>2.89</v>
       </c>
       <c r="U43">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="V43">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W43">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X43">
         <v>1</v>
@@ -7363,19 +7363,19 @@
         <v>2.21</v>
       </c>
       <c r="AC43">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AD43">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE43">
         <v>1.19</v>
       </c>
       <c r="AF43">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG43">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q44">
         <v>4</v>
@@ -7499,7 +7499,7 @@
         <v>1.34</v>
       </c>
       <c r="T44">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="U44">
         <v>2.5</v>
@@ -7514,7 +7514,7 @@
         <v>1</v>
       </c>
       <c r="Y44">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z44">
         <v>3.58</v>
@@ -7526,13 +7526,13 @@
         <v>2</v>
       </c>
       <c r="AC44">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AD44">
         <v>1.34</v>
       </c>
       <c r="AE44">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF44">
         <v>1.67</v>
@@ -7554,7 +7554,7 @@
         <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="O49">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="P49">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8643,7 +8643,7 @@
         <v>3.3</v>
       </c>
       <c r="U51">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="V51">
         <v>1.48</v>
@@ -8658,7 +8658,7 @@
         <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AA51">
         <v>1.71</v>
@@ -8667,7 +8667,7 @@
         <v>2.07</v>
       </c>
       <c r="AC51">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="AD51">
         <v>1.36</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AK51">
         <v>1.23</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="O53">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P53">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="Q53">
         <v>2.68</v>
@@ -8963,16 +8963,16 @@
         <v>2.19</v>
       </c>
       <c r="S53">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T53">
         <v>3.25</v>
       </c>
       <c r="U53">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V53">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W53">
         <v>1.11</v>
@@ -8984,16 +8984,16 @@
         <v>1.15</v>
       </c>
       <c r="Z53">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA53">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB53">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AC53">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AD53">
         <v>1.47</v>
@@ -9005,7 +9005,7 @@
         <v>1.5</v>
       </c>
       <c r="AG53">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9111,28 +9111,28 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q54">
-        <v>5.57</v>
+        <v>5.51</v>
       </c>
       <c r="R54">
         <v>2.41</v>
       </c>
       <c r="S54">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T54">
         <v>3.25</v>
       </c>
       <c r="U54">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V54">
         <v>1.5</v>
@@ -9144,10 +9144,10 @@
         <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z54">
-        <v>3.94</v>
+        <v>4.33</v>
       </c>
       <c r="AA54">
         <v>1.66</v>
@@ -9159,16 +9159,16 @@
         <v>2.69</v>
       </c>
       <c r="AD54">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE54">
         <v>1.12</v>
       </c>
       <c r="AF54">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG54">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.16</v>
+        <v>2.3</v>
       </c>
       <c r="AK54">
         <v>1.08</v>
@@ -9929,13 +9929,13 @@
         <v>4</v>
       </c>
       <c r="O59">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P59">
         <v>1.67</v>
       </c>
       <c r="Q59">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="R59">
         <v>2.27</v>
@@ -9980,10 +9980,10 @@
         <v>1.14</v>
       </c>
       <c r="AF59">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG59">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AK59">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10095,59 +10095,59 @@
         <v>4.05</v>
       </c>
       <c r="P60">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA60">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB60">
+        <v>2.05</v>
+      </c>
+      <c r="AC60">
+        <v>2.7</v>
+      </c>
+      <c r="AD60">
+        <v>1.36</v>
+      </c>
+      <c r="AE60">
+        <v>1.1</v>
+      </c>
+      <c r="AF60">
+        <v>1.73</v>
+      </c>
+      <c r="AG60">
         <v>2</v>
       </c>
-      <c r="AC60">
-        <v>0</v>
-      </c>
-      <c r="AD60">
-        <v>0</v>
-      </c>
-      <c r="AE60">
-        <v>0</v>
-      </c>
-      <c r="AF60">
-        <v>0</v>
-      </c>
-      <c r="AG60">
-        <v>0</v>
-      </c>
       <c r="AH60" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,19 +10252,19 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q61">
         <v>2.56</v>
       </c>
       <c r="R61">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S61">
         <v>1.33</v>
@@ -10282,10 +10282,10 @@
         <v>1.1</v>
       </c>
       <c r="X61">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y61">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z61">
         <v>3.7</v>
@@ -10303,13 +10303,13 @@
         <v>1.38</v>
       </c>
       <c r="AE61">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF61">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG61">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK61">
         <v>1.7</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="O69">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P69">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q69">
         <v>2.73</v>
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="O71">
         <v>3.4</v>
@@ -11891,10 +11891,10 @@
         <v>2.2</v>
       </c>
       <c r="Q71">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R71">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S71">
         <v>1.31</v>
@@ -11906,7 +11906,7 @@
         <v>2.45</v>
       </c>
       <c r="V71">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W71">
         <v>1.08</v>
@@ -11918,10 +11918,10 @@
         <v>1.18</v>
       </c>
       <c r="Z71">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="AA71">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB71">
         <v>2.08</v>
@@ -11933,7 +11933,7 @@
         <v>1.38</v>
       </c>
       <c r="AE71">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF71">
         <v>1.6</v>
@@ -11955,7 +11955,7 @@
         <v>1.27</v>
       </c>
       <c r="AK71">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12054,7 +12054,7 @@
         <v>2.17</v>
       </c>
       <c r="Q72">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="R72">
         <v>2.18</v>
@@ -12075,13 +12075,13 @@
         <v>1.09</v>
       </c>
       <c r="X72">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
         <v>1.16</v>
       </c>
       <c r="Z72">
-        <v>4.1</v>
+        <v>4.54</v>
       </c>
       <c r="AA72">
         <v>1.63</v>
@@ -12096,7 +12096,7 @@
         <v>1.43</v>
       </c>
       <c r="AE72">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF72">
         <v>1.53</v>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK72">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="N74">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="O74">
         <v>4.1</v>
@@ -12392,10 +12392,10 @@
         <v>2.64</v>
       </c>
       <c r="U74">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="V74">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W74">
         <v>1.08</v>
@@ -12404,31 +12404,31 @@
         <v>1</v>
       </c>
       <c r="Y74">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z74">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA74">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB74">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC74">
         <v>3.43</v>
       </c>
       <c r="AD74">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE74">
         <v>1.04</v>
       </c>
       <c r="AF74">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AG74">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>3.25</v>
       </c>
       <c r="P76">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q76">
         <v>3.1</v>
@@ -12727,7 +12727,7 @@
         <v>1.1</v>
       </c>
       <c r="X76">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y76">
         <v>1.23</v>
@@ -12739,7 +12739,7 @@
         <v>1.83</v>
       </c>
       <c r="AB76">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC76">
         <v>2.92</v>
@@ -12748,10 +12748,10 @@
         <v>1.31</v>
       </c>
       <c r="AE76">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF76">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG76">
         <v>2.05</v>
@@ -12875,28 +12875,28 @@
         <v>2.01</v>
       </c>
       <c r="S77">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="T77">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="U77">
-        <v>3.06</v>
+        <v>2.82</v>
       </c>
       <c r="V77">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W77">
+        <v>1.05</v>
+      </c>
+      <c r="X77">
         <v>1.04</v>
       </c>
-      <c r="X77">
-        <v>1.01</v>
-      </c>
       <c r="Y77">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z77">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="AA77">
         <v>2.06</v>
@@ -12905,13 +12905,13 @@
         <v>1.65</v>
       </c>
       <c r="AC77">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="AD77">
         <v>1.19</v>
       </c>
       <c r="AE77">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF77">
         <v>1.9</v>
@@ -13032,55 +13032,55 @@
         <v>1.91</v>
       </c>
       <c r="Q78">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R78">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="S78">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T78">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="U78">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V78">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W78">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X78">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z78">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="AA78">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AB78">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC78">
         <v>2.96</v>
       </c>
       <c r="AD78">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE78">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF78">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG78">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AK78">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13379,7 +13379,7 @@
         <v>1.08</v>
       </c>
       <c r="X80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y80">
         <v>1.27</v>
@@ -13391,7 +13391,7 @@
         <v>1.88</v>
       </c>
       <c r="AB80">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC80">
         <v>3.14</v>
@@ -13400,7 +13400,7 @@
         <v>1.3</v>
       </c>
       <c r="AE80">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF80">
         <v>1.74</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="O83">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P83">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q83">
         <v>2.71</v>
@@ -13862,19 +13862,19 @@
         <v>3.25</v>
       </c>
       <c r="V83">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W83">
         <v>1.01</v>
       </c>
       <c r="X83">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y83">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z83">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AA83">
         <v>2.25</v>
@@ -13883,10 +13883,10 @@
         <v>1.61</v>
       </c>
       <c r="AC83">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AD83">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE83">
         <v>1.01</v>
@@ -14327,10 +14327,10 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O86">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P86">
         <v>3</v>
@@ -14339,10 +14339,10 @@
         <v>2.7</v>
       </c>
       <c r="R86">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S86">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T86">
         <v>3.6</v>
@@ -14351,7 +14351,7 @@
         <v>2.31</v>
       </c>
       <c r="V86">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W86">
         <v>1.12</v>
@@ -14372,10 +14372,10 @@
         <v>2.24</v>
       </c>
       <c r="AC86">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AD86">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE86">
         <v>1.17</v>
@@ -14400,7 +14400,7 @@
         <v>1.3</v>
       </c>
       <c r="AK86">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14499,19 +14499,19 @@
         <v>2.15</v>
       </c>
       <c r="Q87">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R87">
         <v>2.75</v>
       </c>
       <c r="S87">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T87">
         <v>4.9</v>
       </c>
       <c r="U87">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V87">
         <v>1.95</v>
@@ -14529,19 +14529,19 @@
         <v>8.5</v>
       </c>
       <c r="AA87">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AB87">
-        <v>3.42</v>
+        <v>3.63</v>
       </c>
       <c r="AC87">
         <v>1.7</v>
       </c>
       <c r="AD87">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AE87">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AF87">
         <v>1.25</v>
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AK87">
         <v>1.4</v>
@@ -14668,34 +14668,34 @@
         <v>3</v>
       </c>
       <c r="S88">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="T88">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="U88">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="V88">
         <v>1.95</v>
       </c>
       <c r="W88">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z88">
         <v>7.1</v>
       </c>
       <c r="AA88">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB88">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AC88">
         <v>1.76</v>
@@ -14704,7 +14704,7 @@
         <v>2.12</v>
       </c>
       <c r="AE88">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AF88">
         <v>1.55</v>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK88">
-        <v>3.64</v>
+        <v>3.84</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O89">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P89">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q89">
-        <v>3.52</v>
+        <v>2.73</v>
       </c>
       <c r="R89">
-        <v>1.96</v>
+        <v>2.09</v>
       </c>
       <c r="S89">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T89">
         <v>2.48</v>
       </c>
       <c r="U89">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="V89">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W89">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X89">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y89">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z89">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AA89">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AB89">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC89">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AD89">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE89">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF89">
         <v>1.85</v>
       </c>
       <c r="AG89">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK89">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15151,7 +15151,7 @@
         <v>2.8</v>
       </c>
       <c r="Q91">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="R91">
         <v>2.09</v>
@@ -15172,7 +15172,7 @@
         <v>1.08</v>
       </c>
       <c r="X91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y91">
         <v>1.24</v>
@@ -15468,25 +15468,25 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="O93">
         <v>3.4</v>
       </c>
       <c r="P93">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q93">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R93">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S93">
         <v>1.33</v>
       </c>
       <c r="T93">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U93">
         <v>2.5</v>
@@ -15504,13 +15504,13 @@
         <v>1.2</v>
       </c>
       <c r="Z93">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AA93">
         <v>1.74</v>
       </c>
       <c r="AB93">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AC93">
         <v>3</v>
@@ -15519,7 +15519,7 @@
         <v>1.36</v>
       </c>
       <c r="AE93">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF93">
         <v>1.67</v>
@@ -15541,7 +15541,7 @@
         <v>1.22</v>
       </c>
       <c r="AK93">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15634,19 +15634,19 @@
         <v>2.2</v>
       </c>
       <c r="O94">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P94">
         <v>3.41</v>
       </c>
       <c r="Q94">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R94">
         <v>2</v>
       </c>
       <c r="S94">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T94">
         <v>2.36</v>
@@ -15661,25 +15661,25 @@
         <v>1.03</v>
       </c>
       <c r="X94">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y94">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z94">
         <v>2.7</v>
       </c>
       <c r="AA94">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="AB94">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC94">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="AD94">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE94">
         <v>1.03</v>
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK94">
         <v>1.62</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.87</v>
+        <v>1.8</v>
       </c>
       <c r="O96">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="P96">
-        <v>2.15</v>
+        <v>4.33</v>
       </c>
       <c r="Q96">
+        <v>2.4</v>
+      </c>
+      <c r="R96">
+        <v>2.22</v>
+      </c>
+      <c r="S96">
+        <v>1.35</v>
+      </c>
+      <c r="T96">
         <v>3.3</v>
       </c>
-      <c r="R96">
-        <v>2.5</v>
-      </c>
-      <c r="S96">
-        <v>1.23</v>
-      </c>
-      <c r="T96">
-        <v>4.1</v>
-      </c>
       <c r="U96">
-        <v>2.05</v>
+        <v>2.44</v>
       </c>
       <c r="V96">
+        <v>1.47</v>
+      </c>
+      <c r="W96">
+        <v>1.08</v>
+      </c>
+      <c r="X96">
+        <v>1</v>
+      </c>
+      <c r="Y96">
+        <v>1.21</v>
+      </c>
+      <c r="Z96">
+        <v>4.04</v>
+      </c>
+      <c r="AA96">
+        <v>1.74</v>
+      </c>
+      <c r="AB96">
+        <v>2.09</v>
+      </c>
+      <c r="AC96">
+        <v>2.64</v>
+      </c>
+      <c r="AD96">
+        <v>1.39</v>
+      </c>
+      <c r="AE96">
+        <v>1.13</v>
+      </c>
+      <c r="AF96">
         <v>1.67</v>
       </c>
-      <c r="W96">
-        <v>1.19</v>
-      </c>
-      <c r="X96">
-        <v>1.01</v>
-      </c>
-      <c r="Y96">
-        <v>1.11</v>
-      </c>
-      <c r="Z96">
-        <v>5.1</v>
-      </c>
-      <c r="AA96">
-        <v>1.45</v>
-      </c>
-      <c r="AB96">
-        <v>2.55</v>
-      </c>
-      <c r="AC96">
-        <v>2.23</v>
-      </c>
-      <c r="AD96">
-        <v>1.65</v>
-      </c>
-      <c r="AE96">
-        <v>1.26</v>
-      </c>
-      <c r="AF96">
-        <v>1.41</v>
-      </c>
       <c r="AG96">
-        <v>2.73</v>
+        <v>2.1</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AK96">
-        <v>1.39</v>
+        <v>2</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,80 +16120,80 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.8</v>
+        <v>2.87</v>
       </c>
       <c r="O97">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="P97">
-        <v>4.33</v>
+        <v>2.15</v>
       </c>
       <c r="Q97">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="R97">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="S97">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="T97">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="U97">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="V97">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="W97">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="X97">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="Z97">
-        <v>4.04</v>
+        <v>5.1</v>
       </c>
       <c r="AA97">
-        <v>1.74</v>
+        <v>1.45</v>
       </c>
       <c r="AB97">
-        <v>2.09</v>
+        <v>2.55</v>
       </c>
       <c r="AC97">
-        <v>2.64</v>
+        <v>2.23</v>
       </c>
       <c r="AD97">
+        <v>1.65</v>
+      </c>
+      <c r="AE97">
+        <v>1.26</v>
+      </c>
+      <c r="AF97">
+        <v>1.41</v>
+      </c>
+      <c r="AG97">
+        <v>2.73</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ97">
+        <v>1.67</v>
+      </c>
+      <c r="AK97">
         <v>1.39</v>
-      </c>
-      <c r="AE97">
-        <v>1.13</v>
-      </c>
-      <c r="AF97">
-        <v>1.67</v>
-      </c>
-      <c r="AG97">
-        <v>2.1</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ97">
-        <v>1.2</v>
-      </c>
-      <c r="AK97">
-        <v>2</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16482,7 +16482,7 @@
         <v>1.54</v>
       </c>
       <c r="Z99">
-        <v>2.24</v>
+        <v>2.55</v>
       </c>
       <c r="AA99">
         <v>2.62</v>
@@ -16627,10 +16627,10 @@
         <v>1.5</v>
       </c>
       <c r="T100">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="U100">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="V100">
         <v>1.23</v>
@@ -16639,28 +16639,28 @@
         <v>1.04</v>
       </c>
       <c r="X100">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y100">
         <v>1.43</v>
       </c>
       <c r="Z100">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="AA100">
-        <v>2.41</v>
+        <v>2.51</v>
       </c>
       <c r="AB100">
         <v>1.48</v>
       </c>
       <c r="AC100">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AD100">
         <v>1.12</v>
       </c>
       <c r="AE100">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF100">
         <v>2.09</v>
@@ -16772,61 +16772,61 @@
         </is>
       </c>
       <c r="N101">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="O101">
         <v>4.33</v>
       </c>
       <c r="P101">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Q101">
-        <v>8.5</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="R101">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S101">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T101">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U101">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="V101">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W101">
+        <v>1.03</v>
+      </c>
+      <c r="X101">
+        <v>1.05</v>
+      </c>
+      <c r="Y101">
+        <v>1.27</v>
+      </c>
+      <c r="Z101">
+        <v>3.14</v>
+      </c>
+      <c r="AA101">
+        <v>2</v>
+      </c>
+      <c r="AB101">
+        <v>1.8</v>
+      </c>
+      <c r="AC101">
+        <v>3.5</v>
+      </c>
+      <c r="AD101">
+        <v>1.29</v>
+      </c>
+      <c r="AE101">
         <v>1.04</v>
       </c>
-      <c r="X101">
-        <v>1.01</v>
-      </c>
-      <c r="Y101">
-        <v>1.25</v>
-      </c>
-      <c r="Z101">
-        <v>3.28</v>
-      </c>
-      <c r="AA101">
-        <v>1.8</v>
-      </c>
-      <c r="AB101">
-        <v>1.79</v>
-      </c>
-      <c r="AC101">
-        <v>3.2</v>
-      </c>
-      <c r="AD101">
-        <v>1.26</v>
-      </c>
-      <c r="AE101">
-        <v>1.05</v>
-      </c>
       <c r="AF101">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AG101">
         <v>1.5</v>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AK101">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O111">
+        <v>3.25</v>
+      </c>
+      <c r="P111">
         <v>3.2</v>
-      </c>
-      <c r="P111">
-        <v>3.15</v>
       </c>
       <c r="Q111">
         <v>2.91</v>
@@ -18426,7 +18426,7 @@
         <v>2.93</v>
       </c>
       <c r="V111">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W111">
         <v>1.06</v>
@@ -18447,19 +18447,19 @@
         <v>1.7</v>
       </c>
       <c r="AC111">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="AD111">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE111">
         <v>1.05</v>
       </c>
       <c r="AF111">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AG111">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18758,13 +18758,13 @@
         <v>1.1</v>
       </c>
       <c r="X113">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y113">
         <v>1.17</v>
       </c>
       <c r="Z113">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA113">
         <v>1.66</v>
@@ -18773,19 +18773,19 @@
         <v>2.05</v>
       </c>
       <c r="AC113">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="AD113">
         <v>1.43</v>
       </c>
       <c r="AE113">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF113">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG113">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK113">
         <v>1.08</v>
@@ -19075,10 +19075,10 @@
         <v>3.65</v>
       </c>
       <c r="U115">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="V115">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W115">
         <v>1.18</v>
@@ -19229,7 +19229,7 @@
         <v>4</v>
       </c>
       <c r="R116">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S116">
         <v>1.58</v>
@@ -19244,7 +19244,7 @@
         <v>1.3</v>
       </c>
       <c r="W116">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X116">
         <v>1.06</v>
@@ -19271,7 +19271,7 @@
         <v>1.03</v>
       </c>
       <c r="AF116">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG116">
         <v>1.75</v>
@@ -19401,13 +19401,13 @@
         <v>4.3</v>
       </c>
       <c r="U117">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V117">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="W117">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X117">
         <v>1.01</v>
@@ -19416,7 +19416,7 @@
         <v>1.06</v>
       </c>
       <c r="Z117">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AA117">
         <v>1.32</v>
@@ -19425,16 +19425,16 @@
         <v>3.04</v>
       </c>
       <c r="AC117">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AD117">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AE117">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AF117">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG117">
         <v>3.04</v>
@@ -19453,7 +19453,7 @@
         <v>1.26</v>
       </c>
       <c r="AK117">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="O123">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="P123">
         <v>1.37</v>
       </c>
       <c r="Q123">
-        <v>7.31</v>
+        <v>7.6</v>
       </c>
       <c r="R123">
         <v>2.16</v>
       </c>
       <c r="S123">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T123">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="U123">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="V123">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W123">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X123">
         <v>1.01</v>
       </c>
       <c r="Y123">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z123">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA123">
         <v>1.86</v>
       </c>
       <c r="AB123">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC123">
-        <v>2.83</v>
+        <v>3.4</v>
       </c>
       <c r="AD123">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AE123">
         <v>1.1</v>
       </c>
       <c r="AF123">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG123">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK123">
         <v>1.05</v>
@@ -20545,7 +20545,7 @@
         <v>1.85</v>
       </c>
       <c r="V124">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="W124">
         <v>1.22</v>
@@ -20575,7 +20575,7 @@
         <v>1.35</v>
       </c>
       <c r="AF124">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG124">
         <v>1.92</v>
@@ -20690,10 +20690,10 @@
         <v>3.65</v>
       </c>
       <c r="P125">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q125">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R125">
         <v>2.25</v>
@@ -20711,7 +20711,7 @@
         <v>1.5</v>
       </c>
       <c r="W125">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X125">
         <v>1.01</v>
@@ -20856,13 +20856,13 @@
         <v>0</v>
       </c>
       <c r="Q126">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R126">
         <v>2.1</v>
       </c>
       <c r="S126">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T126">
         <v>2.65</v>
@@ -20892,7 +20892,7 @@
         <v>1.72</v>
       </c>
       <c r="AC126">
-        <v>3.28</v>
+        <v>3.53</v>
       </c>
       <c r="AD126">
         <v>1.25</v>
@@ -20901,7 +20901,7 @@
         <v>1.05</v>
       </c>
       <c r="AF126">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG126">
         <v>1.85</v>
@@ -21200,16 +21200,16 @@
         <v>1.49</v>
       </c>
       <c r="W128">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X128">
         <v>1.02</v>
       </c>
       <c r="Y128">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z128">
-        <v>4.13</v>
+        <v>4.15</v>
       </c>
       <c r="AA128">
         <v>1.72</v>
@@ -21218,13 +21218,13 @@
         <v>2.05</v>
       </c>
       <c r="AC128">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD128">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE128">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF128">
         <v>1.67</v>
@@ -21336,16 +21336,16 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O129">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P129">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q129">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="R129">
         <v>2.14</v>
@@ -21363,7 +21363,7 @@
         <v>1.44</v>
       </c>
       <c r="W129">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X129">
         <v>1.01</v>
@@ -21375,10 +21375,10 @@
         <v>3.5</v>
       </c>
       <c r="AA129">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB129">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC129">
         <v>2.83</v>
@@ -21390,10 +21390,10 @@
         <v>1.1</v>
       </c>
       <c r="AF129">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG129">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK129">
         <v>2</v>
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="O130">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P130">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -21997,34 +21997,34 @@
         <v>4.2</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S133">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T133">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U133">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V133">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W133">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X133">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y133">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z133">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA133">
         <v>1.44</v>
@@ -22033,19 +22033,19 @@
         <v>2.7</v>
       </c>
       <c r="AC133">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD133">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE133">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF133">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG133">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK133">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -23796,16 +23796,16 @@
         <v>2.07</v>
       </c>
       <c r="S144">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T144">
         <v>3.1</v>
       </c>
       <c r="U144">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V144">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W144">
         <v>1.06</v>
@@ -23817,13 +23817,13 @@
         <v>1.2</v>
       </c>
       <c r="Z144">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="AA144">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AB144">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC144">
         <v>2.74</v>
@@ -23835,7 +23835,7 @@
         <v>1.1</v>
       </c>
       <c r="AF144">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG144">
         <v>2.15</v>
@@ -23854,7 +23854,7 @@
         <v>1.24</v>
       </c>
       <c r="AK144">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -24270,31 +24270,31 @@
         </is>
       </c>
       <c r="N147">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="O147">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P147">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="Q147">
-        <v>6</v>
+        <v>6.48</v>
       </c>
       <c r="R147">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S147">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T147">
         <v>2.67</v>
       </c>
       <c r="U147">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V147">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W147">
         <v>1.04</v>
@@ -24306,28 +24306,28 @@
         <v>1.28</v>
       </c>
       <c r="Z147">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AA147">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AB147">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AC147">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD147">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE147">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF147">
         <v>2.1</v>
       </c>
       <c r="AG147">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK147">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24433,31 +24433,31 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="O148">
-        <v>3.88</v>
+        <v>4.08</v>
       </c>
       <c r="P148">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="Q148">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="R148">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="S148">
         <v>1.14</v>
       </c>
       <c r="T148">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="U148">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V148">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="W148">
         <v>1.22</v>
@@ -24475,10 +24475,10 @@
         <v>1.36</v>
       </c>
       <c r="AB148">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AC148">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AD148">
         <v>1.86</v>
@@ -24487,7 +24487,7 @@
         <v>1.38</v>
       </c>
       <c r="AF148">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AG148">
         <v>3.2</v>
@@ -24599,7 +24599,7 @@
         <v>2.85</v>
       </c>
       <c r="O149">
-        <v>3.98</v>
+        <v>3.7</v>
       </c>
       <c r="P149">
         <v>1.92</v>
@@ -24653,7 +24653,7 @@
         <v>1.33</v>
       </c>
       <c r="AG149">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK149">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -25251,7 +25251,7 @@
         <v>4.55</v>
       </c>
       <c r="O153">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="P153">
         <v>1.67</v>
@@ -25414,7 +25414,7 @@
         <v>2.5</v>
       </c>
       <c r="O154">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="P154">
         <v>2.8</v>
@@ -25450,10 +25450,10 @@
         <v>0</v>
       </c>
       <c r="AA154">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AB154">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC154">
         <v>0</v>
@@ -26274,7 +26274,7 @@
         <v>2.62</v>
       </c>
       <c r="AD159">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE159">
         <v>1.12</v>
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="O164">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="P164">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q164">
         <v>0</v>
@@ -27080,10 +27080,10 @@
         <v>0</v>
       </c>
       <c r="AA164">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB164">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC164">
         <v>0</v>
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="O167">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="P167">
-        <v>3.46</v>
+        <v>4.2</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27569,10 +27569,10 @@
         <v>0</v>
       </c>
       <c r="AA167">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB167">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC167">
         <v>0</v>
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
+        <v>2.4</v>
+      </c>
+      <c r="O168">
         <v>2.9</v>
       </c>
-      <c r="O168">
+      <c r="P168">
         <v>2.88</v>
-      </c>
-      <c r="P168">
-        <v>2.4</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -29006,10 +29006,10 @@
         <v>2.65</v>
       </c>
       <c r="Q176">
-        <v>2.96</v>
+        <v>3.38</v>
       </c>
       <c r="R176">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S176">
         <v>1.39</v>
@@ -29021,10 +29021,10 @@
         <v>2.75</v>
       </c>
       <c r="V176">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W176">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X176">
         <v>1</v>
@@ -29033,7 +29033,7 @@
         <v>1.24</v>
       </c>
       <c r="Z176">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="AA176">
         <v>1.95</v>
@@ -29054,7 +29054,7 @@
         <v>1.7</v>
       </c>
       <c r="AG176">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AK176">
         <v>1.4</v>
@@ -29329,13 +29329,13 @@
         <v>3.2</v>
       </c>
       <c r="P178">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q178">
-        <v>2.33</v>
+        <v>2.58</v>
       </c>
       <c r="R178">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="S178">
         <v>1.4</v>
@@ -29344,25 +29344,25 @@
         <v>2.57</v>
       </c>
       <c r="U178">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V178">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W178">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X178">
         <v>1.02</v>
       </c>
       <c r="Y178">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z178">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AA178">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AB178">
         <v>1.73</v>
@@ -29377,10 +29377,10 @@
         <v>1.06</v>
       </c>
       <c r="AF178">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG178">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK178">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29658,7 +29658,7 @@
         <v>3.1</v>
       </c>
       <c r="Q180">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="R180">
         <v>2.24</v>
@@ -29667,22 +29667,22 @@
         <v>1.26</v>
       </c>
       <c r="T180">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="U180">
         <v>2.32</v>
       </c>
       <c r="V180">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="W180">
         <v>1.12</v>
       </c>
       <c r="X180">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y180">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z180">
         <v>4.3</v>
@@ -29722,7 +29722,7 @@
         <v>1.22</v>
       </c>
       <c r="AK180">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29815,7 +29815,7 @@
         <v>2.15</v>
       </c>
       <c r="O181">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P181">
         <v>3.25</v>
@@ -29839,16 +29839,16 @@
         <v>1.23</v>
       </c>
       <c r="W181">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X181">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y181">
         <v>1.45</v>
       </c>
       <c r="Z181">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AA181">
         <v>2.46</v>
@@ -29863,7 +29863,7 @@
         <v>1.12</v>
       </c>
       <c r="AE181">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF181">
         <v>2.05</v>
@@ -30313,7 +30313,7 @@
         <v>3.4</v>
       </c>
       <c r="R184">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="S184">
         <v>1.32</v>
@@ -30331,7 +30331,7 @@
         <v>1.06</v>
       </c>
       <c r="X184">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y184">
         <v>1.22</v>
@@ -30371,7 +30371,7 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK184">
         <v>1.4</v>
@@ -30473,16 +30473,16 @@
         <v>4.2</v>
       </c>
       <c r="Q185">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="R185">
         <v>2.09</v>
       </c>
       <c r="S185">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T185">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="U185">
         <v>2.65</v>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK185">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30648,10 +30648,10 @@
         <v>2.73</v>
       </c>
       <c r="U186">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V186">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W186">
         <v>1.06</v>
@@ -30669,7 +30669,7 @@
         <v>2.1</v>
       </c>
       <c r="AB186">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC186">
         <v>3.42</v>
@@ -30790,65 +30790,65 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="O187">
         <v>3</v>
       </c>
       <c r="P187">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q187">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="R187">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="S187">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="T187">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="U187">
-        <v>3.24</v>
+        <v>2.89</v>
       </c>
       <c r="V187">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W187">
         <v>1.04</v>
       </c>
       <c r="X187">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y187">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z187">
-        <v>2.56</v>
+        <v>2.92</v>
       </c>
       <c r="AA187">
-        <v>2.29</v>
+        <v>2.06</v>
       </c>
       <c r="AB187">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="AC187">
-        <v>4.25</v>
+        <v>3.34</v>
       </c>
       <c r="AD187">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AE187">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF187">
+        <v>1.75</v>
+      </c>
+      <c r="AG187">
         <v>1.93</v>
       </c>
-      <c r="AG187">
-        <v>1.75</v>
-      </c>
       <c r="AH187" t="inlineStr">
         <is>
           <t>[]</t>
@@ -30860,7 +30860,7 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AK187">
         <v>1.44</v>
@@ -30977,7 +30977,7 @@
         <v>2.18</v>
       </c>
       <c r="V188">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W188">
         <v>1.17</v>
@@ -30989,7 +30989,7 @@
         <v>1.13</v>
       </c>
       <c r="Z188">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AA188">
         <v>1.48</v>
@@ -31010,7 +31010,7 @@
         <v>1.44</v>
       </c>
       <c r="AG188">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31768,10 +31768,10 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O193">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P193">
         <v>3.2</v>
@@ -31783,28 +31783,28 @@
         <v>1.94</v>
       </c>
       <c r="S193">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T193">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="U193">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="V193">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W193">
         <v>1.02</v>
       </c>
       <c r="X193">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y193">
         <v>1.4</v>
       </c>
       <c r="Z193">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AA193">
         <v>2.25</v>
@@ -31813,19 +31813,19 @@
         <v>1.61</v>
       </c>
       <c r="AC193">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="AD193">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE193">
         <v>1.03</v>
       </c>
       <c r="AF193">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG193">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK193">
         <v>1.62</v>
@@ -31955,7 +31955,7 @@
         <v>2.04</v>
       </c>
       <c r="V194">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W194">
         <v>1.18</v>
@@ -31985,7 +31985,7 @@
         <v>1.23</v>
       </c>
       <c r="AF194">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG194">
         <v>2.3</v>
@@ -32004,7 +32004,7 @@
         <v>1.06</v>
       </c>
       <c r="AK194">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -33413,10 +33413,10 @@
         <v>2.38</v>
       </c>
       <c r="S203">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T203">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U203">
         <v>2.1</v>
@@ -33425,7 +33425,7 @@
         <v>1.65</v>
       </c>
       <c r="W203">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X203">
         <v>1.02</v>
@@ -33434,28 +33434,28 @@
         <v>1.12</v>
       </c>
       <c r="Z203">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="AA203">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AB203">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AC203">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="AD203">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE203">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AF203">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG203">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33911,7 +33911,7 @@
         <v>2.25</v>
       </c>
       <c r="V206">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W206">
         <v>1.14</v>
@@ -33932,13 +33932,13 @@
         <v>2.35</v>
       </c>
       <c r="AC206">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AD206">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AE206">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF206">
         <v>1.85</v>
@@ -33960,7 +33960,7 @@
         <v>1.07</v>
       </c>
       <c r="AK206">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34062,22 +34062,22 @@
         <v>2.1</v>
       </c>
       <c r="R207">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S207">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T207">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U207">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="V207">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W207">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X207">
         <v>1</v>
@@ -34089,13 +34089,13 @@
         <v>3.52</v>
       </c>
       <c r="AA207">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB207">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC207">
-        <v>2.95</v>
+        <v>3.16</v>
       </c>
       <c r="AD207">
         <v>1.38</v>
@@ -34104,10 +34104,10 @@
         <v>1.08</v>
       </c>
       <c r="AF207">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG207">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>1.29</v>
       </c>
       <c r="AK207">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34222,7 +34222,7 @@
         <v>3.5</v>
       </c>
       <c r="Q208">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="R208">
         <v>1.92</v>
@@ -34240,7 +34240,7 @@
         <v>1.26</v>
       </c>
       <c r="W208">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X208">
         <v>1.04</v>
@@ -34249,7 +34249,7 @@
         <v>1.38</v>
       </c>
       <c r="Z208">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="AA208">
         <v>2.24</v>
@@ -34267,7 +34267,7 @@
         <v>1.01</v>
       </c>
       <c r="AF208">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG208">
         <v>1.75</v>
@@ -34283,7 +34283,7 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK208">
         <v>1.6</v>
@@ -34708,7 +34708,7 @@
         <v>2.94</v>
       </c>
       <c r="P211">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -34741,10 +34741,10 @@
         <v>0</v>
       </c>
       <c r="AA211">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AB211">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AC211">
         <v>0</v>
@@ -34868,16 +34868,16 @@
         <v>7</v>
       </c>
       <c r="O212">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="P212">
         <v>1.33</v>
       </c>
       <c r="Q212">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="R212">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="S212">
         <v>1.29</v>
@@ -34889,7 +34889,7 @@
         <v>2.42</v>
       </c>
       <c r="V212">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W212">
         <v>1.08</v>
@@ -34898,31 +34898,31 @@
         <v>1.02</v>
       </c>
       <c r="Y212">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z212">
-        <v>3.88</v>
+        <v>3.93</v>
       </c>
       <c r="AA212">
         <v>1.86</v>
       </c>
       <c r="AB212">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC212">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="AD212">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE212">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF212">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AG212">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -35354,64 +35354,64 @@
         </is>
       </c>
       <c r="N215">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O215">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P215">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q215">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R215">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S215">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T215">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U215">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V215">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W215">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X215">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y215">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z215">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA215">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB215">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC215">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD215">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE215">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF215">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG215">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK215">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35517,43 +35517,43 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="O216">
-        <v>4.3</v>
+        <v>4.16</v>
       </c>
       <c r="P216">
         <v>5</v>
       </c>
       <c r="Q216">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R216">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S216">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T216">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="U216">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V216">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W216">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X216">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y216">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z216">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA216">
         <v>1.4</v>
@@ -35562,19 +35562,19 @@
         <v>2.87</v>
       </c>
       <c r="AC216">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD216">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE216">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF216">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG216">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK216">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -35707,7 +35707,7 @@
         <v>1.33</v>
       </c>
       <c r="W217">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X217">
         <v>1.02</v>
@@ -35734,7 +35734,7 @@
         <v>1.02</v>
       </c>
       <c r="AF217">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG217">
         <v>1.8</v>
@@ -35750,7 +35750,7 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK217">
         <v>1.65</v>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="O221">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="P221">
-        <v>5.26</v>
+        <v>5.21</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36498,10 +36498,10 @@
         <v>1.75</v>
       </c>
       <c r="O222">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P222">
-        <v>4.78</v>
+        <v>4.5</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -36534,10 +36534,10 @@
         <v>0</v>
       </c>
       <c r="AA222">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AB222">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC222">
         <v>0</v>
@@ -36839,7 +36839,7 @@
         <v>1.36</v>
       </c>
       <c r="T224">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="U224">
         <v>2.8</v>
@@ -36851,7 +36851,7 @@
         <v>1.04</v>
       </c>
       <c r="X224">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y224">
         <v>1.28</v>
@@ -36996,7 +36996,7 @@
         <v>2</v>
       </c>
       <c r="R225">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="S225">
         <v>1.26</v>
@@ -37014,7 +37014,7 @@
         <v>1.12</v>
       </c>
       <c r="X225">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y225">
         <v>1.22</v>
@@ -37023,13 +37023,13 @@
         <v>4.07</v>
       </c>
       <c r="AA225">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB225">
         <v>2.05</v>
       </c>
       <c r="AC225">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AD225">
         <v>1.37</v>
@@ -37057,7 +37057,7 @@
         <v>1.16</v>
       </c>
       <c r="AK225">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37482,10 +37482,10 @@
         <v>3</v>
       </c>
       <c r="Q228">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R228">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S228">
         <v>1.29</v>
@@ -37500,7 +37500,7 @@
         <v>1.45</v>
       </c>
       <c r="W228">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X228">
         <v>1.01</v>
@@ -37968,7 +37968,7 @@
         <v>3.25</v>
       </c>
       <c r="P231">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="Q231">
         <v>3.3</v>
@@ -37977,7 +37977,7 @@
         <v>2.02</v>
       </c>
       <c r="S231">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T231">
         <v>2.88</v>
@@ -38035,7 +38035,7 @@
         <v>1.3</v>
       </c>
       <c r="AK231">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38460,34 +38460,34 @@
         <v>0</v>
       </c>
       <c r="Q234">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R234">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S234">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T234">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U234">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V234">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W234">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X234">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y234">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z234">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA234">
         <v>1.7</v>
@@ -38496,19 +38496,19 @@
         <v>2.1</v>
       </c>
       <c r="AC234">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD234">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE234">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF234">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG234">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK234">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38623,19 +38623,19 @@
         <v>5.25</v>
       </c>
       <c r="Q235">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R235">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="S235">
         <v>1.35</v>
       </c>
       <c r="T235">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="U235">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V235">
         <v>1.42</v>
@@ -38644,19 +38644,19 @@
         <v>1.08</v>
       </c>
       <c r="X235">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y235">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z235">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA235">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB235">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC235">
         <v>2.83</v>
@@ -38668,7 +38668,7 @@
         <v>1.09</v>
       </c>
       <c r="AF235">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG235">
         <v>1.91</v>
@@ -38684,7 +38684,7 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK235">
         <v>2.07</v>
@@ -39266,7 +39266,7 @@
         </is>
       </c>
       <c r="N239">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="O239">
         <v>3.25</v>
@@ -39275,16 +39275,16 @@
         <v>3.9</v>
       </c>
       <c r="Q239">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R239">
         <v>2.01</v>
       </c>
       <c r="S239">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T239">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="U239">
         <v>2.83</v>
@@ -39308,7 +39308,7 @@
         <v>2.06</v>
       </c>
       <c r="AB239">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC239">
         <v>3.58</v>
@@ -39320,7 +39320,7 @@
         <v>1.03</v>
       </c>
       <c r="AF239">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG239">
         <v>1.85</v>
@@ -39429,19 +39429,19 @@
         </is>
       </c>
       <c r="N240">
+        <v>4.33</v>
+      </c>
+      <c r="O240">
         <v>4.4</v>
-      </c>
-      <c r="O240">
-        <v>4.33</v>
       </c>
       <c r="P240">
         <v>1.67</v>
       </c>
       <c r="Q240">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="R240">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="S240">
         <v>1.2</v>
@@ -39465,7 +39465,7 @@
         <v>1.08</v>
       </c>
       <c r="Z240">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AA240">
         <v>1.39</v>
@@ -39486,7 +39486,7 @@
         <v>1.44</v>
       </c>
       <c r="AG240">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         </is>
       </c>
       <c r="N247">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="O247">
         <v>3.9</v>
@@ -40600,7 +40600,7 @@
         <v>1.07</v>
       </c>
       <c r="X247">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y247">
         <v>1.23</v>
@@ -40618,7 +40618,7 @@
         <v>2.88</v>
       </c>
       <c r="AD247">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE247">
         <v>1.09</v>
@@ -40627,7 +40627,7 @@
         <v>1.83</v>
       </c>
       <c r="AG247">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -41249,7 +41249,7 @@
         <v>1.79</v>
       </c>
       <c r="W251">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X251">
         <v>1.01</v>
@@ -41292,7 +41292,7 @@
         </is>
       </c>
       <c r="AJ251">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK251">
         <v>3.44</v>
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G252">
@@ -41385,64 +41385,64 @@
         </is>
       </c>
       <c r="N252">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="O252">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="P252">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q252">
-        <v>2.64</v>
+        <v>3.72</v>
       </c>
       <c r="R252">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="S252">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="T252">
-        <v>2.95</v>
+        <v>2.44</v>
       </c>
       <c r="U252">
-        <v>2.61</v>
+        <v>2.72</v>
       </c>
       <c r="V252">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W252">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X252">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y252">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z252">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AA252">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="AB252">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AC252">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AD252">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE252">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF252">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AG252">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK252">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,64 +41548,64 @@
         </is>
       </c>
       <c r="N253">
+        <v>2.05</v>
+      </c>
+      <c r="O253">
+        <v>3.1</v>
+      </c>
+      <c r="P253">
+        <v>3.25</v>
+      </c>
+      <c r="Q253">
         <v>2.75</v>
       </c>
-      <c r="O253">
+      <c r="R253">
+        <v>2.1</v>
+      </c>
+      <c r="S253">
+        <v>1.4</v>
+      </c>
+      <c r="T253">
+        <v>2.66</v>
+      </c>
+      <c r="U253">
         <v>3</v>
       </c>
-      <c r="P253">
-        <v>2.45</v>
-      </c>
-      <c r="Q253">
-        <v>3.72</v>
-      </c>
-      <c r="R253">
-        <v>1.87</v>
-      </c>
-      <c r="S253">
-        <v>1.44</v>
-      </c>
-      <c r="T253">
-        <v>2.44</v>
-      </c>
-      <c r="U253">
-        <v>2.72</v>
-      </c>
       <c r="V253">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W253">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X253">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y253">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z253">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA253">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="AB253">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AC253">
-        <v>2.97</v>
+        <v>3.68</v>
       </c>
       <c r="AD253">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AE253">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF253">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AG253">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK253">
-        <v>1.29</v>
+        <v>1.58</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41883,55 +41883,55 @@
         <v>0</v>
       </c>
       <c r="Q255">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="R255">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S255">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T255">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U255">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="V255">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W255">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X255">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y255">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z255">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA255">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB255">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC255">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD255">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE255">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF255">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG255">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -41944,10 +41944,10 @@
         </is>
       </c>
       <c r="AJ255">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK255">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42037,64 +42037,64 @@
         </is>
       </c>
       <c r="N256">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="O256">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="P256">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q256">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R256">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S256">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T256">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U256">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="V256">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W256">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X256">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y256">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z256">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AA256">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB256">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC256">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD256">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE256">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF256">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG256">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42107,10 +42107,10 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK256">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42200,64 +42200,64 @@
         </is>
       </c>
       <c r="N257">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="O257">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P257">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="Q257">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R257">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S257">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T257">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U257">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V257">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W257">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X257">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y257">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z257">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AA257">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB257">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC257">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD257">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE257">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF257">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG257">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
@@ -42270,10 +42270,10 @@
         </is>
       </c>
       <c r="AJ257">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK257">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -42529,16 +42529,16 @@
         <v>1.25</v>
       </c>
       <c r="O259">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="P259">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q259">
         <v>1.7</v>
       </c>
       <c r="R259">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="S259">
         <v>1.29</v>
@@ -42568,10 +42568,10 @@
         <v>1.72</v>
       </c>
       <c r="AB259">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AC259">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="AD259">
         <v>1.46</v>
@@ -42580,7 +42580,7 @@
         <v>1.15</v>
       </c>
       <c r="AF259">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AG259">
         <v>1.62</v>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -647,7 +647,7 @@
         <v>2.71</v>
       </c>
       <c r="R2">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S2">
         <v>1.4</v>
@@ -807,16 +807,16 @@
         <v>6.4</v>
       </c>
       <c r="Q3">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R3">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="S3">
         <v>1.3</v>
       </c>
       <c r="T3">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="U3">
         <v>2.38</v>
@@ -834,19 +834,19 @@
         <v>1.15</v>
       </c>
       <c r="Z3">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA3">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB3">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AC3">
         <v>2.63</v>
       </c>
       <c r="AD3">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE3">
         <v>1.17</v>
@@ -997,7 +997,7 @@
         <v>1.3</v>
       </c>
       <c r="Z4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA4">
         <v>1.93</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK4">
         <v>1.57</v>
@@ -1139,10 +1139,10 @@
         <v>2.2</v>
       </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T5">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="U5">
         <v>2.8</v>
@@ -1151,7 +1151,7 @@
         <v>1.34</v>
       </c>
       <c r="W5">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
         <v>1.03</v>
@@ -1163,7 +1163,7 @@
         <v>3.2</v>
       </c>
       <c r="AA5">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AB5">
         <v>1.77</v>
@@ -1299,7 +1299,7 @@
         <v>4.02</v>
       </c>
       <c r="R6">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S6">
         <v>1.3</v>
@@ -1323,7 +1323,7 @@
         <v>1.21</v>
       </c>
       <c r="Z6">
-        <v>3.94</v>
+        <v>3.58</v>
       </c>
       <c r="AA6">
         <v>1.74</v>
@@ -1341,10 +1341,10 @@
         <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG6">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1453,7 +1453,7 @@
         <v>3.3</v>
       </c>
       <c r="O7">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="P7">
         <v>2.08</v>
@@ -1465,13 +1465,13 @@
         <v>2.1</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="U7">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V7">
         <v>1.4</v>
@@ -1483,31 +1483,31 @@
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z7">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA7">
         <v>2.03</v>
       </c>
       <c r="AB7">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC7">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD7">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF7">
         <v>1.75</v>
       </c>
       <c r="AG7">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>3.14</v>
       </c>
       <c r="R8">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="S8">
         <v>1.38</v>
@@ -1667,10 +1667,10 @@
         <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG8">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AK8">
         <v>1.45</v>
@@ -1942,7 +1942,7 @@
         <v>2.1</v>
       </c>
       <c r="O10">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P10">
         <v>2.95</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.53</v>
+        <v>3.6</v>
       </c>
       <c r="O21">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="P21">
-        <v>2.31</v>
+        <v>1.86</v>
       </c>
       <c r="Q21">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="R21">
         <v>2.01</v>
       </c>
       <c r="S21">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="T21">
-        <v>2.99</v>
+        <v>2.57</v>
       </c>
       <c r="U21">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="V21">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z21">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AA21">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB21">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AC21">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AD21">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE21">
         <v>1.07</v>
       </c>
       <c r="AF21">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AG21">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="AK21">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="O22">
-        <v>3.23</v>
+        <v>3.38</v>
       </c>
       <c r="P22">
-        <v>1.86</v>
+        <v>2.31</v>
       </c>
       <c r="Q22">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="R22">
         <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T22">
-        <v>2.57</v>
+        <v>2.99</v>
       </c>
       <c r="U22">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="V22">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
+        <v>1.08</v>
+      </c>
+      <c r="X22">
+        <v>1.03</v>
+      </c>
+      <c r="Y22">
+        <v>1.26</v>
+      </c>
+      <c r="Z22">
+        <v>3.2</v>
+      </c>
+      <c r="AA22">
+        <v>1.9</v>
+      </c>
+      <c r="AB22">
+        <v>1.87</v>
+      </c>
+      <c r="AC22">
+        <v>3.14</v>
+      </c>
+      <c r="AD22">
+        <v>1.27</v>
+      </c>
+      <c r="AE22">
         <v>1.07</v>
       </c>
-      <c r="X22">
-        <v>1.02</v>
-      </c>
-      <c r="Y22">
-        <v>1.3</v>
-      </c>
-      <c r="Z22">
-        <v>3.15</v>
-      </c>
-      <c r="AA22">
-        <v>2.05</v>
-      </c>
-      <c r="AB22">
-        <v>1.73</v>
-      </c>
-      <c r="AC22">
-        <v>3.42</v>
-      </c>
-      <c r="AD22">
-        <v>1.23</v>
-      </c>
-      <c r="AE22">
-        <v>1.05</v>
-      </c>
       <c r="AF22">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AG22">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="AK22">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4094,7 +4094,7 @@
         <v>1.3</v>
       </c>
       <c r="Z23">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="AA23">
         <v>2.01</v>
@@ -4230,7 +4230,7 @@
         <v>2.5</v>
       </c>
       <c r="Q24">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="R24">
         <v>2</v>
@@ -4239,10 +4239,10 @@
         <v>1.4</v>
       </c>
       <c r="T24">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="U24">
-        <v>3.07</v>
+        <v>2.8</v>
       </c>
       <c r="V24">
         <v>1.35</v>
@@ -4257,7 +4257,7 @@
         <v>1.34</v>
       </c>
       <c r="Z24">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="AA24">
         <v>2.07</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AK24">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="O26">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P26">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q26">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="R26">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S26">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T26">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="U26">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="V26">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W26">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="Z26">
         <v>2.56</v>
       </c>
       <c r="AA26">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="AB26">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC26">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="AD26">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE26">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF26">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AG26">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK26">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="O27">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P27">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q27">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="R27">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="S27">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T27">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="U27">
-        <v>3.24</v>
+        <v>3.48</v>
       </c>
       <c r="V27">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W27">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X27">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y27">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Z27">
         <v>2.56</v>
       </c>
       <c r="AA27">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="AB27">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC27">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="AD27">
+        <v>1.13</v>
+      </c>
+      <c r="AE27">
+        <v>1.05</v>
+      </c>
+      <c r="AF27">
+        <v>2.1</v>
+      </c>
+      <c r="AG27">
+        <v>1.65</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.16</v>
       </c>
-      <c r="AE27">
-        <v>1.02</v>
-      </c>
-      <c r="AF27">
-        <v>2.04</v>
-      </c>
-      <c r="AG27">
-        <v>1.66</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.15</v>
-      </c>
       <c r="AK27">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC36">
         <v>0</v>
@@ -6539,7 +6539,7 @@
         <v>1.04</v>
       </c>
       <c r="Z38">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="AA38">
         <v>1.3</v>
@@ -7001,7 +7001,7 @@
         <v>2.21</v>
       </c>
       <c r="Q41">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R41">
         <v>2.13</v>
@@ -7022,7 +7022,7 @@
         <v>1.07</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
         <v>1.25</v>
@@ -7043,13 +7043,13 @@
         <v>1.33</v>
       </c>
       <c r="AE41">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF41">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG41">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK41">
         <v>1.36</v>
@@ -7680,7 +7680,7 @@
         <v>1.29</v>
       </c>
       <c r="Z45">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA45">
         <v>1.98</v>
@@ -7692,16 +7692,16 @@
         <v>2.97</v>
       </c>
       <c r="AD45">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE45">
         <v>1.08</v>
       </c>
       <c r="AF45">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG45">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AK45">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,19 +7807,19 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O46">
         <v>3.65</v>
       </c>
       <c r="P46">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q46">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="R46">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S46">
         <v>1.29</v>
@@ -7843,7 +7843,7 @@
         <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA46">
         <v>1.7</v>
@@ -7855,16 +7855,16 @@
         <v>2.71</v>
       </c>
       <c r="AD46">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE46">
         <v>1.12</v>
       </c>
       <c r="AF46">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG46">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O47">
         <v>3.75</v>
       </c>
       <c r="P47">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q47">
         <v>2.3</v>
@@ -7994,7 +7994,7 @@
         <v>2.62</v>
       </c>
       <c r="V47">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W47">
         <v>1.1</v>
@@ -8003,7 +8003,7 @@
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z47">
         <v>3.34</v>
@@ -8015,10 +8015,10 @@
         <v>1.89</v>
       </c>
       <c r="AC47">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AD47">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE47">
         <v>1.08</v>
@@ -8027,7 +8027,7 @@
         <v>1.75</v>
       </c>
       <c r="AG47">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8139,10 +8139,10 @@
         <v>3.3</v>
       </c>
       <c r="P48">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="Q48">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="R48">
         <v>2.12</v>
@@ -8154,13 +8154,13 @@
         <v>3.2</v>
       </c>
       <c r="U48">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V48">
         <v>1.44</v>
       </c>
       <c r="W48">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
         <v>1.03</v>
@@ -8462,7 +8462,7 @@
         <v>2.14</v>
       </c>
       <c r="O50">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="P50">
         <v>3.5</v>
@@ -8495,10 +8495,10 @@
         <v>1.15</v>
       </c>
       <c r="Z50">
-        <v>5.43</v>
+        <v>5.42</v>
       </c>
       <c r="AA50">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB50">
         <v>2.5</v>
@@ -8652,13 +8652,13 @@
         <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
         <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AA51">
         <v>1.71</v>
@@ -8785,19 +8785,19 @@
         </is>
       </c>
       <c r="N52">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="O52">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="Q52">
-        <v>5.05</v>
+        <v>5.3</v>
       </c>
       <c r="R52">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S52">
         <v>1.33</v>
@@ -8812,7 +8812,7 @@
         <v>1.4</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
         <v>1</v>
@@ -8821,10 +8821,10 @@
         <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AA52">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AB52">
         <v>1.8</v>
@@ -8833,16 +8833,16 @@
         <v>3.14</v>
       </c>
       <c r="AD52">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE52">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF52">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AG52">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.96</v>
+        <v>1.19</v>
       </c>
       <c r="AK52">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9277,19 +9277,19 @@
         <v>2.15</v>
       </c>
       <c r="O55">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P55">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q55">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="R55">
         <v>2.3</v>
       </c>
       <c r="S55">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T55">
         <v>3.75</v>
@@ -9298,7 +9298,7 @@
         <v>2.2</v>
       </c>
       <c r="V55">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W55">
         <v>1.14</v>
@@ -9316,10 +9316,10 @@
         <v>1.44</v>
       </c>
       <c r="AB55">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AC55">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AD55">
         <v>1.59</v>
@@ -9331,7 +9331,7 @@
         <v>1.41</v>
       </c>
       <c r="AG55">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK55">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9458,7 +9458,7 @@
         <v>4</v>
       </c>
       <c r="U56">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V56">
         <v>1.72</v>
@@ -9473,22 +9473,22 @@
         <v>1.12</v>
       </c>
       <c r="Z56">
-        <v>6.23</v>
+        <v>6.33</v>
       </c>
       <c r="AA56">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB56">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="AC56">
         <v>2.04</v>
       </c>
       <c r="AD56">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AE56">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AF56">
         <v>1.36</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.73</v>
+        <v>1.18</v>
       </c>
       <c r="AK56">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9609,25 +9609,25 @@
         <v>3.6</v>
       </c>
       <c r="Q57">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="R57">
         <v>2.5</v>
       </c>
       <c r="S57">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T57">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="U57">
         <v>2.1</v>
       </c>
       <c r="V57">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W57">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X57">
         <v>1.02</v>
@@ -9639,25 +9639,25 @@
         <v>5.5</v>
       </c>
       <c r="AA57">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB57">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC57">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AD57">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AE57">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF57">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AG57">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>2.1</v>
       </c>
       <c r="O58">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P58">
         <v>3</v>
@@ -9790,7 +9790,7 @@
         <v>1.58</v>
       </c>
       <c r="W58">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X58">
         <v>1.02</v>
@@ -9811,7 +9811,7 @@
         <v>2.43</v>
       </c>
       <c r="AD58">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE58">
         <v>1.18</v>
@@ -9820,7 +9820,7 @@
         <v>1.45</v>
       </c>
       <c r="AG58">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10095,22 +10095,22 @@
         <v>4.05</v>
       </c>
       <c r="P60">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q60">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="R60">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="S60">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T60">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="U60">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="V60">
         <v>1.46</v>
@@ -10122,13 +10122,13 @@
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z60">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="AA60">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB60">
         <v>2.05</v>
@@ -10143,10 +10143,10 @@
         <v>1.1</v>
       </c>
       <c r="AF60">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG60">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10418,10 +10418,10 @@
         <v>2.36</v>
       </c>
       <c r="O62">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="P62">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -10436,10 +10436,10 @@
         <v>4.8</v>
       </c>
       <c r="U62">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="V62">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="W62">
         <v>1.2</v>
@@ -10448,31 +10448,31 @@
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z62">
-        <v>6.6</v>
+        <v>6.95</v>
       </c>
       <c r="AA62">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AB62">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AC62">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AD62">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE62">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF62">
         <v>1.36</v>
       </c>
       <c r="AG62">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10587,10 +10587,10 @@
         <v>3</v>
       </c>
       <c r="Q63">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="R63">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="S63">
         <v>1.53</v>
@@ -10602,19 +10602,19 @@
         <v>3.9</v>
       </c>
       <c r="V63">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W63">
         <v>1</v>
       </c>
       <c r="X63">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y63">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Z63">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="AA63">
         <v>2.7</v>
@@ -10623,19 +10623,19 @@
         <v>1.44</v>
       </c>
       <c r="AC63">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AD63">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE63">
         <v>1</v>
       </c>
       <c r="AF63">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AG63">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>1.09</v>
       </c>
       <c r="Y65">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="Z65">
         <v>2.44</v>
@@ -10946,10 +10946,10 @@
         <v>2.58</v>
       </c>
       <c r="AB65">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AC65">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AD65">
         <v>1.11</v>
@@ -10958,7 +10958,7 @@
         <v>1.01</v>
       </c>
       <c r="AF65">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AG65">
         <v>1.62</v>
@@ -11088,31 +11088,31 @@
         <v>3.2</v>
       </c>
       <c r="U66">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V66">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W66">
         <v>1.08</v>
       </c>
       <c r="X66">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z66">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA66">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AB66">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC66">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="AD66">
         <v>1.4</v>
@@ -11121,10 +11121,10 @@
         <v>1.11</v>
       </c>
       <c r="AF66">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG66">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11242,10 +11242,10 @@
         <v>2</v>
       </c>
       <c r="R67">
-        <v>2.56</v>
+        <v>2.31</v>
       </c>
       <c r="S67">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T67">
         <v>3.6</v>
@@ -11266,13 +11266,13 @@
         <v>1.2</v>
       </c>
       <c r="Z67">
-        <v>4.42</v>
+        <v>4.5</v>
       </c>
       <c r="AA67">
         <v>1.63</v>
       </c>
       <c r="AB67">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AC67">
         <v>2.6</v>
@@ -11303,7 +11303,7 @@
         <v>1.17</v>
       </c>
       <c r="AK67">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11402,16 +11402,16 @@
         <v>2</v>
       </c>
       <c r="Q68">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="R68">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S68">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T68">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U68">
         <v>2.4</v>
@@ -11423,34 +11423,34 @@
         <v>1.11</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z68">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="AA68">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB68">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC68">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="AD68">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE68">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF68">
         <v>1.53</v>
       </c>
       <c r="AG68">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AK68">
         <v>1.33</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,61 +11882,61 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="O71">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P71">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q71">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R71">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S71">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="U71">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V71">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W71">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X71">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z71">
-        <v>3.84</v>
+        <v>4.54</v>
       </c>
       <c r="AA71">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="AB71">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AC71">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AD71">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE71">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF71">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG71">
         <v>2.3</v>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK71">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,61 +12045,61 @@
         </is>
       </c>
       <c r="N72">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="O72">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P72">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q72">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R72">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S72">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T72">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U72">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V72">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W72">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X72">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y72">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z72">
-        <v>4.54</v>
+        <v>3.84</v>
       </c>
       <c r="AA72">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AB72">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AC72">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AD72">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE72">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF72">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG72">
         <v>2.3</v>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK72">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -13521,16 +13521,16 @@
         <v>3.7</v>
       </c>
       <c r="Q81">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R81">
         <v>2.4</v>
       </c>
       <c r="S81">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T81">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U81">
         <v>2.12</v>
@@ -13554,10 +13554,10 @@
         <v>1.47</v>
       </c>
       <c r="AB81">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AC81">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AD81">
         <v>1.62</v>
@@ -13585,7 +13585,7 @@
         <v>1.29</v>
       </c>
       <c r="AK81">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13678,28 +13678,28 @@
         <v>1.55</v>
       </c>
       <c r="O82">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="P82">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="Q82">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="R82">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="S82">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T82">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U82">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="V82">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W82">
         <v>1.12</v>
@@ -13711,28 +13711,28 @@
         <v>1.13</v>
       </c>
       <c r="Z82">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AA82">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AB82">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="AC82">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AD82">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AE82">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF82">
         <v>1.62</v>
       </c>
       <c r="AG82">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK82">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="N84">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O84">
         <v>5.6</v>
@@ -14010,19 +14010,19 @@
         <v>1.28</v>
       </c>
       <c r="Q84">
-        <v>8</v>
+        <v>6.57</v>
       </c>
       <c r="R84">
         <v>2.66</v>
       </c>
       <c r="S84">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T84">
         <v>3.9</v>
       </c>
       <c r="U84">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="V84">
         <v>1.64</v>
@@ -14034,7 +14034,7 @@
         <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z84">
         <v>5.2</v>
@@ -14046,7 +14046,7 @@
         <v>2.6</v>
       </c>
       <c r="AC84">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AD84">
         <v>1.65</v>
@@ -14071,7 +14071,7 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AK84">
         <v>1.07</v>
@@ -14167,13 +14167,13 @@
         <v>1.91</v>
       </c>
       <c r="O85">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="P85">
         <v>3.65</v>
       </c>
       <c r="Q85">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="R85">
         <v>2.3</v>
@@ -14200,7 +14200,7 @@
         <v>1.16</v>
       </c>
       <c r="Z85">
-        <v>4.16</v>
+        <v>4.17</v>
       </c>
       <c r="AA85">
         <v>1.7</v>
@@ -14221,7 +14221,7 @@
         <v>1.57</v>
       </c>
       <c r="AG85">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>1.21</v>
       </c>
       <c r="AK85">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14508,7 +14508,7 @@
         <v>1.15</v>
       </c>
       <c r="T87">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="U87">
         <v>1.76</v>
@@ -14529,7 +14529,7 @@
         <v>8.5</v>
       </c>
       <c r="AA87">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB87">
         <v>3.63</v>
@@ -14541,7 +14541,7 @@
         <v>2.17</v>
       </c>
       <c r="AE87">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AF87">
         <v>1.25</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="O88">
         <v>6.5</v>
       </c>
       <c r="P88">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Q88">
         <v>1.57</v>
@@ -14671,10 +14671,10 @@
         <v>1.11</v>
       </c>
       <c r="T88">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="U88">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V88">
         <v>1.95</v>
@@ -14686,28 +14686,28 @@
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Z88">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="AA88">
         <v>1.25</v>
       </c>
       <c r="AB88">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="AC88">
         <v>1.76</v>
       </c>
       <c r="AD88">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AE88">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AF88">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG88">
         <v>2.25</v>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AK88">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -15305,19 +15305,19 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="O92">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P92">
         <v>2.75</v>
       </c>
       <c r="Q92">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="R92">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="S92">
         <v>1.2</v>
@@ -15326,43 +15326,43 @@
         <v>4</v>
       </c>
       <c r="U92">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="V92">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="W92">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X92">
         <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z92">
-        <v>6.15</v>
+        <v>5.55</v>
       </c>
       <c r="AA92">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AB92">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AC92">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="AD92">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AE92">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AF92">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AG92">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.29</v>
+        <v>1.73</v>
       </c>
       <c r="O95">
-        <v>6</v>
+        <v>3.63</v>
       </c>
       <c r="P95">
-        <v>8.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q95">
+        <v>2.4</v>
+      </c>
+      <c r="R95">
+        <v>2.24</v>
+      </c>
+      <c r="S95">
+        <v>1.34</v>
+      </c>
+      <c r="T95">
+        <v>3.4</v>
+      </c>
+      <c r="U95">
+        <v>2.41</v>
+      </c>
+      <c r="V95">
+        <v>1.44</v>
+      </c>
+      <c r="W95">
+        <v>1.08</v>
+      </c>
+      <c r="X95">
+        <v>1</v>
+      </c>
+      <c r="Y95">
+        <v>1.19</v>
+      </c>
+      <c r="Z95">
+        <v>4.04</v>
+      </c>
+      <c r="AA95">
+        <v>1.72</v>
+      </c>
+      <c r="AB95">
+        <v>2.12</v>
+      </c>
+      <c r="AC95">
+        <v>2.61</v>
+      </c>
+      <c r="AD95">
+        <v>1.4</v>
+      </c>
+      <c r="AE95">
+        <v>1.13</v>
+      </c>
+      <c r="AF95">
         <v>1.67</v>
       </c>
-      <c r="R95">
-        <v>2.62</v>
-      </c>
-      <c r="S95">
-        <v>1.29</v>
-      </c>
-      <c r="T95">
-        <v>3.6</v>
-      </c>
-      <c r="U95">
-        <v>2.25</v>
-      </c>
-      <c r="V95">
-        <v>1.57</v>
-      </c>
-      <c r="W95">
-        <v>1.12</v>
-      </c>
-      <c r="X95">
-        <v>1.01</v>
-      </c>
-      <c r="Y95">
-        <v>1.13</v>
-      </c>
-      <c r="Z95">
-        <v>4.6</v>
-      </c>
-      <c r="AA95">
-        <v>1.55</v>
-      </c>
-      <c r="AB95">
-        <v>2.36</v>
-      </c>
-      <c r="AC95">
-        <v>2.51</v>
-      </c>
-      <c r="AD95">
-        <v>1.54</v>
-      </c>
-      <c r="AE95">
-        <v>1.17</v>
-      </c>
-      <c r="AF95">
-        <v>1.9</v>
-      </c>
       <c r="AG95">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="AK95">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.8</v>
+        <v>1.29</v>
       </c>
       <c r="O96">
-        <v>3.92</v>
+        <v>6</v>
       </c>
       <c r="P96">
-        <v>4.33</v>
+        <v>8.5</v>
       </c>
       <c r="Q96">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="R96">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="S96">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T96">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="U96">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="V96">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="W96">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X96">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="Z96">
-        <v>4.04</v>
+        <v>4.65</v>
       </c>
       <c r="AA96">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="AB96">
-        <v>2.09</v>
+        <v>2.39</v>
       </c>
       <c r="AC96">
-        <v>2.64</v>
+        <v>2.49</v>
       </c>
       <c r="AD96">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AE96">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF96">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AG96">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AK96">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,7 +16120,7 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="O97">
         <v>3.75</v>
@@ -16129,55 +16129,55 @@
         <v>2.15</v>
       </c>
       <c r="Q97">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R97">
         <v>2.5</v>
       </c>
       <c r="S97">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T97">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="U97">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V97">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W97">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X97">
         <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z97">
-        <v>5.1</v>
+        <v>4.95</v>
       </c>
       <c r="AA97">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AB97">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AC97">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="AD97">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AE97">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF97">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AG97">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>1.67</v>
       </c>
       <c r="AK97">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,65 +16609,65 @@
         </is>
       </c>
       <c r="N100">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="O100">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="P100">
+        <v>1.33</v>
+      </c>
+      <c r="Q100">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="R100">
+        <v>2.3</v>
+      </c>
+      <c r="S100">
+        <v>1.36</v>
+      </c>
+      <c r="T100">
+        <v>2.88</v>
+      </c>
+      <c r="U100">
+        <v>2.83</v>
+      </c>
+      <c r="V100">
+        <v>1.4</v>
+      </c>
+      <c r="W100">
+        <v>1.03</v>
+      </c>
+      <c r="X100">
+        <v>1.05</v>
+      </c>
+      <c r="Y100">
+        <v>1.27</v>
+      </c>
+      <c r="Z100">
+        <v>3.14</v>
+      </c>
+      <c r="AA100">
         <v>2</v>
       </c>
-      <c r="Q100">
-        <v>4.5</v>
-      </c>
-      <c r="R100">
-        <v>2</v>
-      </c>
-      <c r="S100">
+      <c r="AB100">
+        <v>1.8</v>
+      </c>
+      <c r="AC100">
+        <v>3.5</v>
+      </c>
+      <c r="AD100">
+        <v>1.29</v>
+      </c>
+      <c r="AE100">
+        <v>1.04</v>
+      </c>
+      <c r="AF100">
+        <v>2.4</v>
+      </c>
+      <c r="AG100">
         <v>1.5</v>
       </c>
-      <c r="T100">
-        <v>2.29</v>
-      </c>
-      <c r="U100">
-        <v>3.44</v>
-      </c>
-      <c r="V100">
-        <v>1.23</v>
-      </c>
-      <c r="W100">
-        <v>1.04</v>
-      </c>
-      <c r="X100">
-        <v>1.07</v>
-      </c>
-      <c r="Y100">
-        <v>1.43</v>
-      </c>
-      <c r="Z100">
-        <v>2.7</v>
-      </c>
-      <c r="AA100">
-        <v>2.51</v>
-      </c>
-      <c r="AB100">
-        <v>1.48</v>
-      </c>
-      <c r="AC100">
-        <v>5</v>
-      </c>
-      <c r="AD100">
-        <v>1.12</v>
-      </c>
-      <c r="AE100">
-        <v>1.05</v>
-      </c>
-      <c r="AF100">
-        <v>2.09</v>
-      </c>
-      <c r="AG100">
-        <v>1.63</v>
-      </c>
       <c r="AH100" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.36</v>
+        <v>3.2</v>
       </c>
       <c r="AK100">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,80 +16772,80 @@
         </is>
       </c>
       <c r="N101">
-        <v>8</v>
+        <v>3.7</v>
       </c>
       <c r="O101">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="P101">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="Q101">
-        <v>8.380000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="R101">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S101">
+        <v>1.5</v>
+      </c>
+      <c r="T101">
+        <v>2.29</v>
+      </c>
+      <c r="U101">
+        <v>3.44</v>
+      </c>
+      <c r="V101">
+        <v>1.23</v>
+      </c>
+      <c r="W101">
+        <v>1.04</v>
+      </c>
+      <c r="X101">
+        <v>1.07</v>
+      </c>
+      <c r="Y101">
+        <v>1.43</v>
+      </c>
+      <c r="Z101">
+        <v>2.7</v>
+      </c>
+      <c r="AA101">
+        <v>2.51</v>
+      </c>
+      <c r="AB101">
+        <v>1.48</v>
+      </c>
+      <c r="AC101">
+        <v>5</v>
+      </c>
+      <c r="AD101">
+        <v>1.12</v>
+      </c>
+      <c r="AE101">
+        <v>1.05</v>
+      </c>
+      <c r="AF101">
+        <v>2.09</v>
+      </c>
+      <c r="AG101">
+        <v>1.63</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ101">
         <v>1.36</v>
       </c>
-      <c r="T101">
-        <v>2.88</v>
-      </c>
-      <c r="U101">
-        <v>2.83</v>
-      </c>
-      <c r="V101">
-        <v>1.4</v>
-      </c>
-      <c r="W101">
-        <v>1.03</v>
-      </c>
-      <c r="X101">
-        <v>1.05</v>
-      </c>
-      <c r="Y101">
-        <v>1.27</v>
-      </c>
-      <c r="Z101">
-        <v>3.14</v>
-      </c>
-      <c r="AA101">
-        <v>2</v>
-      </c>
-      <c r="AB101">
-        <v>1.8</v>
-      </c>
-      <c r="AC101">
-        <v>3.5</v>
-      </c>
-      <c r="AD101">
-        <v>1.29</v>
-      </c>
-      <c r="AE101">
-        <v>1.04</v>
-      </c>
-      <c r="AF101">
-        <v>2.4</v>
-      </c>
-      <c r="AG101">
-        <v>1.5</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ101">
-        <v>3.2</v>
-      </c>
       <c r="AK101">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16938,10 +16938,10 @@
         <v>2.8</v>
       </c>
       <c r="O102">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P102">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="Q102">
         <v>3.4</v>
@@ -16959,13 +16959,13 @@
         <v>2.44</v>
       </c>
       <c r="V102">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W102">
         <v>1.07</v>
       </c>
       <c r="X102">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y102">
         <v>1.21</v>
@@ -16977,7 +16977,7 @@
         <v>1.87</v>
       </c>
       <c r="AB102">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AC102">
         <v>2.8</v>
@@ -17008,7 +17008,7 @@
         <v>1.25</v>
       </c>
       <c r="AK102">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="O103">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P103">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Q103">
-        <v>6.62</v>
+        <v>7.13</v>
       </c>
       <c r="R103">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="S103">
         <v>1.25</v>
       </c>
       <c r="T103">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U103">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="V103">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W103">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X103">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z103">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AA103">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AB103">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AC103">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AD103">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AE103">
         <v>1.2</v>
       </c>
       <c r="AF103">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AG103">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK103">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17427,10 +17427,10 @@
         <v>3.55</v>
       </c>
       <c r="O105">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="P105">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -17445,7 +17445,7 @@
         <v>2.86</v>
       </c>
       <c r="U105">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="V105">
         <v>1.42</v>
@@ -17460,7 +17460,7 @@
         <v>1.24</v>
       </c>
       <c r="Z105">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA105">
         <v>1.82</v>
@@ -17475,7 +17475,7 @@
         <v>1.33</v>
       </c>
       <c r="AE105">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF105">
         <v>1.7</v>
@@ -17587,52 +17587,52 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="O106">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P106">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q106">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R106">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S106">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T106">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="U106">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V106">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W106">
         <v>1.1</v>
       </c>
       <c r="X106">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y106">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z106">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA106">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB106">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AC106">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AD106">
         <v>1.4</v>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK106">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17759,34 +17759,34 @@
         <v>0</v>
       </c>
       <c r="Q107">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="R107">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S107">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T107">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="U107">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="V107">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W107">
         <v>1.08</v>
       </c>
       <c r="X107">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z107">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="AA107">
         <v>1.85</v>
@@ -17795,7 +17795,7 @@
         <v>1.95</v>
       </c>
       <c r="AC107">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AD107">
         <v>1.33</v>
@@ -17804,10 +17804,10 @@
         <v>1.09</v>
       </c>
       <c r="AF107">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AG107">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>1.08</v>
       </c>
       <c r="AK107">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="O108">
         <v>3.55</v>
       </c>
       <c r="P108">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -17967,7 +17967,7 @@
         <v>1.15</v>
       </c>
       <c r="AF108">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG108">
         <v>2.33</v>
@@ -18242,10 +18242,10 @@
         <v>2.15</v>
       </c>
       <c r="O110">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P110">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="Q110">
         <v>2.75</v>
@@ -18257,10 +18257,10 @@
         <v>1.3</v>
       </c>
       <c r="T110">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U110">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="V110">
         <v>1.43</v>
@@ -18272,28 +18272,28 @@
         <v>1.03</v>
       </c>
       <c r="Y110">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z110">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="AA110">
         <v>1.75</v>
       </c>
       <c r="AB110">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC110">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AD110">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE110">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF110">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG110">
         <v>2.2</v>
@@ -18309,7 +18309,7 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK110">
         <v>1.52</v>
@@ -19066,7 +19066,7 @@
         <v>5</v>
       </c>
       <c r="R115">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="S115">
         <v>1.24</v>
@@ -19078,7 +19078,7 @@
         <v>2.21</v>
       </c>
       <c r="V115">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W115">
         <v>1.18</v>
@@ -19096,22 +19096,22 @@
         <v>1.4</v>
       </c>
       <c r="AB115">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AC115">
         <v>2.15</v>
       </c>
       <c r="AD115">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AE115">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF115">
         <v>1.55</v>
       </c>
       <c r="AG115">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>4</v>
       </c>
       <c r="R116">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="S116">
         <v>1.58</v>
@@ -19244,7 +19244,7 @@
         <v>1.3</v>
       </c>
       <c r="W116">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X116">
         <v>1.06</v>
@@ -19256,10 +19256,10 @@
         <v>2.72</v>
       </c>
       <c r="AA116">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AB116">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC116">
         <v>5</v>
@@ -19416,13 +19416,13 @@
         <v>1.06</v>
       </c>
       <c r="Z117">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="AA117">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AB117">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AC117">
         <v>1.89</v>
@@ -19434,7 +19434,7 @@
         <v>1.42</v>
       </c>
       <c r="AF117">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AG117">
         <v>3.04</v>
@@ -19453,7 +19453,7 @@
         <v>1.26</v>
       </c>
       <c r="AK117">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,80 +19706,80 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q119">
-        <v>3.25</v>
+        <v>1.46</v>
       </c>
       <c r="R119">
-        <v>2.18</v>
+        <v>2.97</v>
       </c>
       <c r="S119">
+        <v>1.14</v>
+      </c>
+      <c r="T119">
+        <v>4.1</v>
+      </c>
+      <c r="U119">
+        <v>2.05</v>
+      </c>
+      <c r="V119">
+        <v>1.71</v>
+      </c>
+      <c r="W119">
+        <v>1.17</v>
+      </c>
+      <c r="X119">
+        <v>1.01</v>
+      </c>
+      <c r="Y119">
+        <v>1.13</v>
+      </c>
+      <c r="Z119">
+        <v>5.7</v>
+      </c>
+      <c r="AA119">
         <v>1.38</v>
       </c>
-      <c r="T119">
-        <v>2.86</v>
-      </c>
-      <c r="U119">
-        <v>2.79</v>
-      </c>
-      <c r="V119">
-        <v>1.37</v>
-      </c>
-      <c r="W119">
-        <v>1.05</v>
-      </c>
-      <c r="X119">
-        <v>1.04</v>
-      </c>
-      <c r="Y119">
-        <v>1.28</v>
-      </c>
-      <c r="Z119">
-        <v>3.25</v>
-      </c>
-      <c r="AA119">
-        <v>1.95</v>
-      </c>
       <c r="AB119">
+        <v>2.62</v>
+      </c>
+      <c r="AC119">
+        <v>2.19</v>
+      </c>
+      <c r="AD119">
+        <v>1.68</v>
+      </c>
+      <c r="AE119">
+        <v>1.23</v>
+      </c>
+      <c r="AF119">
+        <v>2</v>
+      </c>
+      <c r="AG119">
         <v>1.73</v>
       </c>
-      <c r="AC119">
-        <v>3.42</v>
-      </c>
-      <c r="AD119">
-        <v>1.25</v>
-      </c>
-      <c r="AE119">
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ119">
         <v>1.1</v>
       </c>
-      <c r="AF119">
-        <v>1.75</v>
-      </c>
-      <c r="AG119">
-        <v>1.97</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ119">
-        <v>1.3</v>
-      </c>
       <c r="AK119">
-        <v>1.44</v>
+        <v>4.5</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O120">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="P120">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q120">
-        <v>1.46</v>
+        <v>3.25</v>
       </c>
       <c r="R120">
-        <v>2.99</v>
+        <v>2.18</v>
       </c>
       <c r="S120">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="T120">
-        <v>4.1</v>
+        <v>2.86</v>
       </c>
       <c r="U120">
-        <v>2.05</v>
+        <v>2.79</v>
       </c>
       <c r="V120">
-        <v>1.71</v>
+        <v>1.37</v>
       </c>
       <c r="W120">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="X120">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y120">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="Z120">
-        <v>5.75</v>
+        <v>3.25</v>
       </c>
       <c r="AA120">
-        <v>1.38</v>
+        <v>1.95</v>
       </c>
       <c r="AB120">
-        <v>2.62</v>
+        <v>1.73</v>
       </c>
       <c r="AC120">
-        <v>2.14</v>
+        <v>3.42</v>
       </c>
       <c r="AD120">
-        <v>1.69</v>
+        <v>1.25</v>
       </c>
       <c r="AE120">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AF120">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AG120">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AK120">
-        <v>4.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20035,10 +20035,10 @@
         <v>4</v>
       </c>
       <c r="O121">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="P121">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q121">
         <v>4.6</v>
@@ -20068,13 +20068,13 @@
         <v>1.25</v>
       </c>
       <c r="Z121">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="AA121">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AB121">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC121">
         <v>3.08</v>
@@ -20530,10 +20530,10 @@
         <v>1.13</v>
       </c>
       <c r="Q124">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="R124">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="S124">
         <v>1.14</v>
@@ -20545,7 +20545,7 @@
         <v>1.85</v>
       </c>
       <c r="V124">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="W124">
         <v>1.22</v>
@@ -20566,19 +20566,19 @@
         <v>3.25</v>
       </c>
       <c r="AC124">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AD124">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AE124">
         <v>1.35</v>
       </c>
       <c r="AF124">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG124">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK124">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="O125">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P125">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q125">
         <v>2.5</v>
@@ -20711,7 +20711,7 @@
         <v>1.5</v>
       </c>
       <c r="W125">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X125">
         <v>1.01</v>
@@ -20859,7 +20859,7 @@
         <v>2.5</v>
       </c>
       <c r="R126">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S126">
         <v>1.38</v>
@@ -20901,10 +20901,10 @@
         <v>1.05</v>
       </c>
       <c r="AF126">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG126">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -21834,10 +21834,10 @@
         <v>0</v>
       </c>
       <c r="Q132">
-        <v>8.26</v>
+        <v>7.5</v>
       </c>
       <c r="R132">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="S132">
         <v>1.25</v>
@@ -21846,10 +21846,10 @@
         <v>3.48</v>
       </c>
       <c r="U132">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="V132">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W132">
         <v>1.13</v>
@@ -21861,28 +21861,28 @@
         <v>1.17</v>
       </c>
       <c r="Z132">
-        <v>4.99</v>
+        <v>4.9</v>
       </c>
       <c r="AA132">
         <v>1.53</v>
       </c>
       <c r="AB132">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="AC132">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AD132">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE132">
         <v>1.2</v>
       </c>
       <c r="AF132">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG132">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21988,25 +21988,25 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O133">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P133">
         <v>4.2</v>
       </c>
       <c r="Q133">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="R133">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="S133">
         <v>1.22</v>
       </c>
       <c r="T133">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="U133">
         <v>2.02</v>
@@ -22157,7 +22157,7 @@
         <v>3.25</v>
       </c>
       <c r="P134">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="Q134">
         <v>2.95</v>
@@ -22196,7 +22196,7 @@
         <v>1.88</v>
       </c>
       <c r="AC134">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AD134">
         <v>1.27</v>
@@ -22224,7 +22224,7 @@
         <v>1.3</v>
       </c>
       <c r="AK134">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22323,7 +22323,7 @@
         <v>1.95</v>
       </c>
       <c r="Q135">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R135">
         <v>2.38</v>
@@ -22335,7 +22335,7 @@
         <v>4.1</v>
       </c>
       <c r="U135">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="V135">
         <v>1.69</v>
@@ -22356,10 +22356,10 @@
         <v>1.4</v>
       </c>
       <c r="AB135">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AC135">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AD135">
         <v>1.73</v>
@@ -22673,13 +22673,13 @@
         <v>1.01</v>
       </c>
       <c r="Y137">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z137">
-        <v>4.51</v>
+        <v>4.25</v>
       </c>
       <c r="AA137">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AB137">
         <v>2.17</v>
@@ -22806,7 +22806,7 @@
         <v>2.45</v>
       </c>
       <c r="O138">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="P138">
         <v>2.3</v>
@@ -22839,16 +22839,16 @@
         <v>1.07</v>
       </c>
       <c r="Z138">
-        <v>5.95</v>
+        <v>7</v>
       </c>
       <c r="AA138">
         <v>1.4</v>
       </c>
       <c r="AB138">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="AC138">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AD138">
         <v>1.78</v>
@@ -22966,7 +22966,7 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="O139">
         <v>3.5</v>
@@ -22987,25 +22987,25 @@
         <v>3.3</v>
       </c>
       <c r="U139">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="V139">
         <v>1.52</v>
       </c>
       <c r="W139">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X139">
         <v>1.01</v>
       </c>
       <c r="Y139">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z139">
         <v>4.5</v>
       </c>
       <c r="AA139">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB139">
         <v>2.45</v>
@@ -23017,7 +23017,7 @@
         <v>1.47</v>
       </c>
       <c r="AE139">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF139">
         <v>1.48</v>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK139">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23129,7 +23129,7 @@
         </is>
       </c>
       <c r="N140">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="O140">
         <v>5.35</v>
@@ -23138,7 +23138,7 @@
         <v>1.32</v>
       </c>
       <c r="Q140">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="R140">
         <v>2.63</v>
@@ -23147,7 +23147,7 @@
         <v>1.24</v>
       </c>
       <c r="T140">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U140">
         <v>2.32</v>
@@ -23183,10 +23183,10 @@
         <v>1.17</v>
       </c>
       <c r="AF140">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG140">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23325,19 +23325,19 @@
         <v>1.03</v>
       </c>
       <c r="Y141">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z141">
         <v>3.98</v>
       </c>
       <c r="AA141">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB141">
         <v>2.1</v>
       </c>
       <c r="AC141">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AD141">
         <v>1.37</v>
@@ -23349,7 +23349,7 @@
         <v>1.56</v>
       </c>
       <c r="AG141">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AK141">
         <v>1.4</v>
@@ -23464,10 +23464,10 @@
         <v>3.45</v>
       </c>
       <c r="Q142">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="R142">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S142">
         <v>1.44</v>
@@ -23476,7 +23476,7 @@
         <v>2.53</v>
       </c>
       <c r="U142">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="V142">
         <v>1.36</v>
@@ -23503,7 +23503,7 @@
         <v>3.8</v>
       </c>
       <c r="AD142">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE142">
         <v>1.05</v>
@@ -23528,7 +23528,7 @@
         <v>1.32</v>
       </c>
       <c r="AK142">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23621,28 +23621,28 @@
         <v>1.53</v>
       </c>
       <c r="O143">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="P143">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="Q143">
         <v>2</v>
       </c>
       <c r="R143">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="S143">
         <v>1.38</v>
       </c>
       <c r="T143">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="U143">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="V143">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W143">
         <v>1.08</v>
@@ -23654,16 +23654,16 @@
         <v>1.29</v>
       </c>
       <c r="Z143">
-        <v>3.28</v>
+        <v>3.39</v>
       </c>
       <c r="AA143">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB143">
         <v>1.87</v>
       </c>
       <c r="AC143">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="AD143">
         <v>1.29</v>
@@ -23675,7 +23675,7 @@
         <v>2.05</v>
       </c>
       <c r="AG143">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK143">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -24922,37 +24922,37 @@
         </is>
       </c>
       <c r="N151">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O151">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P151">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q151">
-        <v>5.8</v>
+        <v>6.08</v>
       </c>
       <c r="R151">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S151">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="T151">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="U151">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="V151">
         <v>1.36</v>
       </c>
       <c r="W151">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X151">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y151">
         <v>1.28</v>
@@ -24964,22 +24964,22 @@
         <v>1.98</v>
       </c>
       <c r="AB151">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AC151">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AD151">
         <v>1.22</v>
       </c>
       <c r="AE151">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF151">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG151">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>2.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK151">
         <v>1.08</v>
@@ -25130,7 +25130,7 @@
         <v>1.53</v>
       </c>
       <c r="AC152">
-        <v>4.36</v>
+        <v>4.25</v>
       </c>
       <c r="AD152">
         <v>1.16</v>
@@ -25586,7 +25586,7 @@
         <v>2.25</v>
       </c>
       <c r="R155">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="S155">
         <v>1.25</v>
@@ -25604,7 +25604,7 @@
         <v>1.12</v>
       </c>
       <c r="X155">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y155">
         <v>1.15</v>
@@ -25619,19 +25619,19 @@
         <v>2.18</v>
       </c>
       <c r="AC155">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AD155">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE155">
         <v>1.16</v>
       </c>
       <c r="AF155">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG155">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>1.17</v>
       </c>
       <c r="AK155">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25767,7 +25767,7 @@
         <v>1.12</v>
       </c>
       <c r="X156">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y156">
         <v>1.2</v>
@@ -25785,13 +25785,13 @@
         <v>2.58</v>
       </c>
       <c r="AD156">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AE156">
         <v>1.15</v>
       </c>
       <c r="AF156">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG156">
         <v>2.05</v>
@@ -25903,7 +25903,7 @@
         <v>2</v>
       </c>
       <c r="O157">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="P157">
         <v>3.5</v>
@@ -25912,52 +25912,52 @@
         <v>2.5</v>
       </c>
       <c r="R157">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="S157">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T157">
         <v>3.3</v>
       </c>
       <c r="U157">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="V157">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W157">
         <v>1.12</v>
       </c>
       <c r="X157">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y157">
         <v>1.17</v>
       </c>
       <c r="Z157">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA157">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AB157">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="AC157">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AD157">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AE157">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF157">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AG157">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>1.22</v>
       </c>
       <c r="AK157">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26072,7 +26072,7 @@
         <v>5.9</v>
       </c>
       <c r="Q158">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="R158">
         <v>2.88</v>
@@ -26105,10 +26105,10 @@
         <v>1.29</v>
       </c>
       <c r="AB158">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AC158">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AD158">
         <v>2.02</v>
@@ -26117,7 +26117,7 @@
         <v>1.4</v>
       </c>
       <c r="AF158">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG158">
         <v>2.62</v>
@@ -26881,28 +26881,28 @@
         <v>3.8</v>
       </c>
       <c r="O163">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P163">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Q163">
-        <v>4.42</v>
+        <v>4.2</v>
       </c>
       <c r="R163">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="S163">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T163">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U163">
         <v>2.25</v>
       </c>
       <c r="V163">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W163">
         <v>1.14</v>
@@ -26911,31 +26911,31 @@
         <v>1.01</v>
       </c>
       <c r="Y163">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z163">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA163">
+        <v>1.53</v>
+      </c>
+      <c r="AB163">
+        <v>2.45</v>
+      </c>
+      <c r="AC163">
+        <v>2.33</v>
+      </c>
+      <c r="AD163">
         <v>1.51</v>
-      </c>
-      <c r="AB163">
-        <v>2.26</v>
-      </c>
-      <c r="AC163">
-        <v>2.31</v>
-      </c>
-      <c r="AD163">
-        <v>1.52</v>
       </c>
       <c r="AE163">
         <v>1.18</v>
       </c>
       <c r="AF163">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG163">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK163">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27204,16 +27204,16 @@
         </is>
       </c>
       <c r="N165">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O165">
         <v>3.3</v>
       </c>
       <c r="P165">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q165">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="R165">
         <v>2.08</v>
@@ -27258,7 +27258,7 @@
         <v>1.07</v>
       </c>
       <c r="AF165">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AG165">
         <v>2</v>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK165">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27367,16 +27367,16 @@
         </is>
       </c>
       <c r="N166">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O166">
         <v>4</v>
       </c>
       <c r="P166">
-        <v>4.21</v>
+        <v>4.5</v>
       </c>
       <c r="Q166">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="R166">
         <v>2.6</v>
@@ -27388,43 +27388,43 @@
         <v>4.5</v>
       </c>
       <c r="U166">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="V166">
         <v>1.73</v>
       </c>
       <c r="W166">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X166">
         <v>1.01</v>
       </c>
       <c r="Y166">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z166">
-        <v>6.5</v>
+        <v>6.51</v>
       </c>
       <c r="AA166">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AB166">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AC166">
         <v>2.04</v>
       </c>
       <c r="AD166">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AE166">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF166">
         <v>1.4</v>
       </c>
       <c r="AG166">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O169">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P169">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q169">
         <v>2.17</v>
@@ -27874,7 +27874,7 @@
         <v>1.17</v>
       </c>
       <c r="T169">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="U169">
         <v>1.89</v>
@@ -27889,7 +27889,7 @@
         <v>1.01</v>
       </c>
       <c r="Y169">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z169">
         <v>6.58</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="O170">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="P170">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q170">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="R170">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="S170">
         <v>1.13</v>
       </c>
       <c r="T170">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="U170">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="V170">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="W170">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X170">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y170">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z170">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="AA170">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AB170">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="AC170">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AD170">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AE170">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AF170">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AG170">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AK170">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="O171">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="P171">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="Q171">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="R171">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="S171">
         <v>1.13</v>
       </c>
       <c r="T171">
-        <v>4.85</v>
+        <v>5.5</v>
       </c>
       <c r="U171">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="V171">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="W171">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X171">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y171">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z171">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AA171">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AB171">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AC171">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AD171">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="AE171">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AF171">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AG171">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AK171">
-        <v>3.52</v>
+        <v>3</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28345,61 +28345,61 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="O172">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P172">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="Q172">
         <v>2.03</v>
       </c>
       <c r="R172">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="S172">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="T172">
-        <v>5.8</v>
+        <v>6.05</v>
       </c>
       <c r="U172">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="V172">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="W172">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X172">
         <v>1</v>
       </c>
       <c r="Y172">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Z172">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA172">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AB172">
         <v>4.33</v>
       </c>
       <c r="AC172">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AD172">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="AE172">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AF172">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AG172">
         <v>3.75</v>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK172">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28514,7 +28514,7 @@
         <v>6</v>
       </c>
       <c r="P173">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Q173">
         <v>5.22</v>
@@ -28544,13 +28544,13 @@
         <v>1.04</v>
       </c>
       <c r="Z173">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AA173">
         <v>1.24</v>
       </c>
       <c r="AB173">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AC173">
         <v>1.71</v>
@@ -28680,7 +28680,7 @@
         <v>7</v>
       </c>
       <c r="Q174">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="R174">
         <v>3.2</v>
@@ -28689,34 +28689,34 @@
         <v>1.15</v>
       </c>
       <c r="T174">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="U174">
         <v>1.73</v>
       </c>
       <c r="V174">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="W174">
         <v>1.31</v>
       </c>
       <c r="X174">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y174">
         <v>1.02</v>
       </c>
       <c r="Z174">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="AA174">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AB174">
         <v>3.88</v>
       </c>
       <c r="AC174">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AD174">
         <v>2.29</v>
@@ -28725,10 +28725,10 @@
         <v>1.53</v>
       </c>
       <c r="AF174">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG174">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28837,13 +28837,13 @@
         <v>2.13</v>
       </c>
       <c r="O175">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P175">
         <v>2.85</v>
       </c>
       <c r="Q175">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="R175">
         <v>2.36</v>
@@ -29166,10 +29166,10 @@
         <v>3.5</v>
       </c>
       <c r="P177">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="Q177">
-        <v>4.26</v>
+        <v>4.28</v>
       </c>
       <c r="R177">
         <v>2.1</v>
@@ -29199,7 +29199,7 @@
         <v>3.2</v>
       </c>
       <c r="AA177">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB177">
         <v>1.9</v>
@@ -29233,7 +29233,7 @@
         <v>1.8</v>
       </c>
       <c r="AK177">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29486,19 +29486,19 @@
         </is>
       </c>
       <c r="N179">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O179">
         <v>3.7</v>
       </c>
       <c r="P179">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q179">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="R179">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="S179">
         <v>1.22</v>
@@ -29528,16 +29528,16 @@
         <v>1.54</v>
       </c>
       <c r="AB179">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="AC179">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="AD179">
         <v>1.54</v>
       </c>
       <c r="AE179">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF179">
         <v>1.53</v>
@@ -29975,19 +29975,19 @@
         </is>
       </c>
       <c r="N182">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O182">
         <v>3.65</v>
       </c>
       <c r="P182">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q182">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="R182">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="S182">
         <v>1.32</v>
@@ -29999,37 +29999,37 @@
         <v>2.5</v>
       </c>
       <c r="V182">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W182">
         <v>1.1</v>
       </c>
       <c r="X182">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y182">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z182">
-        <v>3.83</v>
+        <v>3.76</v>
       </c>
       <c r="AA182">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB182">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC182">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD182">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE182">
         <v>1.08</v>
       </c>
       <c r="AF182">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG182">
         <v>2</v>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
+        <v>1.91</v>
+      </c>
+      <c r="AK182">
         <v>1.2</v>
-      </c>
-      <c r="AK182">
-        <v>1.14</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30962,7 +30962,7 @@
         <v>2.82</v>
       </c>
       <c r="Q188">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="R188">
         <v>2.4</v>
@@ -30977,7 +30977,7 @@
         <v>2.18</v>
       </c>
       <c r="V188">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W188">
         <v>1.17</v>
@@ -31125,22 +31125,22 @@
         <v>2.9</v>
       </c>
       <c r="Q189">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="R189">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S189">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T189">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="U189">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="V189">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W189">
         <v>1.11</v>
@@ -31152,19 +31152,19 @@
         <v>1.18</v>
       </c>
       <c r="Z189">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="AA189">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AB189">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AC189">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD189">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE189">
         <v>1.12</v>
@@ -31173,7 +31173,7 @@
         <v>1.57</v>
       </c>
       <c r="AG189">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK189">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31291,19 +31291,19 @@
         <v>2</v>
       </c>
       <c r="R190">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="S190">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T190">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="U190">
         <v>2.21</v>
       </c>
       <c r="V190">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W190">
         <v>1.14</v>
@@ -31312,16 +31312,16 @@
         <v>1.03</v>
       </c>
       <c r="Y190">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z190">
-        <v>4.44</v>
+        <v>4.8</v>
       </c>
       <c r="AA190">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AB190">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AC190">
         <v>2.3</v>
@@ -31330,13 +31330,13 @@
         <v>1.49</v>
       </c>
       <c r="AE190">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF190">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AG190">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK190">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="O192">
         <v>3.6</v>
       </c>
       <c r="P192">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA192">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB192">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC192">
         <v>0</v>
@@ -31952,7 +31952,7 @@
         <v>3.85</v>
       </c>
       <c r="U194">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V194">
         <v>1.67</v>
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="O195">
         <v>3.7</v>
       </c>
       <c r="P195">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="Q195">
         <v>2.75</v>
@@ -32145,7 +32145,7 @@
         <v>1.88</v>
       </c>
       <c r="AE195">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AF195">
         <v>1.3</v>
@@ -32164,7 +32164,7 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.51</v>
+        <v>1.2</v>
       </c>
       <c r="AK195">
         <v>1.5</v>
@@ -32260,7 +32260,7 @@
         <v>2.11</v>
       </c>
       <c r="O196">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P196">
         <v>2.8</v>
@@ -32327,7 +32327,7 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK196">
         <v>1.71</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.95</v>
+        <v>2.17</v>
       </c>
       <c r="O197">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P197">
-        <v>1.96</v>
+        <v>2.7</v>
       </c>
       <c r="Q197">
-        <v>3.45</v>
+        <v>2.5</v>
       </c>
       <c r="R197">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="S197">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T197">
         <v>4.5</v>
       </c>
       <c r="U197">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="V197">
         <v>1.82</v>
       </c>
       <c r="W197">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X197">
         <v>1.01</v>
       </c>
       <c r="Y197">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Z197">
-        <v>6.8</v>
+        <v>6.32</v>
       </c>
       <c r="AA197">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AB197">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="AC197">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AD197">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AE197">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AF197">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AG197">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK197">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,80 +32583,80 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.17</v>
+        <v>2.95</v>
       </c>
       <c r="O198">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="P198">
-        <v>2.7</v>
+        <v>1.96</v>
       </c>
       <c r="Q198">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="R198">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="S198">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T198">
         <v>4.5</v>
       </c>
       <c r="U198">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="V198">
         <v>1.82</v>
       </c>
       <c r="W198">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X198">
         <v>1.01</v>
       </c>
       <c r="Y198">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Z198">
-        <v>6.32</v>
+        <v>6.8</v>
       </c>
       <c r="AA198">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AB198">
-        <v>2.93</v>
+        <v>3.04</v>
       </c>
       <c r="AC198">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AD198">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AE198">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AF198">
+        <v>1.31</v>
+      </c>
+      <c r="AG198">
+        <v>3.14</v>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ198">
+        <v>1.25</v>
+      </c>
+      <c r="AK198">
         <v>1.32</v>
-      </c>
-      <c r="AG198">
-        <v>3</v>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ198">
-        <v>1.2</v>
-      </c>
-      <c r="AK198">
-        <v>1.54</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -34071,7 +34071,7 @@
         <v>3.2</v>
       </c>
       <c r="U207">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V207">
         <v>1.46</v>
@@ -34086,7 +34086,7 @@
         <v>1.24</v>
       </c>
       <c r="Z207">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="AA207">
         <v>1.86</v>
@@ -34095,10 +34095,10 @@
         <v>1.95</v>
       </c>
       <c r="AC207">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="AD207">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE207">
         <v>1.08</v>
@@ -34123,7 +34123,7 @@
         <v>1.29</v>
       </c>
       <c r="AK207">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34385,19 +34385,19 @@
         <v>0</v>
       </c>
       <c r="Q209">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="R209">
         <v>2.5</v>
       </c>
       <c r="S209">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T209">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U209">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V209">
         <v>1.61</v>
@@ -34409,25 +34409,25 @@
         <v>1.03</v>
       </c>
       <c r="Y209">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z209">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AA209">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB209">
         <v>2.25</v>
       </c>
       <c r="AC209">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AD209">
         <v>1.49</v>
       </c>
       <c r="AE209">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF209">
         <v>1.85</v>
@@ -34557,13 +34557,13 @@
         <v>1.45</v>
       </c>
       <c r="T210">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="U210">
         <v>3.24</v>
       </c>
       <c r="V210">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W210">
         <v>1.04</v>
@@ -34572,16 +34572,16 @@
         <v>1.04</v>
       </c>
       <c r="Y210">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z210">
         <v>2.92</v>
       </c>
       <c r="AA210">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AB210">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC210">
         <v>3.9</v>
@@ -34612,7 +34612,7 @@
         <v>1.25</v>
       </c>
       <c r="AK210">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -35037,55 +35037,55 @@
         <v>0</v>
       </c>
       <c r="Q213">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="R213">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="S213">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T213">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="U213">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="V213">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W213">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X213">
         <v>1.02</v>
       </c>
       <c r="Y213">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z213">
-        <v>3.81</v>
+        <v>4.03</v>
       </c>
       <c r="AA213">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AB213">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AC213">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="AD213">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE213">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF213">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG213">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK213">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35191,19 +35191,19 @@
         </is>
       </c>
       <c r="N214">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="O214">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P214">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Q214">
         <v>1.95</v>
       </c>
       <c r="R214">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="S214">
         <v>1.24</v>
@@ -35212,37 +35212,37 @@
         <v>3.74</v>
       </c>
       <c r="U214">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="V214">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W214">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X214">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y214">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z214">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AA214">
         <v>1.5</v>
       </c>
       <c r="AB214">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="AC214">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD214">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AE214">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF214">
         <v>1.57</v>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK214">
-        <v>2.47</v>
+        <v>2.67</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="O216">
-        <v>4.16</v>
+        <v>4.75</v>
       </c>
       <c r="P216">
-        <v>5</v>
+        <v>5.65</v>
       </c>
       <c r="Q216">
         <v>1.92</v>
@@ -35553,7 +35553,7 @@
         <v>1.06</v>
       </c>
       <c r="Z216">
-        <v>6.15</v>
+        <v>6.1</v>
       </c>
       <c r="AA216">
         <v>1.4</v>
@@ -35562,10 +35562,10 @@
         <v>2.87</v>
       </c>
       <c r="AC216">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AD216">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AE216">
         <v>1.28</v>
@@ -35843,7 +35843,7 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O218">
         <v>3.5</v>
@@ -35876,10 +35876,10 @@
         <v>1.02</v>
       </c>
       <c r="Y218">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z218">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AA218">
         <v>1.81</v>
@@ -35894,10 +35894,10 @@
         <v>1.36</v>
       </c>
       <c r="AE218">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF218">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG218">
         <v>2.25</v>
@@ -36024,46 +36024,46 @@
         <v>1.25</v>
       </c>
       <c r="T219">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="U219">
         <v>2.4</v>
       </c>
       <c r="V219">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W219">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X219">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y219">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z219">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA219">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB219">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AC219">
         <v>2.6</v>
       </c>
       <c r="AD219">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE219">
         <v>1.15</v>
       </c>
       <c r="AF219">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG219">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36172,28 +36172,28 @@
         <v>1.13</v>
       </c>
       <c r="O220">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="P220">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q220">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R220">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="S220">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="T220">
-        <v>3.78</v>
+        <v>4.05</v>
       </c>
       <c r="U220">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="V220">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="W220">
         <v>1.17</v>
@@ -36202,31 +36202,31 @@
         <v>1.01</v>
       </c>
       <c r="Y220">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z220">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AA220">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AB220">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="AC220">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AD220">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AE220">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AF220">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AG220">
-        <v>1.63</v>
+        <v>1.47</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>1.07</v>
       </c>
       <c r="AK220">
-        <v>5.45</v>
+        <v>5.3</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36839,7 +36839,7 @@
         <v>1.36</v>
       </c>
       <c r="T224">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="U224">
         <v>2.8</v>
@@ -36996,7 +36996,7 @@
         <v>2</v>
       </c>
       <c r="R225">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="S225">
         <v>1.26</v>
@@ -37054,7 +37054,7 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AK225">
         <v>2.3</v>
@@ -37168,16 +37168,16 @@
         <v>2.29</v>
       </c>
       <c r="U226">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V226">
         <v>1.29</v>
       </c>
       <c r="W226">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X226">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y226">
         <v>1.48</v>
@@ -37310,61 +37310,61 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O227">
         <v>3.7</v>
       </c>
       <c r="P227">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Q227">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R227">
         <v>2.15</v>
       </c>
       <c r="S227">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T227">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="U227">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="V227">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W227">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X227">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y227">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z227">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA227">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AB227">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC227">
         <v>3.3</v>
       </c>
       <c r="AD227">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE227">
         <v>1.12</v>
       </c>
       <c r="AF227">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG227">
         <v>1.9</v>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK227">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -38149,7 +38149,7 @@
         <v>1.92</v>
       </c>
       <c r="V232">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="W232">
         <v>1.2</v>
@@ -38164,7 +38164,7 @@
         <v>6.75</v>
       </c>
       <c r="AA232">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB232">
         <v>3.2</v>
@@ -38288,7 +38288,7 @@
         </is>
       </c>
       <c r="N233">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="O233">
         <v>3.4</v>
@@ -38318,7 +38318,7 @@
         <v>1.08</v>
       </c>
       <c r="X233">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y233">
         <v>1.24</v>
@@ -38460,7 +38460,7 @@
         <v>0</v>
       </c>
       <c r="Q234">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="R234">
         <v>2.17</v>
@@ -38496,7 +38496,7 @@
         <v>2.1</v>
       </c>
       <c r="AC234">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD234">
         <v>1.38</v>
@@ -38783,10 +38783,10 @@
         <v>3.9</v>
       </c>
       <c r="P236">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="Q236">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="R236">
         <v>2.25</v>
@@ -38952,7 +38952,7 @@
         <v>3.6</v>
       </c>
       <c r="R237">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="S237">
         <v>1.32</v>
@@ -38976,10 +38976,10 @@
         <v>1.21</v>
       </c>
       <c r="Z237">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA237">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AB237">
         <v>1.94</v>
@@ -38997,7 +38997,7 @@
         <v>1.62</v>
       </c>
       <c r="AG237">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>1.62</v>
       </c>
       <c r="AK237">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39453,7 +39453,7 @@
         <v>2.11</v>
       </c>
       <c r="V240">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W240">
         <v>1.2</v>
@@ -39465,10 +39465,10 @@
         <v>1.08</v>
       </c>
       <c r="Z240">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA240">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB240">
         <v>2.72</v>
@@ -39601,7 +39601,7 @@
         <v>0</v>
       </c>
       <c r="Q241">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="R241">
         <v>2.15</v>
@@ -39625,10 +39625,10 @@
         <v>1.05</v>
       </c>
       <c r="Y241">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="Z241">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AA241">
         <v>2.32</v>
@@ -39646,7 +39646,7 @@
         <v>1.02</v>
       </c>
       <c r="AF241">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AG241">
         <v>1.51</v>
@@ -39662,10 +39662,10 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK241">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -39939,28 +39939,28 @@
         <v>3.3</v>
       </c>
       <c r="U243">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="V243">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W243">
         <v>1.09</v>
       </c>
       <c r="X243">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y243">
         <v>1.15</v>
       </c>
       <c r="Z243">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA243">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AB243">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AC243">
         <v>2.58</v>
@@ -40917,7 +40917,7 @@
         <v>4.4</v>
       </c>
       <c r="U249">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V249">
         <v>1.81</v>
@@ -40932,13 +40932,13 @@
         <v>1.06</v>
       </c>
       <c r="Z249">
-        <v>6.05</v>
+        <v>6.1</v>
       </c>
       <c r="AA249">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AB249">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AC249">
         <v>1.91</v>
@@ -41068,55 +41068,55 @@
         <v>3.25</v>
       </c>
       <c r="Q250">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R250">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S250">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T250">
-        <v>3.13</v>
+        <v>3.07</v>
       </c>
       <c r="U250">
-        <v>2.71</v>
+        <v>2.77</v>
       </c>
       <c r="V250">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W250">
         <v>1.1</v>
       </c>
       <c r="X250">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y250">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z250">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AA250">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AB250">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC250">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AD250">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE250">
         <v>1.13</v>
       </c>
       <c r="AF250">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AG250">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK250">
         <v>1.65</v>
@@ -41717,13 +41717,13 @@
         <v>3.05</v>
       </c>
       <c r="P254">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q254">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="R254">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S254">
         <v>1.44</v>
@@ -41738,7 +41738,7 @@
         <v>1.3</v>
       </c>
       <c r="W254">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X254">
         <v>1.05</v>
@@ -41750,13 +41750,13 @@
         <v>2.49</v>
       </c>
       <c r="AA254">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AB254">
         <v>1.53</v>
       </c>
       <c r="AC254">
-        <v>4.34</v>
+        <v>4.58</v>
       </c>
       <c r="AD254">
         <v>1.18</v>
@@ -41765,10 +41765,10 @@
         <v>1.01</v>
       </c>
       <c r="AF254">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG254">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         </is>
       </c>
       <c r="AJ254">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK254">
         <v>1.59</v>
@@ -42366,10 +42366,10 @@
         <v>6.25</v>
       </c>
       <c r="O258">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="P258">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Q258">
         <v>6</v>
@@ -42399,7 +42399,7 @@
         <v>1.05</v>
       </c>
       <c r="Z258">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="AA258">
         <v>1.36</v>
@@ -42433,7 +42433,7 @@
         </is>
       </c>
       <c r="AJ258">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK258">
         <v>1.11</v>
@@ -42553,7 +42553,7 @@
         <v>1.52</v>
       </c>
       <c r="W259">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X259">
         <v>1.01</v>
@@ -42725,16 +42725,16 @@
         <v>1.46</v>
       </c>
       <c r="Z260">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AA260">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AB260">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC260">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AD260">
         <v>1.14</v>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK260">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42855,25 +42855,25 @@
         <v>2.8</v>
       </c>
       <c r="O261">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P261">
         <v>2.45</v>
       </c>
       <c r="Q261">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="R261">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S261">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T261">
         <v>2.88</v>
       </c>
       <c r="U261">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="V261">
         <v>1.36</v>
@@ -42885,31 +42885,31 @@
         <v>1.04</v>
       </c>
       <c r="Y261">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z261">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA261">
         <v>2.09</v>
       </c>
       <c r="AB261">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AC261">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="AD261">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE261">
         <v>1.04</v>
       </c>
       <c r="AF261">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AG261">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -42925,7 +42925,7 @@
         <v>1.3</v>
       </c>
       <c r="AK261">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -43015,28 +43015,28 @@
         </is>
       </c>
       <c r="N262">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="O262">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P262">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="Q262">
         <v>2.55</v>
       </c>
       <c r="R262">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="S262">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="T262">
         <v>2.13</v>
       </c>
       <c r="U262">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="V262">
         <v>1.2</v>
@@ -43045,34 +43045,34 @@
         <v>1.03</v>
       </c>
       <c r="X262">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y262">
         <v>1.66</v>
       </c>
       <c r="Z262">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AA262">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="AB262">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC262">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="AD262">
         <v>1.07</v>
       </c>
       <c r="AE262">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF262">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AG262">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AH262" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>1.1</v>
       </c>
       <c r="AK262">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -43362,7 +43362,7 @@
         <v>2.56</v>
       </c>
       <c r="U264">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="V264">
         <v>1.29</v>
@@ -43398,7 +43398,7 @@
         <v>2.05</v>
       </c>
       <c r="AG264">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43682,16 +43682,16 @@
         <v>2.26</v>
       </c>
       <c r="S266">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T266">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="U266">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="V266">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W266">
         <v>1.1</v>
@@ -43700,13 +43700,13 @@
         <v>1.01</v>
       </c>
       <c r="Y266">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="Z266">
         <v>3.1</v>
       </c>
       <c r="AA266">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AB266">
         <v>1.92</v>
@@ -43715,13 +43715,13 @@
         <v>3</v>
       </c>
       <c r="AD266">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE266">
         <v>1.07</v>
       </c>
       <c r="AF266">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG266">
         <v>2.05</v>
@@ -43872,10 +43872,10 @@
         <v>2.29</v>
       </c>
       <c r="AB267">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC267">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AD267">
         <v>1.19</v>
@@ -43900,10 +43900,10 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK267">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -44331,13 +44331,13 @@
         <v>2.9</v>
       </c>
       <c r="R270">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="S270">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T270">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U270">
         <v>2.67</v>
@@ -44346,7 +44346,7 @@
         <v>1.44</v>
       </c>
       <c r="W270">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X270">
         <v>1.01</v>
@@ -44373,10 +44373,10 @@
         <v>1.07</v>
       </c>
       <c r="AF270">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AG270">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AK270">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -45795,52 +45795,52 @@
         <v>3.4</v>
       </c>
       <c r="Q279">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R279">
         <v>2.25</v>
       </c>
       <c r="S279">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T279">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="U279">
         <v>2.4</v>
       </c>
       <c r="V279">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W279">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X279">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y279">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z279">
-        <v>4.03</v>
+        <v>3.74</v>
       </c>
       <c r="AA279">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB279">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC279">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD279">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE279">
         <v>1.16</v>
       </c>
       <c r="AF279">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG279">
         <v>2.14</v>
@@ -45856,7 +45856,7 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK279">
         <v>1.71</v>
@@ -45949,25 +45949,25 @@
         </is>
       </c>
       <c r="N280">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="O280">
         <v>3</v>
       </c>
       <c r="P280">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q280">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="R280">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="S280">
         <v>1.5</v>
       </c>
       <c r="T280">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="U280">
         <v>3.22</v>
@@ -45985,16 +45985,16 @@
         <v>1.44</v>
       </c>
       <c r="Z280">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="AA280">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="AB280">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC280">
-        <v>4.81</v>
+        <v>4.59</v>
       </c>
       <c r="AD280">
         <v>1.16</v>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK280">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -46121,16 +46121,16 @@
         <v>0</v>
       </c>
       <c r="Q281">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="R281">
         <v>2.62</v>
       </c>
       <c r="S281">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T281">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U281">
         <v>2.17</v>
@@ -46290,10 +46290,10 @@
         <v>2.7</v>
       </c>
       <c r="S282">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T282">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="U282">
         <v>2.25</v>
@@ -46302,7 +46302,7 @@
         <v>1.57</v>
       </c>
       <c r="W282">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X282">
         <v>1.02</v>
@@ -46311,13 +46311,13 @@
         <v>1.2</v>
       </c>
       <c r="Z282">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AA282">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB282">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AC282">
         <v>2.59</v>
@@ -46329,7 +46329,7 @@
         <v>1.19</v>
       </c>
       <c r="AF282">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG282">
         <v>1.85</v>
@@ -46438,52 +46438,52 @@
         </is>
       </c>
       <c r="N283">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="O283">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P283">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Q283">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="R283">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S283">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T283">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="U283">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="V283">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W283">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X283">
         <v>1.03</v>
       </c>
       <c r="Y283">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z283">
-        <v>2.93</v>
+        <v>2.83</v>
       </c>
       <c r="AA283">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AB283">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AC283">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="AD283">
         <v>1.19</v>
@@ -46492,10 +46492,10 @@
         <v>1.03</v>
       </c>
       <c r="AF283">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AG283">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46511,7 +46511,7 @@
         <v>1.1</v>
       </c>
       <c r="AK283">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46601,34 +46601,34 @@
         </is>
       </c>
       <c r="N284">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="O284">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P284">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="Q284">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R284">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="S284">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T284">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="U284">
-        <v>3.09</v>
+        <v>2.9</v>
       </c>
       <c r="V284">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W284">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X284">
         <v>1.03</v>
@@ -46637,28 +46637,28 @@
         <v>1.36</v>
       </c>
       <c r="Z284">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AA284">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AB284">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC284">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="AD284">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AE284">
         <v>1.04</v>
       </c>
       <c r="AF284">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AG284">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK284">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46773,22 +46773,22 @@
         <v>2.37</v>
       </c>
       <c r="Q285">
-        <v>3.65</v>
+        <v>3.74</v>
       </c>
       <c r="R285">
         <v>1.89</v>
       </c>
       <c r="S285">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T285">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="U285">
         <v>3.24</v>
       </c>
       <c r="V285">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W285">
         <v>1.03</v>
@@ -46806,19 +46806,19 @@
         <v>2.31</v>
       </c>
       <c r="AB285">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC285">
-        <v>4.1</v>
+        <v>4.42</v>
       </c>
       <c r="AD285">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE285">
         <v>1.03</v>
       </c>
       <c r="AF285">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG285">
         <v>1.75</v>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AK285">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -46945,16 +46945,16 @@
         <v>1.33</v>
       </c>
       <c r="T286">
-        <v>3.01</v>
+        <v>3.07</v>
       </c>
       <c r="U286">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="V286">
         <v>1.4</v>
       </c>
       <c r="W286">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X286">
         <v>1.03</v>
@@ -47117,7 +47117,7 @@
         <v>1.3</v>
       </c>
       <c r="W287">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X287">
         <v>1.03</v>
@@ -47126,7 +47126,7 @@
         <v>1.35</v>
       </c>
       <c r="Z287">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="AA287">
         <v>2.21</v>
@@ -47262,55 +47262,55 @@
         <v>0</v>
       </c>
       <c r="Q288">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="R288">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="S288">
         <v>1.29</v>
       </c>
       <c r="T288">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U288">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="V288">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W288">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X288">
         <v>1.04</v>
       </c>
       <c r="Y288">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z288">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="AA288">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB288">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AC288">
-        <v>2.25</v>
+        <v>2.78</v>
       </c>
       <c r="AD288">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE288">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF288">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AG288">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK288">
         <v>1.53</v>
@@ -47431,13 +47431,13 @@
         <v>2.45</v>
       </c>
       <c r="S289">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T289">
         <v>3.6</v>
       </c>
       <c r="U289">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V289">
         <v>1.6</v>
@@ -47461,13 +47461,13 @@
         <v>2.36</v>
       </c>
       <c r="AC289">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AD289">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE289">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF289">
         <v>1.47</v>
@@ -47489,7 +47489,7 @@
         <v>1.22</v>
       </c>
       <c r="AK289">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47748,7 +47748,7 @@
         <v>3.2</v>
       </c>
       <c r="P291">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q291">
         <v>2.78</v>
@@ -47790,13 +47790,13 @@
         <v>3.18</v>
       </c>
       <c r="AD291">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE291">
         <v>1.07</v>
       </c>
       <c r="AF291">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG291">
         <v>2</v>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.11</v>
+        <v>1.44</v>
       </c>
       <c r="O2">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="P2">
-        <v>2.94</v>
+        <v>6.4</v>
       </c>
       <c r="Q2">
-        <v>2.71</v>
+        <v>1.87</v>
       </c>
       <c r="R2">
-        <v>2.03</v>
+        <v>2.41</v>
       </c>
       <c r="S2">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="U2">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="Z2">
-        <v>3.14</v>
+        <v>4.3</v>
       </c>
       <c r="AA2">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="AB2">
-        <v>1.7</v>
+        <v>2.19</v>
       </c>
       <c r="AC2">
-        <v>3.84</v>
+        <v>2.63</v>
       </c>
       <c r="AD2">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AE2">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AF2">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG2">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK2">
-        <v>1.7</v>
+        <v>2.69</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.44</v>
+        <v>2.11</v>
       </c>
       <c r="O3">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="P3">
-        <v>6.4</v>
+        <v>2.94</v>
       </c>
       <c r="Q3">
-        <v>1.87</v>
+        <v>2.71</v>
       </c>
       <c r="R3">
-        <v>2.41</v>
+        <v>2.03</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="U3">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="V3">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="Z3">
-        <v>4.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA3">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="AB3">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AC3">
-        <v>2.63</v>
+        <v>3.84</v>
       </c>
       <c r="AD3">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AE3">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG3">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>2.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -3578,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="Q20">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="R20">
         <v>2.05</v>
@@ -3593,7 +3593,7 @@
         <v>3.18</v>
       </c>
       <c r="V20">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W20">
         <v>1.03</v>
@@ -3623,7 +3623,7 @@
         <v>1.01</v>
       </c>
       <c r="AF20">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AG20">
         <v>1.75</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,31 +4547,31 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="R26">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="S26">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="T26">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="U26">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="V26">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W26">
         <v>1.03</v>
@@ -4580,47 +4580,47 @@
         <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z26">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AA26">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AB26">
+        <v>1.6</v>
+      </c>
+      <c r="AC26">
+        <v>3.98</v>
+      </c>
+      <c r="AD26">
+        <v>1.17</v>
+      </c>
+      <c r="AE26">
+        <v>1.03</v>
+      </c>
+      <c r="AF26">
+        <v>1.91</v>
+      </c>
+      <c r="AG26">
+        <v>1.75</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>1.3</v>
+      </c>
+      <c r="AK26">
         <v>1.55</v>
-      </c>
-      <c r="AC26">
-        <v>4.15</v>
-      </c>
-      <c r="AD26">
-        <v>1.16</v>
-      </c>
-      <c r="AE26">
-        <v>1.02</v>
-      </c>
-      <c r="AF26">
-        <v>2.04</v>
-      </c>
-      <c r="AG26">
-        <v>1.66</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.15</v>
-      </c>
-      <c r="AK26">
-        <v>1.75</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q28">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="R28">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="S28">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="T28">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="U28">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="V28">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W28">
         <v>1.03</v>
@@ -4906,47 +4906,47 @@
         <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z28">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AA28">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AB28">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC28">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="AD28">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE28">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF28">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AG28">
+        <v>1.66</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>1.15</v>
+      </c>
+      <c r="AK28">
         <v>1.75</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.3</v>
-      </c>
-      <c r="AK28">
-        <v>1.55</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="O37">
         <v>3.55</v>
@@ -7988,7 +7988,7 @@
         <v>1.35</v>
       </c>
       <c r="T47">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="U47">
         <v>2.62</v>
@@ -8027,7 +8027,7 @@
         <v>1.75</v>
       </c>
       <c r="AG47">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="O57">
         <v>3.7</v>
       </c>
       <c r="P57">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="Q57">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="R57">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S57">
         <v>1.22</v>
       </c>
       <c r="T57">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="U57">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V57">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="W57">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z57">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA57">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AB57">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="AC57">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="AD57">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE57">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AF57">
         <v>1.45</v>
       </c>
       <c r="AG57">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK57">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="O58">
         <v>3.7</v>
       </c>
       <c r="P58">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="Q58">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="R58">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S58">
         <v>1.22</v>
       </c>
       <c r="T58">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="U58">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V58">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="W58">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X58">
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z58">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA58">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AB58">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="AC58">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="AD58">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE58">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AF58">
         <v>1.45</v>
       </c>
       <c r="AG58">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK58">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O63">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="P63">
         <v>3</v>
@@ -10593,16 +10593,16 @@
         <v>1.85</v>
       </c>
       <c r="S63">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="T63">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="U63">
         <v>3.9</v>
       </c>
       <c r="V63">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W63">
         <v>1</v>
@@ -10611,7 +10611,7 @@
         <v>1.06</v>
       </c>
       <c r="Y63">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Z63">
         <v>2.36</v>
@@ -10623,7 +10623,7 @@
         <v>1.44</v>
       </c>
       <c r="AC63">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AD63">
         <v>1.12</v>
@@ -10635,7 +10635,7 @@
         <v>2.08</v>
       </c>
       <c r="AG63">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>1.09</v>
       </c>
       <c r="Y65">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="Z65">
         <v>2.44</v>
@@ -11568,10 +11568,10 @@
         <v>2.73</v>
       </c>
       <c r="R69">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="S69">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T69">
         <v>3.14</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,61 +11882,61 @@
         </is>
       </c>
       <c r="N71">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="O71">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P71">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q71">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R71">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S71">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T71">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U71">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V71">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W71">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y71">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z71">
-        <v>4.54</v>
+        <v>3.84</v>
       </c>
       <c r="AA71">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AB71">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AC71">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AD71">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE71">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF71">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG71">
         <v>2.3</v>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK71">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,61 +12045,61 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="O72">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P72">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q72">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R72">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S72">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T72">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="U72">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V72">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W72">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X72">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z72">
-        <v>3.84</v>
+        <v>4.54</v>
       </c>
       <c r="AA72">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="AB72">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AC72">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AD72">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE72">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF72">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG72">
         <v>2.3</v>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK72">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -13379,7 +13379,7 @@
         <v>1.08</v>
       </c>
       <c r="X80">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
         <v>1.27</v>
@@ -13388,10 +13388,10 @@
         <v>3.14</v>
       </c>
       <c r="AA80">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB80">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AC80">
         <v>3.14</v>
@@ -13675,7 +13675,7 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O82">
         <v>4.7</v>
@@ -13684,10 +13684,10 @@
         <v>5.8</v>
       </c>
       <c r="Q82">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R82">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="S82">
         <v>1.2</v>
@@ -13696,10 +13696,10 @@
         <v>4</v>
       </c>
       <c r="U82">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="V82">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W82">
         <v>1.12</v>
@@ -13711,7 +13711,7 @@
         <v>1.13</v>
       </c>
       <c r="Z82">
-        <v>6</v>
+        <v>4.95</v>
       </c>
       <c r="AA82">
         <v>1.45</v>
@@ -13720,10 +13720,10 @@
         <v>2.41</v>
       </c>
       <c r="AC82">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AD82">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AE82">
         <v>1.25</v>
@@ -13732,7 +13732,7 @@
         <v>1.62</v>
       </c>
       <c r="AG82">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.17</v>
       </c>
       <c r="AK82">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -15154,7 +15154,7 @@
         <v>2.88</v>
       </c>
       <c r="R91">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S91">
         <v>1.35</v>
@@ -15172,7 +15172,7 @@
         <v>1.08</v>
       </c>
       <c r="X91">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
         <v>1.24</v>
@@ -15474,7 +15474,7 @@
         <v>3.4</v>
       </c>
       <c r="P93">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -15486,7 +15486,7 @@
         <v>1.33</v>
       </c>
       <c r="T93">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="U93">
         <v>2.5</v>
@@ -15501,13 +15501,13 @@
         <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z93">
         <v>3.72</v>
       </c>
       <c r="AA93">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB93">
         <v>2</v>
@@ -15519,7 +15519,7 @@
         <v>1.36</v>
       </c>
       <c r="AE93">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF93">
         <v>1.67</v>
@@ -15806,7 +15806,7 @@
         <v>2.4</v>
       </c>
       <c r="R95">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S95">
         <v>1.34</v>
@@ -15833,13 +15833,13 @@
         <v>4.04</v>
       </c>
       <c r="AA95">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB95">
         <v>2.12</v>
       </c>
       <c r="AC95">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AD95">
         <v>1.4</v>
@@ -15993,22 +15993,22 @@
         <v>1.12</v>
       </c>
       <c r="Z96">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AA96">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AB96">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="AC96">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AD96">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE96">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF96">
         <v>1.95</v>
@@ -16129,7 +16129,7 @@
         <v>2.15</v>
       </c>
       <c r="Q97">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R97">
         <v>2.5</v>
@@ -16156,22 +16156,22 @@
         <v>1.13</v>
       </c>
       <c r="Z97">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA97">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB97">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="AC97">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AD97">
         <v>1.63</v>
       </c>
       <c r="AE97">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF97">
         <v>1.43</v>
@@ -16193,7 +16193,7 @@
         <v>1.67</v>
       </c>
       <c r="AK97">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16941,7 +16941,7 @@
         <v>3.6</v>
       </c>
       <c r="P102">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="Q102">
         <v>3.4</v>
@@ -16977,7 +16977,7 @@
         <v>1.87</v>
       </c>
       <c r="AB102">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AC102">
         <v>2.8</v>
@@ -16986,7 +16986,7 @@
         <v>1.37</v>
       </c>
       <c r="AE102">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF102">
         <v>1.62</v>
@@ -17008,7 +17008,7 @@
         <v>1.25</v>
       </c>
       <c r="AK102">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -18749,7 +18749,7 @@
         <v>3.12</v>
       </c>
       <c r="U113">
-        <v>2.34</v>
+        <v>2.49</v>
       </c>
       <c r="V113">
         <v>1.51</v>
@@ -18758,13 +18758,13 @@
         <v>1.1</v>
       </c>
       <c r="X113">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y113">
         <v>1.17</v>
       </c>
       <c r="Z113">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA113">
         <v>1.66</v>
@@ -18782,7 +18782,7 @@
         <v>1.11</v>
       </c>
       <c r="AF113">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG113">
         <v>2</v>
@@ -20059,7 +20059,7 @@
         <v>1.4</v>
       </c>
       <c r="W121">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X121">
         <v>1.03</v>
@@ -20080,7 +20080,7 @@
         <v>3.08</v>
       </c>
       <c r="AD121">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE121">
         <v>1.07</v>
@@ -22196,7 +22196,7 @@
         <v>1.88</v>
       </c>
       <c r="AC134">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AD134">
         <v>1.27</v>
@@ -22224,7 +22224,7 @@
         <v>1.3</v>
       </c>
       <c r="AK134">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22335,16 +22335,16 @@
         <v>4.1</v>
       </c>
       <c r="U135">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="V135">
         <v>1.69</v>
       </c>
       <c r="W135">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X135">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y135">
         <v>1.1</v>
@@ -22359,10 +22359,10 @@
         <v>2.55</v>
       </c>
       <c r="AC135">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AD135">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AE135">
         <v>1.29</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="O170">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="P170">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="Q170">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="R170">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="S170">
         <v>1.13</v>
       </c>
       <c r="T170">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="U170">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="V170">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="W170">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X170">
         <v>1.01</v>
       </c>
       <c r="Y170">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z170">
         <v>9</v>
       </c>
       <c r="AA170">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AB170">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AC170">
         <v>1.6</v>
       </c>
       <c r="AD170">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AE170">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AF170">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AG170">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AK170">
-        <v>3.52</v>
+        <v>3</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="O171">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="P171">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q171">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="R171">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="S171">
         <v>1.13</v>
       </c>
       <c r="T171">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="U171">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="V171">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="W171">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X171">
         <v>1.01</v>
       </c>
       <c r="Y171">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z171">
         <v>9</v>
       </c>
       <c r="AA171">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AB171">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="AC171">
         <v>1.6</v>
       </c>
       <c r="AD171">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AE171">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AF171">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AG171">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AK171">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -29006,7 +29006,7 @@
         <v>2.65</v>
       </c>
       <c r="Q176">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="R176">
         <v>2.01</v>
@@ -29024,7 +29024,7 @@
         <v>1.37</v>
       </c>
       <c r="W176">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X176">
         <v>1</v>
@@ -29054,7 +29054,7 @@
         <v>1.7</v>
       </c>
       <c r="AG176">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AK176">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29160,16 +29160,16 @@
         </is>
       </c>
       <c r="N177">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O177">
         <v>3.5</v>
       </c>
       <c r="P177">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="Q177">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="R177">
         <v>2.1</v>
@@ -29217,7 +29217,7 @@
         <v>1.73</v>
       </c>
       <c r="AG177">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AK177">
         <v>1.23</v>
@@ -29495,13 +29495,13 @@
         <v>2.05</v>
       </c>
       <c r="Q179">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="R179">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S179">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T179">
         <v>3.8</v>
@@ -29531,7 +29531,7 @@
         <v>2.46</v>
       </c>
       <c r="AC179">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AD179">
         <v>1.54</v>
@@ -29559,7 +29559,7 @@
         <v>1.22</v>
       </c>
       <c r="AK179">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29658,16 +29658,16 @@
         <v>3.1</v>
       </c>
       <c r="Q180">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="R180">
         <v>2.24</v>
       </c>
       <c r="S180">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T180">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="U180">
         <v>2.32</v>
@@ -29685,7 +29685,7 @@
         <v>1.18</v>
       </c>
       <c r="Z180">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA180">
         <v>1.62</v>
@@ -29722,7 +29722,7 @@
         <v>1.22</v>
       </c>
       <c r="AK180">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -30310,19 +30310,19 @@
         <v>2.25</v>
       </c>
       <c r="Q184">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R184">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S184">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T184">
         <v>3.2</v>
       </c>
       <c r="U184">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="V184">
         <v>1.47</v>
@@ -30337,7 +30337,7 @@
         <v>1.22</v>
       </c>
       <c r="Z184">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="AA184">
         <v>1.71</v>
@@ -30358,7 +30358,7 @@
         <v>1.57</v>
       </c>
       <c r="AG184">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK184">
         <v>1.4</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.11</v>
+        <v>2.95</v>
       </c>
       <c r="O196">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="P196">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="Q196">
-        <v>2.43</v>
+        <v>3.45</v>
       </c>
       <c r="R196">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="S196">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T196">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="U196">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="V196">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="W196">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="X196">
         <v>1.01</v>
       </c>
       <c r="Y196">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z196">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="AA196">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AB196">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="AC196">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AD196">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="AE196">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AF196">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AG196">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK196">
-        <v>1.71</v>
+        <v>1.32</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.95</v>
+        <v>2.11</v>
       </c>
       <c r="O198">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="P198">
-        <v>1.96</v>
+        <v>2.8</v>
       </c>
       <c r="Q198">
-        <v>3.45</v>
+        <v>2.43</v>
       </c>
       <c r="R198">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="S198">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T198">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="U198">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="V198">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="W198">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="X198">
         <v>1.01</v>
       </c>
       <c r="Y198">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z198">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="AA198">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AB198">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="AC198">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AD198">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="AE198">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AF198">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AG198">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK198">
-        <v>1.32</v>
+        <v>1.71</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -34213,28 +34213,28 @@
         </is>
       </c>
       <c r="N208">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O208">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P208">
         <v>3.5</v>
       </c>
       <c r="Q208">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="R208">
         <v>1.92</v>
       </c>
       <c r="S208">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T208">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="U208">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="V208">
         <v>1.26</v>
@@ -34249,7 +34249,7 @@
         <v>1.38</v>
       </c>
       <c r="Z208">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="AA208">
         <v>2.24</v>
@@ -34283,7 +34283,7 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK208">
         <v>1.6</v>
@@ -34412,7 +34412,7 @@
         <v>1.2</v>
       </c>
       <c r="Z209">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="AA209">
         <v>1.61</v>
@@ -34572,19 +34572,19 @@
         <v>1.04</v>
       </c>
       <c r="Y210">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z210">
         <v>2.92</v>
       </c>
       <c r="AA210">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AB210">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AC210">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD210">
         <v>1.24</v>
@@ -35037,10 +35037,10 @@
         <v>0</v>
       </c>
       <c r="Q213">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="R213">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="S213">
         <v>1.36</v>
@@ -35064,7 +35064,7 @@
         <v>1.26</v>
       </c>
       <c r="Z213">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="AA213">
         <v>1.89</v>
@@ -35073,7 +35073,7 @@
         <v>2.06</v>
       </c>
       <c r="AC213">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AD213">
         <v>1.37</v>
@@ -35082,10 +35082,10 @@
         <v>1.08</v>
       </c>
       <c r="AF213">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG213">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>1.25</v>
       </c>
       <c r="AK213">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35206,13 +35206,13 @@
         <v>2.54</v>
       </c>
       <c r="S214">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T214">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="U214">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="V214">
         <v>1.67</v>
@@ -35227,10 +35227,10 @@
         <v>1.09</v>
       </c>
       <c r="Z214">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="AA214">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB214">
         <v>2.7</v>
@@ -35239,10 +35239,10 @@
         <v>2.1</v>
       </c>
       <c r="AD214">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AE214">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF214">
         <v>1.57</v>
@@ -35680,13 +35680,13 @@
         </is>
       </c>
       <c r="N217">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O217">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P217">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q217">
         <v>2.69</v>
@@ -35698,7 +35698,7 @@
         <v>1.44</v>
       </c>
       <c r="T217">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="U217">
         <v>3.06</v>
@@ -35707,7 +35707,7 @@
         <v>1.33</v>
       </c>
       <c r="W217">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X217">
         <v>1.02</v>
@@ -38623,7 +38623,7 @@
         <v>5.25</v>
       </c>
       <c r="Q235">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="R235">
         <v>2.13</v>
@@ -38644,7 +38644,7 @@
         <v>1.08</v>
       </c>
       <c r="X235">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y235">
         <v>1.22</v>
@@ -38653,10 +38653,10 @@
         <v>3.5</v>
       </c>
       <c r="AA235">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB235">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AC235">
         <v>2.83</v>
@@ -38668,7 +38668,7 @@
         <v>1.09</v>
       </c>
       <c r="AF235">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG235">
         <v>1.91</v>
@@ -39755,7 +39755,7 @@
         </is>
       </c>
       <c r="N242">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O242">
         <v>3.15</v>
@@ -41246,7 +41246,7 @@
         <v>1.96</v>
       </c>
       <c r="V251">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W251">
         <v>1.2</v>
@@ -41267,7 +41267,7 @@
         <v>2.92</v>
       </c>
       <c r="AC251">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AD251">
         <v>1.88</v>
@@ -42372,7 +42372,7 @@
         <v>1.44</v>
       </c>
       <c r="Q258">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="R258">
         <v>2.7</v>
@@ -42399,7 +42399,7 @@
         <v>1.05</v>
       </c>
       <c r="Z258">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="AA258">
         <v>1.36</v>
@@ -43344,10 +43344,10 @@
         <v>2</v>
       </c>
       <c r="O264">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="P264">
-        <v>4.04</v>
+        <v>3.92</v>
       </c>
       <c r="Q264">
         <v>2.76</v>
@@ -43362,7 +43362,7 @@
         <v>2.56</v>
       </c>
       <c r="U264">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="V264">
         <v>1.29</v>
@@ -43371,7 +43371,7 @@
         <v>1.03</v>
       </c>
       <c r="X264">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Y264">
         <v>1.4</v>
@@ -43380,16 +43380,16 @@
         <v>2.75</v>
       </c>
       <c r="AA264">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AB264">
         <v>1.6</v>
       </c>
       <c r="AC264">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="AD264">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE264">
         <v>1.02</v>
@@ -43414,7 +43414,7 @@
         <v>1.34</v>
       </c>
       <c r="AK264">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -43700,13 +43700,13 @@
         <v>1.01</v>
       </c>
       <c r="Y266">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z266">
         <v>3.1</v>
       </c>
       <c r="AA266">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AB266">
         <v>1.92</v>
@@ -43715,7 +43715,7 @@
         <v>3</v>
       </c>
       <c r="AD266">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE266">
         <v>1.07</v>
@@ -43740,7 +43740,7 @@
         <v>1.35</v>
       </c>
       <c r="AK266">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AL266">
         <v>0</v>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="O21">
-        <v>3.23</v>
+        <v>3.38</v>
       </c>
       <c r="P21">
-        <v>1.86</v>
+        <v>2.31</v>
       </c>
       <c r="Q21">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="R21">
         <v>2.01</v>
       </c>
       <c r="S21">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T21">
-        <v>2.57</v>
+        <v>2.99</v>
       </c>
       <c r="U21">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="V21">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z21">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA21">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB21">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AC21">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="AD21">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE21">
         <v>1.07</v>
       </c>
       <c r="AF21">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AG21">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="AK21">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.53</v>
+        <v>3.6</v>
       </c>
       <c r="O22">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="P22">
-        <v>2.31</v>
+        <v>1.86</v>
       </c>
       <c r="Q22">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="R22">
         <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="T22">
-        <v>2.99</v>
+        <v>2.57</v>
       </c>
       <c r="U22">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="V22">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W22">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z22">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AA22">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB22">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AC22">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AD22">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE22">
         <v>1.07</v>
       </c>
       <c r="AF22">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AG22">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="AK22">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="O57">
         <v>3.7</v>
       </c>
       <c r="P57">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="Q57">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="R57">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S57">
         <v>1.22</v>
       </c>
       <c r="T57">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="U57">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V57">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="W57">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z57">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA57">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AB57">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="AC57">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="AD57">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE57">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AF57">
         <v>1.45</v>
       </c>
       <c r="AG57">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK57">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="O58">
         <v>3.7</v>
       </c>
       <c r="P58">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="Q58">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="R58">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S58">
         <v>1.22</v>
       </c>
       <c r="T58">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="U58">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V58">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="W58">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X58">
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z58">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA58">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AB58">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="AC58">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="AD58">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE58">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AF58">
         <v>1.45</v>
       </c>
       <c r="AG58">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.29</v>
+        <v>2.9</v>
       </c>
       <c r="O96">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="P96">
-        <v>8.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q96">
-        <v>1.67</v>
+        <v>3.3</v>
       </c>
       <c r="R96">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S96">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T96">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="U96">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V96">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="W96">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X96">
         <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z96">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AA96">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB96">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="AC96">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="AD96">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AE96">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AF96">
-        <v>1.95</v>
+        <v>1.43</v>
       </c>
       <c r="AG96">
-        <v>1.76</v>
+        <v>2.66</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="AK96">
-        <v>3.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.9</v>
+        <v>1.29</v>
       </c>
       <c r="O97">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="P97">
-        <v>2.15</v>
+        <v>8.5</v>
       </c>
       <c r="Q97">
-        <v>3.3</v>
+        <v>1.67</v>
       </c>
       <c r="R97">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S97">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T97">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="U97">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V97">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="W97">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X97">
         <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z97">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AA97">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB97">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="AC97">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AD97">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AE97">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AF97">
-        <v>1.43</v>
+        <v>1.95</v>
       </c>
       <c r="AG97">
-        <v>2.66</v>
+        <v>1.76</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.67</v>
+        <v>1.04</v>
       </c>
       <c r="AK97">
-        <v>1.39</v>
+        <v>3.4</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q99">
-        <v>3.6</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="R99">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="S99">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="T99">
-        <v>2.19</v>
+        <v>2.88</v>
       </c>
       <c r="U99">
-        <v>3.35</v>
+        <v>2.83</v>
       </c>
       <c r="V99">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="W99">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X99">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y99">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="Z99">
-        <v>2.55</v>
+        <v>3.14</v>
       </c>
       <c r="AA99">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="AB99">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AC99">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="AD99">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AE99">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF99">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="AG99">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.34</v>
+        <v>3.2</v>
       </c>
       <c r="AK99">
-        <v>1.4</v>
+        <v>1.06</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,80 +16609,80 @@
         </is>
       </c>
       <c r="N100">
-        <v>8</v>
+        <v>3.7</v>
       </c>
       <c r="O100">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="P100">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="Q100">
-        <v>8.380000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="R100">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S100">
+        <v>1.5</v>
+      </c>
+      <c r="T100">
+        <v>2.29</v>
+      </c>
+      <c r="U100">
+        <v>3.44</v>
+      </c>
+      <c r="V100">
+        <v>1.23</v>
+      </c>
+      <c r="W100">
+        <v>1.04</v>
+      </c>
+      <c r="X100">
+        <v>1.07</v>
+      </c>
+      <c r="Y100">
+        <v>1.43</v>
+      </c>
+      <c r="Z100">
+        <v>2.7</v>
+      </c>
+      <c r="AA100">
+        <v>2.51</v>
+      </c>
+      <c r="AB100">
+        <v>1.48</v>
+      </c>
+      <c r="AC100">
+        <v>5</v>
+      </c>
+      <c r="AD100">
+        <v>1.12</v>
+      </c>
+      <c r="AE100">
+        <v>1.05</v>
+      </c>
+      <c r="AF100">
+        <v>2.09</v>
+      </c>
+      <c r="AG100">
+        <v>1.63</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ100">
         <v>1.36</v>
       </c>
-      <c r="T100">
-        <v>2.88</v>
-      </c>
-      <c r="U100">
-        <v>2.83</v>
-      </c>
-      <c r="V100">
-        <v>1.4</v>
-      </c>
-      <c r="W100">
-        <v>1.03</v>
-      </c>
-      <c r="X100">
-        <v>1.05</v>
-      </c>
-      <c r="Y100">
-        <v>1.27</v>
-      </c>
-      <c r="Z100">
-        <v>3.14</v>
-      </c>
-      <c r="AA100">
-        <v>2</v>
-      </c>
-      <c r="AB100">
-        <v>1.8</v>
-      </c>
-      <c r="AC100">
-        <v>3.5</v>
-      </c>
-      <c r="AD100">
-        <v>1.29</v>
-      </c>
-      <c r="AE100">
-        <v>1.04</v>
-      </c>
-      <c r="AF100">
-        <v>2.4</v>
-      </c>
-      <c r="AG100">
-        <v>1.5</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ100">
-        <v>3.2</v>
-      </c>
       <c r="AK100">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O101">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P101">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q101">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="R101">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="S101">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="T101">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="U101">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="V101">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W101">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X101">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y101">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="Z101">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AA101">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="AB101">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AC101">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AD101">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE101">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF101">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AG101">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK101">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O119">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="P119">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q119">
-        <v>1.46</v>
+        <v>3.25</v>
       </c>
       <c r="R119">
-        <v>2.97</v>
+        <v>2.18</v>
       </c>
       <c r="S119">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="T119">
-        <v>4.1</v>
+        <v>2.86</v>
       </c>
       <c r="U119">
-        <v>2.05</v>
+        <v>2.79</v>
       </c>
       <c r="V119">
-        <v>1.71</v>
+        <v>1.37</v>
       </c>
       <c r="W119">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="X119">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y119">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="Z119">
-        <v>5.7</v>
+        <v>3.25</v>
       </c>
       <c r="AA119">
-        <v>1.38</v>
+        <v>1.95</v>
       </c>
       <c r="AB119">
-        <v>2.62</v>
+        <v>1.73</v>
       </c>
       <c r="AC119">
-        <v>2.19</v>
+        <v>3.42</v>
       </c>
       <c r="AD119">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AE119">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AF119">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AG119">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AK119">
-        <v>4.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,80 +19869,80 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q120">
-        <v>3.25</v>
+        <v>1.46</v>
       </c>
       <c r="R120">
-        <v>2.18</v>
+        <v>2.97</v>
       </c>
       <c r="S120">
+        <v>1.14</v>
+      </c>
+      <c r="T120">
+        <v>4.1</v>
+      </c>
+      <c r="U120">
+        <v>2.05</v>
+      </c>
+      <c r="V120">
+        <v>1.71</v>
+      </c>
+      <c r="W120">
+        <v>1.17</v>
+      </c>
+      <c r="X120">
+        <v>1.01</v>
+      </c>
+      <c r="Y120">
+        <v>1.13</v>
+      </c>
+      <c r="Z120">
+        <v>5.7</v>
+      </c>
+      <c r="AA120">
         <v>1.38</v>
       </c>
-      <c r="T120">
-        <v>2.86</v>
-      </c>
-      <c r="U120">
-        <v>2.79</v>
-      </c>
-      <c r="V120">
-        <v>1.37</v>
-      </c>
-      <c r="W120">
-        <v>1.06</v>
-      </c>
-      <c r="X120">
-        <v>1.04</v>
-      </c>
-      <c r="Y120">
-        <v>1.28</v>
-      </c>
-      <c r="Z120">
-        <v>3.25</v>
-      </c>
-      <c r="AA120">
-        <v>1.95</v>
-      </c>
       <c r="AB120">
+        <v>2.62</v>
+      </c>
+      <c r="AC120">
+        <v>2.19</v>
+      </c>
+      <c r="AD120">
+        <v>1.68</v>
+      </c>
+      <c r="AE120">
+        <v>1.23</v>
+      </c>
+      <c r="AF120">
+        <v>2</v>
+      </c>
+      <c r="AG120">
         <v>1.73</v>
       </c>
-      <c r="AC120">
-        <v>3.42</v>
-      </c>
-      <c r="AD120">
-        <v>1.25</v>
-      </c>
-      <c r="AE120">
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ120">
         <v>1.1</v>
       </c>
-      <c r="AF120">
-        <v>1.75</v>
-      </c>
-      <c r="AG120">
-        <v>1.97</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ120">
-        <v>1.3</v>
-      </c>
       <c r="AK120">
-        <v>1.44</v>
+        <v>4.5</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -21858,16 +21858,16 @@
         <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z132">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AA132">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AB132">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="AC132">
         <v>2.31</v>
@@ -21882,7 +21882,7 @@
         <v>2</v>
       </c>
       <c r="AG132">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>2</v>
+        <v>1.39</v>
       </c>
       <c r="O157">
-        <v>3.58</v>
+        <v>5.1</v>
       </c>
       <c r="P157">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="Q157">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
       <c r="R157">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="S157">
+        <v>1.18</v>
+      </c>
+      <c r="T157">
+        <v>4.7</v>
+      </c>
+      <c r="U157">
+        <v>1.91</v>
+      </c>
+      <c r="V157">
+        <v>1.91</v>
+      </c>
+      <c r="W157">
+        <v>1.22</v>
+      </c>
+      <c r="X157">
+        <v>1.01</v>
+      </c>
+      <c r="Y157">
+        <v>1.05</v>
+      </c>
+      <c r="Z157">
+        <v>6.65</v>
+      </c>
+      <c r="AA157">
         <v>1.29</v>
       </c>
-      <c r="T157">
-        <v>3.3</v>
-      </c>
-      <c r="U157">
-        <v>2.28</v>
-      </c>
-      <c r="V157">
-        <v>1.54</v>
-      </c>
-      <c r="W157">
-        <v>1.12</v>
-      </c>
-      <c r="X157">
-        <v>1.02</v>
-      </c>
-      <c r="Y157">
-        <v>1.17</v>
-      </c>
-      <c r="Z157">
-        <v>4.4</v>
-      </c>
-      <c r="AA157">
-        <v>1.61</v>
-      </c>
       <c r="AB157">
-        <v>2.32</v>
+        <v>3.4</v>
       </c>
       <c r="AC157">
-        <v>2.48</v>
+        <v>1.8</v>
       </c>
       <c r="AD157">
-        <v>1.49</v>
+        <v>2.02</v>
       </c>
       <c r="AE157">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AF157">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AG157">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK157">
-        <v>1.73</v>
+        <v>2.82</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,80 +26063,80 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.39</v>
+        <v>2</v>
       </c>
       <c r="O158">
-        <v>5.1</v>
+        <v>3.58</v>
       </c>
       <c r="P158">
-        <v>5.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q158">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="R158">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="S158">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="T158">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="U158">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="V158">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="W158">
+        <v>1.12</v>
+      </c>
+      <c r="X158">
+        <v>1.02</v>
+      </c>
+      <c r="Y158">
+        <v>1.17</v>
+      </c>
+      <c r="Z158">
+        <v>4.4</v>
+      </c>
+      <c r="AA158">
+        <v>1.61</v>
+      </c>
+      <c r="AB158">
+        <v>2.32</v>
+      </c>
+      <c r="AC158">
+        <v>2.48</v>
+      </c>
+      <c r="AD158">
+        <v>1.49</v>
+      </c>
+      <c r="AE158">
+        <v>1.17</v>
+      </c>
+      <c r="AF158">
+        <v>1.51</v>
+      </c>
+      <c r="AG158">
+        <v>2.35</v>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ158">
         <v>1.22</v>
       </c>
-      <c r="X158">
-        <v>1.01</v>
-      </c>
-      <c r="Y158">
-        <v>1.05</v>
-      </c>
-      <c r="Z158">
-        <v>6.65</v>
-      </c>
-      <c r="AA158">
-        <v>1.29</v>
-      </c>
-      <c r="AB158">
-        <v>3.4</v>
-      </c>
-      <c r="AC158">
-        <v>1.8</v>
-      </c>
-      <c r="AD158">
-        <v>2.02</v>
-      </c>
-      <c r="AE158">
-        <v>1.4</v>
-      </c>
-      <c r="AF158">
-        <v>1.44</v>
-      </c>
-      <c r="AG158">
-        <v>2.62</v>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ158">
-        <v>1.11</v>
-      </c>
       <c r="AK158">
-        <v>2.82</v>
+        <v>1.73</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="O170">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="P170">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q170">
-        <v>1.75</v>
+        <v>2.03</v>
       </c>
       <c r="R170">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="S170">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="T170">
-        <v>5.5</v>
+        <v>6.05</v>
       </c>
       <c r="U170">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="V170">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="W170">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="X170">
+        <v>1</v>
+      </c>
+      <c r="Y170">
         <v>1.01</v>
       </c>
-      <c r="Y170">
-        <v>1.06</v>
-      </c>
       <c r="Z170">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA170">
+        <v>1.17</v>
+      </c>
+      <c r="AB170">
+        <v>4.33</v>
+      </c>
+      <c r="AC170">
+        <v>1.51</v>
+      </c>
+      <c r="AD170">
+        <v>2.43</v>
+      </c>
+      <c r="AE170">
+        <v>1.64</v>
+      </c>
+      <c r="AF170">
         <v>1.23</v>
       </c>
-      <c r="AB170">
-        <v>3.74</v>
-      </c>
-      <c r="AC170">
-        <v>1.6</v>
-      </c>
-      <c r="AD170">
-        <v>2.21</v>
-      </c>
-      <c r="AE170">
-        <v>1.5</v>
-      </c>
-      <c r="AF170">
-        <v>1.35</v>
-      </c>
       <c r="AG170">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK170">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="O172">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="P172">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q172">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="R172">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="S172">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="T172">
-        <v>6.05</v>
+        <v>5.5</v>
       </c>
       <c r="U172">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="V172">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="W172">
+        <v>1.3</v>
+      </c>
+      <c r="X172">
+        <v>1.01</v>
+      </c>
+      <c r="Y172">
+        <v>1.06</v>
+      </c>
+      <c r="Z172">
+        <v>9</v>
+      </c>
+      <c r="AA172">
+        <v>1.23</v>
+      </c>
+      <c r="AB172">
+        <v>3.74</v>
+      </c>
+      <c r="AC172">
+        <v>1.6</v>
+      </c>
+      <c r="AD172">
+        <v>2.21</v>
+      </c>
+      <c r="AE172">
+        <v>1.5</v>
+      </c>
+      <c r="AF172">
         <v>1.35</v>
       </c>
-      <c r="X172">
-        <v>1</v>
-      </c>
-      <c r="Y172">
-        <v>1.01</v>
-      </c>
-      <c r="Z172">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AA172">
-        <v>1.17</v>
-      </c>
-      <c r="AB172">
-        <v>4.33</v>
-      </c>
-      <c r="AC172">
-        <v>1.51</v>
-      </c>
-      <c r="AD172">
-        <v>2.43</v>
-      </c>
-      <c r="AE172">
-        <v>1.64</v>
-      </c>
-      <c r="AF172">
-        <v>1.23</v>
-      </c>
       <c r="AG172">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK172">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -43854,7 +43854,7 @@
         <v>3.5</v>
       </c>
       <c r="V267">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W267">
         <v>1.03</v>
@@ -43872,7 +43872,7 @@
         <v>2.29</v>
       </c>
       <c r="AB267">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC267">
         <v>4.5</v>
@@ -43903,7 +43903,7 @@
         <v>1.16</v>
       </c>
       <c r="AK267">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -46779,19 +46779,19 @@
         <v>1.89</v>
       </c>
       <c r="S285">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T285">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="U285">
         <v>3.24</v>
       </c>
       <c r="V285">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W285">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X285">
         <v>1.05</v>
@@ -46803,13 +46803,13 @@
         <v>2.56</v>
       </c>
       <c r="AA285">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AB285">
         <v>1.57</v>
       </c>
       <c r="AC285">
-        <v>4.42</v>
+        <v>4.5</v>
       </c>
       <c r="AD285">
         <v>1.17</v>
@@ -46818,10 +46818,10 @@
         <v>1.03</v>
       </c>
       <c r="AF285">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AG285">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,7 +46834,7 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AK285">
         <v>1.4</v>
@@ -47579,64 +47579,64 @@
         </is>
       </c>
       <c r="N290">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O290">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P290">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q290">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R290">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S290">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T290">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U290">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V290">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="W290">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X290">
         <v>0</v>
       </c>
       <c r="Y290">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z290">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA290">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB290">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AC290">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD290">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE290">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF290">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG290">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK290">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL290">
         <v>0</v>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -1332,7 +1332,7 @@
         <v>2.08</v>
       </c>
       <c r="AC6">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AD6">
         <v>1.35</v>
@@ -1344,7 +1344,7 @@
         <v>1.63</v>
       </c>
       <c r="AG6">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>2.1</v>
       </c>
       <c r="R9">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="S9">
         <v>1.25</v>
@@ -1797,43 +1797,43 @@
         <v>3.5</v>
       </c>
       <c r="U9">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="V9">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z9">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA9">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AB9">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="AC9">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AD9">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AE9">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AG9">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2117,22 +2117,22 @@
         <v>2.25</v>
       </c>
       <c r="S11">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T11">
         <v>3.4</v>
       </c>
       <c r="U11">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W11">
         <v>1.09</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
         <v>1.2</v>
@@ -2159,7 +2159,7 @@
         <v>1.54</v>
       </c>
       <c r="AG11">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AK11">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="O12">
         <v>4.3</v>
@@ -2274,7 +2274,7 @@
         <v>5.5</v>
       </c>
       <c r="Q12">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R12">
         <v>2.25</v>
@@ -2283,13 +2283,13 @@
         <v>1.3</v>
       </c>
       <c r="T12">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U12">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="V12">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W12">
         <v>1.08</v>
@@ -2298,31 +2298,31 @@
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z12">
-        <v>4.33</v>
+        <v>3.92</v>
       </c>
       <c r="AA12">
         <v>1.68</v>
       </c>
       <c r="AB12">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AC12">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD12">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE12">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF12">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG12">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="O13">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="P13">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2597,7 +2597,7 @@
         <v>3.1</v>
       </c>
       <c r="P14">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q14">
         <v>2.8</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="O15">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="P15">
-        <v>3.46</v>
+        <v>3.7</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB16">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="O17">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P17">
         <v>3.2</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="O18">
         <v>3.45</v>
@@ -3578,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="Q20">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="R20">
         <v>2.05</v>
@@ -3593,7 +3593,7 @@
         <v>3.18</v>
       </c>
       <c r="V20">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W20">
         <v>1.03</v>
@@ -3623,7 +3623,7 @@
         <v>1.01</v>
       </c>
       <c r="AF20">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG20">
         <v>1.75</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.53</v>
+        <v>3.6</v>
       </c>
       <c r="O21">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="P21">
-        <v>2.31</v>
+        <v>1.86</v>
       </c>
       <c r="Q21">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="R21">
         <v>2.01</v>
       </c>
       <c r="S21">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="T21">
-        <v>2.99</v>
+        <v>2.57</v>
       </c>
       <c r="U21">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="V21">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z21">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AA21">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB21">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AC21">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AD21">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE21">
         <v>1.07</v>
       </c>
       <c r="AF21">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AG21">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="AK21">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="O22">
-        <v>3.23</v>
+        <v>3.38</v>
       </c>
       <c r="P22">
-        <v>1.86</v>
+        <v>2.31</v>
       </c>
       <c r="Q22">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="R22">
         <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T22">
-        <v>2.57</v>
+        <v>2.99</v>
       </c>
       <c r="U22">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="V22">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X22">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z22">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA22">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB22">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AC22">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="AD22">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE22">
         <v>1.07</v>
       </c>
       <c r="AF22">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AG22">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="AK22">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,31 +4547,31 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q26">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="R26">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="S26">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="T26">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="U26">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="V26">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W26">
         <v>1.03</v>
@@ -4580,47 +4580,47 @@
         <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z26">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AA26">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AB26">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC26">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="AD26">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE26">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF26">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AG26">
+        <v>1.73</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>1.15</v>
+      </c>
+      <c r="AK26">
         <v>1.75</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.3</v>
-      </c>
-      <c r="AK26">
-        <v>1.55</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,10 +4719,10 @@
         <v>3.75</v>
       </c>
       <c r="Q27">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="R27">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S27">
         <v>1.44</v>
@@ -4731,7 +4731,7 @@
         <v>2.45</v>
       </c>
       <c r="U27">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="V27">
         <v>1.22</v>
@@ -4743,16 +4743,16 @@
         <v>1.07</v>
       </c>
       <c r="Y27">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="Z27">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AA27">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="AB27">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AC27">
         <v>4.6</v>
@@ -4783,7 +4783,7 @@
         <v>1.16</v>
       </c>
       <c r="AK27">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="R28">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="S28">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="T28">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="U28">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="V28">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W28">
         <v>1.03</v>
@@ -4906,47 +4906,47 @@
         <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z28">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AA28">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AB28">
+        <v>1.6</v>
+      </c>
+      <c r="AC28">
+        <v>3.98</v>
+      </c>
+      <c r="AD28">
+        <v>1.17</v>
+      </c>
+      <c r="AE28">
+        <v>1.03</v>
+      </c>
+      <c r="AF28">
+        <v>1.91</v>
+      </c>
+      <c r="AG28">
+        <v>1.75</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>1.3</v>
+      </c>
+      <c r="AK28">
         <v>1.55</v>
-      </c>
-      <c r="AC28">
-        <v>4.15</v>
-      </c>
-      <c r="AD28">
-        <v>1.16</v>
-      </c>
-      <c r="AE28">
-        <v>1.02</v>
-      </c>
-      <c r="AF28">
-        <v>2.04</v>
-      </c>
-      <c r="AG28">
-        <v>1.66</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.15</v>
-      </c>
-      <c r="AK28">
-        <v>1.75</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.21</v>
+        <v>2.79</v>
       </c>
       <c r="O29">
         <v>3.6</v>
@@ -5691,10 +5691,10 @@
         <v>1.75</v>
       </c>
       <c r="O33">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="P33">
-        <v>4.54</v>
+        <v>4.45</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="O35">
         <v>3.05</v>
       </c>
       <c r="P35">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6536,7 +6536,7 @@
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z38">
         <v>7.2</v>
@@ -6557,10 +6557,10 @@
         <v>1.4</v>
       </c>
       <c r="AF38">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG38">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6696,34 +6696,34 @@
         <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z39">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AA39">
         <v>1.96</v>
       </c>
       <c r="AB39">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC39">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AD39">
         <v>1.33</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG39">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.61</v>
       </c>
       <c r="AK39">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,22 +6829,22 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="O40">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P40">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="Q40">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="R40">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="S40">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T40">
         <v>2.58</v>
@@ -6856,22 +6856,22 @@
         <v>1.3</v>
       </c>
       <c r="W40">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X40">
         <v>1.05</v>
       </c>
       <c r="Y40">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z40">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="AA40">
         <v>2.2</v>
       </c>
       <c r="AB40">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AC40">
         <v>4.4</v>
@@ -6880,13 +6880,13 @@
         <v>1.18</v>
       </c>
       <c r="AE40">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF40">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG40">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -7031,22 +7031,22 @@
         <v>3.44</v>
       </c>
       <c r="AA41">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AB41">
         <v>2.01</v>
       </c>
       <c r="AC41">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="AD41">
         <v>1.33</v>
       </c>
       <c r="AE41">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF41">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG41">
         <v>2.25</v>
@@ -7324,7 +7324,7 @@
         <v>4.2</v>
       </c>
       <c r="P43">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="Q43">
         <v>5</v>
@@ -7333,49 +7333,49 @@
         <v>2.4</v>
       </c>
       <c r="S43">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="T43">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="U43">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V43">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="W43">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z43">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA43">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AB43">
-        <v>2.21</v>
+        <v>1.98</v>
       </c>
       <c r="AC43">
         <v>2.28</v>
       </c>
       <c r="AD43">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AE43">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF43">
         <v>1.57</v>
       </c>
       <c r="AG43">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7493,13 +7493,13 @@
         <v>4</v>
       </c>
       <c r="R44">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="S44">
         <v>1.34</v>
       </c>
       <c r="T44">
-        <v>3.2</v>
+        <v>2.36</v>
       </c>
       <c r="U44">
         <v>2.5</v>
@@ -7511,13 +7511,13 @@
         <v>1.07</v>
       </c>
       <c r="X44">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z44">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA44">
         <v>1.81</v>
@@ -7526,10 +7526,10 @@
         <v>2</v>
       </c>
       <c r="AC44">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="AD44">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE44">
         <v>1.14</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O49">
         <v>2.9</v>
       </c>
       <c r="P49">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8652,7 +8652,7 @@
         <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
         <v>1.22</v>
@@ -8664,10 +8664,10 @@
         <v>1.71</v>
       </c>
       <c r="AB51">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC51">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="AD51">
         <v>1.36</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AK51">
         <v>1.23</v>
@@ -8948,22 +8948,22 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="O53">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P53">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="Q53">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="R53">
         <v>2.19</v>
       </c>
       <c r="S53">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T53">
         <v>3.25</v>
@@ -8981,7 +8981,7 @@
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z53">
         <v>4.25</v>
@@ -8990,13 +8990,13 @@
         <v>1.57</v>
       </c>
       <c r="AB53">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC53">
         <v>2.46</v>
       </c>
       <c r="AD53">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE53">
         <v>1.14</v>
@@ -9005,7 +9005,7 @@
         <v>1.5</v>
       </c>
       <c r="AG53">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.35</v>
       </c>
       <c r="AK53">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9120,7 +9120,7 @@
         <v>1.42</v>
       </c>
       <c r="Q54">
-        <v>5.51</v>
+        <v>5</v>
       </c>
       <c r="R54">
         <v>2.41</v>
@@ -9132,7 +9132,7 @@
         <v>3.25</v>
       </c>
       <c r="U54">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V54">
         <v>1.5</v>
@@ -9144,10 +9144,10 @@
         <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z54">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="AA54">
         <v>1.66</v>
@@ -9159,7 +9159,7 @@
         <v>2.69</v>
       </c>
       <c r="AD54">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE54">
         <v>1.12</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>2.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK54">
         <v>1.08</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="O57">
         <v>3.7</v>
       </c>
       <c r="P57">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="Q57">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="R57">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S57">
         <v>1.22</v>
       </c>
       <c r="T57">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="U57">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V57">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="W57">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z57">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA57">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AB57">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="AC57">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="AD57">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE57">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AF57">
         <v>1.45</v>
       </c>
       <c r="AG57">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK57">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="O58">
         <v>3.7</v>
       </c>
       <c r="P58">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="Q58">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="R58">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S58">
         <v>1.22</v>
       </c>
       <c r="T58">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="U58">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V58">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="W58">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X58">
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z58">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA58">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AB58">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="AC58">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="AD58">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE58">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AF58">
         <v>1.45</v>
       </c>
       <c r="AG58">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK58">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="N60">
-        <v>4.9</v>
+        <v>5.15</v>
       </c>
       <c r="O60">
         <v>4.05</v>
@@ -10098,7 +10098,7 @@
         <v>1.58</v>
       </c>
       <c r="Q60">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="R60">
         <v>2.29</v>
@@ -10110,40 +10110,40 @@
         <v>3.18</v>
       </c>
       <c r="U60">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="V60">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W60">
         <v>1.07</v>
       </c>
       <c r="X60">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="Z60">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="AA60">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB60">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AC60">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD60">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE60">
         <v>1.1</v>
       </c>
       <c r="AF60">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG60">
         <v>2.01</v>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK60">
         <v>1.16</v>
@@ -10261,13 +10261,13 @@
         <v>2.95</v>
       </c>
       <c r="Q61">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="R61">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S61">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T61">
         <v>3.1</v>
@@ -10282,10 +10282,10 @@
         <v>1.1</v>
       </c>
       <c r="X61">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z61">
         <v>3.7</v>
@@ -10303,13 +10303,13 @@
         <v>1.38</v>
       </c>
       <c r="AE61">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF61">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AG61">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.25</v>
       </c>
       <c r="AK61">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -11595,16 +11595,16 @@
         <v>4.85</v>
       </c>
       <c r="AA69">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB69">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AC69">
         <v>2.22</v>
       </c>
       <c r="AD69">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE69">
         <v>1.19</v>
@@ -11731,13 +11731,13 @@
         <v>3.1</v>
       </c>
       <c r="R70">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S70">
         <v>1.4</v>
       </c>
       <c r="T70">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="U70">
         <v>3.3</v>
@@ -11746,31 +11746,31 @@
         <v>1.29</v>
       </c>
       <c r="W70">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X70">
         <v>1.04</v>
       </c>
       <c r="Y70">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z70">
         <v>2.81</v>
       </c>
       <c r="AA70">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB70">
         <v>1.6</v>
       </c>
       <c r="AC70">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="AD70">
         <v>1.17</v>
       </c>
       <c r="AE70">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF70">
         <v>1.84</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK70">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="O71">
         <v>3.4</v>
@@ -11906,7 +11906,7 @@
         <v>2.45</v>
       </c>
       <c r="V71">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W71">
         <v>1.08</v>
@@ -12066,13 +12066,13 @@
         <v>3.12</v>
       </c>
       <c r="U72">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V72">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W72">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X72">
         <v>1.01</v>
@@ -12081,19 +12081,19 @@
         <v>1.16</v>
       </c>
       <c r="Z72">
-        <v>4.54</v>
+        <v>4.4</v>
       </c>
       <c r="AA72">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB72">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AC72">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="AD72">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE72">
         <v>1.17</v>
@@ -12118,7 +12118,7 @@
         <v>1.22</v>
       </c>
       <c r="AK72">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12386,10 +12386,10 @@
         <v>2.11</v>
       </c>
       <c r="S74">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T74">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="U74">
         <v>2.89</v>
@@ -12398,10 +12398,10 @@
         <v>1.33</v>
       </c>
       <c r="W74">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X74">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y74">
         <v>1.28</v>
@@ -12410,19 +12410,19 @@
         <v>3.08</v>
       </c>
       <c r="AA74">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AB74">
         <v>1.72</v>
       </c>
       <c r="AC74">
-        <v>3.43</v>
+        <v>3.52</v>
       </c>
       <c r="AD74">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE74">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF74">
         <v>2.08</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="O76">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="P76">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="Q76">
         <v>3.1</v>
@@ -12736,7 +12736,7 @@
         <v>3.42</v>
       </c>
       <c r="AA76">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB76">
         <v>1.9</v>
@@ -12748,7 +12748,7 @@
         <v>1.31</v>
       </c>
       <c r="AE76">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF76">
         <v>1.65</v>
@@ -12869,55 +12869,55 @@
         <v>0</v>
       </c>
       <c r="Q77">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R77">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="S77">
         <v>1.43</v>
       </c>
       <c r="T77">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="U77">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="V77">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W77">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X77">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z77">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AA77">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AB77">
         <v>1.65</v>
       </c>
       <c r="AC77">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AD77">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE77">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF77">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG77">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK77">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,7 +13023,7 @@
         </is>
       </c>
       <c r="N78">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O78">
         <v>3.4</v>
@@ -13032,22 +13032,22 @@
         <v>1.91</v>
       </c>
       <c r="Q78">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="R78">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S78">
         <v>1.36</v>
       </c>
       <c r="T78">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="U78">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="V78">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W78">
         <v>1.07</v>
@@ -13056,10 +13056,10 @@
         <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z78">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA78">
         <v>1.85</v>
@@ -13068,7 +13068,7 @@
         <v>1.95</v>
       </c>
       <c r="AC78">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="AD78">
         <v>1.33</v>
@@ -13080,7 +13080,7 @@
         <v>1.65</v>
       </c>
       <c r="AG78">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.69</v>
+        <v>1.25</v>
       </c>
       <c r="AK78">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13391,7 +13391,7 @@
         <v>1.9</v>
       </c>
       <c r="AB80">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AC80">
         <v>3.14</v>
@@ -13853,10 +13853,10 @@
         <v>2</v>
       </c>
       <c r="S83">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T83">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="U83">
         <v>3.25</v>
@@ -13868,13 +13868,13 @@
         <v>1.01</v>
       </c>
       <c r="X83">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y83">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Z83">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AA83">
         <v>2.25</v>
@@ -13883,10 +13883,10 @@
         <v>1.61</v>
       </c>
       <c r="AC83">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AD83">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE83">
         <v>1.01</v>
@@ -13895,7 +13895,7 @@
         <v>2.03</v>
       </c>
       <c r="AG83">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>1.24</v>
       </c>
       <c r="T86">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="U86">
         <v>2.31</v>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK86">
         <v>1.57</v>
@@ -14499,7 +14499,7 @@
         <v>2.15</v>
       </c>
       <c r="Q87">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="R87">
         <v>2.75</v>
@@ -14508,7 +14508,7 @@
         <v>1.15</v>
       </c>
       <c r="T87">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="U87">
         <v>1.76</v>
@@ -14517,7 +14517,7 @@
         <v>1.95</v>
       </c>
       <c r="W87">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X87">
         <v>1.01</v>
@@ -14529,10 +14529,10 @@
         <v>8.5</v>
       </c>
       <c r="AA87">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AB87">
-        <v>3.63</v>
+        <v>3.66</v>
       </c>
       <c r="AC87">
         <v>1.7</v>
@@ -14674,7 +14674,7 @@
         <v>4.95</v>
       </c>
       <c r="U88">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V88">
         <v>1.95</v>
@@ -14695,7 +14695,7 @@
         <v>1.25</v>
       </c>
       <c r="AB88">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="AC88">
         <v>1.76</v>
@@ -14704,7 +14704,7 @@
         <v>2.1</v>
       </c>
       <c r="AE88">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AF88">
         <v>1.57</v>
@@ -14825,52 +14825,52 @@
         <v>0</v>
       </c>
       <c r="Q89">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="R89">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="S89">
         <v>1.43</v>
       </c>
       <c r="T89">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="U89">
-        <v>2.86</v>
+        <v>3.09</v>
       </c>
       <c r="V89">
         <v>1.33</v>
       </c>
       <c r="W89">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X89">
         <v>1.04</v>
       </c>
       <c r="Y89">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z89">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AA89">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB89">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC89">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AD89">
         <v>1.21</v>
       </c>
       <c r="AE89">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF89">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG89">
         <v>1.83</v>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK89">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14982,61 +14982,61 @@
         <v>2.7</v>
       </c>
       <c r="O90">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P90">
         <v>2.37</v>
       </c>
       <c r="Q90">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R90">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S90">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T90">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="U90">
         <v>2.78</v>
       </c>
       <c r="V90">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W90">
         <v>1.05</v>
       </c>
       <c r="X90">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z90">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA90">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB90">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC90">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD90">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE90">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF90">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AG90">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK90">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15480,19 +15480,19 @@
         <v>2.38</v>
       </c>
       <c r="R93">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S93">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T93">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="U93">
         <v>2.5</v>
       </c>
       <c r="V93">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W93">
         <v>1.07</v>
@@ -15504,19 +15504,19 @@
         <v>1.22</v>
       </c>
       <c r="Z93">
-        <v>3.72</v>
+        <v>3.78</v>
       </c>
       <c r="AA93">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB93">
         <v>2</v>
       </c>
       <c r="AC93">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD93">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE93">
         <v>1.14</v>
@@ -15670,7 +15670,7 @@
         <v>2.7</v>
       </c>
       <c r="AA94">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AB94">
         <v>1.61</v>
@@ -15679,7 +15679,7 @@
         <v>4.5</v>
       </c>
       <c r="AD94">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE94">
         <v>1.03</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.9</v>
+        <v>1.29</v>
       </c>
       <c r="O96">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="P96">
-        <v>2.15</v>
+        <v>8.5</v>
       </c>
       <c r="Q96">
-        <v>3.3</v>
+        <v>1.67</v>
       </c>
       <c r="R96">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S96">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T96">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="U96">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V96">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="W96">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X96">
         <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z96">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AA96">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB96">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="AC96">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AD96">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AE96">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AF96">
-        <v>1.43</v>
+        <v>1.95</v>
       </c>
       <c r="AG96">
-        <v>2.66</v>
+        <v>1.76</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.67</v>
+        <v>1.04</v>
       </c>
       <c r="AK96">
-        <v>1.39</v>
+        <v>3.4</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.29</v>
+        <v>2.9</v>
       </c>
       <c r="O97">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="P97">
-        <v>8.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q97">
-        <v>1.67</v>
+        <v>3.3</v>
       </c>
       <c r="R97">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S97">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T97">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="U97">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V97">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="W97">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X97">
         <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z97">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AA97">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB97">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="AC97">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="AD97">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AE97">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AF97">
-        <v>1.95</v>
+        <v>1.43</v>
       </c>
       <c r="AG97">
-        <v>1.76</v>
+        <v>2.66</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="AK97">
-        <v>3.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,80 +16446,80 @@
         </is>
       </c>
       <c r="N99">
-        <v>8</v>
+        <v>3.7</v>
       </c>
       <c r="O99">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="P99">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="Q99">
-        <v>8.380000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="R99">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S99">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="T99">
-        <v>2.88</v>
+        <v>2.39</v>
       </c>
       <c r="U99">
-        <v>2.83</v>
+        <v>3.44</v>
       </c>
       <c r="V99">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="W99">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X99">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y99">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="Z99">
-        <v>3.14</v>
+        <v>2.54</v>
       </c>
       <c r="AA99">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="AB99">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AC99">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="AD99">
+        <v>1.13</v>
+      </c>
+      <c r="AE99">
+        <v>1.02</v>
+      </c>
+      <c r="AF99">
+        <v>2.09</v>
+      </c>
+      <c r="AG99">
+        <v>1.63</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ99">
         <v>1.29</v>
       </c>
-      <c r="AE99">
-        <v>1.04</v>
-      </c>
-      <c r="AF99">
-        <v>2.4</v>
-      </c>
-      <c r="AG99">
-        <v>1.5</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ99">
-        <v>3.2</v>
-      </c>
       <c r="AK99">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O100">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P100">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q100">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="R100">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="S100">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="T100">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="U100">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="V100">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W100">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X100">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y100">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="Z100">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="AA100">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="AB100">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AC100">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AD100">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AE100">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF100">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AG100">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK100">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,65 +16772,65 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q101">
-        <v>3.6</v>
+        <v>8.16</v>
       </c>
       <c r="R101">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="S101">
+        <v>1.36</v>
+      </c>
+      <c r="T101">
+        <v>2.66</v>
+      </c>
+      <c r="U101">
+        <v>2.8</v>
+      </c>
+      <c r="V101">
+        <v>1.4</v>
+      </c>
+      <c r="W101">
+        <v>1.05</v>
+      </c>
+      <c r="X101">
+        <v>1.03</v>
+      </c>
+      <c r="Y101">
+        <v>1.27</v>
+      </c>
+      <c r="Z101">
+        <v>3.14</v>
+      </c>
+      <c r="AA101">
+        <v>1.95</v>
+      </c>
+      <c r="AB101">
+        <v>1.77</v>
+      </c>
+      <c r="AC101">
+        <v>3.34</v>
+      </c>
+      <c r="AD101">
+        <v>1.24</v>
+      </c>
+      <c r="AE101">
+        <v>1.06</v>
+      </c>
+      <c r="AF101">
+        <v>2.5</v>
+      </c>
+      <c r="AG101">
         <v>1.53</v>
       </c>
-      <c r="T101">
-        <v>2.19</v>
-      </c>
-      <c r="U101">
-        <v>3.35</v>
-      </c>
-      <c r="V101">
-        <v>1.24</v>
-      </c>
-      <c r="W101">
-        <v>1.02</v>
-      </c>
-      <c r="X101">
-        <v>1.08</v>
-      </c>
-      <c r="Y101">
-        <v>1.54</v>
-      </c>
-      <c r="Z101">
-        <v>2.55</v>
-      </c>
-      <c r="AA101">
-        <v>2.62</v>
-      </c>
-      <c r="AB101">
-        <v>1.44</v>
-      </c>
-      <c r="AC101">
-        <v>5.5</v>
-      </c>
-      <c r="AD101">
-        <v>1.11</v>
-      </c>
-      <c r="AE101">
-        <v>1.02</v>
-      </c>
-      <c r="AF101">
-        <v>2.12</v>
-      </c>
-      <c r="AG101">
-        <v>1.61</v>
-      </c>
       <c r="AH101" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.34</v>
+        <v>3.2</v>
       </c>
       <c r="AK101">
-        <v>1.4</v>
+        <v>1.06</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -18426,7 +18426,7 @@
         <v>2.93</v>
       </c>
       <c r="V111">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W111">
         <v>1.06</v>
@@ -18447,19 +18447,19 @@
         <v>1.7</v>
       </c>
       <c r="AC111">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="AD111">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE111">
         <v>1.05</v>
       </c>
       <c r="AF111">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG111">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK111">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18755,10 +18755,10 @@
         <v>1.51</v>
       </c>
       <c r="W113">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X113">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y113">
         <v>1.17</v>
@@ -19081,7 +19081,7 @@
         <v>1.7</v>
       </c>
       <c r="W115">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X115">
         <v>1</v>
@@ -19099,7 +19099,7 @@
         <v>2.55</v>
       </c>
       <c r="AC115">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AD115">
         <v>1.78</v>
@@ -19111,7 +19111,7 @@
         <v>1.55</v>
       </c>
       <c r="AG115">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>2.45</v>
       </c>
       <c r="Q116">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="R116">
         <v>1.95</v>
@@ -19253,7 +19253,7 @@
         <v>1.48</v>
       </c>
       <c r="Z116">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="AA116">
         <v>2.29</v>
@@ -19287,7 +19287,7 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AK116">
         <v>1.4</v>
@@ -19416,7 +19416,7 @@
         <v>1.06</v>
       </c>
       <c r="Z117">
-        <v>6.25</v>
+        <v>6.3</v>
       </c>
       <c r="AA117">
         <v>1.31</v>
@@ -19425,7 +19425,7 @@
         <v>3.08</v>
       </c>
       <c r="AC117">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AD117">
         <v>2</v>
@@ -19453,7 +19453,7 @@
         <v>1.26</v>
       </c>
       <c r="AK117">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -20361,40 +20361,40 @@
         <v>7.75</v>
       </c>
       <c r="O123">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="P123">
         <v>1.37</v>
       </c>
       <c r="Q123">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="R123">
         <v>2.16</v>
       </c>
       <c r="S123">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T123">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="U123">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="V123">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W123">
         <v>1.06</v>
       </c>
       <c r="X123">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y123">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z123">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA123">
         <v>1.86</v>
@@ -20406,7 +20406,7 @@
         <v>3.4</v>
       </c>
       <c r="AD123">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE123">
         <v>1.1</v>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK123">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21200,16 +21200,16 @@
         <v>1.49</v>
       </c>
       <c r="W128">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X128">
         <v>1.02</v>
       </c>
       <c r="Y128">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z128">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="AA128">
         <v>1.72</v>
@@ -21221,10 +21221,10 @@
         <v>2.69</v>
       </c>
       <c r="AD128">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE128">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF128">
         <v>1.67</v>
@@ -21345,13 +21345,13 @@
         <v>4.3</v>
       </c>
       <c r="Q129">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="R129">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="S129">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T129">
         <v>3.2</v>
@@ -21366,7 +21366,7 @@
         <v>1.07</v>
       </c>
       <c r="X129">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y129">
         <v>1.22</v>
@@ -21375,10 +21375,10 @@
         <v>3.5</v>
       </c>
       <c r="AA129">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AB129">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AC129">
         <v>2.83</v>
@@ -21387,13 +21387,13 @@
         <v>1.33</v>
       </c>
       <c r="AE129">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF129">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AG129">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="O130">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P130">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -22000,19 +22000,19 @@
         <v>2.03</v>
       </c>
       <c r="R133">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="S133">
         <v>1.22</v>
       </c>
       <c r="T133">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="U133">
         <v>2.02</v>
       </c>
       <c r="V133">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="W133">
         <v>1.17</v>
@@ -22024,7 +22024,7 @@
         <v>1.09</v>
       </c>
       <c r="Z133">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AA133">
         <v>1.44</v>
@@ -22033,19 +22033,19 @@
         <v>2.7</v>
       </c>
       <c r="AC133">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AD133">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AE133">
         <v>1.26</v>
       </c>
       <c r="AF133">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AG133">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK133">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -23790,10 +23790,10 @@
         <v>0</v>
       </c>
       <c r="Q144">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R144">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="S144">
         <v>1.33</v>
@@ -23826,16 +23826,16 @@
         <v>2.05</v>
       </c>
       <c r="AC144">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AD144">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE144">
         <v>1.1</v>
       </c>
       <c r="AF144">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG144">
         <v>2.15</v>
@@ -23854,7 +23854,7 @@
         <v>1.24</v>
       </c>
       <c r="AK144">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -24279,13 +24279,13 @@
         <v>1.53</v>
       </c>
       <c r="Q147">
-        <v>6.48</v>
+        <v>6</v>
       </c>
       <c r="R147">
         <v>2.26</v>
       </c>
       <c r="S147">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T147">
         <v>2.67</v>
@@ -24294,10 +24294,10 @@
         <v>2.88</v>
       </c>
       <c r="V147">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W147">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X147">
         <v>1.01</v>
@@ -24306,13 +24306,13 @@
         <v>1.28</v>
       </c>
       <c r="Z147">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA147">
         <v>2.01</v>
       </c>
       <c r="AB147">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC147">
         <v>3.34</v>
@@ -24324,10 +24324,10 @@
         <v>1.08</v>
       </c>
       <c r="AF147">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG147">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24442,25 +24442,25 @@
         <v>3.54</v>
       </c>
       <c r="Q148">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="R148">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="S148">
         <v>1.14</v>
       </c>
       <c r="T148">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="U148">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V148">
         <v>1.85</v>
       </c>
       <c r="W148">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X148">
         <v>1.01</v>
@@ -24472,22 +24472,22 @@
         <v>7.5</v>
       </c>
       <c r="AA148">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB148">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AC148">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AD148">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AE148">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AF148">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AG148">
         <v>3.2</v>
@@ -24503,7 +24503,7 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK148">
         <v>1.83</v>
@@ -24599,10 +24599,10 @@
         <v>2.85</v>
       </c>
       <c r="O149">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P149">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="Q149">
         <v>3.04</v>
@@ -24611,7 +24611,7 @@
         <v>2.63</v>
       </c>
       <c r="S149">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T149">
         <v>4.6</v>
@@ -24632,10 +24632,10 @@
         <v>1.05</v>
       </c>
       <c r="Z149">
-        <v>6.6</v>
+        <v>6.65</v>
       </c>
       <c r="AA149">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AB149">
         <v>3.05</v>
@@ -24653,7 +24653,7 @@
         <v>1.33</v>
       </c>
       <c r="AG149">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK149">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -25248,10 +25248,10 @@
         </is>
       </c>
       <c r="N153">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="O153">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="P153">
         <v>1.67</v>
@@ -26235,10 +26235,10 @@
         <v>1.32</v>
       </c>
       <c r="Q159">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="R159">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="S159">
         <v>1.31</v>
@@ -26262,10 +26262,10 @@
         <v>1.19</v>
       </c>
       <c r="Z159">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AA159">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB159">
         <v>2.07</v>
@@ -26274,16 +26274,16 @@
         <v>2.62</v>
       </c>
       <c r="AD159">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE159">
         <v>1.12</v>
       </c>
       <c r="AF159">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AG159">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="O164">
         <v>2.95</v>
@@ -27533,10 +27533,10 @@
         <v>1.8</v>
       </c>
       <c r="O167">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P167">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27699,7 +27699,7 @@
         <v>2.9</v>
       </c>
       <c r="P168">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="O170">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="P170">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q170">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="R170">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="S170">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="T170">
-        <v>6.05</v>
+        <v>5.5</v>
       </c>
       <c r="U170">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="V170">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="W170">
+        <v>1.3</v>
+      </c>
+      <c r="X170">
+        <v>1.01</v>
+      </c>
+      <c r="Y170">
+        <v>1.06</v>
+      </c>
+      <c r="Z170">
+        <v>9</v>
+      </c>
+      <c r="AA170">
+        <v>1.23</v>
+      </c>
+      <c r="AB170">
+        <v>3.74</v>
+      </c>
+      <c r="AC170">
+        <v>1.6</v>
+      </c>
+      <c r="AD170">
+        <v>2.21</v>
+      </c>
+      <c r="AE170">
+        <v>1.5</v>
+      </c>
+      <c r="AF170">
         <v>1.35</v>
       </c>
-      <c r="X170">
-        <v>1</v>
-      </c>
-      <c r="Y170">
-        <v>1.01</v>
-      </c>
-      <c r="Z170">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AA170">
-        <v>1.17</v>
-      </c>
-      <c r="AB170">
-        <v>4.33</v>
-      </c>
-      <c r="AC170">
-        <v>1.51</v>
-      </c>
-      <c r="AD170">
-        <v>2.43</v>
-      </c>
-      <c r="AE170">
-        <v>1.64</v>
-      </c>
-      <c r="AF170">
-        <v>1.23</v>
-      </c>
       <c r="AG170">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK170">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="O172">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="P172">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q172">
-        <v>1.75</v>
+        <v>2.03</v>
       </c>
       <c r="R172">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="S172">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="T172">
-        <v>5.5</v>
+        <v>6.05</v>
       </c>
       <c r="U172">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="V172">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="W172">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="X172">
+        <v>1</v>
+      </c>
+      <c r="Y172">
         <v>1.01</v>
       </c>
-      <c r="Y172">
-        <v>1.06</v>
-      </c>
       <c r="Z172">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA172">
+        <v>1.17</v>
+      </c>
+      <c r="AB172">
+        <v>4.33</v>
+      </c>
+      <c r="AC172">
+        <v>1.51</v>
+      </c>
+      <c r="AD172">
+        <v>2.43</v>
+      </c>
+      <c r="AE172">
+        <v>1.64</v>
+      </c>
+      <c r="AF172">
         <v>1.23</v>
       </c>
-      <c r="AB172">
-        <v>3.74</v>
-      </c>
-      <c r="AC172">
-        <v>1.6</v>
-      </c>
-      <c r="AD172">
-        <v>2.21</v>
-      </c>
-      <c r="AE172">
-        <v>1.5</v>
-      </c>
-      <c r="AF172">
-        <v>1.35</v>
-      </c>
       <c r="AG172">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK172">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -29012,7 +29012,7 @@
         <v>2.01</v>
       </c>
       <c r="S176">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T176">
         <v>2.88</v>
@@ -29021,7 +29021,7 @@
         <v>2.75</v>
       </c>
       <c r="V176">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W176">
         <v>1.07</v>
@@ -29033,7 +29033,7 @@
         <v>1.24</v>
       </c>
       <c r="Z176">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="AA176">
         <v>1.95</v>
@@ -29329,7 +29329,7 @@
         <v>3.2</v>
       </c>
       <c r="P178">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q178">
         <v>2.58</v>
@@ -29350,22 +29350,22 @@
         <v>1.36</v>
       </c>
       <c r="W178">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X178">
         <v>1.02</v>
       </c>
       <c r="Y178">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z178">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AA178">
         <v>2.02</v>
       </c>
       <c r="AB178">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC178">
         <v>3.28</v>
@@ -29377,10 +29377,10 @@
         <v>1.06</v>
       </c>
       <c r="AF178">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG178">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>1.19</v>
       </c>
       <c r="AK178">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29661,13 +29661,13 @@
         <v>2.5</v>
       </c>
       <c r="R180">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S180">
         <v>1.25</v>
       </c>
       <c r="T180">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U180">
         <v>2.32</v>
@@ -29682,13 +29682,13 @@
         <v>1.01</v>
       </c>
       <c r="Y180">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z180">
         <v>4.33</v>
       </c>
       <c r="AA180">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB180">
         <v>2.15</v>
@@ -29836,10 +29836,10 @@
         <v>3.42</v>
       </c>
       <c r="V181">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W181">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X181">
         <v>1.07</v>
@@ -29848,7 +29848,7 @@
         <v>1.45</v>
       </c>
       <c r="Z181">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AA181">
         <v>2.46</v>
@@ -29869,7 +29869,7 @@
         <v>2.05</v>
       </c>
       <c r="AG181">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK181">
         <v>1.62</v>
@@ -30144,7 +30144,7 @@
         <v>3.5</v>
       </c>
       <c r="P183">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O185">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P185">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q185">
         <v>2.24</v>
@@ -30479,7 +30479,7 @@
         <v>2.09</v>
       </c>
       <c r="S185">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T185">
         <v>2.83</v>
@@ -30503,7 +30503,7 @@
         <v>3.28</v>
       </c>
       <c r="AA185">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB185">
         <v>1.79</v>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK185">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30636,22 +30636,22 @@
         <v>3.8</v>
       </c>
       <c r="Q186">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="R186">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="S186">
         <v>1.4</v>
       </c>
       <c r="T186">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="U186">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="V186">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W186">
         <v>1.06</v>
@@ -30660,10 +30660,10 @@
         <v>1.02</v>
       </c>
       <c r="Y186">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z186">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA186">
         <v>2.1</v>
@@ -30672,19 +30672,19 @@
         <v>1.73</v>
       </c>
       <c r="AC186">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD186">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE186">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF186">
         <v>1.85</v>
       </c>
       <c r="AG186">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK186">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30790,25 +30790,25 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O187">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P187">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q187">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="R187">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="S187">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T187">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="U187">
         <v>2.89</v>
@@ -30826,10 +30826,10 @@
         <v>1.3</v>
       </c>
       <c r="Z187">
-        <v>2.92</v>
+        <v>3.32</v>
       </c>
       <c r="AA187">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AB187">
         <v>1.74</v>
@@ -30838,13 +30838,13 @@
         <v>3.34</v>
       </c>
       <c r="AD187">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE187">
         <v>1.05</v>
       </c>
       <c r="AF187">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG187">
         <v>1.93</v>
@@ -30860,7 +30860,7 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AK187">
         <v>1.44</v>
@@ -30968,7 +30968,7 @@
         <v>2.4</v>
       </c>
       <c r="S188">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T188">
         <v>3.8</v>
@@ -31768,10 +31768,10 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="O193">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P193">
         <v>3.2</v>
@@ -31783,28 +31783,28 @@
         <v>1.94</v>
       </c>
       <c r="S193">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="T193">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="U193">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="V193">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W193">
         <v>1.02</v>
       </c>
       <c r="X193">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y193">
         <v>1.4</v>
       </c>
       <c r="Z193">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AA193">
         <v>2.25</v>
@@ -31813,19 +31813,19 @@
         <v>1.61</v>
       </c>
       <c r="AC193">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="AD193">
         <v>1.17</v>
       </c>
       <c r="AE193">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF193">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG193">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AK193">
         <v>1.62</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="O197">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="P197">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q197">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="R197">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="S197">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T197">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="U197">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="V197">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="W197">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="X197">
         <v>1.01</v>
       </c>
       <c r="Y197">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Z197">
-        <v>6.32</v>
+        <v>7.3</v>
       </c>
       <c r="AA197">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AB197">
-        <v>2.93</v>
+        <v>3.34</v>
       </c>
       <c r="AC197">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AD197">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AE197">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AF197">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AG197">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK197">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="O198">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P198">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q198">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="R198">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="S198">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T198">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="U198">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="V198">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="W198">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="X198">
         <v>1.01</v>
       </c>
       <c r="Y198">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Z198">
-        <v>7.3</v>
+        <v>6.32</v>
       </c>
       <c r="AA198">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AB198">
-        <v>3.34</v>
+        <v>2.93</v>
       </c>
       <c r="AC198">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AD198">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AE198">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AF198">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AG198">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK198">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -33413,7 +33413,7 @@
         <v>2.38</v>
       </c>
       <c r="S203">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T203">
         <v>3.8</v>
@@ -33425,37 +33425,37 @@
         <v>1.65</v>
       </c>
       <c r="W203">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X203">
         <v>1.02</v>
       </c>
       <c r="Y203">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z203">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AA203">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AB203">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="AC203">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="AD203">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AE203">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AF203">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG203">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33564,10 +33564,10 @@
         <v>2.23</v>
       </c>
       <c r="O204">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="P204">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -33887,7 +33887,7 @@
         </is>
       </c>
       <c r="N206">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="O206">
         <v>5.2</v>
@@ -33920,7 +33920,7 @@
         <v>1.02</v>
       </c>
       <c r="Y206">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z206">
         <v>4.5</v>
@@ -33929,13 +33929,13 @@
         <v>1.52</v>
       </c>
       <c r="AB206">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="AC206">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AD206">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE206">
         <v>1.16</v>
@@ -33957,7 +33957,7 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK206">
         <v>3.18</v>
@@ -34074,7 +34074,7 @@
         <v>2.6</v>
       </c>
       <c r="V207">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W207">
         <v>1.07</v>
@@ -34086,13 +34086,13 @@
         <v>1.24</v>
       </c>
       <c r="Z207">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA207">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB207">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC207">
         <v>3.1</v>
@@ -34104,10 +34104,10 @@
         <v>1.08</v>
       </c>
       <c r="AF207">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG207">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>1.92</v>
       </c>
       <c r="S208">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="T208">
         <v>2.38</v>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK208">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="O211">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="P211">
-        <v>3.56</v>
+        <v>3.43</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -34874,22 +34874,22 @@
         <v>1.33</v>
       </c>
       <c r="Q212">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="R212">
-        <v>2.57</v>
+        <v>2.52</v>
       </c>
       <c r="S212">
         <v>1.29</v>
       </c>
       <c r="T212">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="U212">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="V212">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W212">
         <v>1.08</v>
@@ -34898,31 +34898,31 @@
         <v>1.02</v>
       </c>
       <c r="Y212">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z212">
-        <v>3.93</v>
+        <v>3.78</v>
       </c>
       <c r="AA212">
         <v>1.86</v>
       </c>
       <c r="AB212">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AC212">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="AD212">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE212">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF212">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AG212">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="AK212">
         <v>1.04</v>
@@ -35354,28 +35354,28 @@
         </is>
       </c>
       <c r="N215">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="O215">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P215">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q215">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R215">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S215">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T215">
-        <v>2.84</v>
+        <v>2.65</v>
       </c>
       <c r="U215">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="V215">
         <v>1.36</v>
@@ -35384,34 +35384,34 @@
         <v>1.05</v>
       </c>
       <c r="X215">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y215">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z215">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AA215">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AB215">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC215">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AD215">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE215">
         <v>1.06</v>
       </c>
       <c r="AF215">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG215">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK215">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35517,19 +35517,19 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="O216">
         <v>4.75</v>
       </c>
       <c r="P216">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="Q216">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R216">
-        <v>2.57</v>
+        <v>2.82</v>
       </c>
       <c r="S216">
         <v>1.15</v>
@@ -35538,13 +35538,13 @@
         <v>4.35</v>
       </c>
       <c r="U216">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="V216">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="W216">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X216">
         <v>1.01</v>
@@ -35556,41 +35556,41 @@
         <v>6.1</v>
       </c>
       <c r="AA216">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AB216">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="AC216">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AD216">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AE216">
         <v>1.28</v>
       </c>
       <c r="AF216">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AG216">
+        <v>2.47</v>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ216">
+        <v>1.2</v>
+      </c>
+      <c r="AK216">
         <v>2.5</v>
-      </c>
-      <c r="AH216" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI216" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ216">
-        <v>1.19</v>
-      </c>
-      <c r="AK216">
-        <v>2.54</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -35707,7 +35707,7 @@
         <v>1.33</v>
       </c>
       <c r="W217">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X217">
         <v>1.02</v>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O221">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="P221">
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36371,10 +36371,10 @@
         <v>0</v>
       </c>
       <c r="AA221">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB221">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC221">
         <v>0</v>
@@ -37473,13 +37473,13 @@
         </is>
       </c>
       <c r="N228">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O228">
         <v>3.4</v>
       </c>
       <c r="P228">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q228">
         <v>2.64</v>
@@ -37491,7 +37491,7 @@
         <v>1.29</v>
       </c>
       <c r="T228">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U228">
         <v>2.55</v>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="O231">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P231">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="Q231">
         <v>3.3</v>
@@ -37977,7 +37977,7 @@
         <v>2.02</v>
       </c>
       <c r="S231">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T231">
         <v>2.88</v>
@@ -38460,22 +38460,22 @@
         <v>0</v>
       </c>
       <c r="Q234">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="R234">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="S234">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T234">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="U234">
         <v>2.35</v>
       </c>
       <c r="V234">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W234">
         <v>1.09</v>
@@ -38487,13 +38487,13 @@
         <v>1.17</v>
       </c>
       <c r="Z234">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA234">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB234">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC234">
         <v>2.75</v>
@@ -38502,13 +38502,13 @@
         <v>1.38</v>
       </c>
       <c r="AE234">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF234">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG234">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK234">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38623,7 +38623,7 @@
         <v>5.25</v>
       </c>
       <c r="Q235">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="R235">
         <v>2.13</v>
@@ -38644,7 +38644,7 @@
         <v>1.08</v>
       </c>
       <c r="X235">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y235">
         <v>1.22</v>
@@ -38653,10 +38653,10 @@
         <v>3.5</v>
       </c>
       <c r="AA235">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB235">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC235">
         <v>2.83</v>
@@ -38668,7 +38668,7 @@
         <v>1.09</v>
       </c>
       <c r="AF235">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG235">
         <v>1.91</v>
@@ -38687,7 +38687,7 @@
         <v>1.26</v>
       </c>
       <c r="AK235">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -39266,7 +39266,7 @@
         </is>
       </c>
       <c r="N239">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="O239">
         <v>3.25</v>
@@ -39275,16 +39275,16 @@
         <v>3.9</v>
       </c>
       <c r="Q239">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="R239">
         <v>2.01</v>
       </c>
       <c r="S239">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T239">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="U239">
         <v>2.83</v>
@@ -39293,7 +39293,7 @@
         <v>1.36</v>
       </c>
       <c r="W239">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X239">
         <v>1.01</v>
@@ -39308,7 +39308,7 @@
         <v>2.06</v>
       </c>
       <c r="AB239">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC239">
         <v>3.58</v>
@@ -39317,7 +39317,7 @@
         <v>1.26</v>
       </c>
       <c r="AE239">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF239">
         <v>1.82</v>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK239">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39453,7 +39453,7 @@
         <v>2.11</v>
       </c>
       <c r="V240">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W240">
         <v>1.2</v>
@@ -39465,10 +39465,10 @@
         <v>1.08</v>
       </c>
       <c r="Z240">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA240">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB240">
         <v>2.72</v>
@@ -39477,7 +39477,7 @@
         <v>2.1</v>
       </c>
       <c r="AD240">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AE240">
         <v>1.29</v>
@@ -39486,7 +39486,7 @@
         <v>1.44</v>
       </c>
       <c r="AG240">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39785,7 +39785,7 @@
         <v>1.06</v>
       </c>
       <c r="X242">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y242">
         <v>1.38</v>
@@ -40579,7 +40579,7 @@
         <v>1.58</v>
       </c>
       <c r="Q247">
-        <v>5.66</v>
+        <v>5.74</v>
       </c>
       <c r="R247">
         <v>2.15</v>
@@ -40588,7 +40588,7 @@
         <v>1.34</v>
       </c>
       <c r="T247">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="U247">
         <v>2.6</v>
@@ -40600,7 +40600,7 @@
         <v>1.07</v>
       </c>
       <c r="X247">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y247">
         <v>1.23</v>
@@ -40609,7 +40609,7 @@
         <v>3.42</v>
       </c>
       <c r="AA247">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB247">
         <v>1.92</v>
@@ -40627,7 +40627,7 @@
         <v>1.83</v>
       </c>
       <c r="AG247">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -41385,16 +41385,16 @@
         </is>
       </c>
       <c r="N252">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="O252">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P252">
         <v>2.6</v>
       </c>
       <c r="Q252">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="R252">
         <v>1.87</v>
@@ -41403,10 +41403,10 @@
         <v>1.44</v>
       </c>
       <c r="T252">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="U252">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="V252">
         <v>1.36</v>
@@ -41421,13 +41421,13 @@
         <v>1.26</v>
       </c>
       <c r="Z252">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA252">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB252">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC252">
         <v>2.97</v>
@@ -41439,10 +41439,10 @@
         <v>1.08</v>
       </c>
       <c r="AF252">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG252">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41548,49 +41548,49 @@
         </is>
       </c>
       <c r="N253">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O253">
         <v>3.1</v>
       </c>
       <c r="P253">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q253">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="R253">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S253">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T253">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="U253">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V253">
         <v>1.33</v>
       </c>
       <c r="W253">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X253">
         <v>1.01</v>
       </c>
       <c r="Y253">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z253">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AA253">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AB253">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AC253">
         <v>3.68</v>
@@ -41621,7 +41621,7 @@
         <v>1.25</v>
       </c>
       <c r="AK253">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41720,10 +41720,10 @@
         <v>3.1</v>
       </c>
       <c r="Q254">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="R254">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="S254">
         <v>1.44</v>
@@ -41750,7 +41750,7 @@
         <v>2.49</v>
       </c>
       <c r="AA254">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AB254">
         <v>1.53</v>
@@ -41765,10 +41765,10 @@
         <v>1.01</v>
       </c>
       <c r="AF254">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AG254">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -41781,10 +41781,10 @@
         </is>
       </c>
       <c r="AJ254">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK254">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AL254">
         <v>0</v>
@@ -41883,13 +41883,13 @@
         <v>0</v>
       </c>
       <c r="Q255">
-        <v>5.16</v>
+        <v>4.74</v>
       </c>
       <c r="R255">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="S255">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="T255">
         <v>2.36</v>
@@ -41898,25 +41898,25 @@
         <v>3.44</v>
       </c>
       <c r="V255">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W255">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X255">
         <v>1.04</v>
       </c>
       <c r="Y255">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="Z255">
         <v>2.55</v>
       </c>
       <c r="AA255">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AB255">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AC255">
         <v>4.7</v>
@@ -41925,13 +41925,13 @@
         <v>1.12</v>
       </c>
       <c r="AE255">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF255">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AG255">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -42037,31 +42037,31 @@
         </is>
       </c>
       <c r="N256">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O256">
         <v>3</v>
       </c>
       <c r="P256">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q256">
         <v>3</v>
       </c>
       <c r="R256">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="S256">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="T256">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="U256">
-        <v>3.03</v>
+        <v>3.12</v>
       </c>
       <c r="V256">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W256">
         <v>1.01</v>
@@ -42070,28 +42070,28 @@
         <v>1.04</v>
       </c>
       <c r="Y256">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z256">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="AA256">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AB256">
         <v>1.56</v>
       </c>
       <c r="AC256">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="AD256">
         <v>1.18</v>
       </c>
       <c r="AE256">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF256">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG256">
         <v>1.8</v>
@@ -42110,7 +42110,7 @@
         <v>1.3</v>
       </c>
       <c r="AK256">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42200,80 +42200,80 @@
         </is>
       </c>
       <c r="N257">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="O257">
+        <v>3.25</v>
+      </c>
+      <c r="P257">
+        <v>3.4</v>
+      </c>
+      <c r="Q257">
+        <v>2.53</v>
+      </c>
+      <c r="R257">
+        <v>1.98</v>
+      </c>
+      <c r="S257">
+        <v>1.42</v>
+      </c>
+      <c r="T257">
+        <v>2.57</v>
+      </c>
+      <c r="U257">
         <v>3.2</v>
       </c>
-      <c r="P257">
-        <v>4.9</v>
-      </c>
-      <c r="Q257">
-        <v>2.4</v>
-      </c>
-      <c r="R257">
-        <v>1.91</v>
-      </c>
-      <c r="S257">
-        <v>1.45</v>
-      </c>
-      <c r="T257">
-        <v>2.42</v>
-      </c>
-      <c r="U257">
-        <v>3.06</v>
-      </c>
       <c r="V257">
+        <v>1.3</v>
+      </c>
+      <c r="W257">
+        <v>1.05</v>
+      </c>
+      <c r="X257">
+        <v>1.06</v>
+      </c>
+      <c r="Y257">
+        <v>1.34</v>
+      </c>
+      <c r="Z257">
+        <v>2.93</v>
+      </c>
+      <c r="AA257">
+        <v>2.2</v>
+      </c>
+      <c r="AB257">
+        <v>1.65</v>
+      </c>
+      <c r="AC257">
+        <v>3.82</v>
+      </c>
+      <c r="AD257">
+        <v>1.22</v>
+      </c>
+      <c r="AE257">
+        <v>1.04</v>
+      </c>
+      <c r="AF257">
+        <v>1.93</v>
+      </c>
+      <c r="AG257">
+        <v>1.75</v>
+      </c>
+      <c r="AH257" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI257" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ257">
         <v>1.29</v>
       </c>
-      <c r="W257">
-        <v>1.03</v>
-      </c>
-      <c r="X257">
-        <v>1.04</v>
-      </c>
-      <c r="Y257">
-        <v>1.44</v>
-      </c>
-      <c r="Z257">
-        <v>2.67</v>
-      </c>
-      <c r="AA257">
-        <v>2.35</v>
-      </c>
-      <c r="AB257">
-        <v>1.55</v>
-      </c>
-      <c r="AC257">
-        <v>4.1</v>
-      </c>
-      <c r="AD257">
-        <v>1.16</v>
-      </c>
-      <c r="AE257">
-        <v>1.01</v>
-      </c>
-      <c r="AF257">
-        <v>2.08</v>
-      </c>
-      <c r="AG257">
-        <v>1.62</v>
-      </c>
-      <c r="AH257" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI257" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ257">
-        <v>1.25</v>
-      </c>
       <c r="AK257">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -42580,7 +42580,7 @@
         <v>1.15</v>
       </c>
       <c r="AF259">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AG259">
         <v>1.62</v>
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="O280">
         <v>3</v>
       </c>
       <c r="P280">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="Q280">
         <v>3.24</v>
@@ -45967,7 +45967,7 @@
         <v>1.5</v>
       </c>
       <c r="T280">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="U280">
         <v>3.22</v>
@@ -46006,7 +46006,7 @@
         <v>2</v>
       </c>
       <c r="AG280">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>0</v>
       </c>
       <c r="Q281">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="R281">
         <v>2.62</v>
@@ -46133,10 +46133,10 @@
         <v>4</v>
       </c>
       <c r="U281">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="V281">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W281">
         <v>1.14</v>
@@ -46154,7 +46154,7 @@
         <v>1.48</v>
       </c>
       <c r="AB281">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AC281">
         <v>2.28</v>
@@ -47271,10 +47271,10 @@
         <v>1.29</v>
       </c>
       <c r="T288">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U288">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V288">
         <v>1.43</v>
@@ -47289,19 +47289,19 @@
         <v>1.18</v>
       </c>
       <c r="Z288">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="AA288">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB288">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC288">
         <v>2.78</v>
       </c>
       <c r="AD288">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE288">
         <v>1.09</v>
@@ -47323,7 +47323,7 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK288">
         <v>1.53</v>
@@ -47440,10 +47440,10 @@
         <v>2.2</v>
       </c>
       <c r="V289">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W289">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X289">
         <v>1.02</v>
@@ -47458,7 +47458,7 @@
         <v>1.54</v>
       </c>
       <c r="AB289">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="AC289">
         <v>2.41</v>
@@ -47470,10 +47470,10 @@
         <v>1.16</v>
       </c>
       <c r="AF289">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG289">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47748,7 +47748,7 @@
         <v>3.2</v>
       </c>
       <c r="P291">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q291">
         <v>2.78</v>

--- a/jogos_2026-09-20.xlsx
+++ b/jogos_2026-09-20.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.44</v>
+        <v>2.11</v>
       </c>
       <c r="O2">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>6.4</v>
+        <v>2.94</v>
       </c>
       <c r="Q2">
-        <v>1.87</v>
+        <v>2.71</v>
       </c>
       <c r="R2">
-        <v>2.41</v>
+        <v>2.03</v>
       </c>
       <c r="S2">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="U2">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="V2">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="Z2">
-        <v>4.3</v>
+        <v>3.16</v>
       </c>
       <c r="AA2">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="AB2">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AC2">
-        <v>2.63</v>
+        <v>3.88</v>
       </c>
       <c r="AD2">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AE2">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG2">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>2.69</v>
+        <v>1.67</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.11</v>
+        <v>1.44</v>
       </c>
       <c r="O3">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="P3">
-        <v>2.94</v>
+        <v>6.4</v>
       </c>
       <c r="Q3">
-        <v>2.71</v>
+        <v>1.87</v>
       </c>
       <c r="R3">
-        <v>2.03</v>
+        <v>2.41</v>
       </c>
       <c r="S3">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="U3">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="Z3">
-        <v>3.14</v>
+        <v>4.3</v>
       </c>
       <c r="AA3">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="AB3">
-        <v>1.7</v>
+        <v>2.19</v>
       </c>
       <c r="AC3">
-        <v>3.84</v>
+        <v>2.69</v>
       </c>
       <c r="AD3">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AE3">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AF3">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG3">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK3">
-        <v>1.7</v>
+        <v>2.69</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -994,10 +994,10 @@
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z4">
-        <v>3.25</v>
+        <v>3.37</v>
       </c>
       <c r="AA4">
         <v>1.93</v>
@@ -1012,7 +1012,7 @@
         <v>1.24</v>
       </c>
       <c r="AE4">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF4">
         <v>1.73</v>
@@ -1139,10 +1139,10 @@
         <v>2.2</v>
       </c>
       <c r="S5">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T5">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="U5">
         <v>2.8</v>
@@ -1151,7 +1151,7 @@
         <v>1.34</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
         <v>1.03</v>
@@ -1163,7 +1163,7 @@
         <v>3.2</v>
       </c>
       <c r="AA5">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AB5">
         <v>1.77</v>
@@ -1462,13 +1462,13 @@
         <v>4</v>
       </c>
       <c r="R7">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S7">
         <v>1.33</v>
       </c>
       <c r="T7">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="U7">
         <v>2.75</v>
@@ -1492,7 +1492,7 @@
         <v>2.03</v>
       </c>
       <c r="AB7">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC7">
         <v>3.2</v>
@@ -1504,10 +1504,10 @@
         <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AK7">
         <v>1.27</v>
@@ -1622,10 +1622,10 @@
         <v>2.65</v>
       </c>
       <c r="Q8">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="R8">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S8">
         <v>1.38</v>
@@ -1634,10 +1634,10 @@
         <v>2.88</v>
       </c>
       <c r="U8">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="V8">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W8">
         <v>1.04</v>
@@ -1667,7 +1667,7 @@
         <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
         <v>2.1</v>
@@ -1686,7 +1686,7 @@
         <v>1.33</v>
       </c>
       <c r="AK8">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2111,25 +2111,25 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="R11">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S11">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T11">
         <v>3.4</v>
       </c>
       <c r="U11">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V11">
         <v>1.55</v>
       </c>
       <c r="W11">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X11">
         <v>1.02</v>
@@ -2141,7 +2141,7 @@
         <v>4.5</v>
       </c>
       <c r="AA11">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB11">
         <v>2.2</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,7 +2274,7 @@
         <v>5.5</v>
       </c>
       <c r="Q12">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="R12">
         <v>2.25</v>
@@ -2286,10 +2286,10 @@
         <v>3.3</v>
       </c>
       <c r="U12">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="V12">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W12">
         <v>1.08</v>
@@ -2316,7 +2316,7 @@
         <v>1.41</v>
       </c>
       <c r="AE12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF12">
         <v>1.8</v>
@@ -2338,7 +2338,7 @@
         <v>1.15</v>
       </c>
       <c r="AK12">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O14">
         <v>3.1</v>
@@ -2624,7 +2624,7 @@
         <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z14">
         <v>2.56</v>
@@ -2636,7 +2636,7 @@
         <v>1.52</v>
       </c>
       <c r="AC14">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AD14">
         <v>1.14</v>
@@ -2757,7 +2757,7 @@
         <v>1.95</v>
       </c>
       <c r="O15">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
         <v>3.7</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="O16">
         <v>3.3</v>
@@ -3747,7 +3747,7 @@
         <v>2.01</v>
       </c>
       <c r="S21">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T21">
         <v>2.57</v>
@@ -3768,7 +3768,7 @@
         <v>1.3</v>
       </c>
       <c r="Z21">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="AA21">
         <v>2.05</v>
@@ -3805,7 +3805,7 @@
         <v>1.85</v>
       </c>
       <c r="AK21">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3910,13 +3910,13 @@
         <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T22">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="U22">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="V22">
         <v>1.4</v>
@@ -4076,7 +4076,7 @@
         <v>1.36</v>
       </c>
       <c r="T23">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U23">
         <v>2.9</v>
@@ -4094,19 +4094,19 @@
         <v>1.3</v>
       </c>
       <c r="Z23">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="AA23">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AB23">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC23">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AD23">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE23">
         <v>1.04</v>
@@ -4242,7 +4242,7 @@
         <v>2.69</v>
       </c>
       <c r="U24">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="V24">
         <v>1.35</v>
@@ -4254,16 +4254,16 @@
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z24">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="AA24">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AB24">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AC24">
         <v>3.42</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AK24">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,80 +4547,80 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="O26">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P26">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q26">
-        <v>2.53</v>
+        <v>2.73</v>
       </c>
       <c r="R26">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="S26">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T26">
+        <v>2.45</v>
+      </c>
+      <c r="U26">
+        <v>3.3</v>
+      </c>
+      <c r="V26">
+        <v>1.23</v>
+      </c>
+      <c r="W26">
+        <v>1.02</v>
+      </c>
+      <c r="X26">
+        <v>1.07</v>
+      </c>
+      <c r="Y26">
+        <v>1.42</v>
+      </c>
+      <c r="Z26">
         <v>2.49</v>
       </c>
-      <c r="U26">
-        <v>3.2</v>
-      </c>
-      <c r="V26">
-        <v>1.3</v>
-      </c>
-      <c r="W26">
-        <v>1.03</v>
-      </c>
-      <c r="X26">
+      <c r="AA26">
+        <v>2.38</v>
+      </c>
+      <c r="AB26">
+        <v>1.49</v>
+      </c>
+      <c r="AC26">
+        <v>4.6</v>
+      </c>
+      <c r="AD26">
+        <v>1.13</v>
+      </c>
+      <c r="AE26">
         <v>1.05</v>
       </c>
-      <c r="Y26">
-        <v>1.4</v>
-      </c>
-      <c r="Z26">
-        <v>2.56</v>
-      </c>
-      <c r="AA26">
-        <v>2.28</v>
-      </c>
-      <c r="AB26">
-        <v>1.55</v>
-      </c>
-      <c r="AC26">
-        <v>4.15</v>
-      </c>
-      <c r="AD26">
+      <c r="AF26">
+        <v>2.1</v>
+      </c>
+      <c r="AG26">
+        <v>1.65</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
         <v>1.16</v>
       </c>
-      <c r="AE26">
-        <v>1.02</v>
-      </c>
-      <c r="AF26">
-        <v>2.04</v>
-      </c>
-      <c r="AG26">
-        <v>1.73</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.15</v>
-      </c>
       <c r="AK26">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="O27">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P27">
         <v>3.75</v>
       </c>
       <c r="Q27">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="R27">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="S27">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T27">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="U27">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V27">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W27">
+        <v>1.03</v>
+      </c>
+      <c r="X27">
+        <v>1.05</v>
+      </c>
+      <c r="Y27">
+        <v>1.4</v>
+      </c>
+      <c r="Z27">
+        <v>2.56</v>
+      </c>
+      <c r="AA27">
+        <v>2.28</v>
+      </c>
+      <c r="AB27">
+        <v>1.55</v>
+      </c>
+      <c r="AC27">
+        <v>4.15</v>
+      </c>
+      <c r="AD27">
+        <v>1.16</v>
+      </c>
+      <c r="AE27">
         <v>1.02</v>
       </c>
-      <c r="X27">
-        <v>1.07</v>
-      </c>
-      <c r="Y27">
-        <v>1.42</v>
-      </c>
-      <c r="Z27">
-        <v>2.49</v>
-      </c>
-      <c r="AA27">
-        <v>2.41</v>
-      </c>
-      <c r="AB27">
-        <v>1.48</v>
-      </c>
-      <c r="AC27">
-        <v>4.6</v>
-      </c>
-      <c r="AD27">
-        <v>1.13</v>
-      </c>
-      <c r="AE27">
-        <v>1.05</v>
-      </c>
       <c r="AF27">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AG27">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK27">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4909,7 +4909,7 @@
         <v>1.36</v>
       </c>
       <c r="Z28">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AA28">
         <v>2.27</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK28">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AB36">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AC36">
         <v>0</v>
@@ -6349,7 +6349,7 @@
         <v>2.85</v>
       </c>
       <c r="Q37">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R37">
         <v>2.3</v>
@@ -6361,34 +6361,34 @@
         <v>3.22</v>
       </c>
       <c r="U37">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V37">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W37">
         <v>1.12</v>
       </c>
       <c r="X37">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
         <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="AA37">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB37">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AC37">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="AD37">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE37">
         <v>1.14</v>
@@ -6413,7 +6413,7 @@
         <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -7653,22 +7653,22 @@
         <v>4.4</v>
       </c>
       <c r="Q45">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="R45">
         <v>2.15</v>
       </c>
       <c r="S45">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T45">
         <v>2.9</v>
       </c>
       <c r="U45">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="V45">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W45">
         <v>1.07</v>
@@ -7677,10 +7677,10 @@
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z45">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="AA45">
         <v>1.98</v>
@@ -7692,16 +7692,16 @@
         <v>2.97</v>
       </c>
       <c r="AD45">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE45">
         <v>1.08</v>
       </c>
       <c r="AF45">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG45">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.15</v>
       </c>
       <c r="AK45">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7816,7 +7816,7 @@
         <v>1.97</v>
       </c>
       <c r="Q46">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="R46">
         <v>2.23</v>
@@ -7828,7 +7828,7 @@
         <v>3.3</v>
       </c>
       <c r="U46">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V46">
         <v>1.47</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AK46">
         <v>1.29</v>
@@ -7985,10 +7985,10 @@
         <v>2.2</v>
       </c>
       <c r="S47">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T47">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U47">
         <v>2.62</v>
@@ -8009,19 +8009,19 @@
         <v>3.34</v>
       </c>
       <c r="AA47">
+        <v>1.89</v>
+      </c>
+      <c r="AB47">
         <v>1.9</v>
       </c>
-      <c r="AB47">
-        <v>1.89</v>
-      </c>
       <c r="AC47">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AD47">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE47">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF47">
         <v>1.75</v>
@@ -8154,7 +8154,7 @@
         <v>3.2</v>
       </c>
       <c r="U48">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="V48">
         <v>1.44</v>
@@ -8166,13 +8166,13 @@
         <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AA48">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB48">
         <v>1.94</v>
@@ -8181,7 +8181,7 @@
         <v>2.83</v>
       </c>
       <c r="AD48">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE48">
         <v>1.08</v>
@@ -8459,28 +8459,28 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="O50">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
         <v>3.5</v>
       </c>
       <c r="Q50">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="R50">
         <v>2.29</v>
       </c>
       <c r="S50">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T50">
         <v>3.75</v>
       </c>
       <c r="U50">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="V50">
         <v>1.67</v>
@@ -8492,16 +8492,16 @@
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z50">
-        <v>5.42</v>
+        <v>5.45</v>
       </c>
       <c r="AA50">
         <v>1.53</v>
       </c>
       <c r="AB50">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AC50">
         <v>2.25</v>
@@ -8532,7 +8532,7 @@
         <v>1.33</v>
       </c>
       <c r="AK50">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8794,7 +8794,7 @@
         <v>1.61</v>
       </c>
       <c r="Q52">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="R52">
         <v>2.25</v>
@@ -8821,28 +8821,28 @@
         <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AA52">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB52">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC52">
         <v>3.14</v>
       </c>
       <c r="AD52">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE52">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF52">
         <v>2</v>
       </c>
       <c r="AG52">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.19</v>
+        <v>2.2</v>
       </c>
       <c r="AK52">
         <v>1.1</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O55">
         <v>3.65</v>
@@ -9283,10 +9283,10 @@
         <v>2.95</v>
       </c>
       <c r="Q55">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R55">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S55">
         <v>1.22</v>
@@ -9316,22 +9316,22 @@
         <v>1.44</v>
       </c>
       <c r="AB55">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="AC55">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AD55">
         <v>1.59</v>
       </c>
       <c r="AE55">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF55">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AG55">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AK55">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9458,10 +9458,10 @@
         <v>4</v>
       </c>
       <c r="U56">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="V56">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W56">
         <v>1.14</v>
@@ -9473,16 +9473,16 @@
         <v>1.12</v>
       </c>
       <c r="Z56">
-        <v>6.33</v>
+        <v>6.43</v>
       </c>
       <c r="AA56">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AB56">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="AC56">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AD56">
         <v>1.78</v>
@@ -9491,7 +9491,7 @@
         <v>1.32</v>
       </c>
       <c r="AF56">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG56">
         <v>2.8</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="O57">
         <v>3.7</v>
       </c>
       <c r="P57">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="Q57">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="R57">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S57">
         <v>1.22</v>
       </c>
       <c r="T57">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="U57">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V57">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="W57">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z57">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA57">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AB57">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="AC57">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="AD57">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE57">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AF57">
         <v>1.45</v>
       </c>
       <c r="AG57">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK57">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="O58">
         <v>3.7</v>
       </c>
       <c r="P58">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="Q58">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
       <c r="R58">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S58">
         <v>1.22</v>
       </c>
       <c r="T58">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="U58">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V58">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="W58">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X58">
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z58">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA58">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AB58">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="AC58">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="AD58">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE58">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AF58">
         <v>1.45</v>
       </c>
       <c r="AG58">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9929,10 +9929,10 @@
         <v>4</v>
       </c>
       <c r="O59">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="P59">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q59">
         <v>4.55</v>
@@ -9944,7 +9944,7 @@
         <v>1.24</v>
       </c>
       <c r="T59">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="U59">
         <v>2.22</v>
@@ -9977,7 +9977,7 @@
         <v>1.45</v>
       </c>
       <c r="AE59">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF59">
         <v>1.57</v>
@@ -10463,7 +10463,7 @@
         <v>1.84</v>
       </c>
       <c r="AD62">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AE62">
         <v>1.36</v>
@@ -10587,16 +10587,16 @@
         <v>3</v>
       </c>
       <c r="Q63">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="R63">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="S63">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="T63">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U63">
         <v>3.9</v>
@@ -10608,34 +10608,34 @@
         <v>1</v>
       </c>
       <c r="X63">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y63">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="Z63">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="AA63">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB63">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC63">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AD63">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AE63">
         <v>1</v>
       </c>
       <c r="AF63">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AG63">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK63">
         <v>1.53</v>
@@ -11082,49 +11082,49 @@
         <v>2.2</v>
       </c>
       <c r="S66">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T66">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="U66">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="V66">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W66">
         <v>1.08</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y66">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z66">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AA66">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AB66">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC66">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="AD66">
         <v>1.4</v>
       </c>
       <c r="AE66">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF66">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG66">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>2.31</v>
       </c>
       <c r="S67">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T67">
         <v>3.6</v>
@@ -11260,19 +11260,19 @@
         <v>1.12</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
         <v>1.2</v>
       </c>
       <c r="Z67">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA67">
         <v>1.63</v>
       </c>
       <c r="AB67">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AC67">
         <v>2.6</v>
@@ -11303,7 +11303,7 @@
         <v>1.17</v>
       </c>
       <c r="AK67">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11405,10 +11405,10 @@
         <v>3.74</v>
       </c>
       <c r="R68">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S68">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T68">
         <v>3.6</v>
@@ -11426,28 +11426,28 @@
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z68">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AA68">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB68">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC68">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AD68">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE68">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF68">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG68">
         <v>2.45</v>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AK68">
         <v>1.33</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,61 +11882,61 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="O71">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P71">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q71">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R71">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S71">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="U71">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="V71">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W71">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X71">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z71">
-        <v>3.84</v>
+        <v>4.4</v>
       </c>
       <c r="AA71">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AB71">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AC71">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="AD71">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE71">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF71">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG71">
         <v>2.3</v>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK71">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,61 +12045,61 @@
         </is>
       </c>
       <c r="N72">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="O72">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P72">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q72">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R72">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S72">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T72">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U72">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="V72">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W72">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X72">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y72">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z72">
-        <v>4.4</v>
+        <v>3.84</v>
       </c>
       <c r="AA72">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AB72">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AC72">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="AD72">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE72">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF72">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG72">
         <v>2.3</v>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK72">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12389,7 +12389,7 @@
         <v>1.4</v>
       </c>
       <c r="T74">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="U74">
         <v>2.89</v>
@@ -12401,7 +12401,7 @@
         <v>1.05</v>
       </c>
       <c r="X74">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y74">
         <v>1.28</v>
@@ -12422,7 +12422,7 @@
         <v>1.28</v>
       </c>
       <c r="AE74">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF74">
         <v>2.08</v>
@@ -13512,16 +13512,16 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="O81">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="P81">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="Q81">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="R81">
         <v>2.4</v>
@@ -13554,10 +13554,10 @@
         <v>1.47</v>
       </c>
       <c r="AB81">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AC81">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AD81">
         <v>1.62</v>
@@ -13585,7 +13585,7 @@
         <v>1.29</v>
       </c>
       <c r="AK81">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13684,7 +13684,7 @@
         <v>5.8</v>
       </c>
       <c r="Q82">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R82">
         <v>2.49</v>
@@ -13711,22 +13711,22 @@
         <v>1.13</v>
       </c>
       <c r="Z82">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA82">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB82">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AC82">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AD82">
         <v>1.59</v>
       </c>
       <c r="AE82">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF82">
         <v>1.62</v>
@@ -13748,7 +13748,7 @@
         <v>1.17</v>
       </c>
       <c r="AK82">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="N84">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O84">
         <v>5.6</v>
@@ -14010,7 +14010,7 @@
         <v>1.28</v>
       </c>
       <c r="Q84">
-        <v>6.57</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R84">
         <v>2.66</v>
@@ -14034,7 +14034,7 @@
         <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z84">
         <v>5.2</v>
@@ -14058,7 +14058,7 @@
         <v>1.8</v>
       </c>
       <c r="AG84">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>1.16</v>
       </c>
       <c r="Z85">
-        <v>4.17</v>
+        <v>4.22</v>
       </c>
       <c r="AA85">
         <v>1.7</v>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK85">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -15178,19 +15178,19 @@
         <v>1.24</v>
       </c>
       <c r="Z91">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="AA91">
         <v>1.94</v>
       </c>
       <c r="AB91">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC91">
         <v>2.97</v>
       </c>
       <c r="AD91">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE91">
         <v>1.08</v>
@@ -15311,13 +15311,13 @@
         <v>3.5</v>
       </c>
       <c r="P92">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="Q92">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="R92">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="S92">
         <v>1.2</v>
@@ -15326,10 +15326,10 @@
         <v>4</v>
       </c>
       <c r="U92">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V92">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W92">
         <v>1.17</v>
@@ -15341,28 +15341,28 @@
         <v>1.08</v>
       </c>
       <c r="Z92">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="AA92">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AB92">
         <v>2.7</v>
       </c>
       <c r="AC92">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AD92">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AE92">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF92">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AG92">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>1.35</v>
       </c>
       <c r="AK92">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15836,10 +15836,10 @@
         <v>1.74</v>
       </c>
       <c r="AB95">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AC95">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AD95">
         <v>1.4</v>
@@ -16156,22 +16156,22 @@
         <v>1.13</v>
       </c>
       <c r="Z97">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AA97">
         <v>1.47</v>
       </c>
       <c r="AB97">
-        <v>2.49</v>
+        <v>2.8</v>
       </c>
       <c r="AC97">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AD97">
         <v>1.63</v>
       </c>
       <c r="AE97">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF97">
         <v>1.43</v>
@@ -16986,7 +16986,7 @@
         <v>1.37</v>
       </c>
       <c r="AE102">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF102">
         <v>1.62</v>
@@ -17005,7 +17005,7 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK102">
         <v>1.44</v>
@@ -17098,19 +17098,19 @@
         </is>
       </c>
       <c r="N103">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O103">
         <v>5</v>
       </c>
       <c r="P103">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Q103">
-        <v>7.13</v>
+        <v>7</v>
       </c>
       <c r="R103">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="S103">
         <v>1.25</v>
@@ -17137,25 +17137,25 @@
         <v>5</v>
       </c>
       <c r="AA103">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AB103">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="AC103">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="AD103">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE103">
         <v>1.2</v>
       </c>
       <c r="AF103">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AG103">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>1.13</v>
       </c>
       <c r="AK103">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17442,10 +17442,10 @@
         <v>1.37</v>
       </c>
       <c r="T105">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="U105">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="V105">
         <v>1.42</v>
@@ -17460,7 +17460,7 @@
         <v>1.24</v>
       </c>
       <c r="Z105">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA105">
         <v>1.82</v>
@@ -17472,10 +17472,10 @@
         <v>2.97</v>
       </c>
       <c r="AD105">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE105">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF105">
         <v>1.7</v>
@@ -17587,16 +17587,16 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="O106">
         <v>3.4</v>
       </c>
       <c r="P106">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q106">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R106">
         <v>2.27</v>
@@ -17611,13 +17611,13 @@
         <v>2.56</v>
       </c>
       <c r="V106">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W106">
         <v>1.1</v>
       </c>
       <c r="X106">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
         <v>1.15</v>
@@ -17626,10 +17626,10 @@
         <v>4.25</v>
       </c>
       <c r="AA106">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB106">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AC106">
         <v>2.56</v>
@@ -17768,16 +17768,16 @@
         <v>1.32</v>
       </c>
       <c r="T107">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U107">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="V107">
         <v>1.43</v>
       </c>
       <c r="W107">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X107">
         <v>1.02</v>
@@ -17786,7 +17786,7 @@
         <v>1.19</v>
       </c>
       <c r="Z107">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="AA107">
         <v>1.85</v>
@@ -17795,16 +17795,16 @@
         <v>1.95</v>
       </c>
       <c r="AC107">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AD107">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE107">
         <v>1.09</v>
       </c>
       <c r="AF107">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG107">
         <v>1.73</v>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="O108">
         <v>3.55</v>
       </c>
       <c r="P108">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -17958,7 +17958,7 @@
         <v>2.2</v>
       </c>
       <c r="AC108">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AD108">
         <v>1.44</v>
@@ -18242,22 +18242,22 @@
         <v>2.15</v>
       </c>
       <c r="O110">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P110">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="Q110">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="R110">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S110">
         <v>1.3</v>
       </c>
       <c r="T110">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="U110">
         <v>2.48</v>
@@ -18284,16 +18284,16 @@
         <v>1.98</v>
       </c>
       <c r="AC110">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AD110">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE110">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF110">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG110">
         <v>2.2</v>
@@ -19724,7 +19724,7 @@
         <v>1.38</v>
       </c>
       <c r="T119">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="U119">
         <v>2.79</v>
@@ -19733,7 +19733,7 @@
         <v>1.37</v>
       </c>
       <c r="W119">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X119">
         <v>1.04</v>
@@ -19869,7 +19869,7 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="O120">
         <v>6.9</v>
@@ -19881,7 +19881,7 @@
         <v>1.46</v>
       </c>
       <c r="R120">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="S120">
         <v>1.14</v>
@@ -19890,10 +19890,10 @@
         <v>4.1</v>
       </c>
       <c r="U120">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="V120">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W120">
         <v>1.17</v>
@@ -19905,28 +19905,28 @@
         <v>1.13</v>
       </c>
       <c r="Z120">
-        <v>5.7</v>
+        <v>5.85</v>
       </c>
       <c r="AA120">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AB120">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AC120">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AD120">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AE120">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF120">
         <v>2</v>
       </c>
       <c r="AG120">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -20041,7 +20041,7 @@
         <v>1.83</v>
       </c>
       <c r="Q121">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="R121">
         <v>2.14</v>
@@ -20074,7 +20074,7 @@
         <v>1.88</v>
       </c>
       <c r="AB121">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC121">
         <v>3.08</v>
@@ -20530,10 +20530,10 @@
         <v>1.13</v>
       </c>
       <c r="Q124">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="R124">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="S124">
         <v>1.14</v>
@@ -20545,7 +20545,7 @@
         <v>1.85</v>
       </c>
       <c r="V124">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="W124">
         <v>1.22</v>
@@ -20557,7 +20557,7 @@
         <v>1.04</v>
       </c>
       <c r="Z124">
-        <v>6.9</v>
+        <v>6.95</v>
       </c>
       <c r="AA124">
         <v>1.33</v>
@@ -20566,10 +20566,10 @@
         <v>3.25</v>
       </c>
       <c r="AC124">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AD124">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AE124">
         <v>1.35</v>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK124">
         <v>1.01</v>
@@ -20690,10 +20690,10 @@
         <v>3.7</v>
       </c>
       <c r="P125">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="Q125">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R125">
         <v>2.25</v>
@@ -20711,7 +20711,7 @@
         <v>1.5</v>
       </c>
       <c r="W125">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X125">
         <v>1.01</v>
@@ -20729,7 +20729,7 @@
         <v>2.3</v>
       </c>
       <c r="AC125">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AD125">
         <v>1.45</v>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK125">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20859,7 +20859,7 @@
         <v>2.5</v>
       </c>
       <c r="R126">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S126">
         <v>1.38</v>
@@ -20883,16 +20883,16 @@
         <v>1.32</v>
       </c>
       <c r="Z126">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="AA126">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AB126">
         <v>1.72</v>
       </c>
       <c r="AC126">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="AD126">
         <v>1.25</v>
@@ -20901,7 +20901,7 @@
         <v>1.05</v>
       </c>
       <c r="AF126">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG126">
         <v>1.87</v>
@@ -21837,7 +21837,7 @@
         <v>7.5</v>
       </c>
       <c r="R132">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="S132">
         <v>1.25</v>
@@ -21858,7 +21858,7 @@
         <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z132">
         <v>4.6</v>
@@ -21867,7 +21867,7 @@
         <v>1.49</v>
       </c>
       <c r="AB132">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC132">
         <v>2.31</v>
@@ -22169,13 +22169,13 @@
         <v>1.36</v>
       </c>
       <c r="T134">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="U134">
         <v>2.68</v>
       </c>
       <c r="V134">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W134">
         <v>1.08</v>
@@ -22335,7 +22335,7 @@
         <v>4.1</v>
       </c>
       <c r="U135">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="V135">
         <v>1.69</v>
@@ -22356,13 +22356,13 @@
         <v>1.4</v>
       </c>
       <c r="AB135">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="AC135">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AD135">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AE135">
         <v>1.29</v>
@@ -22371,7 +22371,7 @@
         <v>1.44</v>
       </c>
       <c r="AG135">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22652,7 +22652,7 @@
         <v>4.2</v>
       </c>
       <c r="R137">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S137">
         <v>1.29</v>
@@ -22673,10 +22673,10 @@
         <v>1.01</v>
       </c>
       <c r="Y137">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z137">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA137">
         <v>1.64</v>
@@ -22691,7 +22691,7 @@
         <v>1.44</v>
       </c>
       <c r="AE137">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF137">
         <v>1.57</v>
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AK137">
         <v>1.25</v>
@@ -22827,7 +22827,7 @@
         <v>1.95</v>
       </c>
       <c r="V138">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W138">
         <v>1.2</v>
@@ -22848,13 +22848,13 @@
         <v>2.78</v>
       </c>
       <c r="AC138">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AD138">
         <v>1.78</v>
       </c>
       <c r="AE138">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF138">
         <v>1.33</v>
@@ -22876,7 +22876,7 @@
         <v>1.53</v>
       </c>
       <c r="AK138">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22975,7 +22975,7 @@
         <v>3.05</v>
       </c>
       <c r="Q139">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="R139">
         <v>2.26</v>
@@ -22993,25 +22993,25 @@
         <v>1.52</v>
       </c>
       <c r="W139">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X139">
         <v>1.01</v>
       </c>
       <c r="Y139">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z139">
         <v>4.5</v>
       </c>
       <c r="AA139">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AB139">
+        <v>2.32</v>
+      </c>
+      <c r="AC139">
         <v>2.45</v>
-      </c>
-      <c r="AC139">
-        <v>2.43</v>
       </c>
       <c r="AD139">
         <v>1.47</v>
@@ -23023,7 +23023,7 @@
         <v>1.48</v>
       </c>
       <c r="AG139">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK139">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23144,10 +23144,10 @@
         <v>2.63</v>
       </c>
       <c r="S140">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T140">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U140">
         <v>2.32</v>
@@ -23183,10 +23183,10 @@
         <v>1.17</v>
       </c>
       <c r="AF140">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG140">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>3.3</v>
       </c>
       <c r="U141">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="V141">
         <v>1.5</v>
@@ -23325,19 +23325,19 @@
         <v>1.03</v>
       </c>
       <c r="Y141">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z141">
         <v>3.98</v>
       </c>
       <c r="AA141">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AB141">
         <v>2.1</v>
       </c>
       <c r="AC141">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AD141">
         <v>1.37</v>
@@ -23346,10 +23346,10 @@
         <v>1.1</v>
       </c>
       <c r="AF141">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG141">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>1.52</v>
       </c>
       <c r="AK141">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23464,7 +23464,7 @@
         <v>3.45</v>
       </c>
       <c r="Q142">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="R142">
         <v>2.1</v>
@@ -23488,10 +23488,10 @@
         <v>1.03</v>
       </c>
       <c r="Y142">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z142">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA142">
         <v>2.08</v>
@@ -23500,7 +23500,7 @@
         <v>1.72</v>
       </c>
       <c r="AC142">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AD142">
         <v>1.28</v>
@@ -23633,16 +23633,16 @@
         <v>2.33</v>
       </c>
       <c r="S143">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T143">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="U143">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="V143">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W143">
         <v>1.08</v>
@@ -23654,7 +23654,7 @@
         <v>1.29</v>
       </c>
       <c r="Z143">
-        <v>3.39</v>
+        <v>3.5</v>
       </c>
       <c r="AA143">
         <v>1.9</v>
@@ -23663,7 +23663,7 @@
         <v>1.87</v>
       </c>
       <c r="AC143">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AD143">
         <v>1.29</v>
@@ -24922,80 +24922,80 @@
         </is>
       </c>
       <c r="N151">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O151">
         <v>3.6</v>
       </c>
       <c r="P151">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="Q151">
-        <v>6.08</v>
+        <v>6.46</v>
       </c>
       <c r="R151">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S151">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T151">
         <v>2.88</v>
       </c>
       <c r="U151">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="V151">
         <v>1.36</v>
       </c>
       <c r="W151">
+        <v>1.08</v>
+      </c>
+      <c r="X151">
+        <v>1.02</v>
+      </c>
+      <c r="Y151">
+        <v>1.33</v>
+      </c>
+      <c r="Z151">
+        <v>3.25</v>
+      </c>
+      <c r="AA151">
+        <v>1.95</v>
+      </c>
+      <c r="AB151">
+        <v>1.8</v>
+      </c>
+      <c r="AC151">
+        <v>3.34</v>
+      </c>
+      <c r="AD151">
+        <v>1.24</v>
+      </c>
+      <c r="AE151">
+        <v>1.04</v>
+      </c>
+      <c r="AF151">
+        <v>1.78</v>
+      </c>
+      <c r="AG151">
+        <v>1.57</v>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ151">
+        <v>1.19</v>
+      </c>
+      <c r="AK151">
         <v>1.06</v>
-      </c>
-      <c r="X151">
-        <v>1.05</v>
-      </c>
-      <c r="Y151">
-        <v>1.28</v>
-      </c>
-      <c r="Z151">
-        <v>3.05</v>
-      </c>
-      <c r="AA151">
-        <v>1.98</v>
-      </c>
-      <c r="AB151">
-        <v>1.71</v>
-      </c>
-      <c r="AC151">
-        <v>3.5</v>
-      </c>
-      <c r="AD151">
-        <v>1.22</v>
-      </c>
-      <c r="AE151">
-        <v>1.08</v>
-      </c>
-      <c r="AF151">
-        <v>1.95</v>
-      </c>
-      <c r="AG151">
-        <v>1.74</v>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ151">
-        <v>1.21</v>
-      </c>
-      <c r="AK151">
-        <v>1.08</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25130,7 +25130,7 @@
         <v>1.53</v>
       </c>
       <c r="AC152">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AD152">
         <v>1.16</v>
@@ -25595,10 +25595,10 @@
         <v>3.3</v>
       </c>
       <c r="U155">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="V155">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W155">
         <v>1.12</v>
@@ -25613,10 +25613,10 @@
         <v>4.25</v>
       </c>
       <c r="AA155">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB155">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AC155">
         <v>2.48</v>
@@ -25647,7 +25647,7 @@
         <v>1.17</v>
       </c>
       <c r="AK155">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25794,7 +25794,7 @@
         <v>1.71</v>
       </c>
       <c r="AG156">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>5.9</v>
       </c>
       <c r="Q157">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R157">
         <v>2.88</v>
@@ -25936,13 +25936,13 @@
         <v>1.05</v>
       </c>
       <c r="Z157">
-        <v>6.65</v>
+        <v>6.7</v>
       </c>
       <c r="AA157">
         <v>1.29</v>
       </c>
       <c r="AB157">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AC157">
         <v>1.8</v>
@@ -25951,7 +25951,7 @@
         <v>2.02</v>
       </c>
       <c r="AE157">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AF157">
         <v>1.44</v>
@@ -25973,7 +25973,7 @@
         <v>1.11</v>
       </c>
       <c r="AK157">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26066,10 +26066,10 @@
         <v>2</v>
       </c>
       <c r="O158">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="P158">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="Q158">
         <v>2.5</v>
@@ -26078,13 +26078,13 @@
         <v>2.48</v>
       </c>
       <c r="S158">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T158">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U158">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="V158">
         <v>1.54</v>
@@ -26096,13 +26096,13 @@
         <v>1.02</v>
       </c>
       <c r="Y158">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z158">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA158">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB158">
         <v>2.32</v>
@@ -26111,16 +26111,16 @@
         <v>2.48</v>
       </c>
       <c r="AD158">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE158">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF158">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG158">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK158">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26878,7 +26878,7 @@
         </is>
       </c>
       <c r="N163">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="O163">
         <v>3.75</v>
@@ -26887,10 +26887,10 @@
         <v>1.7</v>
       </c>
       <c r="Q163">
-        <v>4.2</v>
+        <v>4.43</v>
       </c>
       <c r="R163">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="S163">
         <v>1.26</v>
@@ -26899,13 +26899,13 @@
         <v>3.2</v>
       </c>
       <c r="U163">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V163">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W163">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X163">
         <v>1.01</v>
@@ -26914,19 +26914,19 @@
         <v>1.14</v>
       </c>
       <c r="Z163">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA163">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AB163">
         <v>2.45</v>
       </c>
       <c r="AC163">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AD163">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE163">
         <v>1.18</v>
@@ -26935,7 +26935,7 @@
         <v>1.53</v>
       </c>
       <c r="AG163">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>3.3</v>
       </c>
       <c r="Q165">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="R165">
         <v>2.08</v>
@@ -27228,7 +27228,7 @@
         <v>2.63</v>
       </c>
       <c r="V165">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W165">
         <v>1.06</v>
@@ -27252,10 +27252,10 @@
         <v>3.4</v>
       </c>
       <c r="AD165">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE165">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF165">
         <v>1.69</v>
@@ -27277,7 +27277,7 @@
         <v>1.25</v>
       </c>
       <c r="AK165">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27373,13 +27373,13 @@
         <v>4</v>
       </c>
       <c r="P166">
-        <v>4.5</v>
+        <v>4.59</v>
       </c>
       <c r="Q166">
         <v>2.03</v>
       </c>
       <c r="R166">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="S166">
         <v>1.17</v>
@@ -27391,7 +27391,7 @@
         <v>2.01</v>
       </c>
       <c r="V166">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W166">
         <v>1.18</v>
@@ -27403,7 +27403,7 @@
         <v>1.11</v>
       </c>
       <c r="Z166">
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
       <c r="AA166">
         <v>1.33</v>
@@ -27415,7 +27415,7 @@
         <v>2.04</v>
       </c>
       <c r="AD166">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AE166">
         <v>1.3</v>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK166">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27859,7 +27859,7 @@
         <v>1.75</v>
       </c>
       <c r="O169">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P169">
         <v>3.9</v>
@@ -27874,7 +27874,7 @@
         <v>1.17</v>
       </c>
       <c r="T169">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="U169">
         <v>1.89</v>
@@ -27892,7 +27892,7 @@
         <v>1.07</v>
       </c>
       <c r="Z169">
-        <v>6.58</v>
+        <v>6.25</v>
       </c>
       <c r="AA169">
         <v>1.32</v>
@@ -28046,7 +28046,7 @@
         <v>2</v>
       </c>
       <c r="W170">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X170">
         <v>1.01</v>
@@ -28064,7 +28064,7 @@
         <v>3.74</v>
       </c>
       <c r="AC170">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AD170">
         <v>2.21</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.27</v>
+        <v>1.64</v>
       </c>
       <c r="O171">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="P171">
-        <v>8.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="Q171">
-        <v>1.61</v>
+        <v>2.03</v>
       </c>
       <c r="R171">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="S171">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="T171">
-        <v>5.25</v>
+        <v>5.9</v>
       </c>
       <c r="U171">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="V171">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="W171">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="X171">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y171">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Z171">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA171">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AB171">
-        <v>3.58</v>
+        <v>4.33</v>
       </c>
       <c r="AC171">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AD171">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="AE171">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AF171">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AG171">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AK171">
-        <v>3.52</v>
+        <v>2.11</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="O172">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="P172">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="Q172">
-        <v>2.03</v>
+        <v>1.69</v>
       </c>
       <c r="R172">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="S172">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="T172">
-        <v>6.05</v>
+        <v>4.7</v>
       </c>
       <c r="U172">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="V172">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="W172">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="X172">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y172">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Z172">
-        <v>9.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="AA172">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AB172">
-        <v>4.33</v>
+        <v>3.42</v>
       </c>
       <c r="AC172">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="AD172">
-        <v>2.43</v>
+        <v>2.11</v>
       </c>
       <c r="AE172">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AF172">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="AG172">
-        <v>3.75</v>
+        <v>2.56</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK172">
-        <v>2.12</v>
+        <v>3.12</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28544,25 +28544,25 @@
         <v>1.04</v>
       </c>
       <c r="Z173">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="AA173">
         <v>1.24</v>
       </c>
       <c r="AB173">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="AC173">
         <v>1.71</v>
       </c>
       <c r="AD173">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AE173">
         <v>1.47</v>
       </c>
       <c r="AF173">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG173">
         <v>2.33</v>
@@ -28680,7 +28680,7 @@
         <v>7</v>
       </c>
       <c r="Q174">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="R174">
         <v>3.2</v>
@@ -28713,22 +28713,22 @@
         <v>1.23</v>
       </c>
       <c r="AB174">
-        <v>3.88</v>
+        <v>3.91</v>
       </c>
       <c r="AC174">
         <v>1.58</v>
       </c>
       <c r="AD174">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AE174">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AF174">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AG174">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28840,10 +28840,10 @@
         <v>3.75</v>
       </c>
       <c r="P175">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="Q175">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="R175">
         <v>2.36</v>
@@ -29510,7 +29510,7 @@
         <v>2.25</v>
       </c>
       <c r="V179">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="W179">
         <v>1.15</v>
@@ -29525,19 +29525,19 @@
         <v>5</v>
       </c>
       <c r="AA179">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AB179">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="AC179">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AD179">
         <v>1.54</v>
       </c>
       <c r="AE179">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF179">
         <v>1.53</v>
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O182">
         <v>3.65</v>
       </c>
       <c r="P182">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q182">
         <v>4.71</v>
@@ -29990,28 +29990,28 @@
         <v>2.32</v>
       </c>
       <c r="S182">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T182">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="U182">
         <v>2.5</v>
       </c>
       <c r="V182">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W182">
         <v>1.1</v>
       </c>
       <c r="X182">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y182">
         <v>1.21</v>
       </c>
       <c r="Z182">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="AA182">
         <v>1.8</v>
@@ -30020,16 +30020,16 @@
         <v>2</v>
       </c>
       <c r="AC182">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AD182">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE182">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF182">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG182">
         <v>2</v>
@@ -30045,7 +30045,7 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="AK182">
         <v>1.2</v>
@@ -30310,7 +30310,7 @@
         <v>2.25</v>
       </c>
       <c r="Q184">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R184">
         <v>2.1</v>
@@ -30322,7 +30322,7 @@
         <v>3.2</v>
       </c>
       <c r="U184">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V184">
         <v>1.47</v>
@@ -30337,7 +30337,7 @@
         <v>1.22</v>
       </c>
       <c r="Z184">
-        <v>4.21</v>
+        <v>4.26</v>
       </c>
       <c r="AA184">
         <v>1.71</v>
@@ -30349,7 +30349,7 @@
         <v>2.69</v>
       </c>
       <c r="AD184">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE184">
         <v>1.1</v>
@@ -31116,19 +31116,19 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="O189">
         <v>3.45</v>
       </c>
       <c r="P189">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="Q189">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="R189">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S189">
         <v>1.3</v>
@@ -31137,7 +31137,7 @@
         <v>2.99</v>
       </c>
       <c r="U189">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="V189">
         <v>1.5</v>
@@ -31167,13 +31167,13 @@
         <v>1.39</v>
       </c>
       <c r="AE189">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF189">
         <v>1.57</v>
       </c>
       <c r="AG189">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK189">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31291,7 +31291,7 @@
         <v>2</v>
       </c>
       <c r="R190">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="S190">
         <v>1.23</v>
@@ -31300,10 +31300,10 @@
         <v>3.48</v>
       </c>
       <c r="U190">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="V190">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="W190">
         <v>1.14</v>
@@ -31315,28 +31315,28 @@
         <v>1.14</v>
       </c>
       <c r="Z190">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="AA190">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AB190">
         <v>2.33</v>
       </c>
       <c r="AC190">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AD190">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE190">
         <v>1.18</v>
       </c>
       <c r="AF190">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG190">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31605,43 +31605,43 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O192">
+        <v>3.75</v>
+      </c>
+      <c r="P192">
+        <v>2.4</v>
+      </c>
+      <c r="Q192">
+        <v>3</v>
+      </c>
+      <c r="R192">
+        <v>2.36</v>
+      </c>
+      <c r="S192">
+        <v>1.25</v>
+      </c>
+      <c r="T192">
         <v>3.6</v>
       </c>
-      <c r="P192">
-        <v>2.38</v>
-      </c>
-      <c r="Q192">
-        <v>0</v>
-      </c>
-      <c r="R192">
-        <v>0</v>
-      </c>
-      <c r="S192">
-        <v>0</v>
-      </c>
-      <c r="T192">
-        <v>0</v>
-      </c>
       <c r="U192">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V192">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W192">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X192">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y192">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z192">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA192">
         <v>1.57</v>
@@ -31650,19 +31650,19 @@
         <v>2.35</v>
       </c>
       <c r="AC192">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD192">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE192">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF192">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG192">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK192">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31952,10 +31952,10 @@
         <v>3.85</v>
       </c>
       <c r="U194">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="V194">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W194">
         <v>1.18</v>
@@ -31979,13 +31979,13 @@
         <v>2.06</v>
       </c>
       <c r="AD194">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AE194">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AF194">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG194">
         <v>2.3</v>
@@ -32004,7 +32004,7 @@
         <v>1.06</v>
       </c>
       <c r="AK194">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="O195">
         <v>3.7</v>
       </c>
       <c r="P195">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Q195">
         <v>2.75</v>
@@ -32130,7 +32130,7 @@
         <v>1.05</v>
       </c>
       <c r="Z195">
-        <v>6.45</v>
+        <v>4.1</v>
       </c>
       <c r="AA195">
         <v>1.36</v>
@@ -32148,10 +32148,10 @@
         <v>1.4</v>
       </c>
       <c r="AF195">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AG195">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="O196">
         <v>3.71</v>
@@ -32266,7 +32266,7 @@
         <v>1.96</v>
       </c>
       <c r="Q196">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="R196">
         <v>2.46</v>
@@ -32293,7 +32293,7 @@
         <v>1.04</v>
       </c>
       <c r="Z196">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA196">
         <v>1.29</v>
@@ -32302,13 +32302,13 @@
         <v>3.04</v>
       </c>
       <c r="AC196">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AD196">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="AE196">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AF196">
         <v>1.31</v>
@@ -32330,7 +32330,7 @@
         <v>1.25</v>
       </c>
       <c r="AK196">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32420,16 +32420,16 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="O197">
         <v>3.7</v>
       </c>
       <c r="P197">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Q197">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="R197">
         <v>2.8</v>
@@ -33561,10 +33561,10 @@
         </is>
       </c>
       <c r="N204">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="O204">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="P204">
         <v>3.47</v>
@@ -34557,13 +34557,13 @@
         <v>1.45</v>
       </c>
       <c r="T210">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="U210">
         <v>3.24</v>
       </c>
       <c r="V210">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W210">
         <v>1.04</v>
@@ -34584,7 +34584,7 @@
         <v>1.76</v>
       </c>
       <c r="AC210">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD210">
         <v>1.24</v>
@@ -34612,7 +34612,7 @@
         <v>1.25</v>
       </c>
       <c r="AK210">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -35049,7 +35049,7 @@
         <v>3.05</v>
       </c>
       <c r="U213">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="V213">
         <v>1.44</v>
@@ -35203,7 +35203,7 @@
         <v>1.95</v>
       </c>
       <c r="R214">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="S214">
         <v>1.23</v>
@@ -35236,7 +35236,7 @@
         <v>2.7</v>
       </c>
       <c r="AC214">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AD214">
         <v>1.73</v>
@@ -35876,28 +35876,28 @@
         <v>1.02</v>
       </c>
       <c r="Y218">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z218">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA218">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB218">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC218">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AD218">
         <v>1.36</v>
       </c>
       <c r="AE218">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF218">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG218">
         <v>2.25</v>
@@ -36006,64 +36006,64 @@
         </is>
       </c>
       <c r="N219">
+        <v>4.2</v>
+      </c>
+      <c r="O219">
         <v>3.9</v>
       </c>
-      <c r="O219">
-        <v>3.8</v>
-      </c>
       <c r="P219">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q219">
         <v>4</v>
       </c>
       <c r="R219">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="S219">
         <v>1.25</v>
       </c>
       <c r="T219">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="U219">
         <v>2.4</v>
       </c>
       <c r="V219">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W219">
         <v>1.11</v>
       </c>
       <c r="X219">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y219">
         <v>1.17</v>
       </c>
       <c r="Z219">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA219">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB219">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="AC219">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="AD219">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE219">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF219">
         <v>1.58</v>
       </c>
       <c r="AG219">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK219">
         <v>1.22</v>
@@ -36169,13 +36169,13 @@
         </is>
       </c>
       <c r="N220">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="O220">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="P220">
-        <v>12</v>
+        <v>12.94</v>
       </c>
       <c r="Q220">
         <v>1.43</v>
@@ -36190,7 +36190,7 @@
         <v>4.05</v>
       </c>
       <c r="U220">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V220">
         <v>1.54</v>
@@ -36202,16 +36202,16 @@
         <v>1.01</v>
       </c>
       <c r="Y220">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z220">
-        <v>5.9</v>
+        <v>7.09</v>
       </c>
       <c r="AA220">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB220">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="AC220">
         <v>1.99</v>
@@ -36223,10 +36223,10 @@
         <v>1.29</v>
       </c>
       <c r="AF220">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AG220">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36839,13 +36839,13 @@
         <v>1.36</v>
       </c>
       <c r="T224">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="U224">
         <v>2.8</v>
       </c>
       <c r="V224">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W224">
         <v>1.04</v>
@@ -36996,7 +36996,7 @@
         <v>2</v>
       </c>
       <c r="R225">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="S225">
         <v>1.26</v>
@@ -37054,7 +37054,7 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AK225">
         <v>2.3</v>
@@ -37156,7 +37156,7 @@
         <v>2.1</v>
       </c>
       <c r="Q226">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R226">
         <v>1.92</v>
@@ -37204,7 +37204,7 @@
         <v>2.05</v>
       </c>
       <c r="AG226">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37322,7 +37322,7 @@
         <v>2.3</v>
       </c>
       <c r="R227">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S227">
         <v>1.36</v>
@@ -37340,31 +37340,31 @@
         <v>1.06</v>
       </c>
       <c r="X227">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y227">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z227">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA227">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AB227">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AC227">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD227">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE227">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF227">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AG227">
         <v>1.9</v>
@@ -38134,7 +38134,7 @@
         <v>1.63</v>
       </c>
       <c r="Q232">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="R232">
         <v>2.63</v>
@@ -38152,7 +38152,7 @@
         <v>1.87</v>
       </c>
       <c r="W232">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X232">
         <v>1.01</v>
@@ -38161,10 +38161,10 @@
         <v>1.04</v>
       </c>
       <c r="Z232">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="AA232">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AB232">
         <v>3.2</v>
@@ -38294,7 +38294,7 @@
         <v>3.4</v>
       </c>
       <c r="P233">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="Q233">
         <v>2.4</v>
@@ -38318,7 +38318,7 @@
         <v>1.08</v>
       </c>
       <c r="X233">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y233">
         <v>1.24</v>
@@ -38333,7 +38333,7 @@
         <v>1.84</v>
       </c>
       <c r="AC233">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AD233">
         <v>1.28</v>
@@ -38358,7 +38358,7 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK233">
         <v>1.91</v>
@@ -38828,7 +38828,7 @@
         <v>1.46</v>
       </c>
       <c r="AE236">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF236">
         <v>1.6</v>
@@ -38970,34 +38970,34 @@
         <v>1.06</v>
       </c>
       <c r="X237">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y237">
         <v>1.21</v>
       </c>
       <c r="Z237">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AA237">
         <v>1.8</v>
       </c>
       <c r="AB237">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AC237">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="AD237">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE237">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF237">
         <v>1.62</v>
       </c>
       <c r="AG237">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AK237">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39601,7 +39601,7 @@
         <v>0</v>
       </c>
       <c r="Q241">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="R241">
         <v>2.15</v>
@@ -39613,10 +39613,10 @@
         <v>2.5</v>
       </c>
       <c r="U241">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="V241">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W241">
         <v>1.05</v>
@@ -39634,7 +39634,7 @@
         <v>2.32</v>
       </c>
       <c r="AB241">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AC241">
         <v>4.2</v>
@@ -39649,7 +39649,7 @@
         <v>2.4</v>
       </c>
       <c r="AG241">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AH241" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>4.35</v>
       </c>
       <c r="Q243">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R243">
         <v>2.3</v>
@@ -39936,46 +39936,46 @@
         <v>1.27</v>
       </c>
       <c r="T243">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="U243">
-        <v>2.34</v>
+        <v>2.51</v>
       </c>
       <c r="V243">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W243">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X243">
         <v>1.02</v>
       </c>
       <c r="Y243">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z243">
-        <v>3.1</v>
+        <v>4.97</v>
       </c>
       <c r="AA243">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AB243">
         <v>2.1</v>
       </c>
       <c r="AC243">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AD243">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE243">
         <v>1.14</v>
       </c>
       <c r="AF243">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG243">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH243" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>1.18</v>
       </c>
       <c r="AK243">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -40902,7 +40902,7 @@
         <v>6</v>
       </c>
       <c r="P249">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Q249">
         <v>1.55</v>
@@ -40911,16 +40911,16 @@
         <v>2.9</v>
       </c>
       <c r="S249">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="T249">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="U249">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="V249">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="W249">
         <v>1.2</v>
@@ -40929,31 +40929,31 @@
         <v>1.01</v>
       </c>
       <c r="Y249">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Z249">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="AA249">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AB249">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AC249">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AD249">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AE249">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF249">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG249">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -41068,55 +41068,55 @@
         <v>3.25</v>
       </c>
       <c r="Q250">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="R250">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S250">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T250">
-        <v>3.07</v>
+        <v>3.15</v>
       </c>
       <c r="U250">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="V250">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W250">
         <v>1.1</v>
       </c>
       <c r="X250">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y250">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z250">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AA250">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AB250">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC250">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AD250">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE250">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF250">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AG250">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK250">
         <v>1.65</v>
@@ -41222,7 +41222,7 @@
         </is>
       </c>
       <c r="N251">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O251">
         <v>5.4</v>
@@ -41246,7 +41246,7 @@
         <v>1.96</v>
       </c>
       <c r="V251">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W251">
         <v>1.2</v>
@@ -41292,7 +41292,7 @@
         </is>
       </c>
       <c r="AJ251">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK251">
         <v>3.44</v>
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G252">
@@ -41385,64 +41385,64 @@
         </is>
       </c>
       <c r="N252">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="O252">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P252">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q252">
-        <v>3.75</v>
+        <v>2.76</v>
       </c>
       <c r="R252">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="S252">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T252">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="U252">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="V252">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W252">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X252">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y252">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z252">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="AA252">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="AB252">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AC252">
-        <v>2.97</v>
+        <v>3.68</v>
       </c>
       <c r="AD252">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AE252">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF252">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AG252">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK252">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,64 +41548,64 @@
         </is>
       </c>
       <c r="N253">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="O253">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P253">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q253">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="R253">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="S253">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T253">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="U253">
-        <v>2.9</v>
+        <v>2.71</v>
       </c>
       <c r="V253">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W253">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X253">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y253">
+        <v>1.26</v>
+      </c>
+      <c r="Z253">
+        <v>3.4</v>
+      </c>
+      <c r="AA253">
+        <v>1.87</v>
+      </c>
+      <c r="AB253">
+        <v>1.8</v>
+      </c>
+      <c r="AC253">
+        <v>2.97</v>
+      </c>
+      <c r="AD253">
         <v>1.3</v>
       </c>
-      <c r="Z253">
-        <v>2.97</v>
-      </c>
-      <c r="AA253">
-        <v>2.12</v>
-      </c>
-      <c r="AB253">
-        <v>1.69</v>
-      </c>
-      <c r="AC253">
-        <v>3.68</v>
-      </c>
-      <c r="AD253">
-        <v>1.2</v>
-      </c>
       <c r="AE253">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF253">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AG253">
-        <v>1.86</v>
+        <v>2.07</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK253">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41711,16 +41711,16 @@
         </is>
       </c>
       <c r="N254">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O254">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P254">
         <v>3.1</v>
       </c>
       <c r="Q254">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="R254">
         <v>2.01</v>
@@ -41732,7 +41732,7 @@
         <v>2.29</v>
       </c>
       <c r="U254">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V254">
         <v>1.3</v>
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G256">
@@ -42037,64 +42037,64 @@
         </is>
       </c>
       <c r="N256">
+        <v>1.93</v>
+      </c>
+      <c r="O256">
+        <v>3.25</v>
+      </c>
+      <c r="P256">
+        <v>3.4</v>
+      </c>
+      <c r="Q256">
+        <v>2.53</v>
+      </c>
+      <c r="R256">
+        <v>1.98</v>
+      </c>
+      <c r="S256">
+        <v>1.42</v>
+      </c>
+      <c r="T256">
+        <v>2.57</v>
+      </c>
+      <c r="U256">
+        <v>3.2</v>
+      </c>
+      <c r="V256">
+        <v>1.3</v>
+      </c>
+      <c r="W256">
+        <v>1.05</v>
+      </c>
+      <c r="X256">
+        <v>1.06</v>
+      </c>
+      <c r="Y256">
+        <v>1.34</v>
+      </c>
+      <c r="Z256">
+        <v>2.93</v>
+      </c>
+      <c r="AA256">
         <v>2.2</v>
       </c>
-      <c r="O256">
-        <v>3</v>
-      </c>
-      <c r="P256">
-        <v>3</v>
-      </c>
-      <c r="Q256">
-        <v>3</v>
-      </c>
-      <c r="R256">
-        <v>1.86</v>
-      </c>
-      <c r="S256">
-        <v>1.47</v>
-      </c>
-      <c r="T256">
-        <v>2.55</v>
-      </c>
-      <c r="U256">
-        <v>3.12</v>
-      </c>
-      <c r="V256">
-        <v>1.28</v>
-      </c>
-      <c r="W256">
-        <v>1.01</v>
-      </c>
-      <c r="X256">
-        <v>1.04</v>
-      </c>
-      <c r="Y256">
-        <v>1.37</v>
-      </c>
-      <c r="Z256">
-        <v>2.77</v>
-      </c>
-      <c r="AA256">
-        <v>2.3</v>
-      </c>
       <c r="AB256">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AC256">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="AD256">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE256">
         <v>1.04</v>
       </c>
       <c r="AF256">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG256">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42107,10 +42107,10 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK256">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G257">
@@ -42200,64 +42200,64 @@
         </is>
       </c>
       <c r="N257">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="O257">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P257">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="Q257">
-        <v>2.53</v>
+        <v>3</v>
       </c>
       <c r="R257">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="S257">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="T257">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="U257">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="V257">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W257">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X257">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y257">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="Z257">
-        <v>2.93</v>
+        <v>2.77</v>
       </c>
       <c r="AA257">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB257">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AC257">
-        <v>3.82</v>
+        <v>3.88</v>
       </c>
       <c r="AD257">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE257">
         <v>1.04</v>
       </c>
       <c r="AF257">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG257">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
@@ -42270,10 +42270,10 @@
         </is>
       </c>
       <c r="AJ257">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK257">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -42408,7 +42408,7 @@
         <v>2.82</v>
       </c>
       <c r="AC258">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AD258">
         <v>1.95</v>
@@ -42716,7 +42716,7 @@
         <v>1.3</v>
       </c>
       <c r="W260">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X260">
         <v>1.06</v>
@@ -42731,7 +42731,7 @@
         <v>2.31</v>
       </c>
       <c r="AB260">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC260">
         <v>5</v>
@@ -42873,7 +42873,7 @@
         <v>2.88</v>
       </c>
       <c r="U261">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="V261">
         <v>1.36</v>
@@ -42882,13 +42882,13 @@
         <v>1.03</v>
       </c>
       <c r="X261">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y261">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z261">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA261">
         <v>2.09</v>
@@ -42903,13 +42903,13 @@
         <v>1.3</v>
       </c>
       <c r="AE261">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF261">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG261">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -43015,28 +43015,28 @@
         </is>
       </c>
       <c r="N262">
-        <v>1.94</v>
+        <v>1.66</v>
       </c>
       <c r="O262">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="P262">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="Q262">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="R262">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="S262">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="T262">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="U262">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="V262">
         <v>1.2</v>
@@ -43045,34 +43045,34 @@
         <v>1.03</v>
       </c>
       <c r="X262">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y262">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="Z262">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AA262">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB262">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC262">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="AD262">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE262">
         <v>1.02</v>
       </c>
       <c r="AF262">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AG262">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AH262" t="inlineStr">
         <is>
@@ -43085,10 +43085,10 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK262">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -43371,7 +43371,7 @@
         <v>1.03</v>
       </c>
       <c r="X264">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y264">
         <v>1.4</v>
@@ -43389,7 +43389,7 @@
         <v>3.92</v>
       </c>
       <c r="AD264">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE264">
         <v>1.02</v>
@@ -43513,55 +43513,55 @@
         <v>0</v>
       </c>
       <c r="Q265">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R265">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S265">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T265">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U265">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V265">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W265">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X265">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y265">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z265">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA265">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AB265">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="AC265">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD265">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE265">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF265">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG265">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH265" t="inlineStr">
         <is>
@@ -43574,10 +43574,10 @@
         </is>
       </c>
       <c r="AJ265">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK265">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43706,10 +43706,10 @@
         <v>3.1</v>
       </c>
       <c r="AA266">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AB266">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC266">
         <v>3</v>
@@ -43839,7 +43839,7 @@
         <v>0</v>
       </c>
       <c r="Q267">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="R267">
         <v>1.93</v>
@@ -43872,7 +43872,7 @@
         <v>2.29</v>
       </c>
       <c r="AB267">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC267">
         <v>4.5</v>
@@ -43900,10 +43900,10 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK267">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G268">
@@ -43993,80 +43993,80 @@
         </is>
       </c>
       <c r="N268">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="O268">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P268">
+        <v>5</v>
+      </c>
+      <c r="Q268">
+        <v>2.38</v>
+      </c>
+      <c r="R268">
+        <v>1.88</v>
+      </c>
+      <c r="S268">
+        <v>1.61</v>
+      </c>
+      <c r="T268">
+        <v>2.13</v>
+      </c>
+      <c r="U268">
         <v>3.9</v>
       </c>
-      <c r="Q268">
-        <v>2.57</v>
-      </c>
-      <c r="R268">
-        <v>2.11</v>
-      </c>
-      <c r="S268">
-        <v>1.4</v>
-      </c>
-      <c r="T268">
-        <v>2.7</v>
-      </c>
-      <c r="U268">
-        <v>3</v>
-      </c>
       <c r="V268">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="W268">
+        <v>1.03</v>
+      </c>
+      <c r="X268">
+        <v>1.09</v>
+      </c>
+      <c r="Y268">
+        <v>1.61</v>
+      </c>
+      <c r="Z268">
+        <v>2.13</v>
+      </c>
+      <c r="AA268">
+        <v>2.83</v>
+      </c>
+      <c r="AB268">
+        <v>1.36</v>
+      </c>
+      <c r="AC268">
+        <v>5.9</v>
+      </c>
+      <c r="AD268">
         <v>1.07</v>
-      </c>
-      <c r="X268">
-        <v>1.04</v>
-      </c>
-      <c r="Y268">
-        <v>1.35</v>
-      </c>
-      <c r="Z268">
-        <v>2.74</v>
-      </c>
-      <c r="AA268">
-        <v>2.15</v>
-      </c>
-      <c r="AB268">
-        <v>1.65</v>
-      </c>
-      <c r="AC268">
-        <v>4.03</v>
-      </c>
-      <c r="AD268">
-        <v>1.18</v>
       </c>
       <c r="AE268">
         <v>1.03</v>
       </c>
       <c r="AF268">
+        <v>2.57</v>
+      </c>
+      <c r="AG268">
+        <v>1.44</v>
+      </c>
+      <c r="AH268" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI268" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ268">
+        <v>1.36</v>
+      </c>
+      <c r="AK268">
         <v>1.95</v>
-      </c>
-      <c r="AG268">
-        <v>1.8</v>
-      </c>
-      <c r="AH268" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI268" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ268">
-        <v>1.16</v>
-      </c>
-      <c r="AK268">
-        <v>1.7</v>
       </c>
       <c r="AL268">
         <v>0</v>
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G269">
@@ -44156,64 +44156,64 @@
         </is>
       </c>
       <c r="N269">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="O269">
+        <v>3.25</v>
+      </c>
+      <c r="P269">
+        <v>3.9</v>
+      </c>
+      <c r="Q269">
+        <v>2.57</v>
+      </c>
+      <c r="R269">
+        <v>2.11</v>
+      </c>
+      <c r="S269">
+        <v>1.4</v>
+      </c>
+      <c r="T269">
+        <v>2.7</v>
+      </c>
+      <c r="U269">
         <v>3</v>
       </c>
-      <c r="P269">
-        <v>5</v>
-      </c>
-      <c r="Q269">
-        <v>2.38</v>
-      </c>
-      <c r="R269">
-        <v>1.88</v>
-      </c>
-      <c r="S269">
-        <v>1.61</v>
-      </c>
-      <c r="T269">
-        <v>2.13</v>
-      </c>
-      <c r="U269">
-        <v>3.9</v>
-      </c>
       <c r="V269">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="W269">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X269">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y269">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="Z269">
-        <v>2.13</v>
+        <v>2.74</v>
       </c>
       <c r="AA269">
-        <v>2.83</v>
+        <v>2.15</v>
       </c>
       <c r="AB269">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AC269">
-        <v>5.9</v>
+        <v>4.03</v>
       </c>
       <c r="AD269">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AE269">
         <v>1.03</v>
       </c>
       <c r="AF269">
-        <v>2.57</v>
+        <v>1.95</v>
       </c>
       <c r="AG269">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AK269">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44325,7 +44325,7 @@
         <v>3.36</v>
       </c>
       <c r="P270">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q270">
         <v>2.9</v>
@@ -44334,10 +44334,10 @@
         <v>2.08</v>
       </c>
       <c r="S270">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T270">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U270">
         <v>2.67</v>
@@ -44373,10 +44373,10 @@
         <v>1.07</v>
       </c>
       <c r="AF270">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AG270">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="O279">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P279">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q279">
         <v>2.5</v>
@@ -45801,10 +45801,10 @@
         <v>2.25</v>
       </c>
       <c r="S279">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T279">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="U279">
         <v>2.4</v>
@@ -45816,7 +45816,7 @@
         <v>1.1</v>
       </c>
       <c r="X279">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y279">
         <v>1.19</v>
@@ -45828,7 +45828,7 @@
         <v>1.8</v>
       </c>
       <c r="AB279">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AC279">
         <v>2.7</v>
@@ -45837,13 +45837,13 @@
         <v>1.36</v>
       </c>
       <c r="AE279">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF279">
         <v>1.62</v>
       </c>
       <c r="AG279">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK279">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45997,16 +45997,16 @@
         <v>4.59</v>
       </c>
       <c r="AD280">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE280">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF280">
         <v>2</v>
       </c>
       <c r="AG280">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK280">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -46121,22 +46121,22 @@
         <v>0</v>
       </c>
       <c r="Q281">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="R281">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="S281">
         <v>1.22</v>
       </c>
       <c r="T281">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="U281">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="V281">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W281">
         <v>1.14</v>
@@ -46151,19 +46151,19 @@
         <v>4.9</v>
       </c>
       <c r="AA281">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AB281">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AC281">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AD281">
         <v>1.57</v>
       </c>
       <c r="AE281">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF281">
         <v>1.75</v>
@@ -46320,7 +46320,7 @@
         <v>2.23</v>
       </c>
       <c r="AC282">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="AD282">
         <v>1.43</v>
@@ -46438,64 +46438,64 @@
         </is>
       </c>
       <c r="N283">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="O283">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P283">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q283">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="R283">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="S283">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T283">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="U283">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V283">
         <v>1.3</v>
       </c>
       <c r="W283">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X283">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y283">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z283">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AA283">
+        <v>2.25</v>
+      </c>
+      <c r="AB283">
+        <v>1.61</v>
+      </c>
+      <c r="AC283">
+        <v>4.33</v>
+      </c>
+      <c r="AD283">
+        <v>1.18</v>
+      </c>
+      <c r="AE283">
+        <v>1.02</v>
+      </c>
+      <c r="AF283">
         <v>2.1</v>
       </c>
-      <c r="AB283">
-        <v>1.63</v>
-      </c>
-      <c r="AC283">
-        <v>3.75</v>
-      </c>
-      <c r="AD283">
-        <v>1.19</v>
-      </c>
-      <c r="AE283">
-        <v>1.03</v>
-      </c>
-      <c r="AF283">
-        <v>1.95</v>
-      </c>
       <c r="AG283">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK283">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46601,64 +46601,64 @@
         </is>
       </c>
       <c r="N284">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="O284">
         <v>3.2</v>
       </c>
       <c r="P284">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q284">
         <v>2.45</v>
       </c>
       <c r="R284">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="S284">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T284">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="U284">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="V284">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W284">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X284">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y284">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z284">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AA284">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="AB284">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AC284">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AD284">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE284">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF284">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG284">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="AK284">
         <v>1.75</v>
@@ -46782,7 +46782,7 @@
         <v>1.5</v>
       </c>
       <c r="T285">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="U285">
         <v>3.24</v>
@@ -46815,13 +46815,13 @@
         <v>1.17</v>
       </c>
       <c r="AE285">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF285">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG285">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46927,19 +46927,19 @@
         </is>
       </c>
       <c r="N286">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O286">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P286">
         <v>3.25</v>
       </c>
       <c r="Q286">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="R286">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="S286">
         <v>1.33</v>
@@ -46948,7 +46948,7 @@
         <v>3.07</v>
       </c>
       <c r="U286">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="V286">
         <v>1.4</v>
@@ -46975,16 +46975,16 @@
         <v>3.25</v>
       </c>
       <c r="AD286">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE286">
         <v>1.07</v>
       </c>
       <c r="AF286">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG286">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -47123,7 +47123,7 @@
         <v>1.03</v>
       </c>
       <c r="Y287">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="Z287">
         <v>2.74</v>
@@ -47289,13 +47289,13 @@
         <v>1.18</v>
       </c>
       <c r="Z288">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="AA288">
         <v>1.71</v>
       </c>
       <c r="AB288">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC288">
         <v>2.78</v>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
   